--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k2104200063\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBD34D3F-D984-4448-9B2B-C37F64B4DB2F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E566531D-7F71-4E8F-8B2A-DDB48DF1147E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="26745" yWindow="3240" windowWidth="21015" windowHeight="14730" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5482" uniqueCount="2516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5506" uniqueCount="2540">
   <si>
     <t>캐릭터ID</t>
   </si>
@@ -18450,14 +18450,6 @@
     <phoneticPr fontId="31" type="noConversion"/>
   </si>
   <si>
-    <t>압박</t>
-    <phoneticPr fontId="31" type="noConversion"/>
-  </si>
-  <si>
-    <t>압박+</t>
-    <phoneticPr fontId="31" type="noConversion"/>
-  </si>
-  <si>
     <t>연격</t>
     <phoneticPr fontId="31" type="noConversion"/>
   </si>
@@ -18474,11 +18466,115 @@
     <phoneticPr fontId="31" type="noConversion"/>
   </si>
   <si>
+    <t>역풍</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>역풍+</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
     <t>전진일격</t>
     <phoneticPr fontId="31" type="noConversion"/>
   </si>
   <si>
     <t>전진일격+</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>기동타격</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>기동타격+</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>꿰뚫는 빛</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>충격파</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>충격파+</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>낙뢰</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>낙뢰+</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>꿰뚫는 빛+</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>파열</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>파열+</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>저돌맹진</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>저돌맹진+</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>순간타격</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>순간타격+</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>연쇄폭발</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>연쇄폭발+</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>핏빛 수확</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>핏빛 수확+</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>유성우</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>유성우+</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>블러드 피어스</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>블러드 피어스+</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>천공포화</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>천공포화+</t>
     <phoneticPr fontId="31" type="noConversion"/>
   </si>
 </sst>
@@ -37059,7 +37155,9 @@
       <c r="A96" s="217" t="s">
         <v>387</v>
       </c>
-      <c r="B96" s="185"/>
+      <c r="B96" s="185" t="s">
+        <v>2519</v>
+      </c>
       <c r="C96" s="185" t="s">
         <v>326</v>
       </c>
@@ -37106,7 +37204,9 @@
       <c r="A97" s="226" t="s">
         <v>389</v>
       </c>
-      <c r="B97" s="202"/>
+      <c r="B97" s="202" t="s">
+        <v>2520</v>
+      </c>
       <c r="C97" s="200" t="s">
         <v>326</v>
       </c>
@@ -37153,7 +37253,9 @@
       <c r="A98" s="219" t="s">
         <v>391</v>
       </c>
-      <c r="B98" s="194"/>
+      <c r="B98" s="194" t="s">
+        <v>2521</v>
+      </c>
       <c r="C98" s="194" t="s">
         <v>326</v>
       </c>
@@ -37200,7 +37302,9 @@
       <c r="A99" s="226" t="s">
         <v>392</v>
       </c>
-      <c r="B99" s="202"/>
+      <c r="B99" s="202" t="s">
+        <v>2522</v>
+      </c>
       <c r="C99" s="200" t="s">
         <v>326</v>
       </c>
@@ -37246,7 +37350,9 @@
       <c r="A100" s="219" t="s">
         <v>393</v>
       </c>
-      <c r="B100" s="194"/>
+      <c r="B100" s="194" t="s">
+        <v>2518</v>
+      </c>
       <c r="C100" s="194" t="s">
         <v>326</v>
       </c>
@@ -37292,7 +37398,9 @@
       <c r="A101" s="226" t="s">
         <v>394</v>
       </c>
-      <c r="B101" s="202"/>
+      <c r="B101" s="202" t="s">
+        <v>2523</v>
+      </c>
       <c r="C101" s="200" t="s">
         <v>326</v>
       </c>
@@ -37339,7 +37447,7 @@
         <v>395</v>
       </c>
       <c r="B102" s="194" t="s">
-        <v>2510</v>
+        <v>2508</v>
       </c>
       <c r="C102" s="194" t="s">
         <v>326</v>
@@ -37387,7 +37495,7 @@
         <v>397</v>
       </c>
       <c r="B103" s="202" t="s">
-        <v>2511</v>
+        <v>2509</v>
       </c>
       <c r="C103" s="200" t="s">
         <v>326</v>
@@ -37435,7 +37543,7 @@
         <v>398</v>
       </c>
       <c r="B104" s="194" t="s">
-        <v>2514</v>
+        <v>2516</v>
       </c>
       <c r="C104" s="194" t="s">
         <v>326</v>
@@ -37483,7 +37591,7 @@
         <v>399</v>
       </c>
       <c r="B105" s="200" t="s">
-        <v>2515</v>
+        <v>2517</v>
       </c>
       <c r="C105" s="200" t="s">
         <v>326</v>
@@ -37531,7 +37639,7 @@
         <v>400</v>
       </c>
       <c r="B106" s="194" t="s">
-        <v>2508</v>
+        <v>2514</v>
       </c>
       <c r="C106" s="194" t="s">
         <v>326</v>
@@ -37579,7 +37687,7 @@
         <v>402</v>
       </c>
       <c r="B107" s="200" t="s">
-        <v>2509</v>
+        <v>2515</v>
       </c>
       <c r="C107" s="200" t="s">
         <v>326</v>
@@ -37627,7 +37735,7 @@
         <v>403</v>
       </c>
       <c r="B108" s="194" t="s">
-        <v>2512</v>
+        <v>2510</v>
       </c>
       <c r="C108" s="194" t="s">
         <v>326</v>
@@ -37675,7 +37783,7 @@
         <v>405</v>
       </c>
       <c r="B109" s="200" t="s">
-        <v>2513</v>
+        <v>2511</v>
       </c>
       <c r="C109" s="200" t="s">
         <v>326</v>
@@ -37722,7 +37830,9 @@
       <c r="A110" s="219" t="s">
         <v>406</v>
       </c>
-      <c r="B110" s="194"/>
+      <c r="B110" s="194" t="s">
+        <v>2512</v>
+      </c>
       <c r="C110" s="194" t="s">
         <v>326</v>
       </c>
@@ -37768,7 +37878,9 @@
       <c r="A111" s="226" t="s">
         <v>407</v>
       </c>
-      <c r="B111" s="200"/>
+      <c r="B111" s="200" t="s">
+        <v>2513</v>
+      </c>
       <c r="C111" s="200" t="s">
         <v>326</v>
       </c>
@@ -37814,7 +37926,9 @@
       <c r="A112" s="219" t="s">
         <v>408</v>
       </c>
-      <c r="B112" s="194"/>
+      <c r="B112" s="194" t="s">
+        <v>2524</v>
+      </c>
       <c r="C112" s="194" t="s">
         <v>326</v>
       </c>
@@ -37860,7 +37974,9 @@
       <c r="A113" s="226" t="s">
         <v>409</v>
       </c>
-      <c r="B113" s="200"/>
+      <c r="B113" s="200" t="s">
+        <v>2525</v>
+      </c>
       <c r="C113" s="200" t="s">
         <v>326</v>
       </c>
@@ -37906,7 +38022,9 @@
       <c r="A114" s="219" t="s">
         <v>410</v>
       </c>
-      <c r="B114" s="194"/>
+      <c r="B114" s="194" t="s">
+        <v>2536</v>
+      </c>
       <c r="C114" s="194" t="s">
         <v>326</v>
       </c>
@@ -37952,7 +38070,9 @@
       <c r="A115" s="226" t="s">
         <v>411</v>
       </c>
-      <c r="B115" s="200"/>
+      <c r="B115" s="200" t="s">
+        <v>2537</v>
+      </c>
       <c r="C115" s="200" t="s">
         <v>326</v>
       </c>
@@ -37998,7 +38118,9 @@
       <c r="A116" s="219" t="s">
         <v>412</v>
       </c>
-      <c r="B116" s="194"/>
+      <c r="B116" s="194" t="s">
+        <v>2534</v>
+      </c>
       <c r="C116" s="194" t="s">
         <v>326</v>
       </c>
@@ -38044,7 +38166,9 @@
       <c r="A117" s="226" t="s">
         <v>413</v>
       </c>
-      <c r="B117" s="200"/>
+      <c r="B117" s="200" t="s">
+        <v>2535</v>
+      </c>
       <c r="C117" s="200" t="s">
         <v>326</v>
       </c>
@@ -38090,7 +38214,9 @@
       <c r="A118" s="219" t="s">
         <v>414</v>
       </c>
-      <c r="B118" s="194"/>
+      <c r="B118" s="194" t="s">
+        <v>2538</v>
+      </c>
       <c r="C118" s="194" t="s">
         <v>326</v>
       </c>
@@ -38136,7 +38262,9 @@
       <c r="A119" s="226" t="s">
         <v>415</v>
       </c>
-      <c r="B119" s="200"/>
+      <c r="B119" s="200" t="s">
+        <v>2539</v>
+      </c>
       <c r="C119" s="200" t="s">
         <v>326</v>
       </c>
@@ -38182,7 +38310,9 @@
       <c r="A120" s="219" t="s">
         <v>416</v>
       </c>
-      <c r="B120" s="194"/>
+      <c r="B120" s="194" t="s">
+        <v>2532</v>
+      </c>
       <c r="C120" s="194" t="s">
         <v>326</v>
       </c>
@@ -38228,7 +38358,9 @@
       <c r="A121" s="226" t="s">
         <v>417</v>
       </c>
-      <c r="B121" s="200"/>
+      <c r="B121" s="200" t="s">
+        <v>2533</v>
+      </c>
       <c r="C121" s="200" t="s">
         <v>326</v>
       </c>
@@ -38274,7 +38406,9 @@
       <c r="A122" s="219" t="s">
         <v>418</v>
       </c>
-      <c r="B122" s="194"/>
+      <c r="B122" s="194" t="s">
+        <v>2530</v>
+      </c>
       <c r="C122" s="194" t="s">
         <v>326</v>
       </c>
@@ -38320,7 +38454,9 @@
       <c r="A123" s="226" t="s">
         <v>419</v>
       </c>
-      <c r="B123" s="200"/>
+      <c r="B123" s="200" t="s">
+        <v>2531</v>
+      </c>
       <c r="C123" s="200" t="s">
         <v>326</v>
       </c>
@@ -38366,7 +38502,9 @@
       <c r="A124" s="219" t="s">
         <v>2356</v>
       </c>
-      <c r="B124" s="194"/>
+      <c r="B124" s="194" t="s">
+        <v>2528</v>
+      </c>
       <c r="C124" s="194" t="s">
         <v>326</v>
       </c>
@@ -38412,7 +38550,9 @@
       <c r="A125" s="226" t="s">
         <v>2357</v>
       </c>
-      <c r="B125" s="200"/>
+      <c r="B125" s="200" t="s">
+        <v>2529</v>
+      </c>
       <c r="C125" s="200" t="s">
         <v>326</v>
       </c>
@@ -38438,7 +38578,7 @@
         <v>2</v>
       </c>
       <c r="K125" s="201">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L125" s="203">
         <v>1</v>
@@ -38458,7 +38598,9 @@
       <c r="A126" s="219" t="s">
         <v>2358</v>
       </c>
-      <c r="B126" s="194"/>
+      <c r="B126" s="194" t="s">
+        <v>2526</v>
+      </c>
       <c r="C126" s="194" t="s">
         <v>326</v>
       </c>
@@ -38504,7 +38646,9 @@
       <c r="A127" s="229" t="s">
         <v>2359</v>
       </c>
-      <c r="B127" s="188"/>
+      <c r="B127" s="188" t="s">
+        <v>2527</v>
+      </c>
       <c r="C127" s="188" t="s">
         <v>326</v>
       </c>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k2104200063\Desktop\RELIC\Assets\ExcelSource\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erang\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E566531D-7F71-4E8F-8B2A-DDB48DF1147E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DDB5871-F532-4492-BD58-615D4A0EC195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26745" yWindow="3240" windowWidth="21015" windowHeight="14730" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -32646,7 +32646,7 @@
         <v>279</v>
       </c>
       <c r="N3" s="185" t="s">
-        <v>280</v>
+        <v>2134</v>
       </c>
       <c r="O3" s="195" t="s">
         <v>281</v>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erang\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DDB5871-F532-4492-BD58-615D4A0EC195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0296421F-01F7-462E-9B71-AC46BFC17BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21375" yWindow="3060" windowWidth="21015" windowHeight="14730" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -18450,14 +18450,6 @@
     <phoneticPr fontId="31" type="noConversion"/>
   </si>
   <si>
-    <t>연격</t>
-    <phoneticPr fontId="31" type="noConversion"/>
-  </si>
-  <si>
-    <t>연격+</t>
-    <phoneticPr fontId="31" type="noConversion"/>
-  </si>
-  <si>
     <t>돌풍</t>
     <phoneticPr fontId="31" type="noConversion"/>
   </si>
@@ -18575,6 +18567,14 @@
   </si>
   <si>
     <t>천공포화+</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>화살세례</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>화살세례+</t>
     <phoneticPr fontId="31" type="noConversion"/>
   </si>
 </sst>
@@ -37156,7 +37156,7 @@
         <v>387</v>
       </c>
       <c r="B96" s="185" t="s">
-        <v>2519</v>
+        <v>2517</v>
       </c>
       <c r="C96" s="185" t="s">
         <v>326</v>
@@ -37205,7 +37205,7 @@
         <v>389</v>
       </c>
       <c r="B97" s="202" t="s">
-        <v>2520</v>
+        <v>2518</v>
       </c>
       <c r="C97" s="200" t="s">
         <v>326</v>
@@ -37254,7 +37254,7 @@
         <v>391</v>
       </c>
       <c r="B98" s="194" t="s">
-        <v>2521</v>
+        <v>2519</v>
       </c>
       <c r="C98" s="194" t="s">
         <v>326</v>
@@ -37303,7 +37303,7 @@
         <v>392</v>
       </c>
       <c r="B99" s="202" t="s">
-        <v>2522</v>
+        <v>2520</v>
       </c>
       <c r="C99" s="200" t="s">
         <v>326</v>
@@ -37351,7 +37351,7 @@
         <v>393</v>
       </c>
       <c r="B100" s="194" t="s">
-        <v>2518</v>
+        <v>2516</v>
       </c>
       <c r="C100" s="194" t="s">
         <v>326</v>
@@ -37399,7 +37399,7 @@
         <v>394</v>
       </c>
       <c r="B101" s="202" t="s">
-        <v>2523</v>
+        <v>2521</v>
       </c>
       <c r="C101" s="200" t="s">
         <v>326</v>
@@ -37447,7 +37447,7 @@
         <v>395</v>
       </c>
       <c r="B102" s="194" t="s">
-        <v>2508</v>
+        <v>2538</v>
       </c>
       <c r="C102" s="194" t="s">
         <v>326</v>
@@ -37495,7 +37495,7 @@
         <v>397</v>
       </c>
       <c r="B103" s="202" t="s">
-        <v>2509</v>
+        <v>2539</v>
       </c>
       <c r="C103" s="200" t="s">
         <v>326</v>
@@ -37543,7 +37543,7 @@
         <v>398</v>
       </c>
       <c r="B104" s="194" t="s">
-        <v>2516</v>
+        <v>2514</v>
       </c>
       <c r="C104" s="194" t="s">
         <v>326</v>
@@ -37591,7 +37591,7 @@
         <v>399</v>
       </c>
       <c r="B105" s="200" t="s">
-        <v>2517</v>
+        <v>2515</v>
       </c>
       <c r="C105" s="200" t="s">
         <v>326</v>
@@ -37639,7 +37639,7 @@
         <v>400</v>
       </c>
       <c r="B106" s="194" t="s">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="C106" s="194" t="s">
         <v>326</v>
@@ -37687,7 +37687,7 @@
         <v>402</v>
       </c>
       <c r="B107" s="200" t="s">
-        <v>2515</v>
+        <v>2513</v>
       </c>
       <c r="C107" s="200" t="s">
         <v>326</v>
@@ -37735,7 +37735,7 @@
         <v>403</v>
       </c>
       <c r="B108" s="194" t="s">
-        <v>2510</v>
+        <v>2508</v>
       </c>
       <c r="C108" s="194" t="s">
         <v>326</v>
@@ -37783,7 +37783,7 @@
         <v>405</v>
       </c>
       <c r="B109" s="200" t="s">
-        <v>2511</v>
+        <v>2509</v>
       </c>
       <c r="C109" s="200" t="s">
         <v>326</v>
@@ -37831,7 +37831,7 @@
         <v>406</v>
       </c>
       <c r="B110" s="194" t="s">
-        <v>2512</v>
+        <v>2510</v>
       </c>
       <c r="C110" s="194" t="s">
         <v>326</v>
@@ -37879,7 +37879,7 @@
         <v>407</v>
       </c>
       <c r="B111" s="200" t="s">
-        <v>2513</v>
+        <v>2511</v>
       </c>
       <c r="C111" s="200" t="s">
         <v>326</v>
@@ -37927,7 +37927,7 @@
         <v>408</v>
       </c>
       <c r="B112" s="194" t="s">
-        <v>2524</v>
+        <v>2522</v>
       </c>
       <c r="C112" s="194" t="s">
         <v>326</v>
@@ -37975,7 +37975,7 @@
         <v>409</v>
       </c>
       <c r="B113" s="200" t="s">
-        <v>2525</v>
+        <v>2523</v>
       </c>
       <c r="C113" s="200" t="s">
         <v>326</v>
@@ -38023,7 +38023,7 @@
         <v>410</v>
       </c>
       <c r="B114" s="194" t="s">
-        <v>2536</v>
+        <v>2534</v>
       </c>
       <c r="C114" s="194" t="s">
         <v>326</v>
@@ -38071,7 +38071,7 @@
         <v>411</v>
       </c>
       <c r="B115" s="200" t="s">
-        <v>2537</v>
+        <v>2535</v>
       </c>
       <c r="C115" s="200" t="s">
         <v>326</v>
@@ -38119,7 +38119,7 @@
         <v>412</v>
       </c>
       <c r="B116" s="194" t="s">
-        <v>2534</v>
+        <v>2532</v>
       </c>
       <c r="C116" s="194" t="s">
         <v>326</v>
@@ -38167,7 +38167,7 @@
         <v>413</v>
       </c>
       <c r="B117" s="200" t="s">
-        <v>2535</v>
+        <v>2533</v>
       </c>
       <c r="C117" s="200" t="s">
         <v>326</v>
@@ -38215,7 +38215,7 @@
         <v>414</v>
       </c>
       <c r="B118" s="194" t="s">
-        <v>2538</v>
+        <v>2536</v>
       </c>
       <c r="C118" s="194" t="s">
         <v>326</v>
@@ -38263,7 +38263,7 @@
         <v>415</v>
       </c>
       <c r="B119" s="200" t="s">
-        <v>2539</v>
+        <v>2537</v>
       </c>
       <c r="C119" s="200" t="s">
         <v>326</v>
@@ -38311,7 +38311,7 @@
         <v>416</v>
       </c>
       <c r="B120" s="194" t="s">
-        <v>2532</v>
+        <v>2530</v>
       </c>
       <c r="C120" s="194" t="s">
         <v>326</v>
@@ -38359,7 +38359,7 @@
         <v>417</v>
       </c>
       <c r="B121" s="200" t="s">
-        <v>2533</v>
+        <v>2531</v>
       </c>
       <c r="C121" s="200" t="s">
         <v>326</v>
@@ -38407,7 +38407,7 @@
         <v>418</v>
       </c>
       <c r="B122" s="194" t="s">
-        <v>2530</v>
+        <v>2528</v>
       </c>
       <c r="C122" s="194" t="s">
         <v>326</v>
@@ -38455,7 +38455,7 @@
         <v>419</v>
       </c>
       <c r="B123" s="200" t="s">
-        <v>2531</v>
+        <v>2529</v>
       </c>
       <c r="C123" s="200" t="s">
         <v>326</v>
@@ -38503,7 +38503,7 @@
         <v>2356</v>
       </c>
       <c r="B124" s="194" t="s">
-        <v>2528</v>
+        <v>2526</v>
       </c>
       <c r="C124" s="194" t="s">
         <v>326</v>
@@ -38551,7 +38551,7 @@
         <v>2357</v>
       </c>
       <c r="B125" s="200" t="s">
-        <v>2529</v>
+        <v>2527</v>
       </c>
       <c r="C125" s="200" t="s">
         <v>326</v>
@@ -38599,7 +38599,7 @@
         <v>2358</v>
       </c>
       <c r="B126" s="194" t="s">
-        <v>2526</v>
+        <v>2524</v>
       </c>
       <c r="C126" s="194" t="s">
         <v>326</v>
@@ -38647,7 +38647,7 @@
         <v>2359</v>
       </c>
       <c r="B127" s="188" t="s">
-        <v>2527</v>
+        <v>2525</v>
       </c>
       <c r="C127" s="188" t="s">
         <v>326</v>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erang\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07FE7318-468F-4466-A496-EC493B8E69BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C04AFE67-3315-4F34-873A-8D7C884AF839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5506" uniqueCount="2544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5540" uniqueCount="2558">
   <si>
     <t>캐릭터ID</t>
   </si>
@@ -18593,6 +18593,52 @@
   <si>
     <t>Range_Advance06</t>
     <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>Range_m_01</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>Range_m_02</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>Range_Advance01</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>Range_Retreat01</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>Range_Advance02</t>
+  </si>
+  <si>
+    <t>Range_Advance03</t>
+  </si>
+  <si>
+    <t>Range_Advance04</t>
+  </si>
+  <si>
+    <t>Range_Advance05</t>
+  </si>
+  <si>
+    <t>Range_Advance06</t>
+  </si>
+  <si>
+    <t>Range_Retreat02</t>
+  </si>
+  <si>
+    <t>Range_Retreat03</t>
+  </si>
+  <si>
+    <t>Range_Retreat04</t>
+  </si>
+  <si>
+    <t>Range_Retreat05</t>
+  </si>
+  <si>
+    <t>Range_Retreat06</t>
   </si>
 </sst>
 </file>
@@ -19469,7 +19515,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="238">
+  <cellXfs count="244">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -20170,6 +20216,24 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -21030,15 +21094,15 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:AK41"/>
+  <dimension ref="A1:AK55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="16.5" style="12" customWidth="1"/>
+    <col min="1" max="1" width="19.5" style="12" customWidth="1"/>
     <col min="2" max="2" width="20.25" style="12" customWidth="1"/>
     <col min="3" max="32" width="9.125" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37">
+    <row r="1" spans="1:37" ht="16.5" customHeight="1">
       <c r="A1" s="84" t="s">
         <v>255</v>
       </c>
@@ -21136,7 +21200,7 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="2" spans="1:37" ht="17.25" customHeight="1" thickBot="1">
+    <row r="2" spans="1:37" ht="16.5" customHeight="1" thickBot="1">
       <c r="A2" s="171" t="s">
         <v>270</v>
       </c>
@@ -21234,7 +21298,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="3" spans="1:37" ht="20.100000000000001" customHeight="1">
+    <row r="3" spans="1:37" ht="16.5" customHeight="1">
       <c r="A3" s="89" t="s">
         <v>168</v>
       </c>
@@ -21332,7 +21396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:37" ht="20.100000000000001" customHeight="1">
+    <row r="4" spans="1:37" ht="16.5" customHeight="1">
       <c r="A4" s="87" t="s">
         <v>198</v>
       </c>
@@ -21430,7 +21494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:37" ht="20.100000000000001" customHeight="1">
+    <row r="5" spans="1:37" ht="16.5" customHeight="1">
       <c r="A5" s="87" t="s">
         <v>318</v>
       </c>
@@ -21528,7 +21592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" ht="20.100000000000001" customHeight="1">
+    <row r="6" spans="1:37" ht="16.5" customHeight="1">
       <c r="A6" s="87" t="s">
         <v>306</v>
       </c>
@@ -21626,7 +21690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:37" ht="20.100000000000001" customHeight="1">
+    <row r="7" spans="1:37" ht="16.5" customHeight="1">
       <c r="A7" s="87" t="s">
         <v>300</v>
       </c>
@@ -21724,7 +21788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:37" ht="20.100000000000001" customHeight="1">
+    <row r="8" spans="1:37" ht="16.5" customHeight="1">
       <c r="A8" s="87" t="s">
         <v>308</v>
       </c>
@@ -21822,7 +21886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:37" ht="20.100000000000001" customHeight="1">
+    <row r="9" spans="1:37" ht="16.5" customHeight="1">
       <c r="A9" s="87" t="s">
         <v>299</v>
       </c>
@@ -21920,7 +21984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:37" ht="20.100000000000001" customHeight="1">
+    <row r="10" spans="1:37" ht="16.5" customHeight="1">
       <c r="A10" s="87" t="s">
         <v>2144</v>
       </c>
@@ -22018,7 +22082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:37" ht="20.100000000000001" customHeight="1">
+    <row r="11" spans="1:37" ht="16.5" customHeight="1">
       <c r="A11" s="87" t="s">
         <v>396</v>
       </c>
@@ -22116,7 +22180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:37" ht="20.100000000000001" customHeight="1">
+    <row r="12" spans="1:37" ht="16.5" customHeight="1">
       <c r="A12" s="87" t="s">
         <v>404</v>
       </c>
@@ -22214,7 +22278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:37" ht="20.100000000000001" customHeight="1">
+    <row r="13" spans="1:37" ht="16.5" customHeight="1">
       <c r="A13" s="87" t="s">
         <v>1545</v>
       </c>
@@ -22315,7 +22379,7 @@
       <c r="AJ13" s="96"/>
       <c r="AK13" s="96"/>
     </row>
-    <row r="14" spans="1:37" ht="20.100000000000001" customHeight="1">
+    <row r="14" spans="1:37" ht="16.5" customHeight="1">
       <c r="A14" s="87" t="s">
         <v>302</v>
       </c>
@@ -22417,7 +22481,7 @@
       <c r="AJ14" s="97"/>
       <c r="AK14" s="96"/>
     </row>
-    <row r="15" spans="1:37" ht="20.100000000000001" customHeight="1">
+    <row r="15" spans="1:37" ht="16.5" customHeight="1">
       <c r="A15" s="87" t="s">
         <v>365</v>
       </c>
@@ -22518,7 +22582,7 @@
       <c r="AI15" s="64"/>
       <c r="AJ15" s="64"/>
     </row>
-    <row r="16" spans="1:37" ht="20.100000000000001" customHeight="1">
+    <row r="16" spans="1:37" ht="16.5" customHeight="1">
       <c r="A16" s="87" t="s">
         <v>304</v>
       </c>
@@ -22619,7 +22683,7 @@
       <c r="AI16" s="64"/>
       <c r="AJ16" s="64"/>
     </row>
-    <row r="17" spans="1:32" ht="20.100000000000001" customHeight="1">
+    <row r="17" spans="1:32" ht="16.5" customHeight="1">
       <c r="A17" s="87" t="s">
         <v>297</v>
       </c>
@@ -22717,7 +22781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:32" ht="20.100000000000001" customHeight="1">
+    <row r="18" spans="1:32" ht="16.5" customHeight="1">
       <c r="A18" s="87" t="s">
         <v>433</v>
       </c>
@@ -22815,7 +22879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:32" ht="20.100000000000001" customHeight="1">
+    <row r="19" spans="1:32" ht="16.5" customHeight="1">
       <c r="A19" s="87" t="s">
         <v>315</v>
       </c>
@@ -22913,7 +22977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:32" ht="20.100000000000001" customHeight="1">
+    <row r="20" spans="1:32" ht="16.5" customHeight="1">
       <c r="A20" s="87" t="s">
         <v>459</v>
       </c>
@@ -23011,7 +23075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:32" ht="20.100000000000001" customHeight="1">
+    <row r="21" spans="1:32" ht="16.5" customHeight="1">
       <c r="A21" s="87" t="s">
         <v>162</v>
       </c>
@@ -23109,7 +23173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:32" ht="20.100000000000001" customHeight="1">
+    <row r="22" spans="1:32" ht="16.5" customHeight="1">
       <c r="A22" s="87" t="s">
         <v>186</v>
       </c>
@@ -23207,7 +23271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:32" ht="20.100000000000001" customHeight="1">
+    <row r="23" spans="1:32" ht="16.5" customHeight="1">
       <c r="A23" s="176" t="s">
         <v>2165</v>
       </c>
@@ -23305,7 +23369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:32">
+    <row r="24" spans="1:32" ht="16.5" customHeight="1">
       <c r="A24" s="176" t="s">
         <v>373</v>
       </c>
@@ -23403,7 +23467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:32">
+    <row r="25" spans="1:32" ht="16.5" customHeight="1">
       <c r="A25" s="176" t="s">
         <v>311</v>
       </c>
@@ -23501,7 +23565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:32">
+    <row r="26" spans="1:32" ht="16.5" customHeight="1">
       <c r="A26" s="176" t="s">
         <v>192</v>
       </c>
@@ -23599,7 +23663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:32">
+    <row r="27" spans="1:32" ht="16.5" customHeight="1">
       <c r="A27" s="176" t="s">
         <v>2173</v>
       </c>
@@ -23697,7 +23761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:32">
+    <row r="28" spans="1:32" ht="16.5" customHeight="1">
       <c r="A28" s="176" t="s">
         <v>2174</v>
       </c>
@@ -23795,7 +23859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:32">
+    <row r="29" spans="1:32" ht="16.5" customHeight="1">
       <c r="A29" s="176" t="s">
         <v>2175</v>
       </c>
@@ -23893,7 +23957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:32" ht="17.25" thickBot="1">
+    <row r="30" spans="1:32" ht="16.5" customHeight="1" thickBot="1">
       <c r="A30" s="88" t="s">
         <v>2176</v>
       </c>
@@ -23991,7 +24055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:32">
+    <row r="31" spans="1:32" ht="16.5" customHeight="1">
       <c r="A31" s="174" t="s">
         <v>2166</v>
       </c>
@@ -24089,7 +24153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:32">
+    <row r="32" spans="1:32" ht="16.5" customHeight="1">
       <c r="A32" s="87" t="s">
         <v>2167</v>
       </c>
@@ -24187,7 +24251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:32" ht="17.25" thickBot="1">
+    <row r="33" spans="1:32" ht="16.5" customHeight="1" thickBot="1">
       <c r="A33" s="176" t="s">
         <v>2168</v>
       </c>
@@ -24285,7 +24349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:32">
+    <row r="34" spans="1:32" ht="16.5" customHeight="1">
       <c r="A34" s="180" t="s">
         <v>2170</v>
       </c>
@@ -24383,7 +24447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:32">
+    <row r="35" spans="1:32" ht="16.5" customHeight="1">
       <c r="A35" s="181" t="s">
         <v>401</v>
       </c>
@@ -24481,7 +24545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:32">
+    <row r="36" spans="1:32" ht="16.5" customHeight="1">
       <c r="A36" s="181" t="s">
         <v>1553</v>
       </c>
@@ -24579,7 +24643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:32">
+    <row r="37" spans="1:32" ht="16.5" customHeight="1">
       <c r="A37" s="181" t="s">
         <v>1554</v>
       </c>
@@ -24677,7 +24741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:32">
+    <row r="38" spans="1:32" ht="16.5" customHeight="1">
       <c r="A38" s="181" t="s">
         <v>321</v>
       </c>
@@ -24775,7 +24839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:32">
+    <row r="39" spans="1:32" ht="16.5" customHeight="1">
       <c r="A39" s="181" t="s">
         <v>1555</v>
       </c>
@@ -24873,7 +24937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:32">
+    <row r="40" spans="1:32" ht="16.5" customHeight="1">
       <c r="A40" s="181" t="s">
         <v>1556</v>
       </c>
@@ -24971,7 +25035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:32" ht="17.25" thickBot="1">
+    <row r="41" spans="1:32" ht="16.5" customHeight="1" thickBot="1">
       <c r="A41" s="183" t="s">
         <v>2171</v>
       </c>
@@ -25066,6 +25130,1378 @@
         <v>0</v>
       </c>
       <c r="AF41" s="191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:32" ht="16.5" customHeight="1">
+      <c r="A42" s="181" t="s">
+        <v>2544</v>
+      </c>
+      <c r="B42" s="21" t="s">
+        <v>2134</v>
+      </c>
+      <c r="C42" s="21" t="s">
+        <v>2169</v>
+      </c>
+      <c r="D42" s="21">
+        <v>0</v>
+      </c>
+      <c r="E42" s="21">
+        <v>0</v>
+      </c>
+      <c r="F42" s="21">
+        <v>0</v>
+      </c>
+      <c r="G42" s="177">
+        <v>0</v>
+      </c>
+      <c r="H42" s="21">
+        <v>0</v>
+      </c>
+      <c r="I42" s="21">
+        <v>0</v>
+      </c>
+      <c r="J42" s="21">
+        <v>0</v>
+      </c>
+      <c r="K42" s="21">
+        <v>0</v>
+      </c>
+      <c r="L42" s="21">
+        <v>0</v>
+      </c>
+      <c r="M42" s="79">
+        <v>0</v>
+      </c>
+      <c r="N42" s="79">
+        <v>0</v>
+      </c>
+      <c r="O42" s="79">
+        <v>0</v>
+      </c>
+      <c r="P42" s="79">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="79">
+        <v>0</v>
+      </c>
+      <c r="R42" s="79">
+        <v>0</v>
+      </c>
+      <c r="S42" s="79">
+        <v>0</v>
+      </c>
+      <c r="T42" s="79">
+        <v>0</v>
+      </c>
+      <c r="U42" s="79">
+        <v>0</v>
+      </c>
+      <c r="V42" s="79">
+        <v>0</v>
+      </c>
+      <c r="W42" s="79">
+        <v>0</v>
+      </c>
+      <c r="X42" s="79">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="79">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="79">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="79">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="21">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="21">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="21">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="21">
+        <v>0</v>
+      </c>
+      <c r="AF42" s="182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:32" ht="16.5" customHeight="1" thickBot="1">
+      <c r="A43" s="238" t="s">
+        <v>2545</v>
+      </c>
+      <c r="B43" s="177" t="s">
+        <v>2134</v>
+      </c>
+      <c r="C43" s="177" t="s">
+        <v>2169</v>
+      </c>
+      <c r="D43" s="239" t="s">
+        <v>2157</v>
+      </c>
+      <c r="E43" s="239" t="s">
+        <v>2145</v>
+      </c>
+      <c r="F43" s="239" t="s">
+        <v>2158</v>
+      </c>
+      <c r="G43" s="177" t="s">
+        <v>1541</v>
+      </c>
+      <c r="H43" s="239">
+        <v>0</v>
+      </c>
+      <c r="I43" s="239">
+        <v>0</v>
+      </c>
+      <c r="J43" s="239">
+        <v>0</v>
+      </c>
+      <c r="K43" s="239">
+        <v>0</v>
+      </c>
+      <c r="L43" s="239">
+        <v>0</v>
+      </c>
+      <c r="M43" s="177">
+        <v>0</v>
+      </c>
+      <c r="N43" s="177">
+        <v>0</v>
+      </c>
+      <c r="O43" s="177">
+        <v>0</v>
+      </c>
+      <c r="P43" s="177">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="177">
+        <v>0</v>
+      </c>
+      <c r="R43" s="177">
+        <v>0</v>
+      </c>
+      <c r="S43" s="177">
+        <v>0</v>
+      </c>
+      <c r="T43" s="177">
+        <v>0</v>
+      </c>
+      <c r="U43" s="177">
+        <v>0</v>
+      </c>
+      <c r="V43" s="177">
+        <v>0</v>
+      </c>
+      <c r="W43" s="177">
+        <v>0</v>
+      </c>
+      <c r="X43" s="177">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="177">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="177">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="177">
+        <v>0</v>
+      </c>
+      <c r="AB43" s="177">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="177">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="177">
+        <v>0</v>
+      </c>
+      <c r="AE43" s="177">
+        <v>0</v>
+      </c>
+      <c r="AF43" s="240">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:32" ht="16.5" customHeight="1">
+      <c r="A44" s="89" t="s">
+        <v>2546</v>
+      </c>
+      <c r="B44" s="241" t="s">
+        <v>2134</v>
+      </c>
+      <c r="C44" s="17">
+        <v>0</v>
+      </c>
+      <c r="D44" s="17">
+        <v>0</v>
+      </c>
+      <c r="E44" s="17">
+        <v>0</v>
+      </c>
+      <c r="F44" s="17">
+        <v>0</v>
+      </c>
+      <c r="G44" s="17">
+        <v>0</v>
+      </c>
+      <c r="H44" s="17">
+        <v>0</v>
+      </c>
+      <c r="I44" s="17">
+        <v>0</v>
+      </c>
+      <c r="J44" s="17">
+        <v>0</v>
+      </c>
+      <c r="K44" s="17">
+        <v>0</v>
+      </c>
+      <c r="L44" s="16">
+        <v>0</v>
+      </c>
+      <c r="M44" s="16">
+        <v>0</v>
+      </c>
+      <c r="N44" s="16">
+        <v>0</v>
+      </c>
+      <c r="O44" s="16">
+        <v>0</v>
+      </c>
+      <c r="P44" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="16">
+        <v>0</v>
+      </c>
+      <c r="R44" s="16">
+        <v>0</v>
+      </c>
+      <c r="S44" s="16">
+        <v>0</v>
+      </c>
+      <c r="T44" s="16">
+        <v>0</v>
+      </c>
+      <c r="U44" s="16">
+        <v>0</v>
+      </c>
+      <c r="V44" s="16">
+        <v>0</v>
+      </c>
+      <c r="W44" s="16">
+        <v>0</v>
+      </c>
+      <c r="X44" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="16">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="16">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="16">
+        <v>0</v>
+      </c>
+      <c r="AB44" s="16">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="16">
+        <v>0</v>
+      </c>
+      <c r="AD44" s="16">
+        <v>0</v>
+      </c>
+      <c r="AE44" s="16">
+        <v>0</v>
+      </c>
+      <c r="AF44" s="242">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:32" ht="16.5" customHeight="1">
+      <c r="A45" s="87" t="s">
+        <v>2548</v>
+      </c>
+      <c r="B45" s="137" t="s">
+        <v>2134</v>
+      </c>
+      <c r="C45" s="21">
+        <v>0</v>
+      </c>
+      <c r="D45" s="21">
+        <v>0</v>
+      </c>
+      <c r="E45" s="21">
+        <v>0</v>
+      </c>
+      <c r="F45" s="21">
+        <v>0</v>
+      </c>
+      <c r="G45" s="21">
+        <v>0</v>
+      </c>
+      <c r="H45" s="21">
+        <v>0</v>
+      </c>
+      <c r="I45" s="21">
+        <v>0</v>
+      </c>
+      <c r="J45" s="21">
+        <v>0</v>
+      </c>
+      <c r="K45" s="21">
+        <v>0</v>
+      </c>
+      <c r="L45" s="21">
+        <v>0</v>
+      </c>
+      <c r="M45" s="20">
+        <v>0</v>
+      </c>
+      <c r="N45" s="20">
+        <v>0</v>
+      </c>
+      <c r="O45" s="20">
+        <v>0</v>
+      </c>
+      <c r="P45" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="20">
+        <v>0</v>
+      </c>
+      <c r="R45" s="20">
+        <v>0</v>
+      </c>
+      <c r="S45" s="20">
+        <v>0</v>
+      </c>
+      <c r="T45" s="20">
+        <v>0</v>
+      </c>
+      <c r="U45" s="20">
+        <v>0</v>
+      </c>
+      <c r="V45" s="20">
+        <v>0</v>
+      </c>
+      <c r="W45" s="20">
+        <v>0</v>
+      </c>
+      <c r="X45" s="20">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="20">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="20">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="20">
+        <v>0</v>
+      </c>
+      <c r="AB45" s="20">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="20">
+        <v>0</v>
+      </c>
+      <c r="AD45" s="20">
+        <v>0</v>
+      </c>
+      <c r="AE45" s="20">
+        <v>0</v>
+      </c>
+      <c r="AF45" s="93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:32" ht="16.5" customHeight="1">
+      <c r="A46" s="87" t="s">
+        <v>2549</v>
+      </c>
+      <c r="B46" s="137" t="s">
+        <v>2134</v>
+      </c>
+      <c r="C46" s="21">
+        <v>0</v>
+      </c>
+      <c r="D46" s="21">
+        <v>0</v>
+      </c>
+      <c r="E46" s="21">
+        <v>0</v>
+      </c>
+      <c r="F46" s="21">
+        <v>0</v>
+      </c>
+      <c r="G46" s="21">
+        <v>0</v>
+      </c>
+      <c r="H46" s="21">
+        <v>0</v>
+      </c>
+      <c r="I46" s="21">
+        <v>0</v>
+      </c>
+      <c r="J46" s="21">
+        <v>0</v>
+      </c>
+      <c r="K46" s="21">
+        <v>0</v>
+      </c>
+      <c r="L46" s="21">
+        <v>0</v>
+      </c>
+      <c r="M46" s="21">
+        <v>0</v>
+      </c>
+      <c r="N46" s="21">
+        <v>0</v>
+      </c>
+      <c r="O46" s="21">
+        <v>0</v>
+      </c>
+      <c r="P46" s="21">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="21">
+        <v>0</v>
+      </c>
+      <c r="R46" s="21">
+        <v>0</v>
+      </c>
+      <c r="S46" s="21">
+        <v>0</v>
+      </c>
+      <c r="T46" s="21">
+        <v>0</v>
+      </c>
+      <c r="U46" s="21">
+        <v>0</v>
+      </c>
+      <c r="V46" s="20">
+        <v>0</v>
+      </c>
+      <c r="W46" s="20">
+        <v>0</v>
+      </c>
+      <c r="X46" s="20">
+        <v>0</v>
+      </c>
+      <c r="Y46" s="20">
+        <v>0</v>
+      </c>
+      <c r="Z46" s="20">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="20">
+        <v>0</v>
+      </c>
+      <c r="AB46" s="20">
+        <v>0</v>
+      </c>
+      <c r="AC46" s="20">
+        <v>0</v>
+      </c>
+      <c r="AD46" s="20">
+        <v>0</v>
+      </c>
+      <c r="AE46" s="20">
+        <v>0</v>
+      </c>
+      <c r="AF46" s="93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:32" ht="16.5" customHeight="1">
+      <c r="A47" s="87" t="s">
+        <v>2550</v>
+      </c>
+      <c r="B47" s="184" t="s">
+        <v>2134</v>
+      </c>
+      <c r="C47" s="177">
+        <v>0</v>
+      </c>
+      <c r="D47" s="177">
+        <v>0</v>
+      </c>
+      <c r="E47" s="177">
+        <v>0</v>
+      </c>
+      <c r="F47" s="177">
+        <v>0</v>
+      </c>
+      <c r="G47" s="177">
+        <v>0</v>
+      </c>
+      <c r="H47" s="177">
+        <v>0</v>
+      </c>
+      <c r="I47" s="177">
+        <v>0</v>
+      </c>
+      <c r="J47" s="177">
+        <v>0</v>
+      </c>
+      <c r="K47" s="177">
+        <v>0</v>
+      </c>
+      <c r="L47" s="177">
+        <v>0</v>
+      </c>
+      <c r="M47" s="177">
+        <v>0</v>
+      </c>
+      <c r="N47" s="177">
+        <v>0</v>
+      </c>
+      <c r="O47" s="177">
+        <v>0</v>
+      </c>
+      <c r="P47" s="177">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="177">
+        <v>0</v>
+      </c>
+      <c r="R47" s="177">
+        <v>0</v>
+      </c>
+      <c r="S47" s="177">
+        <v>0</v>
+      </c>
+      <c r="T47" s="177">
+        <v>0</v>
+      </c>
+      <c r="U47" s="177">
+        <v>0</v>
+      </c>
+      <c r="V47" s="177">
+        <v>0</v>
+      </c>
+      <c r="W47" s="177">
+        <v>0</v>
+      </c>
+      <c r="X47" s="177">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="177">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="177">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="177">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="177">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="20">
+        <v>0</v>
+      </c>
+      <c r="AD47" s="20">
+        <v>0</v>
+      </c>
+      <c r="AE47" s="20">
+        <v>0</v>
+      </c>
+      <c r="AF47" s="93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:32" ht="16.5" customHeight="1">
+      <c r="A48" s="87" t="s">
+        <v>2551</v>
+      </c>
+      <c r="B48" s="21" t="s">
+        <v>2134</v>
+      </c>
+      <c r="C48" s="21">
+        <v>0</v>
+      </c>
+      <c r="D48" s="21">
+        <v>0</v>
+      </c>
+      <c r="E48" s="21">
+        <v>0</v>
+      </c>
+      <c r="F48" s="21">
+        <v>0</v>
+      </c>
+      <c r="G48" s="21">
+        <v>0</v>
+      </c>
+      <c r="H48" s="21">
+        <v>0</v>
+      </c>
+      <c r="I48" s="21">
+        <v>0</v>
+      </c>
+      <c r="J48" s="21">
+        <v>0</v>
+      </c>
+      <c r="K48" s="21">
+        <v>0</v>
+      </c>
+      <c r="L48" s="21">
+        <v>0</v>
+      </c>
+      <c r="M48" s="21">
+        <v>0</v>
+      </c>
+      <c r="N48" s="21">
+        <v>0</v>
+      </c>
+      <c r="O48" s="21">
+        <v>0</v>
+      </c>
+      <c r="P48" s="21">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="21">
+        <v>0</v>
+      </c>
+      <c r="R48" s="21">
+        <v>0</v>
+      </c>
+      <c r="S48" s="21">
+        <v>0</v>
+      </c>
+      <c r="T48" s="21">
+        <v>0</v>
+      </c>
+      <c r="U48" s="20">
+        <v>0</v>
+      </c>
+      <c r="V48" s="20">
+        <v>0</v>
+      </c>
+      <c r="W48" s="20">
+        <v>0</v>
+      </c>
+      <c r="X48" s="20">
+        <v>0</v>
+      </c>
+      <c r="Y48" s="20">
+        <v>0</v>
+      </c>
+      <c r="Z48" s="20">
+        <v>0</v>
+      </c>
+      <c r="AA48" s="20">
+        <v>0</v>
+      </c>
+      <c r="AB48" s="20">
+        <v>0</v>
+      </c>
+      <c r="AC48" s="20">
+        <v>0</v>
+      </c>
+      <c r="AD48" s="20">
+        <v>0</v>
+      </c>
+      <c r="AE48" s="20">
+        <v>0</v>
+      </c>
+      <c r="AF48" s="93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:32" ht="16.5" customHeight="1">
+      <c r="A49" s="87" t="s">
+        <v>2552</v>
+      </c>
+      <c r="B49" s="137" t="s">
+        <v>2134</v>
+      </c>
+      <c r="C49" s="21">
+        <v>0</v>
+      </c>
+      <c r="D49" s="21">
+        <v>0</v>
+      </c>
+      <c r="E49" s="21">
+        <v>0</v>
+      </c>
+      <c r="F49" s="21">
+        <v>0</v>
+      </c>
+      <c r="G49" s="21">
+        <v>0</v>
+      </c>
+      <c r="H49" s="21">
+        <v>0</v>
+      </c>
+      <c r="I49" s="21">
+        <v>0</v>
+      </c>
+      <c r="J49" s="21">
+        <v>0</v>
+      </c>
+      <c r="K49" s="21">
+        <v>0</v>
+      </c>
+      <c r="L49" s="21">
+        <v>0</v>
+      </c>
+      <c r="M49" s="21">
+        <v>0</v>
+      </c>
+      <c r="N49" s="21">
+        <v>0</v>
+      </c>
+      <c r="O49" s="21">
+        <v>0</v>
+      </c>
+      <c r="P49" s="46">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="46">
+        <v>0</v>
+      </c>
+      <c r="R49" s="46">
+        <v>0</v>
+      </c>
+      <c r="S49" s="46">
+        <v>0</v>
+      </c>
+      <c r="T49" s="46">
+        <v>0</v>
+      </c>
+      <c r="U49" s="20">
+        <v>0</v>
+      </c>
+      <c r="V49" s="20">
+        <v>0</v>
+      </c>
+      <c r="W49" s="20">
+        <v>0</v>
+      </c>
+      <c r="X49" s="20">
+        <v>0</v>
+      </c>
+      <c r="Y49" s="20">
+        <v>0</v>
+      </c>
+      <c r="Z49" s="20">
+        <v>0</v>
+      </c>
+      <c r="AA49" s="20">
+        <v>0</v>
+      </c>
+      <c r="AB49" s="20">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="20">
+        <v>0</v>
+      </c>
+      <c r="AD49" s="20">
+        <v>0</v>
+      </c>
+      <c r="AE49" s="20">
+        <v>0</v>
+      </c>
+      <c r="AF49" s="93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:32" ht="16.5" customHeight="1">
+      <c r="A50" s="87" t="s">
+        <v>2547</v>
+      </c>
+      <c r="B50" s="137" t="s">
+        <v>2134</v>
+      </c>
+      <c r="C50" s="21">
+        <v>0</v>
+      </c>
+      <c r="D50" s="21">
+        <v>0</v>
+      </c>
+      <c r="E50" s="21">
+        <v>0</v>
+      </c>
+      <c r="F50" s="21">
+        <v>0</v>
+      </c>
+      <c r="G50" s="21">
+        <v>0</v>
+      </c>
+      <c r="H50" s="21">
+        <v>0</v>
+      </c>
+      <c r="I50" s="21">
+        <v>0</v>
+      </c>
+      <c r="J50" s="21">
+        <v>0</v>
+      </c>
+      <c r="K50" s="21">
+        <v>0</v>
+      </c>
+      <c r="L50" s="21">
+        <v>0</v>
+      </c>
+      <c r="M50" s="21">
+        <v>0</v>
+      </c>
+      <c r="N50" s="21">
+        <v>0</v>
+      </c>
+      <c r="O50" s="20">
+        <v>0</v>
+      </c>
+      <c r="P50" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="20">
+        <v>0</v>
+      </c>
+      <c r="R50" s="20">
+        <v>0</v>
+      </c>
+      <c r="S50" s="20">
+        <v>0</v>
+      </c>
+      <c r="T50" s="20">
+        <v>0</v>
+      </c>
+      <c r="U50" s="20">
+        <v>0</v>
+      </c>
+      <c r="V50" s="20">
+        <v>0</v>
+      </c>
+      <c r="W50" s="20">
+        <v>0</v>
+      </c>
+      <c r="X50" s="20">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="20">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="20">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="20">
+        <v>0</v>
+      </c>
+      <c r="AB50" s="20">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="20">
+        <v>0</v>
+      </c>
+      <c r="AD50" s="20">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="20">
+        <v>0</v>
+      </c>
+      <c r="AF50" s="93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:32" ht="16.5" customHeight="1">
+      <c r="A51" s="87" t="s">
+        <v>2553</v>
+      </c>
+      <c r="B51" s="137" t="s">
+        <v>2134</v>
+      </c>
+      <c r="C51" s="21">
+        <v>0</v>
+      </c>
+      <c r="D51" s="21">
+        <v>0</v>
+      </c>
+      <c r="E51" s="21">
+        <v>0</v>
+      </c>
+      <c r="F51" s="21">
+        <v>0</v>
+      </c>
+      <c r="G51" s="21">
+        <v>0</v>
+      </c>
+      <c r="H51" s="21">
+        <v>0</v>
+      </c>
+      <c r="I51" s="21">
+        <v>0</v>
+      </c>
+      <c r="J51" s="21">
+        <v>0</v>
+      </c>
+      <c r="K51" s="21">
+        <v>0</v>
+      </c>
+      <c r="L51" s="21">
+        <v>0</v>
+      </c>
+      <c r="M51" s="21">
+        <v>0</v>
+      </c>
+      <c r="N51" s="21">
+        <v>0</v>
+      </c>
+      <c r="O51" s="21">
+        <v>0</v>
+      </c>
+      <c r="P51" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="20">
+        <v>0</v>
+      </c>
+      <c r="R51" s="20">
+        <v>0</v>
+      </c>
+      <c r="S51" s="20">
+        <v>0</v>
+      </c>
+      <c r="T51" s="20">
+        <v>0</v>
+      </c>
+      <c r="U51" s="20">
+        <v>0</v>
+      </c>
+      <c r="V51" s="20">
+        <v>0</v>
+      </c>
+      <c r="W51" s="20">
+        <v>0</v>
+      </c>
+      <c r="X51" s="20">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="20">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="20">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="20">
+        <v>0</v>
+      </c>
+      <c r="AB51" s="20">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="20">
+        <v>0</v>
+      </c>
+      <c r="AD51" s="20">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="20">
+        <v>0</v>
+      </c>
+      <c r="AF51" s="93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:32" ht="16.5" customHeight="1">
+      <c r="A52" s="87" t="s">
+        <v>2554</v>
+      </c>
+      <c r="B52" s="137" t="s">
+        <v>2134</v>
+      </c>
+      <c r="C52" s="21">
+        <v>0</v>
+      </c>
+      <c r="D52" s="21">
+        <v>0</v>
+      </c>
+      <c r="E52" s="21">
+        <v>0</v>
+      </c>
+      <c r="F52" s="21">
+        <v>0</v>
+      </c>
+      <c r="G52" s="21">
+        <v>0</v>
+      </c>
+      <c r="H52" s="21">
+        <v>0</v>
+      </c>
+      <c r="I52" s="21">
+        <v>0</v>
+      </c>
+      <c r="J52" s="21">
+        <v>0</v>
+      </c>
+      <c r="K52" s="21">
+        <v>0</v>
+      </c>
+      <c r="L52" s="21">
+        <v>0</v>
+      </c>
+      <c r="M52" s="21">
+        <v>0</v>
+      </c>
+      <c r="N52" s="21">
+        <v>0</v>
+      </c>
+      <c r="O52" s="21">
+        <v>0</v>
+      </c>
+      <c r="P52" s="21">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="21">
+        <v>0</v>
+      </c>
+      <c r="R52" s="20">
+        <v>0</v>
+      </c>
+      <c r="S52" s="20">
+        <v>0</v>
+      </c>
+      <c r="T52" s="20">
+        <v>0</v>
+      </c>
+      <c r="U52" s="20">
+        <v>0</v>
+      </c>
+      <c r="V52" s="20">
+        <v>0</v>
+      </c>
+      <c r="W52" s="20">
+        <v>0</v>
+      </c>
+      <c r="X52" s="20">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="20">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="20">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="20">
+        <v>0</v>
+      </c>
+      <c r="AB52" s="20">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="20">
+        <v>0</v>
+      </c>
+      <c r="AD52" s="20">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="20">
+        <v>0</v>
+      </c>
+      <c r="AF52" s="93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:32" ht="16.5" customHeight="1">
+      <c r="A53" s="87" t="s">
+        <v>2555</v>
+      </c>
+      <c r="B53" s="184" t="s">
+        <v>2134</v>
+      </c>
+      <c r="C53" s="177">
+        <v>0</v>
+      </c>
+      <c r="D53" s="177">
+        <v>0</v>
+      </c>
+      <c r="E53" s="177">
+        <v>0</v>
+      </c>
+      <c r="F53" s="177">
+        <v>0</v>
+      </c>
+      <c r="G53" s="177">
+        <v>0</v>
+      </c>
+      <c r="H53" s="177">
+        <v>0</v>
+      </c>
+      <c r="I53" s="177">
+        <v>0</v>
+      </c>
+      <c r="J53" s="177">
+        <v>0</v>
+      </c>
+      <c r="K53" s="177">
+        <v>0</v>
+      </c>
+      <c r="L53" s="177">
+        <v>0</v>
+      </c>
+      <c r="M53" s="177">
+        <v>0</v>
+      </c>
+      <c r="N53" s="177">
+        <v>0</v>
+      </c>
+      <c r="O53" s="177">
+        <v>0</v>
+      </c>
+      <c r="P53" s="177">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="177">
+        <v>0</v>
+      </c>
+      <c r="R53" s="177">
+        <v>0</v>
+      </c>
+      <c r="S53" s="177">
+        <v>0</v>
+      </c>
+      <c r="T53" s="177">
+        <v>0</v>
+      </c>
+      <c r="U53" s="177">
+        <v>0</v>
+      </c>
+      <c r="V53" s="177">
+        <v>0</v>
+      </c>
+      <c r="W53" s="177">
+        <v>0</v>
+      </c>
+      <c r="X53" s="177">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="177">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="177">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="177">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="177">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="20">
+        <v>0</v>
+      </c>
+      <c r="AD53" s="20">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="20">
+        <v>0</v>
+      </c>
+      <c r="AF53" s="93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:32" ht="16.5" customHeight="1">
+      <c r="A54" s="87" t="s">
+        <v>2556</v>
+      </c>
+      <c r="B54" s="21" t="s">
+        <v>2134</v>
+      </c>
+      <c r="C54" s="21">
+        <v>0</v>
+      </c>
+      <c r="D54" s="21">
+        <v>0</v>
+      </c>
+      <c r="E54" s="21">
+        <v>0</v>
+      </c>
+      <c r="F54" s="21">
+        <v>0</v>
+      </c>
+      <c r="G54" s="21">
+        <v>0</v>
+      </c>
+      <c r="H54" s="21">
+        <v>0</v>
+      </c>
+      <c r="I54" s="21">
+        <v>0</v>
+      </c>
+      <c r="J54" s="21">
+        <v>0</v>
+      </c>
+      <c r="K54" s="21">
+        <v>0</v>
+      </c>
+      <c r="L54" s="21">
+        <v>0</v>
+      </c>
+      <c r="M54" s="21">
+        <v>0</v>
+      </c>
+      <c r="N54" s="21">
+        <v>0</v>
+      </c>
+      <c r="O54" s="21">
+        <v>0</v>
+      </c>
+      <c r="P54" s="21">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="21">
+        <v>0</v>
+      </c>
+      <c r="R54" s="21">
+        <v>0</v>
+      </c>
+      <c r="S54" s="21">
+        <v>0</v>
+      </c>
+      <c r="T54" s="21">
+        <v>0</v>
+      </c>
+      <c r="U54" s="20">
+        <v>0</v>
+      </c>
+      <c r="V54" s="20">
+        <v>0</v>
+      </c>
+      <c r="W54" s="20">
+        <v>0</v>
+      </c>
+      <c r="X54" s="20">
+        <v>0</v>
+      </c>
+      <c r="Y54" s="20">
+        <v>0</v>
+      </c>
+      <c r="Z54" s="20">
+        <v>0</v>
+      </c>
+      <c r="AA54" s="20">
+        <v>0</v>
+      </c>
+      <c r="AB54" s="20">
+        <v>0</v>
+      </c>
+      <c r="AC54" s="20">
+        <v>0</v>
+      </c>
+      <c r="AD54" s="20">
+        <v>0</v>
+      </c>
+      <c r="AE54" s="20">
+        <v>0</v>
+      </c>
+      <c r="AF54" s="93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:32" ht="16.5" customHeight="1" thickBot="1">
+      <c r="A55" s="88" t="s">
+        <v>2557</v>
+      </c>
+      <c r="B55" s="243" t="s">
+        <v>2134</v>
+      </c>
+      <c r="C55" s="26">
+        <v>0</v>
+      </c>
+      <c r="D55" s="26">
+        <v>0</v>
+      </c>
+      <c r="E55" s="26">
+        <v>0</v>
+      </c>
+      <c r="F55" s="26">
+        <v>0</v>
+      </c>
+      <c r="G55" s="26">
+        <v>0</v>
+      </c>
+      <c r="H55" s="26">
+        <v>0</v>
+      </c>
+      <c r="I55" s="26">
+        <v>0</v>
+      </c>
+      <c r="J55" s="26">
+        <v>0</v>
+      </c>
+      <c r="K55" s="26">
+        <v>0</v>
+      </c>
+      <c r="L55" s="26">
+        <v>0</v>
+      </c>
+      <c r="M55" s="26">
+        <v>0</v>
+      </c>
+      <c r="N55" s="26">
+        <v>0</v>
+      </c>
+      <c r="O55" s="26">
+        <v>0</v>
+      </c>
+      <c r="P55" s="26">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="91">
+        <v>0</v>
+      </c>
+      <c r="R55" s="91">
+        <v>0</v>
+      </c>
+      <c r="S55" s="91">
+        <v>0</v>
+      </c>
+      <c r="T55" s="91">
+        <v>0</v>
+      </c>
+      <c r="U55" s="25">
+        <v>0</v>
+      </c>
+      <c r="V55" s="25">
+        <v>0</v>
+      </c>
+      <c r="W55" s="25">
+        <v>0</v>
+      </c>
+      <c r="X55" s="25">
+        <v>0</v>
+      </c>
+      <c r="Y55" s="25">
+        <v>0</v>
+      </c>
+      <c r="Z55" s="25">
+        <v>0</v>
+      </c>
+      <c r="AA55" s="25">
+        <v>0</v>
+      </c>
+      <c r="AB55" s="25">
+        <v>0</v>
+      </c>
+      <c r="AC55" s="25">
+        <v>0</v>
+      </c>
+      <c r="AD55" s="25">
+        <v>0</v>
+      </c>
+      <c r="AE55" s="25">
+        <v>0</v>
+      </c>
+      <c r="AF55" s="95">
         <v>0</v>
       </c>
     </row>
@@ -41699,7 +43135,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="156" t="s">
-        <v>2260</v>
+        <v>2544</v>
       </c>
       <c r="I4" s="20" t="s">
         <v>294</v>
@@ -42459,7 +43895,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="45" t="s">
-        <v>2132</v>
+        <v>2544</v>
       </c>
       <c r="I24" s="20" t="s">
         <v>294</v>
@@ -42801,7 +44237,7 @@
         <v>0</v>
       </c>
       <c r="H33" s="45" t="s">
-        <v>2132</v>
+        <v>2545</v>
       </c>
       <c r="I33" s="20" t="s">
         <v>294</v>
@@ -43105,7 +44541,7 @@
         <v>0</v>
       </c>
       <c r="H41" s="21" t="s">
-        <v>2132</v>
+        <v>2545</v>
       </c>
       <c r="I41" s="20" t="s">
         <v>294</v>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erang\Desktop\RELIC\Assets\ExcelSource\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k2104200063\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BAEBD5C-53D0-4460-A5D5-DF6D1CA17882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24B8011D-4B48-4DB3-B500-EFCB41F9AEA5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21090" yWindow="1875" windowWidth="21015" windowHeight="14730" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21090" yWindow="1875" windowWidth="21015" windowHeight="14730" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5540" uniqueCount="2559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5549" uniqueCount="2561">
   <si>
     <t>캐릭터ID</t>
   </si>
@@ -17009,10 +17009,6 @@
     <phoneticPr fontId="31" type="noConversion"/>
   </si>
   <si>
-    <t>Attack;Debuff</t>
-    <phoneticPr fontId="31" type="noConversion"/>
-  </si>
-  <si>
     <t>E_Strike;E_Vulnerable</t>
     <phoneticPr fontId="31" type="noConversion"/>
   </si>
@@ -18643,6 +18639,18 @@
   </si>
   <si>
     <t>icon_mon_skill_002</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillType</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>Move</t>
+    <phoneticPr fontId="31" type="noConversion"/>
+  </si>
+  <si>
+    <t>Passive</t>
     <phoneticPr fontId="31" type="noConversion"/>
   </si>
 </sst>
@@ -25140,7 +25148,7 @@
     </row>
     <row r="42" spans="1:32" ht="16.5" customHeight="1">
       <c r="A42" s="181" t="s">
-        <v>2543</v>
+        <v>2542</v>
       </c>
       <c r="B42" s="21" t="s">
         <v>2133</v>
@@ -25238,7 +25246,7 @@
     </row>
     <row r="43" spans="1:32" ht="16.5" customHeight="1" thickBot="1">
       <c r="A43" s="238" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
       <c r="B43" s="177" t="s">
         <v>2133</v>
@@ -25336,7 +25344,7 @@
     </row>
     <row r="44" spans="1:32" ht="16.5" customHeight="1">
       <c r="A44" s="89" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="B44" s="241" t="s">
         <v>2133</v>
@@ -25434,7 +25442,7 @@
     </row>
     <row r="45" spans="1:32" ht="16.5" customHeight="1">
       <c r="A45" s="87" t="s">
-        <v>2547</v>
+        <v>2546</v>
       </c>
       <c r="B45" s="137" t="s">
         <v>2133</v>
@@ -25532,7 +25540,7 @@
     </row>
     <row r="46" spans="1:32" ht="16.5" customHeight="1">
       <c r="A46" s="87" t="s">
-        <v>2548</v>
+        <v>2547</v>
       </c>
       <c r="B46" s="137" t="s">
         <v>2133</v>
@@ -25630,7 +25638,7 @@
     </row>
     <row r="47" spans="1:32" ht="16.5" customHeight="1">
       <c r="A47" s="87" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
       <c r="B47" s="184" t="s">
         <v>2133</v>
@@ -25728,7 +25736,7 @@
     </row>
     <row r="48" spans="1:32" ht="16.5" customHeight="1">
       <c r="A48" s="87" t="s">
-        <v>2550</v>
+        <v>2549</v>
       </c>
       <c r="B48" s="21" t="s">
         <v>2133</v>
@@ -25826,7 +25834,7 @@
     </row>
     <row r="49" spans="1:32" ht="16.5" customHeight="1">
       <c r="A49" s="87" t="s">
-        <v>2551</v>
+        <v>2550</v>
       </c>
       <c r="B49" s="137" t="s">
         <v>2133</v>
@@ -25924,7 +25932,7 @@
     </row>
     <row r="50" spans="1:32" ht="16.5" customHeight="1">
       <c r="A50" s="87" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
       <c r="B50" s="137" t="s">
         <v>2133</v>
@@ -26022,7 +26030,7 @@
     </row>
     <row r="51" spans="1:32" ht="16.5" customHeight="1">
       <c r="A51" s="87" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
       <c r="B51" s="137" t="s">
         <v>2133</v>
@@ -26120,7 +26128,7 @@
     </row>
     <row r="52" spans="1:32" ht="16.5" customHeight="1">
       <c r="A52" s="87" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
       <c r="B52" s="137" t="s">
         <v>2133</v>
@@ -26218,7 +26226,7 @@
     </row>
     <row r="53" spans="1:32" ht="16.5" customHeight="1">
       <c r="A53" s="87" t="s">
-        <v>2554</v>
+        <v>2553</v>
       </c>
       <c r="B53" s="184" t="s">
         <v>2133</v>
@@ -26316,7 +26324,7 @@
     </row>
     <row r="54" spans="1:32" ht="16.5" customHeight="1">
       <c r="A54" s="87" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="B54" s="21" t="s">
         <v>2133</v>
@@ -26414,7 +26422,7 @@
     </row>
     <row r="55" spans="1:32" ht="16.5" customHeight="1" thickBot="1">
       <c r="A55" s="88" t="s">
-        <v>2556</v>
+        <v>2555</v>
       </c>
       <c r="B55" s="243" t="s">
         <v>2133</v>
@@ -32734,7 +32742,7 @@
         <v>0.3</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>2343</v>
+        <v>2342</v>
       </c>
       <c r="K3" s="21" t="s">
         <v>163</v>
@@ -32796,7 +32804,7 @@
         <v>0.3</v>
       </c>
       <c r="J4" s="21" t="s">
-        <v>2537</v>
+        <v>2536</v>
       </c>
       <c r="K4" s="21" t="s">
         <v>169</v>
@@ -32858,7 +32866,7 @@
         <v>0.3</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>2343</v>
+        <v>2342</v>
       </c>
       <c r="K5" s="21" t="s">
         <v>174</v>
@@ -32920,7 +32928,7 @@
         <v>0.3</v>
       </c>
       <c r="J6" s="21" t="s">
-        <v>2343</v>
+        <v>2342</v>
       </c>
       <c r="K6" s="21" t="s">
         <v>180</v>
@@ -32982,7 +32990,7 @@
         <v>0.3</v>
       </c>
       <c r="J7" s="21" t="s">
-        <v>2538</v>
+        <v>2537</v>
       </c>
       <c r="K7" s="21" t="s">
         <v>187</v>
@@ -33106,7 +33114,7 @@
         <v>0.3</v>
       </c>
       <c r="J9" s="21" t="s">
-        <v>2342</v>
+        <v>2341</v>
       </c>
       <c r="K9" s="21" t="s">
         <v>199</v>
@@ -33230,7 +33238,7 @@
         <v>0.2</v>
       </c>
       <c r="J11" s="21" t="s">
-        <v>2342</v>
+        <v>2341</v>
       </c>
       <c r="K11" s="21" t="s">
         <v>212</v>
@@ -34079,7 +34087,7 @@
         <v>263</v>
       </c>
       <c r="H2" s="214" t="s">
-        <v>264</v>
+        <v>2558</v>
       </c>
       <c r="I2" s="214" t="s">
         <v>265</v>
@@ -34128,8 +34136,8 @@
       <c r="G3" s="185">
         <v>1</v>
       </c>
-      <c r="H3" s="185">
-        <v>0</v>
+      <c r="H3" s="185" t="s">
+        <v>2559</v>
       </c>
       <c r="I3" s="185" t="s">
         <v>278</v>
@@ -34178,8 +34186,8 @@
       <c r="G4" s="193">
         <v>0</v>
       </c>
-      <c r="H4" s="193">
-        <v>0</v>
+      <c r="H4" s="193" t="s">
+        <v>2560</v>
       </c>
       <c r="I4" s="193" t="s">
         <v>2124</v>
@@ -34228,8 +34236,8 @@
       <c r="G5" s="193">
         <v>0</v>
       </c>
-      <c r="H5" s="193">
-        <v>0</v>
+      <c r="H5" s="193" t="s">
+        <v>2560</v>
       </c>
       <c r="I5" s="193" t="s">
         <v>2123</v>
@@ -34278,8 +34286,8 @@
       <c r="G6" s="193">
         <v>0</v>
       </c>
-      <c r="H6" s="193">
-        <v>0</v>
+      <c r="H6" s="193" t="s">
+        <v>2560</v>
       </c>
       <c r="I6" s="193" t="s">
         <v>2122</v>
@@ -34323,13 +34331,13 @@
         <v>284</v>
       </c>
       <c r="F7" s="193" t="s">
-        <v>2305</v>
+        <v>2304</v>
       </c>
       <c r="G7" s="193">
         <v>0</v>
       </c>
-      <c r="H7" s="193">
-        <v>0</v>
+      <c r="H7" s="193" t="s">
+        <v>2560</v>
       </c>
       <c r="I7" s="193" t="s">
         <v>2121</v>
@@ -34378,8 +34386,8 @@
       <c r="G8" s="193">
         <v>0</v>
       </c>
-      <c r="H8" s="193">
-        <v>0</v>
+      <c r="H8" s="193" t="s">
+        <v>2560</v>
       </c>
       <c r="I8" s="193" t="s">
         <v>2134</v>
@@ -34394,7 +34402,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="193" t="s">
-        <v>282</v>
+        <v>2560</v>
       </c>
       <c r="N8" s="193" t="s">
         <v>2131</v>
@@ -34428,8 +34436,8 @@
       <c r="G9" s="193">
         <v>0</v>
       </c>
-      <c r="H9" s="193">
-        <v>0</v>
+      <c r="H9" s="193" t="s">
+        <v>2560</v>
       </c>
       <c r="I9" s="193" t="s">
         <v>2136</v>
@@ -34478,8 +34486,8 @@
       <c r="G10" s="193">
         <v>0</v>
       </c>
-      <c r="H10" s="193">
-        <v>0</v>
+      <c r="H10" s="193" t="s">
+        <v>2560</v>
       </c>
       <c r="I10" s="193" t="s">
         <v>2124</v>
@@ -34528,8 +34536,8 @@
       <c r="G11" s="193">
         <v>0</v>
       </c>
-      <c r="H11" s="193">
-        <v>0</v>
+      <c r="H11" s="193" t="s">
+        <v>2560</v>
       </c>
       <c r="I11" s="193" t="s">
         <v>2139</v>
@@ -34547,7 +34555,7 @@
         <v>282</v>
       </c>
       <c r="N11" s="193" t="s">
-        <v>2350</v>
+        <v>2349</v>
       </c>
       <c r="O11" s="195" t="s">
         <v>2140</v>
@@ -34700,7 +34708,7 @@
         <v>2131</v>
       </c>
       <c r="O14" s="194" t="s">
-        <v>2378</v>
+        <v>2377</v>
       </c>
       <c r="P14" s="235">
         <v>0</v>
@@ -34732,7 +34740,7 @@
         <v>294</v>
       </c>
       <c r="I15" s="193" t="s">
-        <v>2341</v>
+        <v>2340</v>
       </c>
       <c r="J15" s="193">
         <v>50</v>
@@ -34750,7 +34758,7 @@
         <v>2201</v>
       </c>
       <c r="O15" s="195" t="s">
-        <v>2344</v>
+        <v>2343</v>
       </c>
       <c r="P15" s="235">
         <v>0</v>
@@ -34800,7 +34808,7 @@
         <v>2202</v>
       </c>
       <c r="O16" s="195" t="s">
-        <v>2268</v>
+        <v>2267</v>
       </c>
       <c r="P16" s="235">
         <v>0</v>
@@ -34870,7 +34878,7 @@
         <v>283</v>
       </c>
       <c r="E18" s="219" t="s">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="F18" s="193" t="s">
         <v>290</v>
@@ -34932,7 +34940,7 @@
         <v>2241</v>
       </c>
       <c r="I19" s="193" t="s">
-        <v>2247</v>
+        <v>2246</v>
       </c>
       <c r="J19" s="193">
         <v>5</v>
@@ -34982,7 +34990,7 @@
         <v>291</v>
       </c>
       <c r="I20" s="193" t="s">
-        <v>2315</v>
+        <v>2314</v>
       </c>
       <c r="J20" s="193">
         <v>3</v>
@@ -35029,10 +35037,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="193" t="s">
+        <v>2215</v>
+      </c>
+      <c r="I21" s="193" t="s">
         <v>2242</v>
-      </c>
-      <c r="I21" s="193" t="s">
-        <v>2243</v>
       </c>
       <c r="J21" s="193" t="s">
         <v>2199</v>
@@ -35194,13 +35202,13 @@
         <v>3</v>
       </c>
       <c r="M24" s="185" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
       <c r="N24" s="185" t="s">
-        <v>2342</v>
+        <v>2341</v>
       </c>
       <c r="O24" s="194" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="P24" s="235">
         <v>0</v>
@@ -35247,10 +35255,10 @@
         <v>292</v>
       </c>
       <c r="N25" s="202" t="s">
-        <v>2343</v>
+        <v>2342</v>
       </c>
       <c r="O25" s="203" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="P25" s="236">
         <v>0</v>
@@ -35282,13 +35290,13 @@
         <v>2215</v>
       </c>
       <c r="I26" s="193" t="s">
-        <v>2245</v>
+        <v>2244</v>
       </c>
       <c r="J26" s="193" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
       <c r="K26" s="193" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
       <c r="L26" s="193">
         <v>3</v>
@@ -35297,10 +35305,10 @@
         <v>292</v>
       </c>
       <c r="N26" s="193" t="s">
-        <v>2252</v>
+        <v>2251</v>
       </c>
       <c r="O26" s="195" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="P26" s="235">
         <v>0</v>
@@ -35332,13 +35340,13 @@
         <v>2215</v>
       </c>
       <c r="I27" s="198" t="s">
-        <v>2245</v>
+        <v>2244</v>
       </c>
       <c r="J27" s="201" t="s">
+        <v>2249</v>
+      </c>
+      <c r="K27" s="198" t="s">
         <v>2250</v>
-      </c>
-      <c r="K27" s="198" t="s">
-        <v>2251</v>
       </c>
       <c r="L27" s="198">
         <v>3</v>
@@ -35347,10 +35355,10 @@
         <v>292</v>
       </c>
       <c r="N27" s="202" t="s">
-        <v>2253</v>
+        <v>2252</v>
       </c>
       <c r="O27" s="203" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="P27" s="236">
         <v>0</v>
@@ -35397,10 +35405,10 @@
         <v>292</v>
       </c>
       <c r="N28" s="193" t="s">
-        <v>2254</v>
+        <v>2253</v>
       </c>
       <c r="O28" s="195" t="s">
-        <v>2268</v>
+        <v>2267</v>
       </c>
       <c r="P28" s="235">
         <v>0</v>
@@ -35447,10 +35455,10 @@
         <v>292</v>
       </c>
       <c r="N29" s="202" t="s">
-        <v>2252</v>
+        <v>2251</v>
       </c>
       <c r="O29" s="203" t="s">
-        <v>2268</v>
+        <v>2267</v>
       </c>
       <c r="P29" s="236">
         <v>0</v>
@@ -35497,10 +35505,10 @@
         <v>292</v>
       </c>
       <c r="N30" s="193" t="s">
-        <v>2256</v>
+        <v>2255</v>
       </c>
       <c r="O30" s="195" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="P30" s="235">
         <v>0</v>
@@ -35547,10 +35555,10 @@
         <v>292</v>
       </c>
       <c r="N31" s="202" t="s">
-        <v>2255</v>
+        <v>2254</v>
       </c>
       <c r="O31" s="203" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="P31" s="236">
         <v>0</v>
@@ -35579,7 +35587,7 @@
         <v>1</v>
       </c>
       <c r="H32" s="193" t="s">
-        <v>2244</v>
+        <v>2243</v>
       </c>
       <c r="I32" s="193" t="s">
         <v>2121</v>
@@ -35597,10 +35605,10 @@
         <v>2221</v>
       </c>
       <c r="N32" s="193" t="s">
-        <v>2257</v>
+        <v>2256</v>
       </c>
       <c r="O32" s="195" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="P32" s="235">
         <v>0</v>
@@ -35629,10 +35637,10 @@
         <v>2</v>
       </c>
       <c r="H33" s="198" t="s">
-        <v>2244</v>
+        <v>2243</v>
       </c>
       <c r="I33" s="198" t="s">
-        <v>2246</v>
+        <v>2245</v>
       </c>
       <c r="J33" s="198">
         <v>1</v>
@@ -35647,10 +35655,10 @@
         <v>292</v>
       </c>
       <c r="N33" s="202" t="s">
-        <v>2258</v>
+        <v>2257</v>
       </c>
       <c r="O33" s="203" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="P33" s="236">
         <v>0</v>
@@ -35682,7 +35690,7 @@
         <v>2241</v>
       </c>
       <c r="I34" s="193" t="s">
-        <v>2247</v>
+        <v>2246</v>
       </c>
       <c r="J34" s="193">
         <v>2</v>
@@ -35697,10 +35705,10 @@
         <v>292</v>
       </c>
       <c r="N34" s="193" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
       <c r="O34" s="195" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="P34" s="235">
         <v>0</v>
@@ -35732,7 +35740,7 @@
         <v>2241</v>
       </c>
       <c r="I35" s="198" t="s">
-        <v>2247</v>
+        <v>2246</v>
       </c>
       <c r="J35" s="199">
         <v>2</v>
@@ -35747,7 +35755,7 @@
         <v>292</v>
       </c>
       <c r="N35" s="202" t="s">
-        <v>2260</v>
+        <v>2259</v>
       </c>
       <c r="O35" s="203" t="s">
         <v>2195</v>
@@ -35779,10 +35787,10 @@
         <v>1</v>
       </c>
       <c r="H36" s="193" t="s">
-        <v>2244</v>
+        <v>2243</v>
       </c>
       <c r="I36" s="193" t="s">
-        <v>2248</v>
+        <v>2247</v>
       </c>
       <c r="J36" s="193">
         <v>3</v>
@@ -35797,10 +35805,10 @@
         <v>292</v>
       </c>
       <c r="N36" s="193" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
       <c r="O36" s="195" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
       <c r="P36" s="235">
         <v>0</v>
@@ -35829,10 +35837,10 @@
         <v>2</v>
       </c>
       <c r="H37" s="198" t="s">
-        <v>2244</v>
+        <v>2243</v>
       </c>
       <c r="I37" s="198" t="s">
-        <v>2248</v>
+        <v>2247</v>
       </c>
       <c r="J37" s="199">
         <v>3</v>
@@ -35847,10 +35855,10 @@
         <v>292</v>
       </c>
       <c r="N37" s="202" t="s">
-        <v>2258</v>
+        <v>2257</v>
       </c>
       <c r="O37" s="203" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
       <c r="P37" s="236">
         <v>0</v>
@@ -35897,10 +35905,10 @@
         <v>292</v>
       </c>
       <c r="N38" s="193" t="s">
-        <v>2252</v>
+        <v>2251</v>
       </c>
       <c r="O38" s="195" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="P38" s="235">
         <v>0</v>
@@ -35947,10 +35955,10 @@
         <v>292</v>
       </c>
       <c r="N39" s="202" t="s">
-        <v>2253</v>
+        <v>2252</v>
       </c>
       <c r="O39" s="205" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="P39" s="236">
         <v>0</v>
@@ -36070,7 +36078,7 @@
         <v>283</v>
       </c>
       <c r="E42" s="218" t="s">
-        <v>2303</v>
+        <v>2302</v>
       </c>
       <c r="F42" s="193" t="s">
         <v>2240</v>
@@ -36161,19 +36169,19 @@
         <v>325</v>
       </c>
       <c r="B44" s="185" t="s">
-        <v>2269</v>
+        <v>2268</v>
       </c>
       <c r="C44" s="185" t="s">
+        <v>2300</v>
+      </c>
+      <c r="D44" s="216" t="s">
         <v>2301</v>
-      </c>
-      <c r="D44" s="216" t="s">
-        <v>2302</v>
       </c>
       <c r="E44" s="185" t="s">
         <v>276</v>
       </c>
       <c r="F44" s="185" t="s">
-        <v>2306</v>
+        <v>2305</v>
       </c>
       <c r="G44" s="185">
         <v>1</v>
@@ -36197,10 +36205,10 @@
         <v>292</v>
       </c>
       <c r="N44" s="185" t="s">
-        <v>2257</v>
+        <v>2256</v>
       </c>
       <c r="O44" s="194" t="s">
-        <v>2361</v>
+        <v>2360</v>
       </c>
       <c r="P44" s="235">
         <v>38</v>
@@ -36211,7 +36219,7 @@
         <v>329</v>
       </c>
       <c r="B45" s="200" t="s">
-        <v>2270</v>
+        <v>2269</v>
       </c>
       <c r="C45" s="198" t="s">
         <v>326</v>
@@ -36232,7 +36240,7 @@
         <v>291</v>
       </c>
       <c r="I45" s="200" t="s">
-        <v>2307</v>
+        <v>2306</v>
       </c>
       <c r="J45" s="212">
         <v>1</v>
@@ -36247,10 +36255,10 @@
         <v>292</v>
       </c>
       <c r="N45" s="202" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="O45" s="203" t="s">
-        <v>2361</v>
+        <v>2360</v>
       </c>
       <c r="P45" s="236">
         <v>38</v>
@@ -36261,7 +36269,7 @@
         <v>330</v>
       </c>
       <c r="B46" s="193" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
       <c r="C46" s="193" t="s">
         <v>326</v>
@@ -36297,10 +36305,10 @@
         <v>292</v>
       </c>
       <c r="N46" s="204" t="s">
-        <v>2347</v>
+        <v>2346</v>
       </c>
       <c r="O46" s="195" t="s">
-        <v>2363</v>
+        <v>2362</v>
       </c>
       <c r="P46" s="235">
         <v>34</v>
@@ -36311,7 +36319,7 @@
         <v>331</v>
       </c>
       <c r="B47" s="200" t="s">
-        <v>2272</v>
+        <v>2271</v>
       </c>
       <c r="C47" s="198" t="s">
         <v>326</v>
@@ -36332,7 +36340,7 @@
         <v>291</v>
       </c>
       <c r="I47" s="200" t="s">
-        <v>2308</v>
+        <v>2307</v>
       </c>
       <c r="J47" s="212">
         <v>4</v>
@@ -36347,10 +36355,10 @@
         <v>292</v>
       </c>
       <c r="N47" s="202" t="s">
-        <v>2391</v>
+        <v>2390</v>
       </c>
       <c r="O47" s="205" t="s">
-        <v>2363</v>
+        <v>2362</v>
       </c>
       <c r="P47" s="236">
         <v>34</v>
@@ -36361,7 +36369,7 @@
         <v>332</v>
       </c>
       <c r="B48" s="193" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="C48" s="193" t="s">
         <v>326</v>
@@ -36382,7 +36390,7 @@
         <v>291</v>
       </c>
       <c r="I48" s="193" t="s">
-        <v>2333</v>
+        <v>2332</v>
       </c>
       <c r="J48" s="204">
         <v>2</v>
@@ -36397,10 +36405,10 @@
         <v>292</v>
       </c>
       <c r="N48" s="204" t="s">
-        <v>2348</v>
+        <v>2347</v>
       </c>
       <c r="O48" s="195" t="s">
-        <v>2365</v>
+        <v>2364</v>
       </c>
       <c r="P48" s="235">
         <v>40</v>
@@ -36411,7 +36419,7 @@
         <v>334</v>
       </c>
       <c r="B49" s="200" t="s">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="C49" s="198" t="s">
         <v>326</v>
@@ -36432,7 +36440,7 @@
         <v>291</v>
       </c>
       <c r="I49" s="200" t="s">
-        <v>2333</v>
+        <v>2332</v>
       </c>
       <c r="J49" s="212">
         <v>2</v>
@@ -36447,10 +36455,10 @@
         <v>292</v>
       </c>
       <c r="N49" s="202" t="s">
-        <v>2392</v>
+        <v>2391</v>
       </c>
       <c r="O49" s="203" t="s">
-        <v>2365</v>
+        <v>2364</v>
       </c>
       <c r="P49" s="236">
         <v>40</v>
@@ -36461,7 +36469,7 @@
         <v>335</v>
       </c>
       <c r="B50" s="193" t="s">
-        <v>2275</v>
+        <v>2274</v>
       </c>
       <c r="C50" s="193" t="s">
         <v>326</v>
@@ -36482,7 +36490,7 @@
         <v>291</v>
       </c>
       <c r="I50" s="193" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
       <c r="J50" s="204">
         <v>2</v>
@@ -36497,10 +36505,10 @@
         <v>292</v>
       </c>
       <c r="N50" s="204" t="s">
-        <v>2349</v>
+        <v>2348</v>
       </c>
       <c r="O50" s="195" t="s">
-        <v>2366</v>
+        <v>2365</v>
       </c>
       <c r="P50" s="235">
         <v>36</v>
@@ -36511,13 +36519,13 @@
         <v>336</v>
       </c>
       <c r="B51" s="200" t="s">
-        <v>2276</v>
+        <v>2275</v>
       </c>
       <c r="C51" s="198" t="s">
         <v>326</v>
       </c>
       <c r="D51" s="226" t="s">
-        <v>2302</v>
+        <v>2301</v>
       </c>
       <c r="E51" s="200" t="s">
         <v>276</v>
@@ -36532,7 +36540,7 @@
         <v>291</v>
       </c>
       <c r="I51" s="200" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
       <c r="J51" s="212">
         <v>2</v>
@@ -36547,10 +36555,10 @@
         <v>292</v>
       </c>
       <c r="N51" s="202" t="s">
-        <v>2393</v>
+        <v>2392</v>
       </c>
       <c r="O51" s="203" t="s">
-        <v>2366</v>
+        <v>2365</v>
       </c>
       <c r="P51" s="236">
         <v>36</v>
@@ -36561,7 +36569,7 @@
         <v>337</v>
       </c>
       <c r="B52" s="193" t="s">
-        <v>2277</v>
+        <v>2276</v>
       </c>
       <c r="C52" s="193" t="s">
         <v>326</v>
@@ -36582,7 +36590,7 @@
         <v>291</v>
       </c>
       <c r="I52" s="193" t="s">
-        <v>2367</v>
+        <v>2366</v>
       </c>
       <c r="J52" s="204">
         <v>1</v>
@@ -36600,7 +36608,7 @@
         <v>286</v>
       </c>
       <c r="O52" s="195" t="s">
-        <v>2368</v>
+        <v>2367</v>
       </c>
       <c r="P52" s="235">
         <v>48</v>
@@ -36611,7 +36619,7 @@
         <v>338</v>
       </c>
       <c r="B53" s="200" t="s">
-        <v>2278</v>
+        <v>2277</v>
       </c>
       <c r="C53" s="198" t="s">
         <v>326</v>
@@ -36632,7 +36640,7 @@
         <v>291</v>
       </c>
       <c r="I53" s="200" t="s">
-        <v>2310</v>
+        <v>2309</v>
       </c>
       <c r="J53" s="212">
         <v>1</v>
@@ -36650,7 +36658,7 @@
         <v>286</v>
       </c>
       <c r="O53" s="203" t="s">
-        <v>2368</v>
+        <v>2367</v>
       </c>
       <c r="P53" s="236">
         <v>48</v>
@@ -36661,7 +36669,7 @@
         <v>339</v>
       </c>
       <c r="B54" s="193" t="s">
-        <v>2279</v>
+        <v>2278</v>
       </c>
       <c r="C54" s="193" t="s">
         <v>326</v>
@@ -36682,7 +36690,7 @@
         <v>291</v>
       </c>
       <c r="I54" s="193" t="s">
-        <v>2334</v>
+        <v>2333</v>
       </c>
       <c r="J54" s="204">
         <v>1</v>
@@ -36700,7 +36708,7 @@
         <v>286</v>
       </c>
       <c r="O54" s="195" t="s">
-        <v>2369</v>
+        <v>2368</v>
       </c>
       <c r="P54" s="235">
         <v>52</v>
@@ -36711,7 +36719,7 @@
         <v>340</v>
       </c>
       <c r="B55" s="200" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="C55" s="198" t="s">
         <v>326</v>
@@ -36732,7 +36740,7 @@
         <v>291</v>
       </c>
       <c r="I55" s="200" t="s">
-        <v>2334</v>
+        <v>2333</v>
       </c>
       <c r="J55" s="212">
         <v>1</v>
@@ -36750,7 +36758,7 @@
         <v>286</v>
       </c>
       <c r="O55" s="205" t="s">
-        <v>2369</v>
+        <v>2368</v>
       </c>
       <c r="P55" s="236">
         <v>52</v>
@@ -36761,7 +36769,7 @@
         <v>341</v>
       </c>
       <c r="B56" s="193" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
       <c r="C56" s="193" t="s">
         <v>326</v>
@@ -36782,7 +36790,7 @@
         <v>291</v>
       </c>
       <c r="I56" s="193" t="s">
-        <v>2340</v>
+        <v>2339</v>
       </c>
       <c r="J56" s="204">
         <v>1</v>
@@ -36800,7 +36808,7 @@
         <v>286</v>
       </c>
       <c r="O56" s="195" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="P56" s="235">
         <v>54</v>
@@ -36811,7 +36819,7 @@
         <v>342</v>
       </c>
       <c r="B57" s="200" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="C57" s="198" t="s">
         <v>326</v>
@@ -36832,7 +36840,7 @@
         <v>291</v>
       </c>
       <c r="I57" s="200" t="s">
-        <v>2340</v>
+        <v>2339</v>
       </c>
       <c r="J57" s="212">
         <v>1</v>
@@ -36850,7 +36858,7 @@
         <v>286</v>
       </c>
       <c r="O57" s="203" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="P57" s="236">
         <v>54</v>
@@ -36861,13 +36869,13 @@
         <v>343</v>
       </c>
       <c r="B58" s="193" t="s">
-        <v>2283</v>
+        <v>2282</v>
       </c>
       <c r="C58" s="193" t="s">
         <v>326</v>
       </c>
       <c r="D58" s="218" t="s">
-        <v>2421</v>
+        <v>2420</v>
       </c>
       <c r="E58" s="193" t="s">
         <v>276</v>
@@ -36882,7 +36890,7 @@
         <v>291</v>
       </c>
       <c r="I58" s="193" t="s">
-        <v>2311</v>
+        <v>2310</v>
       </c>
       <c r="J58" s="204">
         <v>1</v>
@@ -36900,7 +36908,7 @@
         <v>286</v>
       </c>
       <c r="O58" s="195" t="s">
-        <v>2371</v>
+        <v>2370</v>
       </c>
       <c r="P58" s="235">
         <v>55</v>
@@ -36911,7 +36919,7 @@
         <v>345</v>
       </c>
       <c r="B59" s="200" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="C59" s="198" t="s">
         <v>326</v>
@@ -36932,7 +36940,7 @@
         <v>291</v>
       </c>
       <c r="I59" s="200" t="s">
-        <v>2311</v>
+        <v>2310</v>
       </c>
       <c r="J59" s="212">
         <v>1</v>
@@ -36950,7 +36958,7 @@
         <v>286</v>
       </c>
       <c r="O59" s="203" t="s">
-        <v>2371</v>
+        <v>2370</v>
       </c>
       <c r="P59" s="236">
         <v>55</v>
@@ -36961,7 +36969,7 @@
         <v>346</v>
       </c>
       <c r="B60" s="193" t="s">
-        <v>2285</v>
+        <v>2284</v>
       </c>
       <c r="C60" s="193" t="s">
         <v>326</v>
@@ -36982,13 +36990,13 @@
         <v>291</v>
       </c>
       <c r="I60" s="193" t="s">
-        <v>2312</v>
+        <v>2311</v>
       </c>
       <c r="J60" s="204" t="s">
-        <v>2317</v>
+        <v>2316</v>
       </c>
       <c r="K60" s="204" t="s">
-        <v>2372</v>
+        <v>2371</v>
       </c>
       <c r="L60" s="204">
         <v>5</v>
@@ -37000,7 +37008,7 @@
         <v>286</v>
       </c>
       <c r="O60" s="195" t="s">
-        <v>2380</v>
+        <v>2379</v>
       </c>
       <c r="P60" s="235">
         <v>66</v>
@@ -37011,7 +37019,7 @@
         <v>347</v>
       </c>
       <c r="B61" s="200" t="s">
-        <v>2286</v>
+        <v>2285</v>
       </c>
       <c r="C61" s="198" t="s">
         <v>326</v>
@@ -37032,13 +37040,13 @@
         <v>291</v>
       </c>
       <c r="I61" s="200" t="s">
-        <v>2312</v>
+        <v>2311</v>
       </c>
       <c r="J61" s="202" t="s">
-        <v>2394</v>
+        <v>2393</v>
       </c>
       <c r="K61" s="212" t="s">
-        <v>2372</v>
+        <v>2371</v>
       </c>
       <c r="L61" s="212">
         <v>5</v>
@@ -37050,7 +37058,7 @@
         <v>286</v>
       </c>
       <c r="O61" s="203" t="s">
-        <v>2380</v>
+        <v>2379</v>
       </c>
       <c r="P61" s="236">
         <v>66</v>
@@ -37061,7 +37069,7 @@
         <v>348</v>
       </c>
       <c r="B62" s="193" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="C62" s="193" t="s">
         <v>326</v>
@@ -37082,7 +37090,7 @@
         <v>291</v>
       </c>
       <c r="I62" s="193" t="s">
-        <v>2308</v>
+        <v>2307</v>
       </c>
       <c r="J62" s="204">
         <v>12</v>
@@ -37100,7 +37108,7 @@
         <v>286</v>
       </c>
       <c r="O62" s="195" t="s">
-        <v>2364</v>
+        <v>2363</v>
       </c>
       <c r="P62" s="235">
         <v>68</v>
@@ -37111,7 +37119,7 @@
         <v>349</v>
       </c>
       <c r="B63" s="200" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="C63" s="198" t="s">
         <v>326</v>
@@ -37132,7 +37140,7 @@
         <v>291</v>
       </c>
       <c r="I63" s="200" t="s">
-        <v>2308</v>
+        <v>2307</v>
       </c>
       <c r="J63" s="202">
         <v>15</v>
@@ -37150,7 +37158,7 @@
         <v>286</v>
       </c>
       <c r="O63" s="205" t="s">
-        <v>2364</v>
+        <v>2363</v>
       </c>
       <c r="P63" s="236">
         <v>68</v>
@@ -37161,7 +37169,7 @@
         <v>350</v>
       </c>
       <c r="B64" s="193" t="s">
-        <v>2290</v>
+        <v>2289</v>
       </c>
       <c r="C64" s="193" t="s">
         <v>326</v>
@@ -37182,7 +37190,7 @@
         <v>291</v>
       </c>
       <c r="I64" s="193" t="s">
-        <v>2307</v>
+        <v>2306</v>
       </c>
       <c r="J64" s="204">
         <v>2</v>
@@ -37197,7 +37205,7 @@
         <v>292</v>
       </c>
       <c r="N64" s="204" t="s">
-        <v>2351</v>
+        <v>2350</v>
       </c>
       <c r="O64" s="195" t="s">
         <v>2196</v>
@@ -37211,7 +37219,7 @@
         <v>352</v>
       </c>
       <c r="B65" s="200" t="s">
-        <v>2291</v>
+        <v>2290</v>
       </c>
       <c r="C65" s="198" t="s">
         <v>326</v>
@@ -37232,7 +37240,7 @@
         <v>291</v>
       </c>
       <c r="I65" s="200" t="s">
-        <v>2307</v>
+        <v>2306</v>
       </c>
       <c r="J65" s="202">
         <v>3</v>
@@ -37247,10 +37255,10 @@
         <v>292</v>
       </c>
       <c r="N65" s="212" t="s">
-        <v>2395</v>
+        <v>2394</v>
       </c>
       <c r="O65" s="205" t="s">
-        <v>2361</v>
+        <v>2360</v>
       </c>
       <c r="P65" s="236">
         <v>72</v>
@@ -37261,13 +37269,13 @@
         <v>353</v>
       </c>
       <c r="B66" s="193" t="s">
-        <v>2287</v>
+        <v>2286</v>
       </c>
       <c r="C66" s="193" t="s">
         <v>326</v>
       </c>
       <c r="D66" s="218" t="s">
-        <v>2420</v>
+        <v>2419</v>
       </c>
       <c r="E66" s="193" t="s">
         <v>327</v>
@@ -37282,13 +37290,13 @@
         <v>291</v>
       </c>
       <c r="I66" s="193" t="s">
-        <v>2313</v>
+        <v>2312</v>
       </c>
       <c r="J66" s="204" t="s">
-        <v>2317</v>
+        <v>2316</v>
       </c>
       <c r="K66" s="204" t="s">
-        <v>2372</v>
+        <v>2371</v>
       </c>
       <c r="L66" s="204">
         <v>4</v>
@@ -37297,10 +37305,10 @@
         <v>292</v>
       </c>
       <c r="N66" s="204" t="s">
-        <v>2352</v>
+        <v>2351</v>
       </c>
       <c r="O66" s="195" t="s">
-        <v>2373</v>
+        <v>2372</v>
       </c>
       <c r="P66" s="235">
         <v>70</v>
@@ -37311,7 +37319,7 @@
         <v>354</v>
       </c>
       <c r="B67" s="200" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="C67" s="198" t="s">
         <v>326</v>
@@ -37332,13 +37340,13 @@
         <v>291</v>
       </c>
       <c r="I67" s="200" t="s">
-        <v>2313</v>
+        <v>2312</v>
       </c>
       <c r="J67" s="202" t="s">
-        <v>2394</v>
+        <v>2393</v>
       </c>
       <c r="K67" s="212" t="s">
-        <v>2372</v>
+        <v>2371</v>
       </c>
       <c r="L67" s="212">
         <v>4</v>
@@ -37347,10 +37355,10 @@
         <v>292</v>
       </c>
       <c r="N67" s="212" t="s">
-        <v>2392</v>
+        <v>2391</v>
       </c>
       <c r="O67" s="205" t="s">
-        <v>2373</v>
+        <v>2372</v>
       </c>
       <c r="P67" s="236">
         <v>70</v>
@@ -37361,7 +37369,7 @@
         <v>355</v>
       </c>
       <c r="B68" s="193" t="s">
-        <v>2292</v>
+        <v>2291</v>
       </c>
       <c r="C68" s="193" t="s">
         <v>326</v>
@@ -37382,13 +37390,13 @@
         <v>291</v>
       </c>
       <c r="I68" s="193" t="s">
-        <v>2314</v>
+        <v>2313</v>
       </c>
       <c r="J68" s="204" t="s">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="K68" s="204" t="s">
-        <v>2372</v>
+        <v>2371</v>
       </c>
       <c r="L68" s="204">
         <v>6</v>
@@ -37397,10 +37405,10 @@
         <v>292</v>
       </c>
       <c r="N68" s="204" t="s">
-        <v>2346</v>
+        <v>2345</v>
       </c>
       <c r="O68" s="230" t="s">
-        <v>2375</v>
+        <v>2374</v>
       </c>
       <c r="P68" s="235">
         <v>88</v>
@@ -37411,7 +37419,7 @@
         <v>356</v>
       </c>
       <c r="B69" s="200" t="s">
-        <v>2293</v>
+        <v>2292</v>
       </c>
       <c r="C69" s="198" t="s">
         <v>326</v>
@@ -37432,13 +37440,13 @@
         <v>291</v>
       </c>
       <c r="I69" s="200" t="s">
-        <v>2314</v>
+        <v>2313</v>
       </c>
       <c r="J69" s="212" t="s">
-        <v>2396</v>
+        <v>2395</v>
       </c>
       <c r="K69" s="212" t="s">
-        <v>2372</v>
+        <v>2371</v>
       </c>
       <c r="L69" s="202">
         <v>5</v>
@@ -37447,10 +37455,10 @@
         <v>292</v>
       </c>
       <c r="N69" s="202" t="s">
-        <v>2391</v>
+        <v>2390</v>
       </c>
       <c r="O69" s="205" t="s">
-        <v>2374</v>
+        <v>2373</v>
       </c>
       <c r="P69" s="236">
         <v>88</v>
@@ -37461,7 +37469,7 @@
         <v>357</v>
       </c>
       <c r="B70" s="193" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
       <c r="C70" s="193" t="s">
         <v>326</v>
@@ -37482,7 +37490,7 @@
         <v>291</v>
       </c>
       <c r="I70" s="193" t="s">
-        <v>2315</v>
+        <v>2314</v>
       </c>
       <c r="J70" s="204">
         <v>3</v>
@@ -37497,10 +37505,10 @@
         <v>292</v>
       </c>
       <c r="N70" s="204" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
       <c r="O70" s="195" t="s">
-        <v>2376</v>
+        <v>2375</v>
       </c>
       <c r="P70" s="235">
         <v>84</v>
@@ -37511,7 +37519,7 @@
         <v>358</v>
       </c>
       <c r="B71" s="200" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="C71" s="198" t="s">
         <v>326</v>
@@ -37532,7 +37540,7 @@
         <v>291</v>
       </c>
       <c r="I71" s="200" t="s">
-        <v>2315</v>
+        <v>2314</v>
       </c>
       <c r="J71" s="212">
         <v>3</v>
@@ -37547,10 +37555,10 @@
         <v>2193</v>
       </c>
       <c r="N71" s="202" t="s">
-        <v>2391</v>
+        <v>2390</v>
       </c>
       <c r="O71" s="203" t="s">
-        <v>2362</v>
+        <v>2361</v>
       </c>
       <c r="P71" s="236">
         <v>84</v>
@@ -37561,7 +37569,7 @@
         <v>359</v>
       </c>
       <c r="B72" s="193" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="C72" s="193" t="s">
         <v>326</v>
@@ -37597,10 +37605,10 @@
         <v>292</v>
       </c>
       <c r="N72" s="204" t="s">
-        <v>2353</v>
+        <v>2352</v>
       </c>
       <c r="O72" s="195" t="s">
-        <v>2377</v>
+        <v>2376</v>
       </c>
       <c r="P72" s="235">
         <v>92</v>
@@ -37611,7 +37619,7 @@
         <v>360</v>
       </c>
       <c r="B73" s="200" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="C73" s="198" t="s">
         <v>326</v>
@@ -37620,7 +37628,7 @@
         <v>289</v>
       </c>
       <c r="E73" s="200" t="s">
-        <v>2303</v>
+        <v>2302</v>
       </c>
       <c r="F73" s="200" t="s">
         <v>290</v>
@@ -37632,7 +37640,7 @@
         <v>291</v>
       </c>
       <c r="I73" s="200" t="s">
-        <v>2316</v>
+        <v>2315</v>
       </c>
       <c r="J73" s="212">
         <v>1</v>
@@ -37647,10 +37655,10 @@
         <v>292</v>
       </c>
       <c r="N73" s="212" t="s">
-        <v>2353</v>
+        <v>2352</v>
       </c>
       <c r="O73" s="205" t="s">
-        <v>2377</v>
+        <v>2376</v>
       </c>
       <c r="P73" s="236">
         <v>92</v>
@@ -37661,16 +37669,16 @@
         <v>361</v>
       </c>
       <c r="B74" s="193" t="s">
-        <v>2297</v>
+        <v>2296</v>
       </c>
       <c r="C74" s="193" t="s">
         <v>326</v>
       </c>
       <c r="D74" s="218" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
       <c r="E74" s="193" t="s">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="F74" s="193" t="s">
         <v>290</v>
@@ -37682,7 +37690,7 @@
         <v>291</v>
       </c>
       <c r="I74" s="193" t="s">
-        <v>2330</v>
+        <v>2329</v>
       </c>
       <c r="J74" s="204">
         <v>1</v>
@@ -37697,10 +37705,10 @@
         <v>292</v>
       </c>
       <c r="N74" s="204" t="s">
-        <v>2353</v>
+        <v>2352</v>
       </c>
       <c r="O74" s="195" t="s">
-        <v>2379</v>
+        <v>2378</v>
       </c>
       <c r="P74" s="235">
         <v>96</v>
@@ -37711,7 +37719,7 @@
         <v>363</v>
       </c>
       <c r="B75" s="189" t="s">
-        <v>2298</v>
+        <v>2297</v>
       </c>
       <c r="C75" s="188" t="s">
         <v>326</v>
@@ -37720,7 +37728,7 @@
         <v>289</v>
       </c>
       <c r="E75" s="189" t="s">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="F75" s="189" t="s">
         <v>290</v>
@@ -37732,7 +37740,7 @@
         <v>291</v>
       </c>
       <c r="I75" s="189" t="s">
-        <v>2330</v>
+        <v>2329</v>
       </c>
       <c r="J75" s="213">
         <v>1</v>
@@ -37747,10 +37755,10 @@
         <v>292</v>
       </c>
       <c r="N75" s="213" t="s">
-        <v>2353</v>
+        <v>2352</v>
       </c>
       <c r="O75" s="206" t="s">
-        <v>2379</v>
+        <v>2378</v>
       </c>
       <c r="P75" s="236">
         <v>96</v>
@@ -37761,7 +37769,7 @@
         <v>364</v>
       </c>
       <c r="B76" s="185" t="s">
-        <v>2422</v>
+        <v>2421</v>
       </c>
       <c r="C76" s="185" t="s">
         <v>326</v>
@@ -37770,7 +37778,7 @@
         <v>160</v>
       </c>
       <c r="E76" s="185" t="s">
-        <v>2303</v>
+        <v>2302</v>
       </c>
       <c r="F76" s="185" t="s">
         <v>293</v>
@@ -37779,10 +37787,10 @@
         <v>1</v>
       </c>
       <c r="H76" s="185" t="s">
-        <v>2358</v>
+        <v>2357</v>
       </c>
       <c r="I76" s="185" t="s">
-        <v>2397</v>
+        <v>2396</v>
       </c>
       <c r="J76" s="185">
         <v>2</v>
@@ -37797,10 +37805,10 @@
         <v>2193</v>
       </c>
       <c r="N76" s="229" t="s">
-        <v>2256</v>
+        <v>2255</v>
       </c>
       <c r="O76" s="194" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="P76" s="235">
         <v>40</v>
@@ -37811,7 +37819,7 @@
         <v>366</v>
       </c>
       <c r="B77" s="200" t="s">
-        <v>2423</v>
+        <v>2422</v>
       </c>
       <c r="C77" s="198" t="s">
         <v>326</v>
@@ -37832,7 +37840,7 @@
         <v>313</v>
       </c>
       <c r="I77" s="200" t="s">
-        <v>2397</v>
+        <v>2396</v>
       </c>
       <c r="J77" s="200">
         <v>2</v>
@@ -37847,10 +37855,10 @@
         <v>292</v>
       </c>
       <c r="N77" s="202" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="O77" s="203" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="P77" s="236">
         <v>40</v>
@@ -37861,7 +37869,7 @@
         <v>367</v>
       </c>
       <c r="B78" s="193" t="s">
-        <v>2424</v>
+        <v>2423</v>
       </c>
       <c r="C78" s="193" t="s">
         <v>326</v>
@@ -37882,7 +37890,7 @@
         <v>313</v>
       </c>
       <c r="I78" s="193" t="s">
-        <v>2398</v>
+        <v>2397</v>
       </c>
       <c r="J78" s="193">
         <v>2</v>
@@ -37897,10 +37905,10 @@
         <v>292</v>
       </c>
       <c r="N78" s="193" t="s">
-        <v>2254</v>
+        <v>2253</v>
       </c>
       <c r="O78" s="195" t="s">
-        <v>2447</v>
+        <v>2446</v>
       </c>
       <c r="P78" s="235">
         <v>38</v>
@@ -37911,7 +37919,7 @@
         <v>369</v>
       </c>
       <c r="B79" s="200" t="s">
-        <v>2425</v>
+        <v>2424</v>
       </c>
       <c r="C79" s="198" t="s">
         <v>326</v>
@@ -37932,7 +37940,7 @@
         <v>313</v>
       </c>
       <c r="I79" s="200" t="s">
-        <v>2398</v>
+        <v>2397</v>
       </c>
       <c r="J79" s="200">
         <v>2</v>
@@ -37947,10 +37955,10 @@
         <v>292</v>
       </c>
       <c r="N79" s="202" t="s">
-        <v>2252</v>
+        <v>2251</v>
       </c>
       <c r="O79" s="203" t="s">
-        <v>2447</v>
+        <v>2446</v>
       </c>
       <c r="P79" s="236">
         <v>38</v>
@@ -37961,7 +37969,7 @@
         <v>370</v>
       </c>
       <c r="B80" s="193" t="s">
-        <v>2426</v>
+        <v>2425</v>
       </c>
       <c r="C80" s="193" t="s">
         <v>326</v>
@@ -37997,7 +38005,7 @@
         <v>292</v>
       </c>
       <c r="N80" s="193" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
       <c r="O80" s="195" t="s">
         <v>2195</v>
@@ -38011,7 +38019,7 @@
         <v>371</v>
       </c>
       <c r="B81" s="200" t="s">
-        <v>2427</v>
+        <v>2426</v>
       </c>
       <c r="C81" s="198" t="s">
         <v>326</v>
@@ -38061,7 +38069,7 @@
         <v>372</v>
       </c>
       <c r="B82" s="193" t="s">
-        <v>2428</v>
+        <v>2427</v>
       </c>
       <c r="C82" s="193" t="s">
         <v>326</v>
@@ -38082,7 +38090,7 @@
         <v>313</v>
       </c>
       <c r="I82" s="193" t="s">
-        <v>2399</v>
+        <v>2398</v>
       </c>
       <c r="J82" s="204">
         <v>3</v>
@@ -38097,10 +38105,10 @@
         <v>292</v>
       </c>
       <c r="N82" s="193" t="s">
-        <v>2256</v>
+        <v>2255</v>
       </c>
       <c r="O82" s="195" t="s">
-        <v>2448</v>
+        <v>2447</v>
       </c>
       <c r="P82" s="235">
         <v>48</v>
@@ -38111,7 +38119,7 @@
         <v>374</v>
       </c>
       <c r="B83" s="200" t="s">
-        <v>2429</v>
+        <v>2428</v>
       </c>
       <c r="C83" s="198" t="s">
         <v>326</v>
@@ -38132,7 +38140,7 @@
         <v>313</v>
       </c>
       <c r="I83" s="200" t="s">
-        <v>2399</v>
+        <v>2398</v>
       </c>
       <c r="J83" s="212">
         <v>3</v>
@@ -38147,10 +38155,10 @@
         <v>292</v>
       </c>
       <c r="N83" s="202" t="s">
-        <v>2443</v>
+        <v>2442</v>
       </c>
       <c r="O83" s="203" t="s">
-        <v>2448</v>
+        <v>2447</v>
       </c>
       <c r="P83" s="236">
         <v>48</v>
@@ -38161,7 +38169,7 @@
         <v>375</v>
       </c>
       <c r="B84" s="193" t="s">
-        <v>2430</v>
+        <v>2429</v>
       </c>
       <c r="C84" s="193" t="s">
         <v>326</v>
@@ -38182,7 +38190,7 @@
         <v>313</v>
       </c>
       <c r="I84" s="218" t="s">
-        <v>2402</v>
+        <v>2401</v>
       </c>
       <c r="J84" s="204">
         <v>2</v>
@@ -38197,10 +38205,10 @@
         <v>292</v>
       </c>
       <c r="N84" s="193" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
       <c r="O84" s="195" t="s">
-        <v>2449</v>
+        <v>2448</v>
       </c>
       <c r="P84" s="235">
         <v>46</v>
@@ -38211,7 +38219,7 @@
         <v>376</v>
       </c>
       <c r="B85" s="200" t="s">
-        <v>2431</v>
+        <v>2430</v>
       </c>
       <c r="C85" s="198" t="s">
         <v>326</v>
@@ -38232,7 +38240,7 @@
         <v>313</v>
       </c>
       <c r="I85" s="232" t="s">
-        <v>2402</v>
+        <v>2401</v>
       </c>
       <c r="J85" s="202">
         <v>3</v>
@@ -38250,7 +38258,7 @@
         <v>2207</v>
       </c>
       <c r="O85" s="203" t="s">
-        <v>2449</v>
+        <v>2448</v>
       </c>
       <c r="P85" s="236">
         <v>46</v>
@@ -38261,7 +38269,7 @@
         <v>377</v>
       </c>
       <c r="B86" s="193" t="s">
-        <v>2432</v>
+        <v>2431</v>
       </c>
       <c r="C86" s="193" t="s">
         <v>326</v>
@@ -38282,7 +38290,7 @@
         <v>313</v>
       </c>
       <c r="I86" s="193" t="s">
-        <v>2405</v>
+        <v>2404</v>
       </c>
       <c r="J86" s="204">
         <v>3</v>
@@ -38297,10 +38305,10 @@
         <v>292</v>
       </c>
       <c r="N86" s="193" t="s">
-        <v>2443</v>
+        <v>2442</v>
       </c>
       <c r="O86" s="195" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
       <c r="P86" s="235">
         <v>68</v>
@@ -38311,7 +38319,7 @@
         <v>378</v>
       </c>
       <c r="B87" s="200" t="s">
-        <v>2433</v>
+        <v>2432</v>
       </c>
       <c r="C87" s="198" t="s">
         <v>326</v>
@@ -38332,7 +38340,7 @@
         <v>313</v>
       </c>
       <c r="I87" s="200" t="s">
-        <v>2405</v>
+        <v>2404</v>
       </c>
       <c r="J87" s="202">
         <v>4</v>
@@ -38350,7 +38358,7 @@
         <v>2202</v>
       </c>
       <c r="O87" s="203" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
       <c r="P87" s="236">
         <v>68</v>
@@ -38361,7 +38369,7 @@
         <v>379</v>
       </c>
       <c r="B88" s="193" t="s">
-        <v>2434</v>
+        <v>2433</v>
       </c>
       <c r="C88" s="193" t="s">
         <v>326</v>
@@ -38382,7 +38390,7 @@
         <v>313</v>
       </c>
       <c r="I88" s="193" t="s">
-        <v>2400</v>
+        <v>2399</v>
       </c>
       <c r="J88" s="204" t="s">
         <v>2162</v>
@@ -38397,10 +38405,10 @@
         <v>292</v>
       </c>
       <c r="N88" s="193" t="s">
-        <v>2343</v>
+        <v>2342</v>
       </c>
       <c r="O88" s="195" t="s">
-        <v>2450</v>
+        <v>2449</v>
       </c>
       <c r="P88" s="235">
         <v>74</v>
@@ -38411,7 +38419,7 @@
         <v>380</v>
       </c>
       <c r="B89" s="200" t="s">
-        <v>2435</v>
+        <v>2434</v>
       </c>
       <c r="C89" s="198" t="s">
         <v>326</v>
@@ -38432,10 +38440,10 @@
         <v>313</v>
       </c>
       <c r="I89" s="200" t="s">
-        <v>2400</v>
+        <v>2399</v>
       </c>
       <c r="J89" s="202" t="s">
-        <v>2317</v>
+        <v>2316</v>
       </c>
       <c r="K89" s="212" t="s">
         <v>2150</v>
@@ -38450,7 +38458,7 @@
         <v>2164</v>
       </c>
       <c r="O89" s="203" t="s">
-        <v>2450</v>
+        <v>2449</v>
       </c>
       <c r="P89" s="236">
         <v>74</v>
@@ -38461,7 +38469,7 @@
         <v>381</v>
       </c>
       <c r="B90" s="193" t="s">
-        <v>2436</v>
+        <v>2435</v>
       </c>
       <c r="C90" s="193" t="s">
         <v>326</v>
@@ -38470,7 +38478,7 @@
         <v>344</v>
       </c>
       <c r="E90" s="193" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
       <c r="F90" s="193" t="s">
         <v>293</v>
@@ -38482,7 +38490,7 @@
         <v>313</v>
       </c>
       <c r="I90" s="193" t="s">
-        <v>2407</v>
+        <v>2406</v>
       </c>
       <c r="J90" s="204">
         <v>1</v>
@@ -38494,13 +38502,13 @@
         <v>8</v>
       </c>
       <c r="M90" s="193" t="s">
-        <v>2455</v>
+        <v>2454</v>
       </c>
       <c r="N90" s="193" t="s">
-        <v>2254</v>
+        <v>2253</v>
       </c>
       <c r="O90" s="195" t="s">
-        <v>2453</v>
+        <v>2452</v>
       </c>
       <c r="P90" s="235">
         <v>76</v>
@@ -38511,7 +38519,7 @@
         <v>382</v>
       </c>
       <c r="B91" s="200" t="s">
-        <v>2437</v>
+        <v>2436</v>
       </c>
       <c r="C91" s="198" t="s">
         <v>326</v>
@@ -38532,7 +38540,7 @@
         <v>313</v>
       </c>
       <c r="I91" s="200" t="s">
-        <v>2407</v>
+        <v>2406</v>
       </c>
       <c r="J91" s="202">
         <v>2</v>
@@ -38547,10 +38555,10 @@
         <v>292</v>
       </c>
       <c r="N91" s="202" t="s">
-        <v>2252</v>
+        <v>2251</v>
       </c>
       <c r="O91" s="203" t="s">
-        <v>2453</v>
+        <v>2452</v>
       </c>
       <c r="P91" s="236">
         <v>76</v>
@@ -38561,7 +38569,7 @@
         <v>383</v>
       </c>
       <c r="B92" s="193" t="s">
-        <v>2438</v>
+        <v>2437</v>
       </c>
       <c r="C92" s="193" t="s">
         <v>326</v>
@@ -38582,7 +38590,7 @@
         <v>313</v>
       </c>
       <c r="I92" s="193" t="s">
-        <v>2409</v>
+        <v>2408</v>
       </c>
       <c r="J92" s="204">
         <v>2</v>
@@ -38597,10 +38605,10 @@
         <v>292</v>
       </c>
       <c r="N92" s="193" t="s">
-        <v>2252</v>
+        <v>2251</v>
       </c>
       <c r="O92" s="195" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="P92" s="235">
         <v>94</v>
@@ -38611,7 +38619,7 @@
         <v>384</v>
       </c>
       <c r="B93" s="200" t="s">
-        <v>2439</v>
+        <v>2438</v>
       </c>
       <c r="C93" s="198" t="s">
         <v>326</v>
@@ -38632,7 +38640,7 @@
         <v>313</v>
       </c>
       <c r="I93" s="200" t="s">
-        <v>2409</v>
+        <v>2408</v>
       </c>
       <c r="J93" s="212">
         <v>2</v>
@@ -38650,7 +38658,7 @@
         <v>2202</v>
       </c>
       <c r="O93" s="203" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="P93" s="236">
         <v>94</v>
@@ -38661,7 +38669,7 @@
         <v>385</v>
       </c>
       <c r="B94" s="193" t="s">
-        <v>2440</v>
+        <v>2439</v>
       </c>
       <c r="C94" s="193" t="s">
         <v>326</v>
@@ -38670,7 +38678,7 @@
         <v>289</v>
       </c>
       <c r="E94" s="193" t="s">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="F94" s="193" t="s">
         <v>293</v>
@@ -38682,7 +38690,7 @@
         <v>313</v>
       </c>
       <c r="I94" s="193" t="s">
-        <v>2411</v>
+        <v>2410</v>
       </c>
       <c r="J94" s="204">
         <v>1</v>
@@ -38697,10 +38705,10 @@
         <v>292</v>
       </c>
       <c r="N94" s="193" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
       <c r="O94" s="195" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
       <c r="P94" s="235">
         <v>88</v>
@@ -38711,16 +38719,16 @@
         <v>386</v>
       </c>
       <c r="B95" s="189" t="s">
-        <v>2441</v>
+        <v>2440</v>
       </c>
       <c r="C95" s="188" t="s">
         <v>326</v>
       </c>
       <c r="D95" s="228" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
       <c r="E95" s="189" t="s">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="F95" s="189" t="s">
         <v>293</v>
@@ -38732,7 +38740,7 @@
         <v>313</v>
       </c>
       <c r="I95" s="189" t="s">
-        <v>2411</v>
+        <v>2410</v>
       </c>
       <c r="J95" s="213">
         <v>1</v>
@@ -38747,10 +38755,10 @@
         <v>292</v>
       </c>
       <c r="N95" s="231" t="s">
-        <v>2445</v>
+        <v>2444</v>
       </c>
       <c r="O95" s="206" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
       <c r="P95" s="236">
         <v>88</v>
@@ -38761,7 +38769,7 @@
         <v>387</v>
       </c>
       <c r="B96" s="185" t="s">
-        <v>2514</v>
+        <v>2513</v>
       </c>
       <c r="C96" s="185" t="s">
         <v>326</v>
@@ -38782,7 +38790,7 @@
         <v>294</v>
       </c>
       <c r="I96" s="229" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
       <c r="J96" s="229">
         <v>6</v>
@@ -38797,10 +38805,10 @@
         <v>292</v>
       </c>
       <c r="N96" s="229" t="s">
-        <v>2489</v>
+        <v>2488</v>
       </c>
       <c r="O96" s="194" t="s">
-        <v>2461</v>
+        <v>2460</v>
       </c>
       <c r="P96" s="235">
         <v>34</v>
@@ -38812,7 +38820,7 @@
         <v>389</v>
       </c>
       <c r="B97" s="200" t="s">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="C97" s="198" t="s">
         <v>326</v>
@@ -38833,7 +38841,7 @@
         <v>294</v>
       </c>
       <c r="I97" s="212" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
       <c r="J97" s="202">
         <v>9</v>
@@ -38848,10 +38856,10 @@
         <v>292</v>
       </c>
       <c r="N97" s="212" t="s">
-        <v>2489</v>
+        <v>2488</v>
       </c>
       <c r="O97" s="203" t="s">
-        <v>2461</v>
+        <v>2460</v>
       </c>
       <c r="P97" s="236">
         <v>34</v>
@@ -38863,7 +38871,7 @@
         <v>391</v>
       </c>
       <c r="B98" s="193" t="s">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="C98" s="193" t="s">
         <v>326</v>
@@ -38884,7 +38892,7 @@
         <v>294</v>
       </c>
       <c r="I98" s="204" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
       <c r="J98" s="204">
         <v>6</v>
@@ -38899,10 +38907,10 @@
         <v>292</v>
       </c>
       <c r="N98" s="204" t="s">
-        <v>2504</v>
+        <v>2503</v>
       </c>
       <c r="O98" s="195" t="s">
-        <v>2461</v>
+        <v>2460</v>
       </c>
       <c r="P98" s="235">
         <v>36</v>
@@ -38914,7 +38922,7 @@
         <v>392</v>
       </c>
       <c r="B99" s="200" t="s">
-        <v>2517</v>
+        <v>2516</v>
       </c>
       <c r="C99" s="198" t="s">
         <v>326</v>
@@ -38935,7 +38943,7 @@
         <v>294</v>
       </c>
       <c r="I99" s="212" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
       <c r="J99" s="202">
         <v>9</v>
@@ -38950,10 +38958,10 @@
         <v>292</v>
       </c>
       <c r="N99" s="212" t="s">
-        <v>2504</v>
+        <v>2503</v>
       </c>
       <c r="O99" s="205" t="s">
-        <v>2461</v>
+        <v>2460</v>
       </c>
       <c r="P99" s="236">
         <v>36</v>
@@ -38964,7 +38972,7 @@
         <v>393</v>
       </c>
       <c r="B100" s="193" t="s">
-        <v>2513</v>
+        <v>2512</v>
       </c>
       <c r="C100" s="193" t="s">
         <v>326</v>
@@ -38985,7 +38993,7 @@
         <v>294</v>
       </c>
       <c r="I100" s="204" t="s">
-        <v>2467</v>
+        <v>2466</v>
       </c>
       <c r="J100" s="204">
         <v>6</v>
@@ -39000,10 +39008,10 @@
         <v>292</v>
       </c>
       <c r="N100" s="204" t="s">
-        <v>2503</v>
+        <v>2502</v>
       </c>
       <c r="O100" s="195" t="s">
-        <v>2468</v>
+        <v>2467</v>
       </c>
       <c r="P100" s="235">
         <v>38</v>
@@ -39014,7 +39022,7 @@
         <v>394</v>
       </c>
       <c r="B101" s="200" t="s">
-        <v>2518</v>
+        <v>2517</v>
       </c>
       <c r="C101" s="198" t="s">
         <v>326</v>
@@ -39035,7 +39043,7 @@
         <v>294</v>
       </c>
       <c r="I101" s="212" t="s">
-        <v>2467</v>
+        <v>2466</v>
       </c>
       <c r="J101" s="202">
         <v>9</v>
@@ -39050,10 +39058,10 @@
         <v>292</v>
       </c>
       <c r="N101" s="212" t="s">
-        <v>2503</v>
+        <v>2502</v>
       </c>
       <c r="O101" s="203" t="s">
-        <v>2468</v>
+        <v>2467</v>
       </c>
       <c r="P101" s="236">
         <v>38</v>
@@ -39064,7 +39072,7 @@
         <v>395</v>
       </c>
       <c r="B102" s="193" t="s">
-        <v>2535</v>
+        <v>2534</v>
       </c>
       <c r="C102" s="193" t="s">
         <v>326</v>
@@ -39085,7 +39093,7 @@
         <v>294</v>
       </c>
       <c r="I102" s="204" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
       <c r="J102" s="204">
         <v>3</v>
@@ -39100,10 +39108,10 @@
         <v>292</v>
       </c>
       <c r="N102" s="204" t="s">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="O102" s="195" t="s">
-        <v>2462</v>
+        <v>2461</v>
       </c>
       <c r="P102" s="235">
         <v>40</v>
@@ -39114,7 +39122,7 @@
         <v>397</v>
       </c>
       <c r="B103" s="200" t="s">
-        <v>2536</v>
+        <v>2535</v>
       </c>
       <c r="C103" s="198" t="s">
         <v>326</v>
@@ -39135,7 +39143,7 @@
         <v>294</v>
       </c>
       <c r="I103" s="199" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
       <c r="J103" s="212">
         <v>3</v>
@@ -39150,10 +39158,10 @@
         <v>292</v>
       </c>
       <c r="N103" s="212" t="s">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="O103" s="203" t="s">
-        <v>2462</v>
+        <v>2461</v>
       </c>
       <c r="P103" s="236">
         <v>40</v>
@@ -39164,7 +39172,7 @@
         <v>398</v>
       </c>
       <c r="B104" s="193" t="s">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="C104" s="193" t="s">
         <v>326</v>
@@ -39185,13 +39193,13 @@
         <v>294</v>
       </c>
       <c r="I104" s="204" t="s">
-        <v>2482</v>
+        <v>2481</v>
       </c>
       <c r="J104" s="204" t="s">
-        <v>2477</v>
+        <v>2476</v>
       </c>
       <c r="K104" s="204" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
       <c r="L104" s="204">
         <v>3</v>
@@ -39200,10 +39208,10 @@
         <v>292</v>
       </c>
       <c r="N104" s="204" t="s">
-        <v>2499</v>
+        <v>2498</v>
       </c>
       <c r="O104" s="195" t="s">
-        <v>2483</v>
+        <v>2482</v>
       </c>
       <c r="P104" s="235">
         <v>48</v>
@@ -39214,7 +39222,7 @@
         <v>399</v>
       </c>
       <c r="B105" s="198" t="s">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="C105" s="198" t="s">
         <v>326</v>
@@ -39235,13 +39243,13 @@
         <v>294</v>
       </c>
       <c r="I105" s="199" t="s">
-        <v>2482</v>
+        <v>2481</v>
       </c>
       <c r="J105" s="199" t="s">
-        <v>2497</v>
+        <v>2496</v>
       </c>
       <c r="K105" s="199" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
       <c r="L105" s="199">
         <v>3</v>
@@ -39250,10 +39258,10 @@
         <v>292</v>
       </c>
       <c r="N105" s="202" t="s">
-        <v>2489</v>
+        <v>2488</v>
       </c>
       <c r="O105" s="203" t="s">
-        <v>2483</v>
+        <v>2482</v>
       </c>
       <c r="P105" s="236">
         <v>48</v>
@@ -39264,7 +39272,7 @@
         <v>400</v>
       </c>
       <c r="B106" s="193" t="s">
-        <v>2509</v>
+        <v>2508</v>
       </c>
       <c r="C106" s="193" t="s">
         <v>326</v>
@@ -39285,13 +39293,13 @@
         <v>294</v>
       </c>
       <c r="I106" s="204" t="s">
+        <v>2478</v>
+      </c>
+      <c r="J106" s="204" t="s">
         <v>2479</v>
       </c>
-      <c r="J106" s="204" t="s">
-        <v>2480</v>
-      </c>
       <c r="K106" s="204" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
       <c r="L106" s="204">
         <v>3</v>
@@ -39300,10 +39308,10 @@
         <v>292</v>
       </c>
       <c r="N106" s="204" t="s">
-        <v>2490</v>
+        <v>2489</v>
       </c>
       <c r="O106" s="195" t="s">
-        <v>2481</v>
+        <v>2480</v>
       </c>
       <c r="P106" s="235">
         <v>46</v>
@@ -39314,7 +39322,7 @@
         <v>402</v>
       </c>
       <c r="B107" s="198" t="s">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="C107" s="198" t="s">
         <v>326</v>
@@ -39335,13 +39343,13 @@
         <v>294</v>
       </c>
       <c r="I107" s="199" t="s">
-        <v>2479</v>
+        <v>2478</v>
       </c>
       <c r="J107" s="199" t="s">
-        <v>2498</v>
+        <v>2497</v>
       </c>
       <c r="K107" s="199" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
       <c r="L107" s="199">
         <v>3</v>
@@ -39350,10 +39358,10 @@
         <v>292</v>
       </c>
       <c r="N107" s="202" t="s">
-        <v>2489</v>
+        <v>2488</v>
       </c>
       <c r="O107" s="203" t="s">
-        <v>2481</v>
+        <v>2480</v>
       </c>
       <c r="P107" s="236">
         <v>46</v>
@@ -39364,7 +39372,7 @@
         <v>403</v>
       </c>
       <c r="B108" s="193" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="C108" s="193" t="s">
         <v>326</v>
@@ -39385,13 +39393,13 @@
         <v>294</v>
       </c>
       <c r="I108" s="204" t="s">
+        <v>2475</v>
+      </c>
+      <c r="J108" s="204" t="s">
         <v>2476</v>
       </c>
-      <c r="J108" s="204" t="s">
-        <v>2477</v>
-      </c>
       <c r="K108" s="204" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
       <c r="L108" s="204">
         <v>3</v>
@@ -39400,10 +39408,10 @@
         <v>292</v>
       </c>
       <c r="N108" s="204" t="s">
-        <v>2487</v>
+        <v>2486</v>
       </c>
       <c r="O108" s="195" t="s">
-        <v>2478</v>
+        <v>2477</v>
       </c>
       <c r="P108" s="235">
         <v>52</v>
@@ -39414,7 +39422,7 @@
         <v>405</v>
       </c>
       <c r="B109" s="198" t="s">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="C109" s="198" t="s">
         <v>326</v>
@@ -39435,13 +39443,13 @@
         <v>294</v>
       </c>
       <c r="I109" s="199" t="s">
-        <v>2476</v>
+        <v>2475</v>
       </c>
       <c r="J109" s="199" t="s">
-        <v>2497</v>
+        <v>2496</v>
       </c>
       <c r="K109" s="199" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
       <c r="L109" s="199">
         <v>3</v>
@@ -39450,10 +39458,10 @@
         <v>292</v>
       </c>
       <c r="N109" s="202" t="s">
-        <v>2488</v>
+        <v>2487</v>
       </c>
       <c r="O109" s="203" t="s">
-        <v>2478</v>
+        <v>2477</v>
       </c>
       <c r="P109" s="236">
         <v>52</v>
@@ -39464,7 +39472,7 @@
         <v>406</v>
       </c>
       <c r="B110" s="193" t="s">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="C110" s="193" t="s">
         <v>326</v>
@@ -39485,13 +39493,13 @@
         <v>294</v>
       </c>
       <c r="I110" s="204" t="s">
+        <v>2472</v>
+      </c>
+      <c r="J110" s="204" t="s">
         <v>2473</v>
       </c>
-      <c r="J110" s="204" t="s">
-        <v>2474</v>
-      </c>
       <c r="K110" s="204" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
       <c r="L110" s="204">
         <v>3</v>
@@ -39500,10 +39508,10 @@
         <v>292</v>
       </c>
       <c r="N110" s="204" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="O110" s="195" t="s">
-        <v>2475</v>
+        <v>2474</v>
       </c>
       <c r="P110" s="235">
         <v>50</v>
@@ -39514,7 +39522,7 @@
         <v>407</v>
       </c>
       <c r="B111" s="198" t="s">
-        <v>2508</v>
+        <v>2507</v>
       </c>
       <c r="C111" s="198" t="s">
         <v>326</v>
@@ -39535,13 +39543,13 @@
         <v>294</v>
       </c>
       <c r="I111" s="199" t="s">
-        <v>2473</v>
+        <v>2472</v>
       </c>
       <c r="J111" s="199" t="s">
-        <v>2496</v>
+        <v>2495</v>
       </c>
       <c r="K111" s="199" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
       <c r="L111" s="199">
         <v>3</v>
@@ -39550,10 +39558,10 @@
         <v>292</v>
       </c>
       <c r="N111" s="202" t="s">
-        <v>2501</v>
+        <v>2500</v>
       </c>
       <c r="O111" s="203" t="s">
-        <v>2475</v>
+        <v>2474</v>
       </c>
       <c r="P111" s="236">
         <v>50</v>
@@ -39564,7 +39572,7 @@
         <v>408</v>
       </c>
       <c r="B112" s="193" t="s">
-        <v>2519</v>
+        <v>2518</v>
       </c>
       <c r="C112" s="193" t="s">
         <v>326</v>
@@ -39585,7 +39593,7 @@
         <v>294</v>
       </c>
       <c r="I112" s="204" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
       <c r="J112" s="204">
         <v>16</v>
@@ -39600,10 +39608,10 @@
         <v>292</v>
       </c>
       <c r="N112" s="204" t="s">
-        <v>2471</v>
+        <v>2470</v>
       </c>
       <c r="O112" s="195" t="s">
-        <v>2493</v>
+        <v>2492</v>
       </c>
       <c r="P112" s="235">
         <v>64</v>
@@ -39614,7 +39622,7 @@
         <v>409</v>
       </c>
       <c r="B113" s="198" t="s">
-        <v>2520</v>
+        <v>2519</v>
       </c>
       <c r="C113" s="198" t="s">
         <v>326</v>
@@ -39635,7 +39643,7 @@
         <v>294</v>
       </c>
       <c r="I113" s="199" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
       <c r="J113" s="199">
         <v>16</v>
@@ -39650,10 +39658,10 @@
         <v>292</v>
       </c>
       <c r="N113" s="212" t="s">
-        <v>2471</v>
+        <v>2470</v>
       </c>
       <c r="O113" s="203" t="s">
-        <v>2494</v>
+        <v>2493</v>
       </c>
       <c r="P113" s="236">
         <v>64</v>
@@ -39664,7 +39672,7 @@
         <v>410</v>
       </c>
       <c r="B114" s="193" t="s">
-        <v>2531</v>
+        <v>2530</v>
       </c>
       <c r="C114" s="193" t="s">
         <v>326</v>
@@ -39685,7 +39693,7 @@
         <v>294</v>
       </c>
       <c r="I114" s="204" t="s">
-        <v>2467</v>
+        <v>2466</v>
       </c>
       <c r="J114" s="204">
         <v>12</v>
@@ -39700,10 +39708,10 @@
         <v>292</v>
       </c>
       <c r="N114" s="204" t="s">
-        <v>2484</v>
+        <v>2483</v>
       </c>
       <c r="O114" s="195" t="s">
-        <v>2470</v>
+        <v>2469</v>
       </c>
       <c r="P114" s="235">
         <v>68</v>
@@ -39714,7 +39722,7 @@
         <v>411</v>
       </c>
       <c r="B115" s="198" t="s">
-        <v>2532</v>
+        <v>2531</v>
       </c>
       <c r="C115" s="198" t="s">
         <v>326</v>
@@ -39735,7 +39743,7 @@
         <v>294</v>
       </c>
       <c r="I115" s="199" t="s">
-        <v>2467</v>
+        <v>2466</v>
       </c>
       <c r="J115" s="199">
         <v>12</v>
@@ -39750,10 +39758,10 @@
         <v>292</v>
       </c>
       <c r="N115" s="212" t="s">
-        <v>2484</v>
+        <v>2483</v>
       </c>
       <c r="O115" s="203" t="s">
-        <v>2495</v>
+        <v>2494</v>
       </c>
       <c r="P115" s="236">
         <v>68</v>
@@ -39764,7 +39772,7 @@
         <v>412</v>
       </c>
       <c r="B116" s="193" t="s">
-        <v>2529</v>
+        <v>2528</v>
       </c>
       <c r="C116" s="193" t="s">
         <v>326</v>
@@ -39785,7 +39793,7 @@
         <v>294</v>
       </c>
       <c r="I116" s="204" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
       <c r="J116" s="204">
         <v>9</v>
@@ -39800,10 +39808,10 @@
         <v>292</v>
       </c>
       <c r="N116" s="204" t="s">
-        <v>2492</v>
+        <v>2491</v>
       </c>
       <c r="O116" s="195" t="s">
-        <v>2469</v>
+        <v>2468</v>
       </c>
       <c r="P116" s="235">
         <v>74</v>
@@ -39814,7 +39822,7 @@
         <v>413</v>
       </c>
       <c r="B117" s="198" t="s">
-        <v>2530</v>
+        <v>2529</v>
       </c>
       <c r="C117" s="198" t="s">
         <v>326</v>
@@ -39835,7 +39843,7 @@
         <v>294</v>
       </c>
       <c r="I117" s="199" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
       <c r="J117" s="201">
         <v>10</v>
@@ -39850,10 +39858,10 @@
         <v>292</v>
       </c>
       <c r="N117" s="212" t="s">
-        <v>2492</v>
+        <v>2491</v>
       </c>
       <c r="O117" s="205" t="s">
-        <v>2469</v>
+        <v>2468</v>
       </c>
       <c r="P117" s="236">
         <v>74</v>
@@ -39864,7 +39872,7 @@
         <v>414</v>
       </c>
       <c r="B118" s="193" t="s">
-        <v>2533</v>
+        <v>2532</v>
       </c>
       <c r="C118" s="193" t="s">
         <v>326</v>
@@ -39885,7 +39893,7 @@
         <v>294</v>
       </c>
       <c r="I118" s="204" t="s">
-        <v>2467</v>
+        <v>2466</v>
       </c>
       <c r="J118" s="204">
         <v>4</v>
@@ -39900,10 +39908,10 @@
         <v>292</v>
       </c>
       <c r="N118" s="204" t="s">
-        <v>2466</v>
+        <v>2465</v>
       </c>
       <c r="O118" s="195" t="s">
-        <v>2468</v>
+        <v>2467</v>
       </c>
       <c r="P118" s="235">
         <v>72</v>
@@ -39914,7 +39922,7 @@
         <v>415</v>
       </c>
       <c r="B119" s="198" t="s">
-        <v>2534</v>
+        <v>2533</v>
       </c>
       <c r="C119" s="198" t="s">
         <v>326</v>
@@ -39935,7 +39943,7 @@
         <v>294</v>
       </c>
       <c r="I119" s="199" t="s">
-        <v>2467</v>
+        <v>2466</v>
       </c>
       <c r="J119" s="201">
         <v>5</v>
@@ -39950,10 +39958,10 @@
         <v>292</v>
       </c>
       <c r="N119" s="212" t="s">
-        <v>2466</v>
+        <v>2465</v>
       </c>
       <c r="O119" s="203" t="s">
-        <v>2468</v>
+        <v>2467</v>
       </c>
       <c r="P119" s="236">
         <v>72</v>
@@ -39964,7 +39972,7 @@
         <v>416</v>
       </c>
       <c r="B120" s="193" t="s">
-        <v>2527</v>
+        <v>2526</v>
       </c>
       <c r="C120" s="193" t="s">
         <v>326</v>
@@ -39985,7 +39993,7 @@
         <v>294</v>
       </c>
       <c r="I120" s="204" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
       <c r="J120" s="204">
         <v>6</v>
@@ -40000,10 +40008,10 @@
         <v>292</v>
       </c>
       <c r="N120" s="204" t="s">
-        <v>2490</v>
+        <v>2489</v>
       </c>
       <c r="O120" s="195" t="s">
-        <v>2465</v>
+        <v>2464</v>
       </c>
       <c r="P120" s="235">
         <v>88</v>
@@ -40014,7 +40022,7 @@
         <v>417</v>
       </c>
       <c r="B121" s="198" t="s">
-        <v>2528</v>
+        <v>2527</v>
       </c>
       <c r="C121" s="198" t="s">
         <v>326</v>
@@ -40035,7 +40043,7 @@
         <v>294</v>
       </c>
       <c r="I121" s="199" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
       <c r="J121" s="201">
         <v>8</v>
@@ -40050,10 +40058,10 @@
         <v>292</v>
       </c>
       <c r="N121" s="202" t="s">
-        <v>2487</v>
+        <v>2486</v>
       </c>
       <c r="O121" s="205" t="s">
-        <v>2465</v>
+        <v>2464</v>
       </c>
       <c r="P121" s="236">
         <v>88</v>
@@ -40064,7 +40072,7 @@
         <v>418</v>
       </c>
       <c r="B122" s="193" t="s">
-        <v>2525</v>
+        <v>2524</v>
       </c>
       <c r="C122" s="193" t="s">
         <v>326</v>
@@ -40085,7 +40093,7 @@
         <v>294</v>
       </c>
       <c r="I122" s="204" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
       <c r="J122" s="204">
         <v>2</v>
@@ -40100,10 +40108,10 @@
         <v>292</v>
       </c>
       <c r="N122" s="204" t="s">
-        <v>2490</v>
+        <v>2489</v>
       </c>
       <c r="O122" s="195" t="s">
-        <v>2464</v>
+        <v>2463</v>
       </c>
       <c r="P122" s="235">
         <v>96</v>
@@ -40114,7 +40122,7 @@
         <v>419</v>
       </c>
       <c r="B123" s="198" t="s">
-        <v>2526</v>
+        <v>2525</v>
       </c>
       <c r="C123" s="198" t="s">
         <v>326</v>
@@ -40135,7 +40143,7 @@
         <v>294</v>
       </c>
       <c r="I123" s="199" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
       <c r="J123" s="199">
         <v>2</v>
@@ -40150,10 +40158,10 @@
         <v>292</v>
       </c>
       <c r="N123" s="202" t="s">
-        <v>2488</v>
+        <v>2487</v>
       </c>
       <c r="O123" s="203" t="s">
-        <v>2464</v>
+        <v>2463</v>
       </c>
       <c r="P123" s="236">
         <v>96</v>
@@ -40161,10 +40169,10 @@
     </row>
     <row r="124" spans="1:16" ht="18" thickBot="1">
       <c r="A124" s="217" t="s">
-        <v>2354</v>
+        <v>2353</v>
       </c>
       <c r="B124" s="193" t="s">
-        <v>2523</v>
+        <v>2522</v>
       </c>
       <c r="C124" s="193" t="s">
         <v>326</v>
@@ -40185,7 +40193,7 @@
         <v>294</v>
       </c>
       <c r="I124" s="204" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
       <c r="J124" s="204">
         <v>2</v>
@@ -40200,10 +40208,10 @@
         <v>292</v>
       </c>
       <c r="N124" s="204" t="s">
-        <v>2491</v>
+        <v>2490</v>
       </c>
       <c r="O124" s="195" t="s">
-        <v>2461</v>
+        <v>2460</v>
       </c>
       <c r="P124" s="235">
         <v>84</v>
@@ -40211,10 +40219,10 @@
     </row>
     <row r="125" spans="1:16" ht="18" thickBot="1">
       <c r="A125" s="224" t="s">
-        <v>2355</v>
+        <v>2354</v>
       </c>
       <c r="B125" s="198" t="s">
-        <v>2524</v>
+        <v>2523</v>
       </c>
       <c r="C125" s="198" t="s">
         <v>326</v>
@@ -40235,7 +40243,7 @@
         <v>294</v>
       </c>
       <c r="I125" s="199" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
       <c r="J125" s="199">
         <v>2</v>
@@ -40250,10 +40258,10 @@
         <v>292</v>
       </c>
       <c r="N125" s="202" t="s">
-        <v>2490</v>
+        <v>2489</v>
       </c>
       <c r="O125" s="203" t="s">
-        <v>2461</v>
+        <v>2460</v>
       </c>
       <c r="P125" s="236">
         <v>84</v>
@@ -40261,10 +40269,10 @@
     </row>
     <row r="126" spans="1:16" ht="18" thickBot="1">
       <c r="A126" s="217" t="s">
-        <v>2356</v>
+        <v>2355</v>
       </c>
       <c r="B126" s="193" t="s">
-        <v>2521</v>
+        <v>2520</v>
       </c>
       <c r="C126" s="193" t="s">
         <v>326</v>
@@ -40285,13 +40293,13 @@
         <v>294</v>
       </c>
       <c r="I126" s="204" t="s">
+        <v>2456</v>
+      </c>
+      <c r="J126" s="204" t="s">
         <v>2457</v>
       </c>
-      <c r="J126" s="204" t="s">
+      <c r="K126" s="204" t="s">
         <v>2458</v>
-      </c>
-      <c r="K126" s="204" t="s">
-        <v>2459</v>
       </c>
       <c r="L126" s="204">
         <v>4</v>
@@ -40300,10 +40308,10 @@
         <v>292</v>
       </c>
       <c r="N126" s="204" t="s">
-        <v>2540</v>
+        <v>2539</v>
       </c>
       <c r="O126" s="195" t="s">
-        <v>2463</v>
+        <v>2462</v>
       </c>
       <c r="P126" s="235">
         <v>90</v>
@@ -40311,10 +40319,10 @@
     </row>
     <row r="127" spans="1:16" ht="18" thickBot="1">
       <c r="A127" s="227" t="s">
-        <v>2357</v>
+        <v>2356</v>
       </c>
       <c r="B127" s="188" t="s">
-        <v>2522</v>
+        <v>2521</v>
       </c>
       <c r="C127" s="188" t="s">
         <v>326</v>
@@ -40335,13 +40343,13 @@
         <v>294</v>
       </c>
       <c r="I127" s="197" t="s">
-        <v>2457</v>
+        <v>2456</v>
       </c>
       <c r="J127" s="197" t="s">
-        <v>2486</v>
+        <v>2485</v>
       </c>
       <c r="K127" s="197" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
       <c r="L127" s="197">
         <v>4</v>
@@ -40350,10 +40358,10 @@
         <v>292</v>
       </c>
       <c r="N127" s="231" t="s">
-        <v>2541</v>
+        <v>2540</v>
       </c>
       <c r="O127" s="206" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="P127" s="236">
         <v>90</v>
@@ -43102,7 +43110,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="45" t="s">
-        <v>2342</v>
+        <v>2341</v>
       </c>
       <c r="I3" s="20" t="s">
         <v>275</v>
@@ -43111,7 +43119,7 @@
         <v>430</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>2557</v>
+        <v>2556</v>
       </c>
       <c r="L3" s="21" t="s">
         <v>274</v>
@@ -43140,7 +43148,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="156" t="s">
-        <v>2543</v>
+        <v>2542</v>
       </c>
       <c r="I4" s="20" t="s">
         <v>294</v>
@@ -43149,7 +43157,7 @@
         <v>434</v>
       </c>
       <c r="K4" s="21" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="L4" s="21" t="s">
         <v>435</v>
@@ -43178,7 +43186,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="45" t="s">
-        <v>2537</v>
+        <v>2536</v>
       </c>
       <c r="I5" s="20" t="s">
         <v>275</v>
@@ -43216,7 +43224,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="156" t="s">
-        <v>2491</v>
+        <v>2490</v>
       </c>
       <c r="I6" s="20" t="s">
         <v>294</v>
@@ -43254,7 +43262,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="45" t="s">
-        <v>2343</v>
+        <v>2342</v>
       </c>
       <c r="I7" s="20" t="s">
         <v>275</v>
@@ -43292,7 +43300,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="156" t="s">
-        <v>2342</v>
+        <v>2341</v>
       </c>
       <c r="I8" s="20" t="s">
         <v>294</v>
@@ -43406,7 +43414,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="156" t="s">
-        <v>2342</v>
+        <v>2341</v>
       </c>
       <c r="I11" s="20" t="s">
         <v>294</v>
@@ -43482,7 +43490,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="45" t="s">
-        <v>2538</v>
+        <v>2537</v>
       </c>
       <c r="I13" s="20" t="s">
         <v>275</v>
@@ -43520,7 +43528,7 @@
         <v>6</v>
       </c>
       <c r="H14" s="45" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="I14" s="20" t="s">
         <v>294</v>
@@ -43558,7 +43566,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="45" t="s">
-        <v>2342</v>
+        <v>2341</v>
       </c>
       <c r="I15" s="20" t="s">
         <v>275</v>
@@ -43634,7 +43642,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="45" t="s">
-        <v>2342</v>
+        <v>2341</v>
       </c>
       <c r="I17" s="20" t="s">
         <v>275</v>
@@ -43748,7 +43756,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="156" t="s">
-        <v>2254</v>
+        <v>2253</v>
       </c>
       <c r="I20" s="20" t="s">
         <v>294</v>
@@ -43824,7 +43832,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="45" t="s">
-        <v>2538</v>
+        <v>2537</v>
       </c>
       <c r="I22" s="20" t="s">
         <v>275</v>
@@ -43862,7 +43870,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="45" t="s">
-        <v>2342</v>
+        <v>2341</v>
       </c>
       <c r="I23" s="20" t="s">
         <v>294</v>
@@ -43900,7 +43908,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="45" t="s">
-        <v>2543</v>
+        <v>2542</v>
       </c>
       <c r="I24" s="20" t="s">
         <v>294</v>
@@ -43938,7 +43946,7 @@
         <v>0</v>
       </c>
       <c r="H25" s="45" t="s">
-        <v>2543</v>
+        <v>2542</v>
       </c>
       <c r="I25" s="20" t="s">
         <v>313</v>
@@ -43976,7 +43984,7 @@
         <v>0</v>
       </c>
       <c r="H26" s="45" t="s">
-        <v>2543</v>
+        <v>2542</v>
       </c>
       <c r="I26" s="20" t="s">
         <v>313</v>
@@ -44052,7 +44060,7 @@
         <v>0</v>
       </c>
       <c r="H28" s="45" t="s">
-        <v>2342</v>
+        <v>2341</v>
       </c>
       <c r="I28" s="20" t="s">
         <v>275</v>
@@ -44090,7 +44098,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="45" t="s">
-        <v>2252</v>
+        <v>2251</v>
       </c>
       <c r="I29" s="20" t="s">
         <v>294</v>
@@ -44128,7 +44136,7 @@
         <v>0</v>
       </c>
       <c r="H30" s="45" t="s">
-        <v>2491</v>
+        <v>2490</v>
       </c>
       <c r="I30" s="20" t="s">
         <v>294</v>
@@ -44242,7 +44250,7 @@
         <v>0</v>
       </c>
       <c r="H33" s="45" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
       <c r="I33" s="20" t="s">
         <v>294</v>
@@ -44280,7 +44288,7 @@
         <v>0</v>
       </c>
       <c r="H34" s="21" t="s">
-        <v>2342</v>
+        <v>2341</v>
       </c>
       <c r="I34" s="20" t="s">
         <v>275</v>
@@ -44318,7 +44326,7 @@
         <v>6</v>
       </c>
       <c r="H35" s="45" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="I35" s="20" t="s">
         <v>294</v>
@@ -44356,7 +44364,7 @@
         <v>0</v>
       </c>
       <c r="H36" s="45" t="s">
-        <v>2254</v>
+        <v>2253</v>
       </c>
       <c r="I36" s="20" t="s">
         <v>294</v>
@@ -44470,7 +44478,7 @@
         <v>0</v>
       </c>
       <c r="H39" s="21" t="s">
-        <v>2342</v>
+        <v>2341</v>
       </c>
       <c r="I39" s="20" t="s">
         <v>275</v>
@@ -44490,7 +44498,7 @@
         <v>229</v>
       </c>
       <c r="B40" s="21" t="s">
-        <v>2539</v>
+        <v>2538</v>
       </c>
       <c r="C40" s="20" t="s">
         <v>290</v>
@@ -44546,7 +44554,7 @@
         <v>0</v>
       </c>
       <c r="H41" s="21" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
       <c r="I41" s="20" t="s">
         <v>294</v>
@@ -44584,7 +44592,7 @@
         <v>0</v>
       </c>
       <c r="H42" s="21" t="s">
-        <v>2343</v>
+        <v>2342</v>
       </c>
       <c r="I42" s="20" t="s">
         <v>313</v>
@@ -44814,7 +44822,7 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="21" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="B5" s="21" t="s">
         <v>557</v>
@@ -44847,7 +44855,7 @@
         <v>555</v>
       </c>
       <c r="L5" s="152" t="s">
-        <v>2360</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -45244,19 +45252,19 @@
     </row>
     <row r="7" spans="1:7" ht="16.5" customHeight="1">
       <c r="A7" s="55" t="s">
+        <v>2381</v>
+      </c>
+      <c r="B7" s="41" t="s">
         <v>2382</v>
       </c>
-      <c r="B7" s="41" t="s">
+      <c r="C7" s="156" t="s">
         <v>2383</v>
       </c>
-      <c r="C7" s="156" t="s">
+      <c r="D7" s="137" t="s">
         <v>2384</v>
       </c>
-      <c r="D7" s="137" t="s">
+      <c r="E7" s="209" t="s">
         <v>2385</v>
-      </c>
-      <c r="E7" s="209" t="s">
-        <v>2386</v>
       </c>
       <c r="F7" s="134"/>
       <c r="G7" s="140" t="s">
@@ -45307,7 +45315,7 @@
     </row>
     <row r="10" spans="1:7" ht="16.5" customHeight="1">
       <c r="A10" s="55" t="s">
-        <v>2472</v>
+        <v>2471</v>
       </c>
       <c r="B10" s="46" t="s">
         <v>605</v>
@@ -45433,7 +45441,7 @@
     </row>
     <row r="16" spans="1:7" ht="16.5" customHeight="1">
       <c r="A16" s="55" t="s">
-        <v>2316</v>
+        <v>2315</v>
       </c>
       <c r="B16" s="46" t="s">
         <v>624</v>
@@ -45496,7 +45504,7 @@
     </row>
     <row r="19" spans="1:7" ht="16.5" customHeight="1">
       <c r="A19" s="55" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
       <c r="B19" s="46" t="s">
         <v>632</v>
@@ -45580,7 +45588,7 @@
     </row>
     <row r="23" spans="1:7" ht="16.5" customHeight="1">
       <c r="A23" s="55" t="s">
-        <v>2399</v>
+        <v>2398</v>
       </c>
       <c r="B23" s="46" t="s">
         <v>644</v>
@@ -45601,7 +45609,7 @@
     </row>
     <row r="24" spans="1:7" ht="16.5" customHeight="1">
       <c r="A24" s="55" t="s">
-        <v>2397</v>
+        <v>2396</v>
       </c>
       <c r="B24" s="46" t="s">
         <v>647</v>
@@ -45622,7 +45630,7 @@
     </row>
     <row r="25" spans="1:7" ht="16.5" customHeight="1">
       <c r="A25" s="55" t="s">
-        <v>2398</v>
+        <v>2397</v>
       </c>
       <c r="B25" s="46" t="s">
         <v>650</v>
@@ -45706,7 +45714,7 @@
     </row>
     <row r="29" spans="1:7" ht="16.5" customHeight="1">
       <c r="A29" s="55" t="s">
-        <v>2311</v>
+        <v>2310</v>
       </c>
       <c r="B29" s="143" t="s">
         <v>662</v>
@@ -45715,7 +45723,7 @@
         <v>613</v>
       </c>
       <c r="D29" s="156" t="s">
-        <v>2319</v>
+        <v>2318</v>
       </c>
       <c r="E29" s="144" t="s">
         <v>663</v>
@@ -45814,7 +45822,7 @@
         <v>673</v>
       </c>
       <c r="B34" s="156" t="s">
-        <v>2320</v>
+        <v>2319</v>
       </c>
       <c r="C34" s="136" t="s">
         <v>588</v>
@@ -47743,7 +47751,7 @@
     </row>
     <row r="126" spans="1:7" ht="16.5" customHeight="1">
       <c r="A126" s="149" t="s">
-        <v>2339</v>
+        <v>2338</v>
       </c>
       <c r="B126" s="136" t="s">
         <v>1023</v>
@@ -47943,10 +47951,10 @@
     </row>
     <row r="136" spans="1:7" ht="16.5" customHeight="1">
       <c r="A136" s="149" t="s">
+        <v>2401</v>
+      </c>
+      <c r="B136" s="156" t="s">
         <v>2402</v>
-      </c>
-      <c r="B136" s="156" t="s">
-        <v>2403</v>
       </c>
       <c r="C136" s="136" t="s">
         <v>641</v>
@@ -47955,7 +47963,7 @@
         <v>625</v>
       </c>
       <c r="E136" s="149" t="s">
-        <v>2321</v>
+        <v>2320</v>
       </c>
       <c r="G136" s="139" t="s">
         <v>1063</v>
@@ -48015,7 +48023,7 @@
         <v>0</v>
       </c>
       <c r="E139" s="149" t="s">
-        <v>2322</v>
+        <v>2321</v>
       </c>
       <c r="G139" s="139" t="s">
         <v>1074</v>
@@ -48043,112 +48051,112 @@
     </row>
     <row r="141" spans="1:7" ht="16.5" customHeight="1">
       <c r="A141" s="208" t="s">
+        <v>2322</v>
+      </c>
+      <c r="B141" s="111" t="s">
         <v>2323</v>
       </c>
-      <c r="B141" s="111" t="s">
+      <c r="C141" s="111" t="s">
         <v>2324</v>
       </c>
-      <c r="C141" s="111" t="s">
+      <c r="D141" s="111">
+        <v>0</v>
+      </c>
+      <c r="E141" s="208" t="s">
         <v>2325</v>
-      </c>
-      <c r="D141" s="111">
-        <v>0</v>
-      </c>
-      <c r="E141" s="208" t="s">
-        <v>2326</v>
       </c>
     </row>
     <row r="142" spans="1:7" ht="16.5" customHeight="1">
       <c r="A142" s="208" t="s">
-        <v>2340</v>
+        <v>2339</v>
       </c>
       <c r="B142" s="111" t="s">
+        <v>2326</v>
+      </c>
+      <c r="C142" s="111" t="s">
         <v>2327</v>
       </c>
-      <c r="C142" s="111" t="s">
+      <c r="D142" s="111" t="s">
+        <v>2318</v>
+      </c>
+      <c r="E142" s="207" t="s">
         <v>2328</v>
-      </c>
-      <c r="D142" s="111" t="s">
-        <v>2319</v>
-      </c>
-      <c r="E142" s="207" t="s">
-        <v>2329</v>
       </c>
     </row>
     <row r="143" spans="1:7" ht="16.5" customHeight="1">
       <c r="A143" s="208" t="s">
+        <v>2329</v>
+      </c>
+      <c r="B143" s="111" t="s">
         <v>2330</v>
       </c>
-      <c r="B143" s="111" t="s">
+      <c r="C143" s="111" t="s">
+        <v>2327</v>
+      </c>
+      <c r="D143" s="111" t="s">
+        <v>2318</v>
+      </c>
+      <c r="E143" s="207" t="s">
         <v>2331</v>
-      </c>
-      <c r="C143" s="111" t="s">
-        <v>2328</v>
-      </c>
-      <c r="D143" s="111" t="s">
-        <v>2319</v>
-      </c>
-      <c r="E143" s="207" t="s">
-        <v>2332</v>
       </c>
     </row>
     <row r="144" spans="1:7" ht="16.5" customHeight="1">
       <c r="A144" s="208" t="s">
-        <v>2333</v>
+        <v>2332</v>
       </c>
       <c r="B144" s="111" t="s">
-        <v>2335</v>
+        <v>2334</v>
       </c>
       <c r="C144" s="111" t="s">
-        <v>2325</v>
+        <v>2324</v>
       </c>
       <c r="D144" s="111">
         <v>0</v>
       </c>
       <c r="E144" s="207" t="s">
-        <v>2337</v>
+        <v>2336</v>
       </c>
     </row>
     <row r="145" spans="1:5" ht="16.5" customHeight="1">
       <c r="A145" s="208" t="s">
-        <v>2334</v>
+        <v>2333</v>
       </c>
       <c r="B145" s="111" t="s">
-        <v>2336</v>
+        <v>2335</v>
       </c>
       <c r="C145" s="111" t="s">
-        <v>2325</v>
+        <v>2324</v>
       </c>
       <c r="D145" s="111">
         <v>0</v>
       </c>
       <c r="E145" s="207" t="s">
-        <v>2338</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="146" spans="1:5" ht="16.5" customHeight="1">
       <c r="A146" s="208" t="s">
+        <v>2386</v>
+      </c>
+      <c r="B146" s="111" t="s">
+        <v>2380</v>
+      </c>
+      <c r="C146" s="111" t="s">
         <v>2387</v>
       </c>
-      <c r="B146" s="111" t="s">
-        <v>2381</v>
-      </c>
-      <c r="C146" s="111" t="s">
+      <c r="D146" s="111">
+        <v>0</v>
+      </c>
+      <c r="E146" s="207" t="s">
         <v>2388</v>
-      </c>
-      <c r="D146" s="111">
-        <v>0</v>
-      </c>
-      <c r="E146" s="207" t="s">
-        <v>2389</v>
       </c>
     </row>
     <row r="147" spans="1:5" ht="16.5" customHeight="1">
       <c r="A147" s="139" t="s">
-        <v>2404</v>
+        <v>2403</v>
       </c>
       <c r="B147" s="211" t="s">
-        <v>2412</v>
+        <v>2411</v>
       </c>
       <c r="C147" s="211" t="s">
         <v>588</v>
@@ -48157,15 +48165,15 @@
         <v>0</v>
       </c>
       <c r="E147" s="210" t="s">
-        <v>2413</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="148" spans="1:5" ht="16.5" customHeight="1">
       <c r="A148" s="139" t="s">
-        <v>2406</v>
+        <v>2405</v>
       </c>
       <c r="B148" s="211" t="s">
-        <v>2414</v>
+        <v>2413</v>
       </c>
       <c r="C148" s="211" t="s">
         <v>588</v>
@@ -48174,15 +48182,15 @@
         <v>0</v>
       </c>
       <c r="E148" s="210" t="s">
-        <v>2415</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="149" spans="1:5" ht="16.5" customHeight="1">
       <c r="A149" s="139" t="s">
-        <v>2408</v>
+        <v>2407</v>
       </c>
       <c r="B149" s="211" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="C149" s="211" t="s">
         <v>588</v>
@@ -48191,15 +48199,15 @@
         <v>0</v>
       </c>
       <c r="E149" s="210" t="s">
-        <v>2417</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="16.5" customHeight="1">
       <c r="A150" s="139" t="s">
-        <v>2410</v>
+        <v>2409</v>
       </c>
       <c r="B150" s="211" t="s">
-        <v>2401</v>
+        <v>2400</v>
       </c>
       <c r="C150" s="211" t="s">
         <v>588</v>
@@ -48208,7 +48216,7 @@
         <v>0</v>
       </c>
       <c r="E150" s="210" t="s">
-        <v>2418</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="151" spans="1:5" ht="16.5" customHeight="1">

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erang\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5667FDD6-B865-4312-BC19-52FF5513CFBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D26501E2-22AA-4AB1-A953-FC1C1C892BEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -33164,7 +33164,7 @@
         <v>0.3</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>2336</v>
+        <v>2335</v>
       </c>
       <c r="K3" s="21" t="s">
         <v>163</v>
@@ -33288,7 +33288,7 @@
         <v>0.3</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>2336</v>
+        <v>2531</v>
       </c>
       <c r="K5" s="21" t="s">
         <v>174</v>
@@ -33350,7 +33350,7 @@
         <v>0.3</v>
       </c>
       <c r="J6" s="21" t="s">
-        <v>2336</v>
+        <v>2531</v>
       </c>
       <c r="K6" s="21" t="s">
         <v>180</v>
@@ -33474,7 +33474,7 @@
         <v>0.3</v>
       </c>
       <c r="J8" s="21" t="s">
-        <v>2158</v>
+        <v>2335</v>
       </c>
       <c r="K8" s="21" t="s">
         <v>193</v>
@@ -33598,7 +33598,7 @@
         <v>0.3</v>
       </c>
       <c r="J10" s="21" t="s">
-        <v>186</v>
+        <v>2531</v>
       </c>
       <c r="K10" s="21" t="s">
         <v>205</v>
@@ -33722,7 +33722,7 @@
         <v>0.2</v>
       </c>
       <c r="J12" s="21" t="s">
-        <v>2158</v>
+        <v>2335</v>
       </c>
       <c r="K12" s="21" t="s">
         <v>220</v>
@@ -33846,7 +33846,7 @@
         <v>0.5</v>
       </c>
       <c r="J14" s="21" t="s">
-        <v>162</v>
+        <v>2531</v>
       </c>
       <c r="K14" s="21" t="s">
         <v>237</v>
@@ -43684,7 +43684,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="45" t="s">
-        <v>2336</v>
+        <v>2531</v>
       </c>
       <c r="I7" s="20" t="s">
         <v>275</v>
@@ -43798,7 +43798,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="45" t="s">
-        <v>186</v>
+        <v>2531</v>
       </c>
       <c r="I10" s="20" t="s">
         <v>275</v>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ydjh1\Desktop\ProjectDustium\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{557420ED-1611-4C35-9A0D-DD1A19602A4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{762F6AC5-417C-4D1B-86A4-06B256530FD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20102,42 +20102,6 @@
     <phoneticPr fontId="27" type="noConversion"/>
   </si>
   <si>
-    <t>끝없는 검세</t>
-    <phoneticPr fontId="27" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>끝없는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>검세+</t>
-    </r>
-    <phoneticPr fontId="27" type="noConversion"/>
-  </si>
-  <si>
     <t>E_Pierce;E_Bleed</t>
     <phoneticPr fontId="27" type="noConversion"/>
   </si>
@@ -20162,14 +20126,6 @@
     <phoneticPr fontId="27" type="noConversion"/>
   </si>
   <si>
-    <t>발현검무</t>
-    <phoneticPr fontId="27" type="noConversion"/>
-  </si>
-  <si>
-    <t>발현검무+</t>
-    <phoneticPr fontId="27" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">{E_Pierce} {ValueRate1} / </t>
     </r>
@@ -22702,6 +22658,22 @@
       </rPr>
       <t>+</t>
     </r>
+    <phoneticPr fontId="27" type="noConversion"/>
+  </si>
+  <si>
+    <t>환영검무</t>
+    <phoneticPr fontId="27" type="noConversion"/>
+  </si>
+  <si>
+    <t>환영검무+</t>
+    <phoneticPr fontId="27" type="noConversion"/>
+  </si>
+  <si>
+    <t>공단참</t>
+    <phoneticPr fontId="27" type="noConversion"/>
+  </si>
+  <si>
+    <t>공단참+</t>
     <phoneticPr fontId="27" type="noConversion"/>
   </si>
 </sst>
@@ -38785,7 +38757,7 @@
         <v>65</v>
       </c>
       <c r="B6" s="198" t="s">
-        <v>2614</v>
+        <v>2610</v>
       </c>
       <c r="C6" s="153" t="s">
         <v>288</v>
@@ -38891,7 +38863,7 @@
         <v>81</v>
       </c>
       <c r="B8" s="197" t="s">
-        <v>2615</v>
+        <v>2611</v>
       </c>
       <c r="C8" s="153" t="s">
         <v>288</v>
@@ -38915,7 +38887,7 @@
         <v>288</v>
       </c>
       <c r="J8" s="153" t="s">
-        <v>2438</v>
+        <v>2434</v>
       </c>
       <c r="K8" s="153">
         <v>1</v>
@@ -38930,10 +38902,10 @@
         <v>288</v>
       </c>
       <c r="O8" s="153" t="s">
-        <v>2431</v>
+        <v>2427</v>
       </c>
       <c r="P8" s="222" t="s">
-        <v>2429</v>
+        <v>2425</v>
       </c>
       <c r="Q8" s="181">
         <v>0</v>
@@ -38944,7 +38916,7 @@
         <v>82</v>
       </c>
       <c r="B9" s="197" t="s">
-        <v>2428</v>
+        <v>2424</v>
       </c>
       <c r="C9" s="153" t="s">
         <v>288</v>
@@ -38986,7 +38958,7 @@
         <v>286</v>
       </c>
       <c r="P9" s="222" t="s">
-        <v>2430</v>
+        <v>2426</v>
       </c>
       <c r="Q9" s="181">
         <v>0</v>
@@ -39039,7 +39011,7 @@
         <v>298</v>
       </c>
       <c r="P10" s="222" t="s">
-        <v>2432</v>
+        <v>2428</v>
       </c>
       <c r="Q10" s="181">
         <v>0</v>
@@ -39092,7 +39064,7 @@
         <v>292</v>
       </c>
       <c r="P11" s="222" t="s">
-        <v>2433</v>
+        <v>2429</v>
       </c>
       <c r="Q11" s="181">
         <v>0</v>
@@ -39127,7 +39099,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="223" t="s">
-        <v>2434</v>
+        <v>2430</v>
       </c>
       <c r="K12" s="153" t="s">
         <v>305</v>
@@ -39368,7 +39340,7 @@
         <v>68</v>
       </c>
       <c r="B17" s="221" t="s">
-        <v>2418</v>
+        <v>2416</v>
       </c>
       <c r="C17" s="153" t="s">
         <v>307</v>
@@ -39421,7 +39393,7 @@
         <v>83</v>
       </c>
       <c r="B18" s="197" t="s">
-        <v>2435</v>
+        <v>2431</v>
       </c>
       <c r="C18" s="153" t="s">
         <v>307</v>
@@ -39445,7 +39417,7 @@
         <v>308</v>
       </c>
       <c r="J18" s="153" t="s">
-        <v>2439</v>
+        <v>2435</v>
       </c>
       <c r="K18" s="153" t="s">
         <v>2285</v>
@@ -39463,7 +39435,7 @@
         <v>318</v>
       </c>
       <c r="P18" s="166" t="s">
-        <v>2440</v>
+        <v>2436</v>
       </c>
       <c r="Q18" s="181">
         <v>0</v>
@@ -39474,7 +39446,7 @@
         <v>84</v>
       </c>
       <c r="B19" s="197" t="s">
-        <v>2436</v>
+        <v>2432</v>
       </c>
       <c r="C19" s="153" t="s">
         <v>307</v>
@@ -39498,7 +39470,7 @@
         <v>2392</v>
       </c>
       <c r="J19" s="153" t="s">
-        <v>2441</v>
+        <v>2437</v>
       </c>
       <c r="K19" s="153">
         <v>5</v>
@@ -39516,7 +39488,7 @@
         <v>320</v>
       </c>
       <c r="P19" s="166" t="s">
-        <v>2442</v>
+        <v>2438</v>
       </c>
       <c r="Q19" s="181">
         <v>0</v>
@@ -39566,10 +39538,10 @@
         <v>309</v>
       </c>
       <c r="O20" s="153" t="s">
-        <v>2443</v>
+        <v>2439</v>
       </c>
       <c r="P20" s="166" t="s">
-        <v>2444</v>
+        <v>2440</v>
       </c>
       <c r="Q20" s="181">
         <v>0</v>
@@ -39622,7 +39594,7 @@
         <v>328</v>
       </c>
       <c r="P21" s="166" t="s">
-        <v>2445</v>
+        <v>2441</v>
       </c>
       <c r="Q21" s="181">
         <v>0</v>
@@ -39842,10 +39814,10 @@
     </row>
     <row r="26" spans="1:17" ht="19.95" customHeight="1" thickBot="1">
       <c r="A26" s="152" t="s">
-        <v>2618</v>
+        <v>2614</v>
       </c>
       <c r="B26" s="198" t="s">
-        <v>2619</v>
+        <v>2615</v>
       </c>
       <c r="C26" s="153" t="s">
         <v>331</v>
@@ -39898,7 +39870,7 @@
         <v>338</v>
       </c>
       <c r="B27" s="242" t="s">
-        <v>2620</v>
+        <v>2616</v>
       </c>
       <c r="C27" s="157" t="s">
         <v>331</v>
@@ -40505,13 +40477,13 @@
         <v>310</v>
       </c>
       <c r="J38" s="153" t="s">
-        <v>2593</v>
+        <v>2589</v>
       </c>
       <c r="K38" s="153" t="s">
-        <v>2594</v>
+        <v>2590</v>
       </c>
       <c r="L38" s="153" t="s">
-        <v>2560</v>
+        <v>2556</v>
       </c>
       <c r="M38" s="153">
         <v>3</v>
@@ -40520,7 +40492,7 @@
         <v>309</v>
       </c>
       <c r="O38" s="153" t="s">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="P38" s="166" t="s">
         <v>332</v>
@@ -40558,13 +40530,13 @@
         <v>310</v>
       </c>
       <c r="J39" s="157" t="s">
-        <v>2593</v>
+        <v>2589</v>
       </c>
       <c r="K39" s="168" t="s">
-        <v>2595</v>
+        <v>2591</v>
       </c>
       <c r="L39" s="157" t="s">
-        <v>2560</v>
+        <v>2556</v>
       </c>
       <c r="M39" s="157">
         <v>3</v>
@@ -41615,7 +41587,7 @@
         <v>2326</v>
       </c>
       <c r="B60" s="240" t="s">
-        <v>2616</v>
+        <v>2612</v>
       </c>
       <c r="C60" s="160" t="s">
         <v>371</v>
@@ -41666,7 +41638,7 @@
         <v>2327</v>
       </c>
       <c r="B61" s="241" t="s">
-        <v>2617</v>
+        <v>2613</v>
       </c>
       <c r="C61" s="162" t="s">
         <v>371</v>
@@ -41921,7 +41893,7 @@
         <v>2370</v>
       </c>
       <c r="B66" s="199" t="s">
-        <v>2419</v>
+        <v>2417</v>
       </c>
       <c r="C66" s="160" t="s">
         <v>371</v>
@@ -41972,7 +41944,7 @@
         <v>2371</v>
       </c>
       <c r="B67" s="200" t="s">
-        <v>2420</v>
+        <v>2418</v>
       </c>
       <c r="C67" s="162" t="s">
         <v>371</v>
@@ -42023,7 +41995,7 @@
         <v>2372</v>
       </c>
       <c r="B68" s="199" t="s">
-        <v>2421</v>
+        <v>2419</v>
       </c>
       <c r="C68" s="160" t="s">
         <v>371</v>
@@ -42074,7 +42046,7 @@
         <v>2373</v>
       </c>
       <c r="B69" s="200" t="s">
-        <v>2422</v>
+        <v>2420</v>
       </c>
       <c r="C69" s="162" t="s">
         <v>371</v>
@@ -42455,7 +42427,7 @@
         <v>310</v>
       </c>
       <c r="J76" s="160" t="s">
-        <v>2417</v>
+        <v>2415</v>
       </c>
       <c r="K76" s="207" t="s">
         <v>390</v>
@@ -42635,7 +42607,7 @@
         <v>2384</v>
       </c>
       <c r="B80" s="199" t="s">
-        <v>2423</v>
+        <v>2622</v>
       </c>
       <c r="C80" s="160" t="s">
         <v>371</v>
@@ -42686,7 +42658,7 @@
         <v>2385</v>
       </c>
       <c r="B81" s="200" t="s">
-        <v>2424</v>
+        <v>2623</v>
       </c>
       <c r="C81" s="162" t="s">
         <v>371</v>
@@ -42737,7 +42709,7 @@
         <v>2386</v>
       </c>
       <c r="B82" s="199" t="s">
-        <v>2415</v>
+        <v>2624</v>
       </c>
       <c r="C82" s="160" t="s">
         <v>371</v>
@@ -42761,7 +42733,7 @@
         <v>310</v>
       </c>
       <c r="J82" s="160" t="s">
-        <v>2426</v>
+        <v>2422</v>
       </c>
       <c r="K82" s="207" t="s">
         <v>2281</v>
@@ -42779,7 +42751,7 @@
         <v>2397</v>
       </c>
       <c r="P82" s="174" t="s">
-        <v>2425</v>
+        <v>2421</v>
       </c>
       <c r="Q82" s="183"/>
     </row>
@@ -42787,8 +42759,8 @@
       <c r="A83" s="161" t="s">
         <v>2387</v>
       </c>
-      <c r="B83" s="202" t="s">
-        <v>2416</v>
+      <c r="B83" s="227" t="s">
+        <v>2625</v>
       </c>
       <c r="C83" s="163" t="s">
         <v>371</v>
@@ -42812,10 +42784,10 @@
         <v>310</v>
       </c>
       <c r="J83" s="163" t="s">
-        <v>2426</v>
+        <v>2422</v>
       </c>
       <c r="K83" s="177" t="s">
-        <v>2427</v>
+        <v>2423</v>
       </c>
       <c r="L83" s="209" t="s">
         <v>2277</v>
@@ -42836,10 +42808,10 @@
     </row>
     <row r="84" spans="1:17" s="148" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A84" s="206" t="s">
-        <v>2447</v>
+        <v>2443</v>
       </c>
       <c r="B84" s="226" t="s">
-        <v>2467</v>
+        <v>2463</v>
       </c>
       <c r="C84" s="160" t="s">
         <v>371</v>
@@ -42887,10 +42859,10 @@
     </row>
     <row r="85" spans="1:17" s="147" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A85" s="162" t="s">
-        <v>2446</v>
+        <v>2442</v>
       </c>
       <c r="B85" s="201" t="s">
-        <v>2468</v>
+        <v>2464</v>
       </c>
       <c r="C85" s="162" t="s">
         <v>371</v>
@@ -42929,7 +42901,7 @@
         <v>309</v>
       </c>
       <c r="O85" s="175" t="s">
-        <v>2496</v>
+        <v>2492</v>
       </c>
       <c r="P85" s="176" t="s">
         <v>2299</v>
@@ -42938,10 +42910,10 @@
     </row>
     <row r="86" spans="1:17" s="148" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A86" s="160" t="s">
-        <v>2448</v>
+        <v>2444</v>
       </c>
       <c r="B86" s="199" t="s">
-        <v>2469</v>
+        <v>2465</v>
       </c>
       <c r="C86" s="160" t="s">
         <v>371</v>
@@ -42965,7 +42937,7 @@
         <v>308</v>
       </c>
       <c r="J86" s="160" t="s">
-        <v>2438</v>
+        <v>2434</v>
       </c>
       <c r="K86" s="207">
         <v>2</v>
@@ -42980,19 +42952,19 @@
         <v>309</v>
       </c>
       <c r="O86" s="207" t="s">
-        <v>2443</v>
+        <v>2439</v>
       </c>
       <c r="P86" s="174" t="s">
-        <v>2505</v>
+        <v>2501</v>
       </c>
       <c r="Q86" s="228"/>
     </row>
     <row r="87" spans="1:17" s="147" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A87" s="162" t="s">
-        <v>2449</v>
+        <v>2445</v>
       </c>
       <c r="B87" s="200" t="s">
-        <v>2470</v>
+        <v>2466</v>
       </c>
       <c r="C87" s="162" t="s">
         <v>371</v>
@@ -43016,7 +42988,7 @@
         <v>308</v>
       </c>
       <c r="J87" s="162" t="s">
-        <v>2486</v>
+        <v>2482</v>
       </c>
       <c r="K87" s="175">
         <v>3</v>
@@ -43031,19 +43003,19 @@
         <v>309</v>
       </c>
       <c r="O87" s="208" t="s">
-        <v>2443</v>
+        <v>2439</v>
       </c>
       <c r="P87" s="176" t="s">
-        <v>2505</v>
+        <v>2501</v>
       </c>
       <c r="Q87" s="229"/>
     </row>
     <row r="88" spans="1:17" s="148" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A88" s="160" t="s">
-        <v>2450</v>
+        <v>2446</v>
       </c>
       <c r="B88" s="199" t="s">
-        <v>2471</v>
+        <v>2467</v>
       </c>
       <c r="C88" s="160" t="s">
         <v>371</v>
@@ -43082,7 +43054,7 @@
         <v>309</v>
       </c>
       <c r="O88" s="207" t="s">
-        <v>2497</v>
+        <v>2493</v>
       </c>
       <c r="P88" s="174" t="s">
         <v>2258</v>
@@ -43091,10 +43063,10 @@
     </row>
     <row r="89" spans="1:17" s="147" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A89" s="162" t="s">
-        <v>2451</v>
+        <v>2447</v>
       </c>
       <c r="B89" s="200" t="s">
-        <v>2474</v>
+        <v>2470</v>
       </c>
       <c r="C89" s="162" t="s">
         <v>371</v>
@@ -43133,7 +43105,7 @@
         <v>309</v>
       </c>
       <c r="O89" s="175" t="s">
-        <v>2498</v>
+        <v>2494</v>
       </c>
       <c r="P89" s="176" t="s">
         <v>2258</v>
@@ -43142,10 +43114,10 @@
     </row>
     <row r="90" spans="1:17" s="148" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A90" s="160" t="s">
-        <v>2452</v>
+        <v>2448</v>
       </c>
       <c r="B90" s="199" t="s">
-        <v>2472</v>
+        <v>2468</v>
       </c>
       <c r="C90" s="160" t="s">
         <v>371</v>
@@ -43169,7 +43141,7 @@
         <v>319</v>
       </c>
       <c r="J90" s="160" t="s">
-        <v>2489</v>
+        <v>2485</v>
       </c>
       <c r="K90" s="207" t="s">
         <v>2278</v>
@@ -43184,19 +43156,19 @@
         <v>309</v>
       </c>
       <c r="O90" s="207" t="s">
-        <v>2499</v>
+        <v>2495</v>
       </c>
       <c r="P90" s="174" t="s">
-        <v>2506</v>
+        <v>2502</v>
       </c>
       <c r="Q90" s="228"/>
     </row>
     <row r="91" spans="1:17" s="147" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A91" s="162" t="s">
-        <v>2453</v>
+        <v>2449</v>
       </c>
       <c r="B91" s="200" t="s">
-        <v>2473</v>
+        <v>2469</v>
       </c>
       <c r="C91" s="162" t="s">
         <v>371</v>
@@ -43220,7 +43192,7 @@
         <v>319</v>
       </c>
       <c r="J91" s="162" t="s">
-        <v>2489</v>
+        <v>2485</v>
       </c>
       <c r="K91" s="175" t="s">
         <v>2281</v>
@@ -43235,19 +43207,19 @@
         <v>309</v>
       </c>
       <c r="O91" s="208" t="s">
-        <v>2499</v>
+        <v>2495</v>
       </c>
       <c r="P91" s="176" t="s">
-        <v>2506</v>
+        <v>2502</v>
       </c>
       <c r="Q91" s="229"/>
     </row>
     <row r="92" spans="1:17" s="148" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A92" s="160" t="s">
-        <v>2454</v>
+        <v>2450</v>
       </c>
       <c r="B92" s="199" t="s">
-        <v>2475</v>
+        <v>2471</v>
       </c>
       <c r="C92" s="160" t="s">
         <v>371</v>
@@ -43259,7 +43231,7 @@
         <v>281</v>
       </c>
       <c r="F92" s="160" t="s">
-        <v>2605</v>
+        <v>2601</v>
       </c>
       <c r="G92" s="160">
         <v>1</v>
@@ -43271,7 +43243,7 @@
         <v>319</v>
       </c>
       <c r="J92" s="160" t="s">
-        <v>2487</v>
+        <v>2483</v>
       </c>
       <c r="K92" s="207">
         <v>2</v>
@@ -43286,19 +43258,19 @@
         <v>309</v>
       </c>
       <c r="O92" s="207" t="s">
-        <v>2500</v>
+        <v>2496</v>
       </c>
       <c r="P92" s="174" t="s">
-        <v>2507</v>
+        <v>2503</v>
       </c>
       <c r="Q92" s="228"/>
     </row>
     <row r="93" spans="1:17" s="147" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A93" s="162" t="s">
-        <v>2455</v>
+        <v>2451</v>
       </c>
       <c r="B93" s="201" t="s">
-        <v>2476</v>
+        <v>2472</v>
       </c>
       <c r="C93" s="162" t="s">
         <v>371</v>
@@ -43337,19 +43309,19 @@
         <v>309</v>
       </c>
       <c r="O93" s="208" t="s">
-        <v>2500</v>
+        <v>2496</v>
       </c>
       <c r="P93" s="176" t="s">
-        <v>2507</v>
+        <v>2503</v>
       </c>
       <c r="Q93" s="229"/>
     </row>
     <row r="94" spans="1:17" s="148" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A94" s="160" t="s">
-        <v>2456</v>
+        <v>2452</v>
       </c>
       <c r="B94" s="199" t="s">
-        <v>2477</v>
+        <v>2473</v>
       </c>
       <c r="C94" s="160" t="s">
         <v>371</v>
@@ -43370,10 +43342,10 @@
         <v>79</v>
       </c>
       <c r="I94" s="160" t="s">
-        <v>2558</v>
+        <v>2554</v>
       </c>
       <c r="J94" s="160" t="s">
-        <v>2491</v>
+        <v>2487</v>
       </c>
       <c r="K94" s="207" t="s">
         <v>2274</v>
@@ -43388,19 +43360,19 @@
         <v>309</v>
       </c>
       <c r="O94" s="207" t="s">
-        <v>2501</v>
+        <v>2497</v>
       </c>
       <c r="P94" s="174" t="s">
-        <v>2510</v>
+        <v>2506</v>
       </c>
       <c r="Q94" s="228"/>
     </row>
     <row r="95" spans="1:17" s="147" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A95" s="162" t="s">
-        <v>2457</v>
+        <v>2453</v>
       </c>
       <c r="B95" s="201" t="s">
-        <v>2625</v>
+        <v>2621</v>
       </c>
       <c r="C95" s="162" t="s">
         <v>371</v>
@@ -43424,10 +43396,10 @@
         <v>310</v>
       </c>
       <c r="J95" s="162" t="s">
-        <v>2491</v>
+        <v>2487</v>
       </c>
       <c r="K95" s="175" t="s">
-        <v>2492</v>
+        <v>2488</v>
       </c>
       <c r="L95" s="208" t="s">
         <v>2277</v>
@@ -43439,19 +43411,19 @@
         <v>309</v>
       </c>
       <c r="O95" s="208" t="s">
-        <v>2501</v>
+        <v>2497</v>
       </c>
       <c r="P95" s="176" t="s">
-        <v>2509</v>
+        <v>2505</v>
       </c>
       <c r="Q95" s="229"/>
     </row>
     <row r="96" spans="1:17" s="148" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A96" s="160" t="s">
-        <v>2458</v>
+        <v>2454</v>
       </c>
       <c r="B96" s="199" t="s">
-        <v>2478</v>
+        <v>2474</v>
       </c>
       <c r="C96" s="160" t="s">
         <v>371</v>
@@ -43488,19 +43460,19 @@
         <v>309</v>
       </c>
       <c r="O96" s="207" t="s">
-        <v>2502</v>
+        <v>2498</v>
       </c>
       <c r="P96" s="232" t="s">
-        <v>2511</v>
+        <v>2507</v>
       </c>
       <c r="Q96" s="228"/>
     </row>
     <row r="97" spans="1:17" s="147" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A97" s="162" t="s">
-        <v>2459</v>
+        <v>2455</v>
       </c>
       <c r="B97" s="200" t="s">
-        <v>2479</v>
+        <v>2475</v>
       </c>
       <c r="C97" s="162" t="s">
         <v>371</v>
@@ -43537,19 +43509,19 @@
         <v>309</v>
       </c>
       <c r="O97" s="175" t="s">
-        <v>2503</v>
+        <v>2499</v>
       </c>
       <c r="P97" s="210" t="s">
-        <v>2512</v>
+        <v>2508</v>
       </c>
       <c r="Q97" s="229"/>
     </row>
     <row r="98" spans="1:17" s="148" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A98" s="160" t="s">
-        <v>2460</v>
+        <v>2456</v>
       </c>
       <c r="B98" s="199" t="s">
-        <v>2480</v>
+        <v>2476</v>
       </c>
       <c r="C98" s="160" t="s">
         <v>371</v>
@@ -43573,7 +43545,7 @@
         <v>319</v>
       </c>
       <c r="J98" s="160" t="s">
-        <v>2513</v>
+        <v>2509</v>
       </c>
       <c r="K98" s="207">
         <v>1</v>
@@ -43591,16 +43563,16 @@
         <v>2293</v>
       </c>
       <c r="P98" s="174" t="s">
-        <v>2514</v>
+        <v>2510</v>
       </c>
       <c r="Q98" s="228"/>
     </row>
     <row r="99" spans="1:17" s="147" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A99" s="162" t="s">
-        <v>2461</v>
+        <v>2457</v>
       </c>
       <c r="B99" s="201" t="s">
-        <v>2481</v>
+        <v>2477</v>
       </c>
       <c r="C99" s="162" t="s">
         <v>371</v>
@@ -43621,7 +43593,7 @@
         <v>79</v>
       </c>
       <c r="I99" s="162" t="s">
-        <v>2559</v>
+        <v>2555</v>
       </c>
       <c r="J99" s="162" t="s">
         <v>407</v>
@@ -43639,19 +43611,19 @@
         <v>309</v>
       </c>
       <c r="O99" s="175" t="s">
-        <v>2504</v>
+        <v>2500</v>
       </c>
       <c r="P99" s="176" t="s">
-        <v>2514</v>
+        <v>2510</v>
       </c>
       <c r="Q99" s="229"/>
     </row>
     <row r="100" spans="1:17" s="148" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A100" s="160" t="s">
-        <v>2462</v>
+        <v>2458</v>
       </c>
       <c r="B100" s="199" t="s">
-        <v>2482</v>
+        <v>2478</v>
       </c>
       <c r="C100" s="160" t="s">
         <v>371</v>
@@ -43672,10 +43644,10 @@
         <v>79</v>
       </c>
       <c r="I100" s="160" t="s">
-        <v>2557</v>
+        <v>2553</v>
       </c>
       <c r="J100" s="160" t="s">
-        <v>2515</v>
+        <v>2511</v>
       </c>
       <c r="K100" s="160">
         <v>1</v>
@@ -43690,19 +43662,19 @@
         <v>309</v>
       </c>
       <c r="O100" s="207" t="s">
-        <v>2431</v>
+        <v>2427</v>
       </c>
       <c r="P100" s="174" t="s">
-        <v>2516</v>
+        <v>2512</v>
       </c>
       <c r="Q100" s="228"/>
     </row>
     <row r="101" spans="1:17" s="147" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A101" s="162" t="s">
-        <v>2463</v>
+        <v>2459</v>
       </c>
       <c r="B101" s="201" t="s">
-        <v>2483</v>
+        <v>2479</v>
       </c>
       <c r="C101" s="162" t="s">
         <v>371</v>
@@ -43714,7 +43686,7 @@
         <v>281</v>
       </c>
       <c r="F101" s="162" t="s">
-        <v>2604</v>
+        <v>2600</v>
       </c>
       <c r="G101" s="162">
         <v>2</v>
@@ -43741,19 +43713,19 @@
         <v>309</v>
       </c>
       <c r="O101" s="208" t="s">
-        <v>2431</v>
+        <v>2427</v>
       </c>
       <c r="P101" s="176" t="s">
-        <v>2516</v>
+        <v>2512</v>
       </c>
       <c r="Q101" s="229"/>
     </row>
     <row r="102" spans="1:17" s="148" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A102" s="160" t="s">
-        <v>2464</v>
+        <v>2460</v>
       </c>
       <c r="B102" s="199" t="s">
-        <v>2484</v>
+        <v>2480</v>
       </c>
       <c r="C102" s="160" t="s">
         <v>371</v>
@@ -43777,7 +43749,7 @@
         <v>319</v>
       </c>
       <c r="J102" s="160" t="s">
-        <v>2488</v>
+        <v>2484</v>
       </c>
       <c r="K102" s="207" t="s">
         <v>2278</v>
@@ -43792,19 +43764,19 @@
         <v>309</v>
       </c>
       <c r="O102" s="207" t="s">
-        <v>2497</v>
+        <v>2493</v>
       </c>
       <c r="P102" s="174" t="s">
-        <v>2517</v>
+        <v>2513</v>
       </c>
       <c r="Q102" s="228"/>
     </row>
     <row r="103" spans="1:17" s="147" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A103" s="161" t="s">
-        <v>2465</v>
+        <v>2461</v>
       </c>
       <c r="B103" s="227" t="s">
-        <v>2485</v>
+        <v>2481</v>
       </c>
       <c r="C103" s="163" t="s">
         <v>371</v>
@@ -43828,10 +43800,10 @@
         <v>319</v>
       </c>
       <c r="J103" s="163" t="s">
-        <v>2488</v>
+        <v>2484</v>
       </c>
       <c r="K103" s="177" t="s">
-        <v>2495</v>
+        <v>2491</v>
       </c>
       <c r="L103" s="209" t="s">
         <v>2277</v>
@@ -43843,19 +43815,19 @@
         <v>309</v>
       </c>
       <c r="O103" s="177" t="s">
-        <v>2499</v>
+        <v>2495</v>
       </c>
       <c r="P103" s="178" t="s">
-        <v>2518</v>
+        <v>2514</v>
       </c>
       <c r="Q103" s="230"/>
     </row>
     <row r="104" spans="1:17" s="148" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A104" s="206" t="s">
-        <v>2519</v>
+        <v>2515</v>
       </c>
       <c r="B104" s="233" t="s">
-        <v>2621</v>
+        <v>2617</v>
       </c>
       <c r="C104" s="160" t="s">
         <v>371</v>
@@ -43867,7 +43839,7 @@
         <v>372</v>
       </c>
       <c r="F104" s="160" t="s">
-        <v>2604</v>
+        <v>2600</v>
       </c>
       <c r="G104" s="160">
         <v>1</v>
@@ -43876,16 +43848,16 @@
         <v>79</v>
       </c>
       <c r="I104" s="160" t="s">
+        <v>2553</v>
+      </c>
+      <c r="J104" s="160" t="s">
         <v>2557</v>
       </c>
-      <c r="J104" s="160" t="s">
-        <v>2561</v>
-      </c>
       <c r="K104" s="207" t="s">
-        <v>2562</v>
+        <v>2558</v>
       </c>
       <c r="L104" s="207" t="s">
-        <v>2560</v>
+        <v>2556</v>
       </c>
       <c r="M104" s="207">
         <v>3</v>
@@ -43894,19 +43866,19 @@
         <v>309</v>
       </c>
       <c r="O104" s="207" t="s">
-        <v>2597</v>
+        <v>2593</v>
       </c>
       <c r="P104" s="174" t="s">
-        <v>2577</v>
+        <v>2573</v>
       </c>
       <c r="Q104" s="183"/>
     </row>
     <row r="105" spans="1:17" s="147" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A105" s="162" t="s">
-        <v>2520</v>
+        <v>2516</v>
       </c>
       <c r="B105" s="234" t="s">
-        <v>2622</v>
+        <v>2618</v>
       </c>
       <c r="C105" s="162" t="s">
         <v>371</v>
@@ -43930,13 +43902,13 @@
         <v>308</v>
       </c>
       <c r="J105" s="162" t="s">
-        <v>2561</v>
+        <v>2557</v>
       </c>
       <c r="K105" s="175" t="s">
-        <v>2563</v>
+        <v>2559</v>
       </c>
       <c r="L105" s="208" t="s">
-        <v>2560</v>
+        <v>2556</v>
       </c>
       <c r="M105" s="208">
         <v>3</v>
@@ -43945,19 +43917,19 @@
         <v>309</v>
       </c>
       <c r="O105" s="175" t="s">
-        <v>2598</v>
+        <v>2594</v>
       </c>
       <c r="P105" s="176" t="s">
-        <v>2578</v>
+        <v>2574</v>
       </c>
       <c r="Q105" s="184"/>
     </row>
     <row r="106" spans="1:17" s="148" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A106" s="160" t="s">
-        <v>2521</v>
+        <v>2517</v>
       </c>
       <c r="B106" s="235" t="s">
-        <v>2539</v>
+        <v>2535</v>
       </c>
       <c r="C106" s="160" t="s">
         <v>371</v>
@@ -43981,13 +43953,13 @@
         <v>310</v>
       </c>
       <c r="J106" s="160" t="s">
-        <v>2565</v>
+        <v>2561</v>
       </c>
       <c r="K106" s="207" t="s">
-        <v>2566</v>
+        <v>2562</v>
       </c>
       <c r="L106" s="207" t="s">
-        <v>2560</v>
+        <v>2556</v>
       </c>
       <c r="M106" s="207">
         <v>3</v>
@@ -43996,19 +43968,19 @@
         <v>309</v>
       </c>
       <c r="O106" s="207" t="s">
-        <v>2599</v>
+        <v>2595</v>
       </c>
       <c r="P106" s="174" t="s">
-        <v>2579</v>
+        <v>2575</v>
       </c>
       <c r="Q106" s="183"/>
     </row>
     <row r="107" spans="1:17" s="147" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A107" s="162" t="s">
-        <v>2522</v>
+        <v>2518</v>
       </c>
       <c r="B107" s="234" t="s">
-        <v>2540</v>
+        <v>2536</v>
       </c>
       <c r="C107" s="162" t="s">
         <v>371</v>
@@ -44035,10 +44007,10 @@
         <v>475</v>
       </c>
       <c r="K107" s="175" t="s">
-        <v>2567</v>
+        <v>2563</v>
       </c>
       <c r="L107" s="208" t="s">
-        <v>2560</v>
+        <v>2556</v>
       </c>
       <c r="M107" s="208">
         <v>3</v>
@@ -44047,19 +44019,19 @@
         <v>309</v>
       </c>
       <c r="O107" s="175" t="s">
-        <v>2600</v>
+        <v>2596</v>
       </c>
       <c r="P107" s="176" t="s">
-        <v>2579</v>
+        <v>2575</v>
       </c>
       <c r="Q107" s="184"/>
     </row>
     <row r="108" spans="1:17" s="148" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A108" s="160" t="s">
-        <v>2523</v>
+        <v>2519</v>
       </c>
       <c r="B108" s="235" t="s">
-        <v>2541</v>
+        <v>2537</v>
       </c>
       <c r="C108" s="160" t="s">
         <v>371</v>
@@ -44080,16 +44052,16 @@
         <v>95</v>
       </c>
       <c r="I108" s="160" t="s">
-        <v>2557</v>
+        <v>2553</v>
       </c>
       <c r="J108" s="160" t="s">
-        <v>2570</v>
+        <v>2566</v>
       </c>
       <c r="K108" s="207" t="s">
-        <v>2568</v>
+        <v>2564</v>
       </c>
       <c r="L108" s="207" t="s">
-        <v>2560</v>
+        <v>2556</v>
       </c>
       <c r="M108" s="207">
         <v>3</v>
@@ -44098,19 +44070,19 @@
         <v>309</v>
       </c>
       <c r="O108" s="207" t="s">
-        <v>2601</v>
+        <v>2597</v>
       </c>
       <c r="P108" s="174" t="s">
-        <v>2580</v>
+        <v>2576</v>
       </c>
       <c r="Q108" s="183"/>
     </row>
     <row r="109" spans="1:17" s="147" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A109" s="162" t="s">
-        <v>2524</v>
+        <v>2520</v>
       </c>
       <c r="B109" s="234" t="s">
-        <v>2542</v>
+        <v>2538</v>
       </c>
       <c r="C109" s="162" t="s">
         <v>371</v>
@@ -44134,13 +44106,13 @@
         <v>308</v>
       </c>
       <c r="J109" s="162" t="s">
-        <v>2570</v>
+        <v>2566</v>
       </c>
       <c r="K109" s="175" t="s">
-        <v>2569</v>
+        <v>2565</v>
       </c>
       <c r="L109" s="208" t="s">
-        <v>2560</v>
+        <v>2556</v>
       </c>
       <c r="M109" s="208">
         <v>3</v>
@@ -44149,19 +44121,19 @@
         <v>309</v>
       </c>
       <c r="O109" s="175" t="s">
-        <v>2602</v>
+        <v>2598</v>
       </c>
       <c r="P109" s="176" t="s">
-        <v>2580</v>
+        <v>2576</v>
       </c>
       <c r="Q109" s="184"/>
     </row>
     <row r="110" spans="1:17" s="148" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A110" s="160" t="s">
-        <v>2525</v>
+        <v>2521</v>
       </c>
       <c r="B110" s="235" t="s">
-        <v>2543</v>
+        <v>2539</v>
       </c>
       <c r="C110" s="160" t="s">
         <v>371</v>
@@ -44170,7 +44142,7 @@
         <v>375</v>
       </c>
       <c r="E110" s="160" t="s">
-        <v>2556</v>
+        <v>2552</v>
       </c>
       <c r="F110" s="160" t="s">
         <v>282</v>
@@ -44185,7 +44157,7 @@
         <v>308</v>
       </c>
       <c r="J110" s="160" t="s">
-        <v>2581</v>
+        <v>2577</v>
       </c>
       <c r="K110" s="207">
         <v>1</v>
@@ -44200,19 +44172,19 @@
         <v>309</v>
       </c>
       <c r="O110" s="207" t="s">
-        <v>2603</v>
+        <v>2599</v>
       </c>
       <c r="P110" s="174" t="s">
-        <v>2582</v>
+        <v>2578</v>
       </c>
       <c r="Q110" s="183"/>
     </row>
     <row r="111" spans="1:17" s="147" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A111" s="162" t="s">
-        <v>2526</v>
+        <v>2522</v>
       </c>
       <c r="B111" s="234" t="s">
-        <v>2544</v>
+        <v>2540</v>
       </c>
       <c r="C111" s="162" t="s">
         <v>371</v>
@@ -44251,19 +44223,19 @@
         <v>309</v>
       </c>
       <c r="O111" s="208" t="s">
-        <v>2603</v>
+        <v>2599</v>
       </c>
       <c r="P111" s="176" t="s">
-        <v>2583</v>
+        <v>2579</v>
       </c>
       <c r="Q111" s="184"/>
     </row>
     <row r="112" spans="1:17" s="148" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A112" s="160" t="s">
-        <v>2527</v>
+        <v>2523</v>
       </c>
       <c r="B112" s="235" t="s">
-        <v>2545</v>
+        <v>2541</v>
       </c>
       <c r="C112" s="160" t="s">
         <v>371</v>
@@ -44287,7 +44259,7 @@
         <v>310</v>
       </c>
       <c r="J112" s="160" t="s">
-        <v>2571</v>
+        <v>2567</v>
       </c>
       <c r="K112" s="207">
         <v>4</v>
@@ -44302,19 +44274,19 @@
         <v>309</v>
       </c>
       <c r="O112" s="207" t="s">
-        <v>2606</v>
+        <v>2602</v>
       </c>
       <c r="P112" s="174" t="s">
-        <v>2584</v>
+        <v>2580</v>
       </c>
       <c r="Q112" s="183"/>
     </row>
     <row r="113" spans="1:17" s="147" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A113" s="162" t="s">
-        <v>2528</v>
+        <v>2524</v>
       </c>
       <c r="B113" s="234" t="s">
-        <v>2546</v>
+        <v>2542</v>
       </c>
       <c r="C113" s="162" t="s">
         <v>371</v>
@@ -44338,7 +44310,7 @@
         <v>310</v>
       </c>
       <c r="J113" s="162" t="s">
-        <v>2571</v>
+        <v>2567</v>
       </c>
       <c r="K113" s="175">
         <v>6</v>
@@ -44353,19 +44325,19 @@
         <v>309</v>
       </c>
       <c r="O113" s="175" t="s">
-        <v>2607</v>
+        <v>2603</v>
       </c>
       <c r="P113" s="176" t="s">
-        <v>2508</v>
+        <v>2504</v>
       </c>
       <c r="Q113" s="184"/>
     </row>
     <row r="114" spans="1:17" s="148" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A114" s="160" t="s">
-        <v>2529</v>
+        <v>2525</v>
       </c>
       <c r="B114" s="235" t="s">
-        <v>2547</v>
+        <v>2543</v>
       </c>
       <c r="C114" s="160" t="s">
         <v>371</v>
@@ -44386,10 +44358,10 @@
         <v>95</v>
       </c>
       <c r="I114" s="160" t="s">
-        <v>2559</v>
+        <v>2555</v>
       </c>
       <c r="J114" s="160" t="s">
-        <v>2585</v>
+        <v>2581</v>
       </c>
       <c r="K114" s="207">
         <v>2</v>
@@ -44404,19 +44376,19 @@
         <v>309</v>
       </c>
       <c r="O114" s="207" t="s">
-        <v>2608</v>
+        <v>2604</v>
       </c>
       <c r="P114" s="174" t="s">
-        <v>2586</v>
+        <v>2582</v>
       </c>
       <c r="Q114" s="183"/>
     </row>
     <row r="115" spans="1:17" s="147" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A115" s="162" t="s">
-        <v>2530</v>
+        <v>2526</v>
       </c>
       <c r="B115" s="234" t="s">
-        <v>2548</v>
+        <v>2544</v>
       </c>
       <c r="C115" s="162" t="s">
         <v>371</v>
@@ -44455,19 +44427,19 @@
         <v>309</v>
       </c>
       <c r="O115" s="208" t="s">
-        <v>2608</v>
+        <v>2604</v>
       </c>
       <c r="P115" s="176" t="s">
-        <v>2586</v>
+        <v>2582</v>
       </c>
       <c r="Q115" s="184"/>
     </row>
     <row r="116" spans="1:17" s="148" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A116" s="160" t="s">
-        <v>2531</v>
+        <v>2527</v>
       </c>
       <c r="B116" s="235" t="s">
-        <v>2623</v>
+        <v>2619</v>
       </c>
       <c r="C116" s="160" t="s">
         <v>371</v>
@@ -44476,7 +44448,7 @@
         <v>374</v>
       </c>
       <c r="E116" s="160" t="s">
-        <v>2556</v>
+        <v>2552</v>
       </c>
       <c r="F116" s="160" t="s">
         <v>296</v>
@@ -44491,7 +44463,7 @@
         <v>308</v>
       </c>
       <c r="J116" s="160" t="s">
-        <v>2572</v>
+        <v>2568</v>
       </c>
       <c r="K116" s="207">
         <v>1</v>
@@ -44506,19 +44478,19 @@
         <v>309</v>
       </c>
       <c r="O116" s="207" t="s">
-        <v>2609</v>
+        <v>2605</v>
       </c>
       <c r="P116" s="174" t="s">
-        <v>2587</v>
+        <v>2583</v>
       </c>
       <c r="Q116" s="183"/>
     </row>
     <row r="117" spans="1:17" s="147" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A117" s="162" t="s">
-        <v>2532</v>
+        <v>2528</v>
       </c>
       <c r="B117" s="234" t="s">
-        <v>2624</v>
+        <v>2620</v>
       </c>
       <c r="C117" s="162" t="s">
         <v>371</v>
@@ -44542,7 +44514,7 @@
         <v>308</v>
       </c>
       <c r="J117" s="162" t="s">
-        <v>2572</v>
+        <v>2568</v>
       </c>
       <c r="K117" s="208">
         <v>1</v>
@@ -44557,19 +44529,19 @@
         <v>309</v>
       </c>
       <c r="O117" s="208" t="s">
-        <v>2609</v>
+        <v>2605</v>
       </c>
       <c r="P117" s="176" t="s">
-        <v>2587</v>
+        <v>2583</v>
       </c>
       <c r="Q117" s="184"/>
     </row>
     <row r="118" spans="1:17" s="148" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A118" s="160" t="s">
-        <v>2533</v>
+        <v>2529</v>
       </c>
       <c r="B118" s="235" t="s">
-        <v>2549</v>
+        <v>2545</v>
       </c>
       <c r="C118" s="160" t="s">
         <v>371</v>
@@ -44578,7 +44550,7 @@
         <v>374</v>
       </c>
       <c r="E118" s="160" t="s">
-        <v>2556</v>
+        <v>2552</v>
       </c>
       <c r="F118" s="160" t="s">
         <v>299</v>
@@ -44593,13 +44565,13 @@
         <v>310</v>
       </c>
       <c r="J118" s="160" t="s">
-        <v>2574</v>
+        <v>2570</v>
       </c>
       <c r="K118" s="207" t="s">
-        <v>2568</v>
+        <v>2564</v>
       </c>
       <c r="L118" s="207" t="s">
-        <v>2560</v>
+        <v>2556</v>
       </c>
       <c r="M118" s="207">
         <v>5</v>
@@ -44608,19 +44580,19 @@
         <v>309</v>
       </c>
       <c r="O118" s="207" t="s">
-        <v>2600</v>
+        <v>2596</v>
       </c>
       <c r="P118" s="174" t="s">
-        <v>2588</v>
+        <v>2584</v>
       </c>
       <c r="Q118" s="183"/>
     </row>
     <row r="119" spans="1:17" s="147" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A119" s="162" t="s">
-        <v>2534</v>
+        <v>2530</v>
       </c>
       <c r="B119" s="234" t="s">
-        <v>2550</v>
+        <v>2546</v>
       </c>
       <c r="C119" s="162" t="s">
         <v>371</v>
@@ -44644,13 +44616,13 @@
         <v>310</v>
       </c>
       <c r="J119" s="162" t="s">
-        <v>2574</v>
+        <v>2570</v>
       </c>
       <c r="K119" s="208" t="s">
-        <v>2568</v>
+        <v>2564</v>
       </c>
       <c r="L119" s="208" t="s">
-        <v>2560</v>
+        <v>2556</v>
       </c>
       <c r="M119" s="175">
         <v>4</v>
@@ -44659,19 +44631,19 @@
         <v>309</v>
       </c>
       <c r="O119" s="175" t="s">
-        <v>2610</v>
+        <v>2606</v>
       </c>
       <c r="P119" s="176" t="s">
-        <v>2589</v>
+        <v>2585</v>
       </c>
       <c r="Q119" s="184"/>
     </row>
     <row r="120" spans="1:17" s="148" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A120" s="160" t="s">
-        <v>2535</v>
+        <v>2531</v>
       </c>
       <c r="B120" s="235" t="s">
-        <v>2551</v>
+        <v>2547</v>
       </c>
       <c r="C120" s="160" t="s">
         <v>371</v>
@@ -44695,7 +44667,7 @@
         <v>319</v>
       </c>
       <c r="J120" s="160" t="s">
-        <v>2575</v>
+        <v>2571</v>
       </c>
       <c r="K120" s="207">
         <v>2</v>
@@ -44710,19 +44682,19 @@
         <v>309</v>
       </c>
       <c r="O120" s="207" t="s">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="P120" s="174" t="s">
-        <v>2590</v>
+        <v>2586</v>
       </c>
       <c r="Q120" s="183"/>
     </row>
     <row r="121" spans="1:17" s="147" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A121" s="162" t="s">
-        <v>2536</v>
+        <v>2532</v>
       </c>
       <c r="B121" s="234" t="s">
-        <v>2552</v>
+        <v>2548</v>
       </c>
       <c r="C121" s="162" t="s">
         <v>371</v>
@@ -44746,7 +44718,7 @@
         <v>319</v>
       </c>
       <c r="J121" s="162" t="s">
-        <v>2575</v>
+        <v>2571</v>
       </c>
       <c r="K121" s="208">
         <v>2</v>
@@ -44761,19 +44733,19 @@
         <v>309</v>
       </c>
       <c r="O121" s="175" t="s">
-        <v>2613</v>
+        <v>2609</v>
       </c>
       <c r="P121" s="176" t="s">
-        <v>2590</v>
+        <v>2586</v>
       </c>
       <c r="Q121" s="184"/>
     </row>
     <row r="122" spans="1:17" s="148" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A122" s="160" t="s">
-        <v>2537</v>
+        <v>2533</v>
       </c>
       <c r="B122" s="235" t="s">
-        <v>2553</v>
+        <v>2549</v>
       </c>
       <c r="C122" s="160" t="s">
         <v>371</v>
@@ -44782,7 +44754,7 @@
         <v>2261</v>
       </c>
       <c r="E122" s="160" t="s">
-        <v>2555</v>
+        <v>2551</v>
       </c>
       <c r="F122" s="160" t="s">
         <v>299</v>
@@ -44794,10 +44766,10 @@
         <v>95</v>
       </c>
       <c r="I122" s="160" t="s">
-        <v>2558</v>
+        <v>2554</v>
       </c>
       <c r="J122" s="160" t="s">
-        <v>2576</v>
+        <v>2572</v>
       </c>
       <c r="K122" s="207">
         <v>1</v>
@@ -44812,19 +44784,19 @@
         <v>309</v>
       </c>
       <c r="O122" s="207" t="s">
-        <v>2612</v>
+        <v>2608</v>
       </c>
       <c r="P122" s="238" t="s">
-        <v>2591</v>
+        <v>2587</v>
       </c>
       <c r="Q122" s="183"/>
     </row>
     <row r="123" spans="1:17" s="147" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A123" s="161" t="s">
-        <v>2538</v>
+        <v>2534</v>
       </c>
       <c r="B123" s="236" t="s">
-        <v>2554</v>
+        <v>2550</v>
       </c>
       <c r="C123" s="163" t="s">
         <v>371</v>
@@ -44848,7 +44820,7 @@
         <v>310</v>
       </c>
       <c r="J123" s="163" t="s">
-        <v>2576</v>
+        <v>2572</v>
       </c>
       <c r="K123" s="209">
         <v>1</v>
@@ -44863,10 +44835,10 @@
         <v>309</v>
       </c>
       <c r="O123" s="177" t="s">
-        <v>2611</v>
+        <v>2607</v>
       </c>
       <c r="P123" s="239" t="s">
-        <v>2592</v>
+        <v>2588</v>
       </c>
       <c r="Q123" s="185"/>
     </row>
@@ -50232,7 +50204,7 @@
     </row>
     <row r="10" spans="1:7" ht="16.5" customHeight="1">
       <c r="A10" s="42" t="s">
-        <v>2564</v>
+        <v>2560</v>
       </c>
       <c r="B10" s="37" t="s">
         <v>617</v>
@@ -52868,10 +52840,10 @@
     </row>
     <row r="136" spans="1:7" ht="16.5" customHeight="1">
       <c r="A136" s="231" t="s">
-        <v>2487</v>
+        <v>2483</v>
       </c>
       <c r="B136" s="225" t="s">
-        <v>2466</v>
+        <v>2462</v>
       </c>
       <c r="C136" s="132" t="s">
         <v>652</v>
@@ -52985,7 +52957,7 @@
     </row>
     <row r="142" spans="1:7" ht="16.5" customHeight="1">
       <c r="A142" s="224" t="s">
-        <v>2437</v>
+        <v>2433</v>
       </c>
       <c r="B142" s="30" t="s">
         <v>1095</v>
@@ -53002,7 +52974,7 @@
     </row>
     <row r="143" spans="1:7" ht="16.5" customHeight="1">
       <c r="A143" s="224" t="s">
-        <v>2572</v>
+        <v>2568</v>
       </c>
       <c r="B143" s="30" t="s">
         <v>1097</v>
@@ -53104,7 +53076,7 @@
     </row>
     <row r="149" spans="1:7" ht="16.5" customHeight="1">
       <c r="A149" s="237" t="s">
-        <v>2575</v>
+        <v>2571</v>
       </c>
       <c r="B149" s="115" t="s">
         <v>1111</v>
@@ -53121,7 +53093,7 @@
     </row>
     <row r="150" spans="1:7" ht="16.5" customHeight="1">
       <c r="A150" s="237" t="s">
-        <v>2576</v>
+        <v>2572</v>
       </c>
       <c r="B150" s="115" t="s">
         <v>1113</v>
@@ -53258,7 +53230,7 @@
     </row>
     <row r="157" spans="1:7" ht="16.5" customHeight="1">
       <c r="A157" s="218" t="s">
-        <v>2493</v>
+        <v>2489</v>
       </c>
       <c r="B157" s="30" t="s">
         <v>1137</v>
@@ -53298,7 +53270,7 @@
     </row>
     <row r="159" spans="1:7" ht="16.5" customHeight="1">
       <c r="A159" s="218" t="s">
-        <v>2494</v>
+        <v>2490</v>
       </c>
       <c r="B159" s="30" t="s">
         <v>1106</v>
@@ -53318,7 +53290,7 @@
     </row>
     <row r="160" spans="1:7" ht="16.5" customHeight="1">
       <c r="A160" s="218" t="s">
-        <v>2490</v>
+        <v>2486</v>
       </c>
       <c r="B160" s="30" t="s">
         <v>1145</v>
@@ -53358,7 +53330,7 @@
     </row>
     <row r="162" spans="1:7" ht="16.5" customHeight="1">
       <c r="A162" s="218" t="s">
-        <v>2573</v>
+        <v>2569</v>
       </c>
       <c r="B162" s="30" t="s">
         <v>1151</v>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erang\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{746E71DD-6512-4E4E-A8EF-9B0331CB2054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EACA0F46-98F2-4B56-BDD4-FDFED4A8DA39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5813" uniqueCount="2626">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5813" uniqueCount="2624">
   <si>
     <t>캐릭터ID</t>
   </si>
@@ -20996,78 +20996,6 @@
     <phoneticPr fontId="27" type="noConversion"/>
   </si>
   <si>
-    <t>그림자 올가미</t>
-    <phoneticPr fontId="27" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>그림자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>올가미+</t>
-    </r>
-    <phoneticPr fontId="27" type="noConversion"/>
-  </si>
-  <si>
-    <t>인도하는 불빛</t>
-    <phoneticPr fontId="27" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>인도하는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>불빛+</t>
-    </r>
-    <phoneticPr fontId="27" type="noConversion"/>
-  </si>
-  <si>
     <t>극성맹독</t>
     <phoneticPr fontId="27" type="noConversion"/>
   </si>
@@ -21200,9 +21128,6 @@
     <phoneticPr fontId="27" type="noConversion"/>
   </si>
   <si>
-    <t>{E_Strike} {ValueRate1}</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">{E_Strike} {ValueRate1} / </t>
     </r>
@@ -21995,10 +21920,6 @@
     <phoneticPr fontId="27" type="noConversion"/>
   </si>
   <si>
-    <t>{E_Strike} {ValueRate1}</t>
-    <phoneticPr fontId="27" type="noConversion"/>
-  </si>
-  <si>
     <t>E_Vulnerable</t>
     <phoneticPr fontId="27" type="noConversion"/>
   </si>
@@ -22751,6 +22672,50 @@
   </si>
   <si>
     <t>함께 휴식한다.</t>
+    <phoneticPr fontId="27" type="noConversion"/>
+  </si>
+  <si>
+    <t>니아의 불꽃</t>
+    <phoneticPr fontId="27" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>니아의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>불꽃+</t>
+    </r>
+    <phoneticPr fontId="27" type="noConversion"/>
+  </si>
+  <si>
+    <t>니아의 속삭임</t>
+    <phoneticPr fontId="27" type="noConversion"/>
+  </si>
+  <si>
+    <t>니아의 속삭임+</t>
     <phoneticPr fontId="27" type="noConversion"/>
   </si>
 </sst>
@@ -38843,7 +38808,7 @@
         <v>65</v>
       </c>
       <c r="B6" s="198" t="s">
-        <v>2604</v>
+        <v>2598</v>
       </c>
       <c r="C6" s="153" t="s">
         <v>288</v>
@@ -38949,7 +38914,7 @@
         <v>81</v>
       </c>
       <c r="B8" s="197" t="s">
-        <v>2605</v>
+        <v>2599</v>
       </c>
       <c r="C8" s="153" t="s">
         <v>288</v>
@@ -39900,10 +39865,10 @@
     </row>
     <row r="26" spans="1:17" ht="19.899999999999999" customHeight="1" thickBot="1">
       <c r="A26" s="152" t="s">
-        <v>2608</v>
+        <v>2602</v>
       </c>
       <c r="B26" s="198" t="s">
-        <v>2609</v>
+        <v>2603</v>
       </c>
       <c r="C26" s="153" t="s">
         <v>331</v>
@@ -39956,7 +39921,7 @@
         <v>338</v>
       </c>
       <c r="B27" s="242" t="s">
-        <v>2610</v>
+        <v>2604</v>
       </c>
       <c r="C27" s="157" t="s">
         <v>331</v>
@@ -40221,7 +40186,7 @@
         <v>85</v>
       </c>
       <c r="B32" s="221" t="s">
-        <v>2620</v>
+        <v>2614</v>
       </c>
       <c r="C32" s="153" t="s">
         <v>331</v>
@@ -40263,7 +40228,7 @@
         <v>350</v>
       </c>
       <c r="P32" s="166" t="s">
-        <v>2622</v>
+        <v>2616</v>
       </c>
       <c r="Q32" s="181">
         <v>0</v>
@@ -40274,7 +40239,7 @@
         <v>351</v>
       </c>
       <c r="B33" s="243" t="s">
-        <v>2621</v>
+        <v>2615</v>
       </c>
       <c r="C33" s="157" t="s">
         <v>331</v>
@@ -40316,7 +40281,7 @@
         <v>318</v>
       </c>
       <c r="P33" s="171" t="s">
-        <v>2622</v>
+        <v>2616</v>
       </c>
       <c r="Q33" s="182">
         <v>0</v>
@@ -40563,13 +40528,13 @@
         <v>310</v>
       </c>
       <c r="J38" s="153" t="s">
-        <v>2583</v>
+        <v>2577</v>
       </c>
       <c r="K38" s="153" t="s">
-        <v>2584</v>
+        <v>2578</v>
       </c>
       <c r="L38" s="153" t="s">
-        <v>2550</v>
+        <v>2545</v>
       </c>
       <c r="M38" s="153">
         <v>3</v>
@@ -40578,7 +40543,7 @@
         <v>309</v>
       </c>
       <c r="O38" s="153" t="s">
-        <v>2586</v>
+        <v>2580</v>
       </c>
       <c r="P38" s="166" t="s">
         <v>332</v>
@@ -40616,13 +40581,13 @@
         <v>310</v>
       </c>
       <c r="J39" s="157" t="s">
-        <v>2583</v>
+        <v>2577</v>
       </c>
       <c r="K39" s="168" t="s">
-        <v>2585</v>
+        <v>2579</v>
       </c>
       <c r="L39" s="157" t="s">
-        <v>2550</v>
+        <v>2545</v>
       </c>
       <c r="M39" s="157">
         <v>3</v>
@@ -41673,7 +41638,7 @@
         <v>2320</v>
       </c>
       <c r="B60" s="240" t="s">
-        <v>2606</v>
+        <v>2600</v>
       </c>
       <c r="C60" s="160" t="s">
         <v>368</v>
@@ -41724,7 +41689,7 @@
         <v>2321</v>
       </c>
       <c r="B61" s="241" t="s">
-        <v>2607</v>
+        <v>2601</v>
       </c>
       <c r="C61" s="162" t="s">
         <v>368</v>
@@ -42693,7 +42658,7 @@
         <v>2378</v>
       </c>
       <c r="B80" s="199" t="s">
-        <v>2616</v>
+        <v>2610</v>
       </c>
       <c r="C80" s="160" t="s">
         <v>368</v>
@@ -42744,7 +42709,7 @@
         <v>2379</v>
       </c>
       <c r="B81" s="200" t="s">
-        <v>2617</v>
+        <v>2611</v>
       </c>
       <c r="C81" s="162" t="s">
         <v>368</v>
@@ -42795,7 +42760,7 @@
         <v>2380</v>
       </c>
       <c r="B82" s="199" t="s">
-        <v>2618</v>
+        <v>2612</v>
       </c>
       <c r="C82" s="160" t="s">
         <v>368</v>
@@ -42846,7 +42811,7 @@
         <v>2381</v>
       </c>
       <c r="B83" s="227" t="s">
-        <v>2619</v>
+        <v>2613</v>
       </c>
       <c r="C83" s="163" t="s">
         <v>368</v>
@@ -42987,7 +42952,7 @@
         <v>309</v>
       </c>
       <c r="O85" s="175" t="s">
-        <v>2486</v>
+        <v>2482</v>
       </c>
       <c r="P85" s="176" t="s">
         <v>2293</v>
@@ -43041,7 +43006,7 @@
         <v>2433</v>
       </c>
       <c r="P86" s="174" t="s">
-        <v>2495</v>
+        <v>2491</v>
       </c>
       <c r="Q86" s="228"/>
     </row>
@@ -43074,7 +43039,7 @@
         <v>308</v>
       </c>
       <c r="J87" s="162" t="s">
-        <v>2476</v>
+        <v>2472</v>
       </c>
       <c r="K87" s="175">
         <v>3</v>
@@ -43092,7 +43057,7 @@
         <v>2433</v>
       </c>
       <c r="P87" s="176" t="s">
-        <v>2495</v>
+        <v>2491</v>
       </c>
       <c r="Q87" s="229"/>
     </row>
@@ -43140,7 +43105,7 @@
         <v>309</v>
       </c>
       <c r="O88" s="207" t="s">
-        <v>2487</v>
+        <v>2483</v>
       </c>
       <c r="P88" s="174" t="s">
         <v>2252</v>
@@ -43191,7 +43156,7 @@
         <v>309</v>
       </c>
       <c r="O89" s="175" t="s">
-        <v>2488</v>
+        <v>2484</v>
       </c>
       <c r="P89" s="176" t="s">
         <v>2252</v>
@@ -43227,7 +43192,7 @@
         <v>319</v>
       </c>
       <c r="J90" s="160" t="s">
-        <v>2479</v>
+        <v>2475</v>
       </c>
       <c r="K90" s="207" t="s">
         <v>2272</v>
@@ -43242,10 +43207,10 @@
         <v>309</v>
       </c>
       <c r="O90" s="207" t="s">
-        <v>2489</v>
+        <v>2485</v>
       </c>
       <c r="P90" s="174" t="s">
-        <v>2496</v>
+        <v>2492</v>
       </c>
       <c r="Q90" s="228"/>
     </row>
@@ -43278,7 +43243,7 @@
         <v>319</v>
       </c>
       <c r="J91" s="162" t="s">
-        <v>2479</v>
+        <v>2475</v>
       </c>
       <c r="K91" s="175" t="s">
         <v>2275</v>
@@ -43293,10 +43258,10 @@
         <v>309</v>
       </c>
       <c r="O91" s="208" t="s">
-        <v>2489</v>
+        <v>2485</v>
       </c>
       <c r="P91" s="176" t="s">
-        <v>2496</v>
+        <v>2492</v>
       </c>
       <c r="Q91" s="229"/>
     </row>
@@ -43317,7 +43282,7 @@
         <v>281</v>
       </c>
       <c r="F92" s="160" t="s">
-        <v>2595</v>
+        <v>2589</v>
       </c>
       <c r="G92" s="160">
         <v>1</v>
@@ -43329,7 +43294,7 @@
         <v>319</v>
       </c>
       <c r="J92" s="160" t="s">
-        <v>2477</v>
+        <v>2473</v>
       </c>
       <c r="K92" s="207">
         <v>2</v>
@@ -43344,10 +43309,10 @@
         <v>309</v>
       </c>
       <c r="O92" s="207" t="s">
-        <v>2490</v>
+        <v>2486</v>
       </c>
       <c r="P92" s="174" t="s">
-        <v>2497</v>
+        <v>2493</v>
       </c>
       <c r="Q92" s="228"/>
     </row>
@@ -43395,10 +43360,10 @@
         <v>309</v>
       </c>
       <c r="O93" s="208" t="s">
-        <v>2490</v>
+        <v>2486</v>
       </c>
       <c r="P93" s="176" t="s">
-        <v>2497</v>
+        <v>2493</v>
       </c>
       <c r="Q93" s="229"/>
     </row>
@@ -43428,10 +43393,10 @@
         <v>79</v>
       </c>
       <c r="I94" s="160" t="s">
-        <v>2548</v>
+        <v>2543</v>
       </c>
       <c r="J94" s="160" t="s">
-        <v>2481</v>
+        <v>2477</v>
       </c>
       <c r="K94" s="207" t="s">
         <v>2268</v>
@@ -43446,10 +43411,10 @@
         <v>309</v>
       </c>
       <c r="O94" s="207" t="s">
-        <v>2491</v>
+        <v>2487</v>
       </c>
       <c r="P94" s="174" t="s">
-        <v>2500</v>
+        <v>2495</v>
       </c>
       <c r="Q94" s="228"/>
     </row>
@@ -43458,7 +43423,7 @@
         <v>2447</v>
       </c>
       <c r="B95" s="201" t="s">
-        <v>2615</v>
+        <v>2609</v>
       </c>
       <c r="C95" s="162" t="s">
         <v>368</v>
@@ -43482,10 +43447,10 @@
         <v>310</v>
       </c>
       <c r="J95" s="162" t="s">
-        <v>2481</v>
+        <v>2477</v>
       </c>
       <c r="K95" s="175" t="s">
-        <v>2482</v>
+        <v>2478</v>
       </c>
       <c r="L95" s="208" t="s">
         <v>2271</v>
@@ -43497,10 +43462,10 @@
         <v>309</v>
       </c>
       <c r="O95" s="208" t="s">
-        <v>2491</v>
+        <v>2487</v>
       </c>
       <c r="P95" s="176" t="s">
-        <v>2499</v>
+        <v>2494</v>
       </c>
       <c r="Q95" s="229"/>
     </row>
@@ -43546,10 +43511,10 @@
         <v>309</v>
       </c>
       <c r="O96" s="207" t="s">
-        <v>2492</v>
+        <v>2488</v>
       </c>
       <c r="P96" s="232" t="s">
-        <v>2501</v>
+        <v>2496</v>
       </c>
       <c r="Q96" s="228"/>
     </row>
@@ -43595,10 +43560,10 @@
         <v>309</v>
       </c>
       <c r="O97" s="175" t="s">
-        <v>2493</v>
+        <v>2489</v>
       </c>
       <c r="P97" s="210" t="s">
-        <v>2502</v>
+        <v>2497</v>
       </c>
       <c r="Q97" s="229"/>
     </row>
@@ -43607,7 +43572,7 @@
         <v>2450</v>
       </c>
       <c r="B98" s="199" t="s">
-        <v>2470</v>
+        <v>2620</v>
       </c>
       <c r="C98" s="160" t="s">
         <v>368</v>
@@ -43631,7 +43596,7 @@
         <v>319</v>
       </c>
       <c r="J98" s="160" t="s">
-        <v>2503</v>
+        <v>2498</v>
       </c>
       <c r="K98" s="207">
         <v>1</v>
@@ -43649,7 +43614,7 @@
         <v>2287</v>
       </c>
       <c r="P98" s="174" t="s">
-        <v>2504</v>
+        <v>2499</v>
       </c>
       <c r="Q98" s="228"/>
     </row>
@@ -43658,7 +43623,7 @@
         <v>2451</v>
       </c>
       <c r="B99" s="201" t="s">
-        <v>2471</v>
+        <v>2621</v>
       </c>
       <c r="C99" s="162" t="s">
         <v>368</v>
@@ -43679,7 +43644,7 @@
         <v>79</v>
       </c>
       <c r="I99" s="162" t="s">
-        <v>2549</v>
+        <v>2544</v>
       </c>
       <c r="J99" s="162" t="s">
         <v>404</v>
@@ -43697,10 +43662,10 @@
         <v>309</v>
       </c>
       <c r="O99" s="175" t="s">
-        <v>2494</v>
+        <v>2490</v>
       </c>
       <c r="P99" s="176" t="s">
-        <v>2504</v>
+        <v>2499</v>
       </c>
       <c r="Q99" s="229"/>
     </row>
@@ -43709,7 +43674,7 @@
         <v>2452</v>
       </c>
       <c r="B100" s="199" t="s">
-        <v>2472</v>
+        <v>2622</v>
       </c>
       <c r="C100" s="160" t="s">
         <v>368</v>
@@ -43730,10 +43695,10 @@
         <v>79</v>
       </c>
       <c r="I100" s="160" t="s">
-        <v>2547</v>
+        <v>2542</v>
       </c>
       <c r="J100" s="160" t="s">
-        <v>2505</v>
+        <v>2500</v>
       </c>
       <c r="K100" s="160">
         <v>1</v>
@@ -43751,7 +43716,7 @@
         <v>2421</v>
       </c>
       <c r="P100" s="174" t="s">
-        <v>2506</v>
+        <v>2501</v>
       </c>
       <c r="Q100" s="228"/>
     </row>
@@ -43759,8 +43724,8 @@
       <c r="A101" s="162" t="s">
         <v>2453</v>
       </c>
-      <c r="B101" s="201" t="s">
-        <v>2473</v>
+      <c r="B101" s="200" t="s">
+        <v>2623</v>
       </c>
       <c r="C101" s="162" t="s">
         <v>368</v>
@@ -43772,7 +43737,7 @@
         <v>281</v>
       </c>
       <c r="F101" s="162" t="s">
-        <v>2594</v>
+        <v>2588</v>
       </c>
       <c r="G101" s="162">
         <v>2</v>
@@ -43802,7 +43767,7 @@
         <v>2421</v>
       </c>
       <c r="P101" s="176" t="s">
-        <v>2506</v>
+        <v>2501</v>
       </c>
       <c r="Q101" s="229"/>
     </row>
@@ -43811,7 +43776,7 @@
         <v>2454</v>
       </c>
       <c r="B102" s="199" t="s">
-        <v>2474</v>
+        <v>2470</v>
       </c>
       <c r="C102" s="160" t="s">
         <v>368</v>
@@ -43835,7 +43800,7 @@
         <v>319</v>
       </c>
       <c r="J102" s="160" t="s">
-        <v>2478</v>
+        <v>2474</v>
       </c>
       <c r="K102" s="207" t="s">
         <v>2272</v>
@@ -43850,10 +43815,10 @@
         <v>309</v>
       </c>
       <c r="O102" s="207" t="s">
-        <v>2487</v>
+        <v>2483</v>
       </c>
       <c r="P102" s="174" t="s">
-        <v>2507</v>
+        <v>2502</v>
       </c>
       <c r="Q102" s="228"/>
     </row>
@@ -43862,7 +43827,7 @@
         <v>2455</v>
       </c>
       <c r="B103" s="227" t="s">
-        <v>2475</v>
+        <v>2471</v>
       </c>
       <c r="C103" s="163" t="s">
         <v>368</v>
@@ -43886,10 +43851,10 @@
         <v>319</v>
       </c>
       <c r="J103" s="163" t="s">
-        <v>2478</v>
+        <v>2474</v>
       </c>
       <c r="K103" s="177" t="s">
-        <v>2485</v>
+        <v>2481</v>
       </c>
       <c r="L103" s="209" t="s">
         <v>2271</v>
@@ -43901,19 +43866,19 @@
         <v>309</v>
       </c>
       <c r="O103" s="177" t="s">
-        <v>2489</v>
+        <v>2485</v>
       </c>
       <c r="P103" s="178" t="s">
-        <v>2508</v>
+        <v>2503</v>
       </c>
       <c r="Q103" s="230"/>
     </row>
     <row r="104" spans="1:17" s="148" customFormat="1" ht="19.899999999999999" customHeight="1" thickBot="1">
       <c r="A104" s="206" t="s">
-        <v>2509</v>
+        <v>2504</v>
       </c>
       <c r="B104" s="233" t="s">
-        <v>2611</v>
+        <v>2605</v>
       </c>
       <c r="C104" s="160" t="s">
         <v>368</v>
@@ -43925,7 +43890,7 @@
         <v>369</v>
       </c>
       <c r="F104" s="160" t="s">
-        <v>2594</v>
+        <v>2588</v>
       </c>
       <c r="G104" s="160">
         <v>1</v>
@@ -43934,16 +43899,16 @@
         <v>79</v>
       </c>
       <c r="I104" s="160" t="s">
+        <v>2542</v>
+      </c>
+      <c r="J104" s="160" t="s">
+        <v>2546</v>
+      </c>
+      <c r="K104" s="207" t="s">
         <v>2547</v>
       </c>
-      <c r="J104" s="160" t="s">
-        <v>2551</v>
-      </c>
-      <c r="K104" s="207" t="s">
-        <v>2552</v>
-      </c>
       <c r="L104" s="207" t="s">
-        <v>2550</v>
+        <v>2545</v>
       </c>
       <c r="M104" s="207">
         <v>3</v>
@@ -43952,19 +43917,19 @@
         <v>309</v>
       </c>
       <c r="O104" s="207" t="s">
-        <v>2587</v>
+        <v>2581</v>
       </c>
       <c r="P104" s="174" t="s">
-        <v>2567</v>
+        <v>2562</v>
       </c>
       <c r="Q104" s="183"/>
     </row>
     <row r="105" spans="1:17" s="147" customFormat="1" ht="19.899999999999999" customHeight="1" thickBot="1">
       <c r="A105" s="162" t="s">
-        <v>2510</v>
+        <v>2505</v>
       </c>
       <c r="B105" s="234" t="s">
-        <v>2612</v>
+        <v>2606</v>
       </c>
       <c r="C105" s="162" t="s">
         <v>368</v>
@@ -43988,13 +43953,13 @@
         <v>308</v>
       </c>
       <c r="J105" s="162" t="s">
-        <v>2551</v>
+        <v>2546</v>
       </c>
       <c r="K105" s="175" t="s">
-        <v>2553</v>
+        <v>2548</v>
       </c>
       <c r="L105" s="208" t="s">
-        <v>2550</v>
+        <v>2545</v>
       </c>
       <c r="M105" s="208">
         <v>3</v>
@@ -44003,19 +43968,19 @@
         <v>309</v>
       </c>
       <c r="O105" s="175" t="s">
-        <v>2588</v>
+        <v>2582</v>
       </c>
       <c r="P105" s="176" t="s">
-        <v>2568</v>
+        <v>2563</v>
       </c>
       <c r="Q105" s="184"/>
     </row>
     <row r="106" spans="1:17" s="148" customFormat="1" ht="19.899999999999999" customHeight="1" thickBot="1">
       <c r="A106" s="160" t="s">
-        <v>2511</v>
+        <v>2506</v>
       </c>
       <c r="B106" s="235" t="s">
-        <v>2529</v>
+        <v>2524</v>
       </c>
       <c r="C106" s="160" t="s">
         <v>368</v>
@@ -44039,13 +44004,13 @@
         <v>310</v>
       </c>
       <c r="J106" s="160" t="s">
-        <v>2555</v>
+        <v>2550</v>
       </c>
       <c r="K106" s="207" t="s">
-        <v>2556</v>
+        <v>2551</v>
       </c>
       <c r="L106" s="207" t="s">
-        <v>2550</v>
+        <v>2545</v>
       </c>
       <c r="M106" s="207">
         <v>3</v>
@@ -44054,19 +44019,19 @@
         <v>309</v>
       </c>
       <c r="O106" s="207" t="s">
-        <v>2589</v>
+        <v>2583</v>
       </c>
       <c r="P106" s="174" t="s">
-        <v>2569</v>
+        <v>2564</v>
       </c>
       <c r="Q106" s="183"/>
     </row>
     <row r="107" spans="1:17" s="147" customFormat="1" ht="19.899999999999999" customHeight="1" thickBot="1">
       <c r="A107" s="162" t="s">
-        <v>2512</v>
+        <v>2507</v>
       </c>
       <c r="B107" s="234" t="s">
-        <v>2530</v>
+        <v>2525</v>
       </c>
       <c r="C107" s="162" t="s">
         <v>368</v>
@@ -44093,10 +44058,10 @@
         <v>472</v>
       </c>
       <c r="K107" s="175" t="s">
-        <v>2557</v>
+        <v>2552</v>
       </c>
       <c r="L107" s="208" t="s">
-        <v>2550</v>
+        <v>2545</v>
       </c>
       <c r="M107" s="208">
         <v>3</v>
@@ -44105,19 +44070,19 @@
         <v>309</v>
       </c>
       <c r="O107" s="175" t="s">
-        <v>2590</v>
+        <v>2584</v>
       </c>
       <c r="P107" s="176" t="s">
-        <v>2569</v>
+        <v>2564</v>
       </c>
       <c r="Q107" s="184"/>
     </row>
     <row r="108" spans="1:17" s="148" customFormat="1" ht="19.899999999999999" customHeight="1" thickBot="1">
       <c r="A108" s="160" t="s">
-        <v>2513</v>
+        <v>2508</v>
       </c>
       <c r="B108" s="235" t="s">
-        <v>2531</v>
+        <v>2526</v>
       </c>
       <c r="C108" s="160" t="s">
         <v>368</v>
@@ -44138,16 +44103,16 @@
         <v>95</v>
       </c>
       <c r="I108" s="160" t="s">
-        <v>2547</v>
+        <v>2542</v>
       </c>
       <c r="J108" s="160" t="s">
-        <v>2560</v>
+        <v>2555</v>
       </c>
       <c r="K108" s="207" t="s">
-        <v>2558</v>
+        <v>2553</v>
       </c>
       <c r="L108" s="207" t="s">
-        <v>2550</v>
+        <v>2545</v>
       </c>
       <c r="M108" s="207">
         <v>3</v>
@@ -44156,19 +44121,19 @@
         <v>309</v>
       </c>
       <c r="O108" s="207" t="s">
-        <v>2591</v>
+        <v>2585</v>
       </c>
       <c r="P108" s="174" t="s">
-        <v>2570</v>
+        <v>2565</v>
       </c>
       <c r="Q108" s="183"/>
     </row>
     <row r="109" spans="1:17" s="147" customFormat="1" ht="19.899999999999999" customHeight="1" thickBot="1">
       <c r="A109" s="162" t="s">
-        <v>2514</v>
+        <v>2509</v>
       </c>
       <c r="B109" s="234" t="s">
-        <v>2532</v>
+        <v>2527</v>
       </c>
       <c r="C109" s="162" t="s">
         <v>368</v>
@@ -44192,13 +44157,13 @@
         <v>308</v>
       </c>
       <c r="J109" s="162" t="s">
-        <v>2560</v>
+        <v>2555</v>
       </c>
       <c r="K109" s="175" t="s">
-        <v>2559</v>
+        <v>2554</v>
       </c>
       <c r="L109" s="208" t="s">
-        <v>2550</v>
+        <v>2545</v>
       </c>
       <c r="M109" s="208">
         <v>3</v>
@@ -44207,19 +44172,19 @@
         <v>309</v>
       </c>
       <c r="O109" s="175" t="s">
-        <v>2592</v>
+        <v>2586</v>
       </c>
       <c r="P109" s="176" t="s">
-        <v>2570</v>
+        <v>2565</v>
       </c>
       <c r="Q109" s="184"/>
     </row>
     <row r="110" spans="1:17" s="148" customFormat="1" ht="19.899999999999999" customHeight="1" thickBot="1">
       <c r="A110" s="160" t="s">
-        <v>2515</v>
+        <v>2510</v>
       </c>
       <c r="B110" s="235" t="s">
-        <v>2533</v>
+        <v>2528</v>
       </c>
       <c r="C110" s="160" t="s">
         <v>368</v>
@@ -44228,7 +44193,7 @@
         <v>372</v>
       </c>
       <c r="E110" s="160" t="s">
-        <v>2546</v>
+        <v>2541</v>
       </c>
       <c r="F110" s="160" t="s">
         <v>282</v>
@@ -44243,7 +44208,7 @@
         <v>308</v>
       </c>
       <c r="J110" s="160" t="s">
-        <v>2571</v>
+        <v>2566</v>
       </c>
       <c r="K110" s="207">
         <v>1</v>
@@ -44258,19 +44223,19 @@
         <v>309</v>
       </c>
       <c r="O110" s="207" t="s">
-        <v>2593</v>
+        <v>2587</v>
       </c>
       <c r="P110" s="174" t="s">
-        <v>2572</v>
+        <v>2567</v>
       </c>
       <c r="Q110" s="183"/>
     </row>
     <row r="111" spans="1:17" s="147" customFormat="1" ht="19.899999999999999" customHeight="1" thickBot="1">
       <c r="A111" s="162" t="s">
-        <v>2516</v>
+        <v>2511</v>
       </c>
       <c r="B111" s="234" t="s">
-        <v>2534</v>
+        <v>2529</v>
       </c>
       <c r="C111" s="162" t="s">
         <v>368</v>
@@ -44309,19 +44274,19 @@
         <v>309</v>
       </c>
       <c r="O111" s="208" t="s">
-        <v>2593</v>
+        <v>2587</v>
       </c>
       <c r="P111" s="176" t="s">
-        <v>2573</v>
+        <v>2568</v>
       </c>
       <c r="Q111" s="184"/>
     </row>
     <row r="112" spans="1:17" s="148" customFormat="1" ht="19.899999999999999" customHeight="1" thickBot="1">
       <c r="A112" s="160" t="s">
-        <v>2517</v>
+        <v>2512</v>
       </c>
       <c r="B112" s="235" t="s">
-        <v>2535</v>
+        <v>2530</v>
       </c>
       <c r="C112" s="160" t="s">
         <v>368</v>
@@ -44345,13 +44310,13 @@
         <v>310</v>
       </c>
       <c r="J112" s="160" t="s">
-        <v>2561</v>
+        <v>2556</v>
       </c>
       <c r="K112" s="207">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L112" s="207">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M112" s="207">
         <v>4</v>
@@ -44360,19 +44325,19 @@
         <v>309</v>
       </c>
       <c r="O112" s="207" t="s">
-        <v>2596</v>
+        <v>2590</v>
       </c>
       <c r="P112" s="174" t="s">
-        <v>2574</v>
+        <v>2403</v>
       </c>
       <c r="Q112" s="183"/>
     </row>
     <row r="113" spans="1:17" s="147" customFormat="1" ht="19.899999999999999" customHeight="1" thickBot="1">
       <c r="A113" s="162" t="s">
-        <v>2518</v>
+        <v>2513</v>
       </c>
       <c r="B113" s="234" t="s">
-        <v>2536</v>
+        <v>2531</v>
       </c>
       <c r="C113" s="162" t="s">
         <v>368</v>
@@ -44396,13 +44361,13 @@
         <v>310</v>
       </c>
       <c r="J113" s="162" t="s">
-        <v>2561</v>
-      </c>
-      <c r="K113" s="175">
-        <v>6</v>
-      </c>
-      <c r="L113" s="208">
+        <v>2556</v>
+      </c>
+      <c r="K113" s="208">
         <v>1</v>
+      </c>
+      <c r="L113" s="175">
+        <v>4</v>
       </c>
       <c r="M113" s="208">
         <v>4</v>
@@ -44411,19 +44376,19 @@
         <v>309</v>
       </c>
       <c r="O113" s="175" t="s">
-        <v>2597</v>
+        <v>2591</v>
       </c>
       <c r="P113" s="176" t="s">
-        <v>2498</v>
+        <v>2403</v>
       </c>
       <c r="Q113" s="184"/>
     </row>
     <row r="114" spans="1:17" s="148" customFormat="1" ht="19.899999999999999" customHeight="1" thickBot="1">
       <c r="A114" s="160" t="s">
-        <v>2519</v>
+        <v>2514</v>
       </c>
       <c r="B114" s="235" t="s">
-        <v>2537</v>
+        <v>2532</v>
       </c>
       <c r="C114" s="160" t="s">
         <v>368</v>
@@ -44444,10 +44409,10 @@
         <v>95</v>
       </c>
       <c r="I114" s="160" t="s">
-        <v>2549</v>
+        <v>2544</v>
       </c>
       <c r="J114" s="160" t="s">
-        <v>2575</v>
+        <v>2569</v>
       </c>
       <c r="K114" s="207">
         <v>2</v>
@@ -44462,19 +44427,19 @@
         <v>309</v>
       </c>
       <c r="O114" s="207" t="s">
-        <v>2598</v>
+        <v>2592</v>
       </c>
       <c r="P114" s="174" t="s">
-        <v>2576</v>
+        <v>2570</v>
       </c>
       <c r="Q114" s="183"/>
     </row>
     <row r="115" spans="1:17" s="147" customFormat="1" ht="19.899999999999999" customHeight="1" thickBot="1">
       <c r="A115" s="162" t="s">
-        <v>2520</v>
+        <v>2515</v>
       </c>
       <c r="B115" s="234" t="s">
-        <v>2538</v>
+        <v>2533</v>
       </c>
       <c r="C115" s="162" t="s">
         <v>368</v>
@@ -44513,19 +44478,19 @@
         <v>309</v>
       </c>
       <c r="O115" s="208" t="s">
-        <v>2598</v>
+        <v>2592</v>
       </c>
       <c r="P115" s="176" t="s">
-        <v>2576</v>
+        <v>2570</v>
       </c>
       <c r="Q115" s="184"/>
     </row>
     <row r="116" spans="1:17" s="148" customFormat="1" ht="19.899999999999999" customHeight="1" thickBot="1">
       <c r="A116" s="160" t="s">
-        <v>2521</v>
+        <v>2516</v>
       </c>
       <c r="B116" s="235" t="s">
-        <v>2613</v>
+        <v>2607</v>
       </c>
       <c r="C116" s="160" t="s">
         <v>368</v>
@@ -44534,7 +44499,7 @@
         <v>371</v>
       </c>
       <c r="E116" s="160" t="s">
-        <v>2546</v>
+        <v>2541</v>
       </c>
       <c r="F116" s="160" t="s">
         <v>296</v>
@@ -44549,7 +44514,7 @@
         <v>308</v>
       </c>
       <c r="J116" s="160" t="s">
-        <v>2562</v>
+        <v>2557</v>
       </c>
       <c r="K116" s="207">
         <v>1</v>
@@ -44564,19 +44529,19 @@
         <v>309</v>
       </c>
       <c r="O116" s="207" t="s">
-        <v>2599</v>
+        <v>2593</v>
       </c>
       <c r="P116" s="174" t="s">
-        <v>2577</v>
+        <v>2571</v>
       </c>
       <c r="Q116" s="183"/>
     </row>
     <row r="117" spans="1:17" s="147" customFormat="1" ht="19.899999999999999" customHeight="1" thickBot="1">
       <c r="A117" s="162" t="s">
-        <v>2522</v>
+        <v>2517</v>
       </c>
       <c r="B117" s="234" t="s">
-        <v>2614</v>
+        <v>2608</v>
       </c>
       <c r="C117" s="162" t="s">
         <v>368</v>
@@ -44600,7 +44565,7 @@
         <v>308</v>
       </c>
       <c r="J117" s="162" t="s">
-        <v>2562</v>
+        <v>2557</v>
       </c>
       <c r="K117" s="208">
         <v>1</v>
@@ -44615,19 +44580,19 @@
         <v>309</v>
       </c>
       <c r="O117" s="208" t="s">
-        <v>2599</v>
+        <v>2593</v>
       </c>
       <c r="P117" s="176" t="s">
-        <v>2577</v>
+        <v>2571</v>
       </c>
       <c r="Q117" s="184"/>
     </row>
     <row r="118" spans="1:17" s="148" customFormat="1" ht="19.899999999999999" customHeight="1" thickBot="1">
       <c r="A118" s="160" t="s">
-        <v>2523</v>
+        <v>2518</v>
       </c>
       <c r="B118" s="235" t="s">
-        <v>2539</v>
+        <v>2534</v>
       </c>
       <c r="C118" s="160" t="s">
         <v>368</v>
@@ -44636,7 +44601,7 @@
         <v>371</v>
       </c>
       <c r="E118" s="160" t="s">
-        <v>2546</v>
+        <v>2541</v>
       </c>
       <c r="F118" s="160" t="s">
         <v>299</v>
@@ -44651,13 +44616,13 @@
         <v>310</v>
       </c>
       <c r="J118" s="160" t="s">
-        <v>2564</v>
+        <v>2559</v>
       </c>
       <c r="K118" s="207" t="s">
-        <v>2558</v>
+        <v>2553</v>
       </c>
       <c r="L118" s="207" t="s">
-        <v>2550</v>
+        <v>2545</v>
       </c>
       <c r="M118" s="207">
         <v>5</v>
@@ -44666,19 +44631,19 @@
         <v>309</v>
       </c>
       <c r="O118" s="207" t="s">
-        <v>2590</v>
+        <v>2584</v>
       </c>
       <c r="P118" s="174" t="s">
-        <v>2578</v>
+        <v>2572</v>
       </c>
       <c r="Q118" s="183"/>
     </row>
     <row r="119" spans="1:17" s="147" customFormat="1" ht="19.899999999999999" customHeight="1" thickBot="1">
       <c r="A119" s="162" t="s">
-        <v>2524</v>
+        <v>2519</v>
       </c>
       <c r="B119" s="234" t="s">
-        <v>2540</v>
+        <v>2535</v>
       </c>
       <c r="C119" s="162" t="s">
         <v>368</v>
@@ -44702,13 +44667,13 @@
         <v>310</v>
       </c>
       <c r="J119" s="162" t="s">
-        <v>2564</v>
+        <v>2559</v>
       </c>
       <c r="K119" s="208" t="s">
-        <v>2558</v>
+        <v>2553</v>
       </c>
       <c r="L119" s="208" t="s">
-        <v>2550</v>
+        <v>2545</v>
       </c>
       <c r="M119" s="175">
         <v>4</v>
@@ -44717,19 +44682,19 @@
         <v>309</v>
       </c>
       <c r="O119" s="175" t="s">
-        <v>2600</v>
+        <v>2594</v>
       </c>
       <c r="P119" s="176" t="s">
-        <v>2579</v>
+        <v>2573</v>
       </c>
       <c r="Q119" s="184"/>
     </row>
     <row r="120" spans="1:17" s="148" customFormat="1" ht="19.899999999999999" customHeight="1" thickBot="1">
       <c r="A120" s="160" t="s">
-        <v>2525</v>
+        <v>2520</v>
       </c>
       <c r="B120" s="235" t="s">
-        <v>2541</v>
+        <v>2536</v>
       </c>
       <c r="C120" s="160" t="s">
         <v>368</v>
@@ -44753,7 +44718,7 @@
         <v>319</v>
       </c>
       <c r="J120" s="160" t="s">
-        <v>2565</v>
+        <v>2560</v>
       </c>
       <c r="K120" s="207">
         <v>2</v>
@@ -44768,19 +44733,19 @@
         <v>309</v>
       </c>
       <c r="O120" s="207" t="s">
-        <v>2586</v>
+        <v>2580</v>
       </c>
       <c r="P120" s="174" t="s">
-        <v>2580</v>
+        <v>2574</v>
       </c>
       <c r="Q120" s="183"/>
     </row>
     <row r="121" spans="1:17" s="147" customFormat="1" ht="19.899999999999999" customHeight="1" thickBot="1">
       <c r="A121" s="162" t="s">
-        <v>2526</v>
+        <v>2521</v>
       </c>
       <c r="B121" s="234" t="s">
-        <v>2542</v>
+        <v>2537</v>
       </c>
       <c r="C121" s="162" t="s">
         <v>368</v>
@@ -44804,7 +44769,7 @@
         <v>319</v>
       </c>
       <c r="J121" s="162" t="s">
-        <v>2565</v>
+        <v>2560</v>
       </c>
       <c r="K121" s="208">
         <v>2</v>
@@ -44819,19 +44784,19 @@
         <v>309</v>
       </c>
       <c r="O121" s="175" t="s">
-        <v>2603</v>
+        <v>2597</v>
       </c>
       <c r="P121" s="176" t="s">
-        <v>2580</v>
+        <v>2574</v>
       </c>
       <c r="Q121" s="184"/>
     </row>
     <row r="122" spans="1:17" s="148" customFormat="1" ht="19.899999999999999" customHeight="1" thickBot="1">
       <c r="A122" s="160" t="s">
-        <v>2527</v>
+        <v>2522</v>
       </c>
       <c r="B122" s="235" t="s">
-        <v>2543</v>
+        <v>2538</v>
       </c>
       <c r="C122" s="160" t="s">
         <v>368</v>
@@ -44840,7 +44805,7 @@
         <v>2255</v>
       </c>
       <c r="E122" s="160" t="s">
-        <v>2545</v>
+        <v>2540</v>
       </c>
       <c r="F122" s="160" t="s">
         <v>299</v>
@@ -44852,10 +44817,10 @@
         <v>95</v>
       </c>
       <c r="I122" s="160" t="s">
-        <v>2548</v>
+        <v>2543</v>
       </c>
       <c r="J122" s="160" t="s">
-        <v>2566</v>
+        <v>2561</v>
       </c>
       <c r="K122" s="207">
         <v>1</v>
@@ -44870,19 +44835,19 @@
         <v>309</v>
       </c>
       <c r="O122" s="207" t="s">
-        <v>2602</v>
+        <v>2596</v>
       </c>
       <c r="P122" s="238" t="s">
-        <v>2581</v>
+        <v>2575</v>
       </c>
       <c r="Q122" s="183"/>
     </row>
     <row r="123" spans="1:17" s="147" customFormat="1" ht="19.899999999999999" customHeight="1" thickBot="1">
       <c r="A123" s="161" t="s">
-        <v>2528</v>
+        <v>2523</v>
       </c>
       <c r="B123" s="236" t="s">
-        <v>2544</v>
+        <v>2539</v>
       </c>
       <c r="C123" s="163" t="s">
         <v>368</v>
@@ -44906,7 +44871,7 @@
         <v>310</v>
       </c>
       <c r="J123" s="163" t="s">
-        <v>2566</v>
+        <v>2561</v>
       </c>
       <c r="K123" s="209">
         <v>1</v>
@@ -44921,10 +44886,10 @@
         <v>309</v>
       </c>
       <c r="O123" s="177" t="s">
-        <v>2601</v>
+        <v>2595</v>
       </c>
       <c r="P123" s="239" t="s">
-        <v>2582</v>
+        <v>2576</v>
       </c>
       <c r="Q123" s="185"/>
     </row>
@@ -50290,7 +50255,7 @@
     </row>
     <row r="10" spans="1:7" ht="16.5" customHeight="1">
       <c r="A10" s="42" t="s">
-        <v>2554</v>
+        <v>2549</v>
       </c>
       <c r="B10" s="37" t="s">
         <v>614</v>
@@ -52926,7 +52891,7 @@
     </row>
     <row r="136" spans="1:7" ht="16.5" customHeight="1">
       <c r="A136" s="231" t="s">
-        <v>2477</v>
+        <v>2473</v>
       </c>
       <c r="B136" s="225" t="s">
         <v>2456</v>
@@ -53060,7 +53025,7 @@
     </row>
     <row r="143" spans="1:7" ht="16.5" customHeight="1">
       <c r="A143" s="224" t="s">
-        <v>2562</v>
+        <v>2557</v>
       </c>
       <c r="B143" s="30" t="s">
         <v>1094</v>
@@ -53162,7 +53127,7 @@
     </row>
     <row r="149" spans="1:7" ht="16.5" customHeight="1">
       <c r="A149" s="237" t="s">
-        <v>2565</v>
+        <v>2560</v>
       </c>
       <c r="B149" s="115" t="s">
         <v>1108</v>
@@ -53179,7 +53144,7 @@
     </row>
     <row r="150" spans="1:7" ht="16.5" customHeight="1">
       <c r="A150" s="237" t="s">
-        <v>2566</v>
+        <v>2561</v>
       </c>
       <c r="B150" s="115" t="s">
         <v>1110</v>
@@ -53316,7 +53281,7 @@
     </row>
     <row r="157" spans="1:7" ht="16.5" customHeight="1">
       <c r="A157" s="218" t="s">
-        <v>2483</v>
+        <v>2479</v>
       </c>
       <c r="B157" s="30" t="s">
         <v>1134</v>
@@ -53356,7 +53321,7 @@
     </row>
     <row r="159" spans="1:7" ht="16.5" customHeight="1">
       <c r="A159" s="218" t="s">
-        <v>2484</v>
+        <v>2480</v>
       </c>
       <c r="B159" s="30" t="s">
         <v>1103</v>
@@ -53376,7 +53341,7 @@
     </row>
     <row r="160" spans="1:7" ht="16.5" customHeight="1">
       <c r="A160" s="218" t="s">
-        <v>2480</v>
+        <v>2476</v>
       </c>
       <c r="B160" s="30" t="s">
         <v>1142</v>
@@ -53416,7 +53381,7 @@
     </row>
     <row r="162" spans="1:7" ht="16.5" customHeight="1">
       <c r="A162" s="218" t="s">
-        <v>2563</v>
+        <v>2558</v>
       </c>
       <c r="B162" s="30" t="s">
         <v>1148</v>
@@ -58989,7 +58954,7 @@
         <v>1577</v>
       </c>
       <c r="C53" s="97" t="s">
-        <v>2623</v>
+        <v>2617</v>
       </c>
       <c r="D53" s="30">
         <v>1</v>
@@ -59043,13 +59008,13 @@
         <v>1582</v>
       </c>
       <c r="C54" s="244" t="s">
-        <v>2624</v>
+        <v>2618</v>
       </c>
       <c r="D54" s="30">
         <v>1</v>
       </c>
       <c r="E54" s="245" t="s">
-        <v>2625</v>
+        <v>2619</v>
       </c>
       <c r="F54" s="99" t="s">
         <v>1583</v>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erang\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E7CEF57-F574-4D1E-8CB5-059F8C5E50D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E487887C-5948-401E-854A-BA6377EE1E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -57287,7 +57287,7 @@
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="92">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E17" s="93" t="s">
         <v>1712</v>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erang\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{714A84E0-4D6B-4598-903B-EA2F27AC2609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08904E29-5562-4943-AD3B-1C93B7F4EBAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5005" uniqueCount="2392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5002" uniqueCount="2391">
   <si>
     <t>캐릭터ID</t>
   </si>
@@ -12854,15 +12854,11 @@
     <phoneticPr fontId="42" type="noConversion"/>
   </si>
   <si>
-    <t>Mon_04</t>
+    <t>Mon_07</t>
     <phoneticPr fontId="42" type="noConversion"/>
   </si>
   <si>
-    <t>Mon_05</t>
-    <phoneticPr fontId="42" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mon_06</t>
+    <t>Mon_08</t>
     <phoneticPr fontId="42" type="noConversion"/>
   </si>
 </sst>
@@ -41338,7 +41334,7 @@
         <v>2389</v>
       </c>
       <c r="C49" s="4">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D49" s="4">
         <v>-1</v>
@@ -41388,7 +41384,7 @@
         <v>2390</v>
       </c>
       <c r="C50" s="4">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D50" s="4">
         <v>-1</v>
@@ -41408,27 +41404,6 @@
       <c r="P50" s="183"/>
     </row>
     <row r="51" spans="1:16">
-      <c r="A51" s="4" t="s">
-        <v>1429</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>2391</v>
-      </c>
-      <c r="C51" s="4">
-        <v>28</v>
-      </c>
-      <c r="D51" s="4">
-        <v>-1</v>
-      </c>
-      <c r="E51" s="4">
-        <v>-1</v>
-      </c>
-      <c r="F51" s="4">
-        <v>-1</v>
-      </c>
-      <c r="G51" s="4" t="s">
-        <v>1479</v>
-      </c>
       <c r="M51" s="183"/>
       <c r="N51" s="183"/>
       <c r="O51" s="183"/>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erang\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08904E29-5562-4943-AD3B-1C93B7F4EBAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3CE1BDB-5B45-461C-B15A-96890A02CEED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5002" uniqueCount="2391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4999" uniqueCount="2392">
   <si>
     <t>캐릭터ID</t>
   </si>
@@ -12854,11 +12854,15 @@
     <phoneticPr fontId="42" type="noConversion"/>
   </si>
   <si>
-    <t>Mon_07</t>
+    <t>Mon_09</t>
     <phoneticPr fontId="42" type="noConversion"/>
   </si>
   <si>
-    <t>Mon_08</t>
+    <t>Range_10</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>Range_16</t>
     <phoneticPr fontId="42" type="noConversion"/>
   </si>
 </sst>
@@ -32007,7 +32011,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="84" t="s">
-        <v>378</v>
+        <v>2390</v>
       </c>
       <c r="J18" s="16" t="s">
         <v>336</v>
@@ -32301,7 +32305,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="84" t="s">
-        <v>439</v>
+        <v>2391</v>
       </c>
       <c r="J25" s="16" t="s">
         <v>336</v>
@@ -41377,27 +41381,6 @@
       </c>
     </row>
     <row r="50" spans="1:16">
-      <c r="A50" s="4" t="s">
-        <v>1429</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>2390</v>
-      </c>
-      <c r="C50" s="4">
-        <v>25</v>
-      </c>
-      <c r="D50" s="4">
-        <v>-1</v>
-      </c>
-      <c r="E50" s="4">
-        <v>-1</v>
-      </c>
-      <c r="F50" s="4">
-        <v>-1</v>
-      </c>
-      <c r="G50" s="4" t="s">
-        <v>1479</v>
-      </c>
       <c r="M50" s="183"/>
       <c r="N50" s="183"/>
       <c r="O50" s="183"/>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erang\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3CE1BDB-5B45-461C-B15A-96890A02CEED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74C8AFD4-A74E-47B6-B270-566540F7AE9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -12854,15 +12854,15 @@
     <phoneticPr fontId="42" type="noConversion"/>
   </si>
   <si>
-    <t>Mon_09</t>
-    <phoneticPr fontId="42" type="noConversion"/>
-  </si>
-  <si>
     <t>Range_10</t>
     <phoneticPr fontId="42" type="noConversion"/>
   </si>
   <si>
     <t>Range_16</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mon_01</t>
     <phoneticPr fontId="42" type="noConversion"/>
   </si>
 </sst>
@@ -32011,7 +32011,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="84" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="J18" s="16" t="s">
         <v>336</v>
@@ -32305,7 +32305,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="84" t="s">
-        <v>2391</v>
+        <v>2390</v>
       </c>
       <c r="J25" s="16" t="s">
         <v>336</v>
@@ -41335,7 +41335,7 @@
         <v>1429</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>2389</v>
+        <v>2391</v>
       </c>
       <c r="C49" s="4">
         <v>22</v>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erang\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74C8AFD4-A74E-47B6-B270-566540F7AE9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E00D5CD-45BA-4B05-BAA2-BA2E24A61867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4999" uniqueCount="2392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5001" uniqueCount="2393">
   <si>
     <t>캐릭터ID</t>
   </si>
@@ -12862,7 +12862,11 @@
     <phoneticPr fontId="42" type="noConversion"/>
   </si>
   <si>
-    <t>Mon_01</t>
+    <t>Mon_07</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mon_08</t>
     <phoneticPr fontId="42" type="noConversion"/>
   </si>
 </sst>
@@ -41338,7 +41342,7 @@
         <v>2391</v>
       </c>
       <c r="C49" s="4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D49" s="4">
         <v>-1</v>
@@ -41381,6 +41385,24 @@
       </c>
     </row>
     <row r="50" spans="1:16">
+      <c r="A50" s="4" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>2392</v>
+      </c>
+      <c r="C50" s="4">
+        <v>23</v>
+      </c>
+      <c r="D50" s="4">
+        <v>-1</v>
+      </c>
+      <c r="E50" s="4">
+        <v>-1</v>
+      </c>
+      <c r="F50" s="4">
+        <v>-1</v>
+      </c>
       <c r="M50" s="183"/>
       <c r="N50" s="183"/>
       <c r="O50" s="183"/>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erang\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E00D5CD-45BA-4B05-BAA2-BA2E24A61867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37BC50F5-399C-48EE-8CE0-2D9748691BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5001" uniqueCount="2393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5003" uniqueCount="2395">
   <si>
     <t>캐릭터ID</t>
   </si>
@@ -12867,6 +12867,14 @@
   </si>
   <si>
     <t>Mon_08</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>Char_05</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>Char_06</t>
     <phoneticPr fontId="42" type="noConversion"/>
   </si>
 </sst>
@@ -13795,7 +13803,7 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="266">
+  <cellXfs count="267">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -14584,6 +14592,9 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Normal" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
@@ -15467,8 +15478,8 @@
       </c>
     </row>
     <row r="7" spans="1:23" ht="16.5" customHeight="1">
-      <c r="A7" s="10" t="s">
-        <v>111</v>
+      <c r="A7" s="266" t="s">
+        <v>2393</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>111</v>
@@ -15538,8 +15549,12 @@
       </c>
     </row>
     <row r="8" spans="1:23">
-      <c r="A8" s="14"/>
-      <c r="B8" s="14"/>
+      <c r="A8" s="14" t="s">
+        <v>2394</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>2394</v>
+      </c>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erang\Desktop\RELIC\Assets\ExcelSource\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k2104200063\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37BC50F5-399C-48EE-8CE0-2D9748691BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1822E854-B8B2-48B2-9301-843E9A185008}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25838,6 +25838,7 @@
   </sheetData>
   <phoneticPr fontId="42" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -30599,7 +30600,7 @@
         <v>1</v>
       </c>
       <c r="H61" s="65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I61" s="65" t="s">
         <v>79</v>
@@ -31235,7 +31236,7 @@
         <v>1</v>
       </c>
       <c r="H73" s="71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I73" s="71" t="s">
         <v>95</v>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erang\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B78B157B-3AE3-4A6B-8BA7-C52ADC6238FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E3148B1-AFEF-44C6-8544-ED945EA4450F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5001" uniqueCount="2395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5003" uniqueCount="2396">
   <si>
     <t>캐릭터ID</t>
   </si>
@@ -12864,10 +12864,6 @@
     <phoneticPr fontId="42" type="noConversion"/>
   </si>
   <si>
-    <t>Mon_10</t>
-    <phoneticPr fontId="42" type="noConversion"/>
-  </si>
-  <si>
     <t>S_Monster_28</t>
     <phoneticPr fontId="42" type="noConversion"/>
   </si>
@@ -12877,6 +12873,14 @@
   </si>
   <si>
     <t>Range_15</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mon_08</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mon_09</t>
     <phoneticPr fontId="42" type="noConversion"/>
   </si>
 </sst>
@@ -32495,7 +32499,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="17" t="s">
-        <v>2394</v>
+        <v>2393</v>
       </c>
       <c r="J29" s="16" t="s">
         <v>336</v>
@@ -32513,7 +32517,7 @@
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="16" t="s">
-        <v>2392</v>
+        <v>2391</v>
       </c>
       <c r="B30" s="84" t="s">
         <v>678</v>
@@ -33444,7 +33448,7 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="91" t="s">
-        <v>2393</v>
+        <v>2392</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>765</v>
@@ -41357,10 +41361,10 @@
         <v>1427</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>2391</v>
+        <v>2394</v>
       </c>
       <c r="C49" s="4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D49" s="4">
         <v>-1</v>
@@ -41403,6 +41407,24 @@
       </c>
     </row>
     <row r="50" spans="1:16">
+      <c r="A50" s="4" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>2395</v>
+      </c>
+      <c r="C50" s="4">
+        <v>22</v>
+      </c>
+      <c r="D50" s="4">
+        <v>-1</v>
+      </c>
+      <c r="E50" s="4">
+        <v>-1</v>
+      </c>
+      <c r="F50" s="4">
+        <v>-1</v>
+      </c>
       <c r="M50" s="183"/>
       <c r="N50" s="183"/>
       <c r="O50" s="183"/>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erang\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{545C8FCC-002E-4DE4-883E-E708B015DF2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{443C0138-FC4E-430E-B995-F0E46DED9C66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25860" yWindow="480" windowWidth="21015" windowHeight="27555" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5113" uniqueCount="2498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5078" uniqueCount="2496">
   <si>
     <t>캐릭터ID</t>
   </si>
@@ -13088,10 +13088,6 @@
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
   <si>
-    <t>예측 : 뒷면, 레드 더스티움 25 획득</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
     <t>event7</t>
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
@@ -13103,34 +13099,6 @@
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
   <si>
-    <t>Heads</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tails</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>예측 : 뒷면, 레드 더스티움 30 획득</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>예측 : 뒷면, 레드 더스티움 35 획득</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>예측 : 앞면, 레드 더스티움 25 획득</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>예측 : 앞면, 레드 더스티움 30 획득</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>예측 : 앞면, 레드 더스티움 35 획득</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
     <t>“광맥 곳곳에 균열이 생겼다."</t>
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
@@ -13368,10 +13336,6 @@
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
   <si>
-    <t>Event_10_E</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
     <t>생명을 대가로 바친다.</t>
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
@@ -13384,10 +13348,6 @@
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
   <si>
-    <t>"낡은 동전 하나를 꺼내 손바닥 위에 올려놓았다."</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
     <t>"대가에 만족한 듯 희미한 미소를 지었다."</t>
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
@@ -13404,14 +13364,6 @@
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
   <si>
-    <t>앞면에 건다.</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>뒷면에 건다.</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
     <t>전체 생명력 5감소, 무작위 레어~유니크 유물 획득</t>
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
@@ -13428,18 +13380,6 @@
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
   <si>
-    <t>예측 : 앞면, 무작위 일반~유니크 유물 획득</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>예측 : 뒷면, 무작위 레어~에픽 유물 획득</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>예측 성공 시 무작위 유물 획득</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
     <t>event10</t>
   </si>
   <si>
@@ -13539,6 +13479,54 @@
   </si>
   <si>
     <t>Event_T_02</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>예측 성공 시, 레드 더스티움 25 획득</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>이벤트 종료</t>
+  </si>
+  <si>
+    <t>무시한다.</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>그만한다.</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>예측 성공 시, 레드 더스티움 30 획득</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>예측 성공 시, 레드 더스티움 35 획득</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>Immediate</t>
+  </si>
+  <si>
+    <t>EndEvent</t>
+  </si>
+  <si>
+    <t>PlayerChoice</t>
+  </si>
+  <si>
+    <t>Event_07_E</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>“광맥을 건드리지 않고 자리를 떠났다.”</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>예측 성공 시, 무작위 유물 획득</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>PlayerChoice</t>
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
 </sst>
@@ -14478,7 +14466,7 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="322">
+  <cellXfs count="327">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -15382,10 +15370,6 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -15428,6 +15412,25 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
@@ -39841,7 +39844,7 @@
         <v>216</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>2488</v>
+        <v>2473</v>
       </c>
       <c r="E11" s="16">
         <v>0</v>
@@ -39867,7 +39870,7 @@
         <v>216</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>2490</v>
+        <v>2475</v>
       </c>
       <c r="E12" s="16">
         <v>0</v>
@@ -40199,7 +40202,7 @@
         <v>1371</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>2481</v>
+        <v>2466</v>
       </c>
       <c r="C25" s="16" t="s">
         <v>1356</v>
@@ -40208,7 +40211,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>2396</v>
+        <v>2388</v>
       </c>
       <c r="F25" s="16" t="s">
         <v>1314</v>
@@ -40222,7 +40225,7 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="16" t="s">
-        <v>2487</v>
+        <v>2472</v>
       </c>
       <c r="B26" s="16" t="s">
         <v>1372</v>
@@ -40251,7 +40254,7 @@
         <v>1374</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>2482</v>
+        <v>2467</v>
       </c>
       <c r="C27" s="16" t="s">
         <v>1356</v>
@@ -40260,7 +40263,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>2445</v>
+        <v>2437</v>
       </c>
       <c r="F27" s="16" t="s">
         <v>1314</v>
@@ -40277,7 +40280,7 @@
         <v>1377</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>2483</v>
+        <v>2468</v>
       </c>
       <c r="C28" s="16" t="s">
         <v>1356</v>
@@ -40286,7 +40289,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>2485</v>
+        <v>2470</v>
       </c>
       <c r="F28" s="16" t="s">
         <v>1314</v>
@@ -40303,7 +40306,7 @@
         <v>1379</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>2484</v>
+        <v>2469</v>
       </c>
       <c r="C29" s="16" t="s">
         <v>1356</v>
@@ -40312,7 +40315,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>2486</v>
+        <v>2471</v>
       </c>
       <c r="F29" s="16" t="s">
         <v>1314</v>
@@ -40446,7 +40449,7 @@
         <v>0</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>2496</v>
+        <v>2481</v>
       </c>
       <c r="F36" s="16" t="s">
         <v>1314</v>
@@ -41466,7 +41469,7 @@
     </row>
     <row r="24" spans="1:26" ht="17.25" customHeight="1">
       <c r="A24" s="258" t="s">
-        <v>2489</v>
+        <v>2474</v>
       </c>
       <c r="B24" s="212" t="s">
         <v>214</v>
@@ -41525,7 +41528,7 @@
     </row>
     <row r="25" spans="1:26" ht="17.25" thickBot="1">
       <c r="A25" s="163" t="s">
-        <v>2489</v>
+        <v>2474</v>
       </c>
       <c r="B25" s="164" t="s">
         <v>178</v>
@@ -41564,7 +41567,7 @@
     </row>
     <row r="26" spans="1:26">
       <c r="A26" s="156" t="s">
-        <v>2491</v>
+        <v>2476</v>
       </c>
       <c r="B26" s="157" t="s">
         <v>214</v>
@@ -41623,7 +41626,7 @@
     </row>
     <row r="27" spans="1:26" ht="17.25" customHeight="1" thickBot="1">
       <c r="A27" s="163" t="s">
-        <v>2491</v>
+        <v>2476</v>
       </c>
       <c r="B27" s="164" t="s">
         <v>185</v>
@@ -41662,7 +41665,7 @@
     </row>
     <row r="28" spans="1:26" ht="17.25" thickBot="1">
       <c r="A28" s="168" t="s">
-        <v>2492</v>
+        <v>2477</v>
       </c>
       <c r="B28" s="169" t="s">
         <v>222</v>
@@ -41716,7 +41719,7 @@
     </row>
     <row r="29" spans="1:26">
       <c r="A29" s="156" t="s">
-        <v>2493</v>
+        <v>2478</v>
       </c>
       <c r="B29" s="157" t="s">
         <v>202</v>
@@ -41770,7 +41773,7 @@
     </row>
     <row r="30" spans="1:26" ht="17.25" customHeight="1" thickBot="1">
       <c r="A30" s="163" t="s">
-        <v>2493</v>
+        <v>2478</v>
       </c>
       <c r="B30" s="164" t="s">
         <v>229</v>
@@ -41805,7 +41808,7 @@
     </row>
     <row r="31" spans="1:26">
       <c r="A31" s="156" t="s">
-        <v>2494</v>
+        <v>2479</v>
       </c>
       <c r="B31" s="157" t="s">
         <v>208</v>
@@ -41864,7 +41867,7 @@
     </row>
     <row r="32" spans="1:26" ht="17.25" customHeight="1" thickBot="1">
       <c r="A32" s="163" t="s">
-        <v>2494</v>
+        <v>2479</v>
       </c>
       <c r="B32" s="164" t="s">
         <v>229</v>
@@ -41903,7 +41906,7 @@
     </row>
     <row r="33" spans="1:26" ht="17.25" thickBot="1">
       <c r="A33" s="168" t="s">
-        <v>2495</v>
+        <v>2480</v>
       </c>
       <c r="B33" s="169" t="s">
         <v>2127</v>
@@ -42267,16 +42270,16 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:AA73"/>
+  <dimension ref="A1:AA72"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="11.5" style="316" customWidth="1"/>
-    <col min="2" max="2" width="22.5" style="316" customWidth="1"/>
-    <col min="3" max="3" width="90.25" style="316" customWidth="1"/>
+    <col min="1" max="1" width="11.5" style="314" customWidth="1"/>
+    <col min="2" max="2" width="22.5" style="314" customWidth="1"/>
+    <col min="3" max="3" width="90.25" style="314" customWidth="1"/>
     <col min="4" max="4" width="13.25" style="287" customWidth="1"/>
     <col min="5" max="5" width="31.875" style="287" customWidth="1"/>
-    <col min="6" max="6" width="58.625" style="316" customWidth="1"/>
-    <col min="7" max="7" width="58.625" style="317" customWidth="1"/>
+    <col min="6" max="6" width="58.625" style="314" customWidth="1"/>
+    <col min="7" max="7" width="58.625" style="315" customWidth="1"/>
     <col min="8" max="8" width="13.75" style="287" customWidth="1"/>
     <col min="9" max="9" width="26.625" style="287" customWidth="1"/>
     <col min="10" max="10" width="15.5" style="287" customWidth="1"/>
@@ -42290,8 +42293,8 @@
     <col min="19" max="23" width="17.75" style="287" customWidth="1"/>
     <col min="24" max="24" width="33.5" style="287" customWidth="1"/>
     <col min="25" max="25" width="43.875" style="287" customWidth="1"/>
-    <col min="26" max="26" width="26.75" style="318" customWidth="1"/>
-    <col min="27" max="27" width="24.75" style="318" customWidth="1"/>
+    <col min="26" max="26" width="26.75" style="316" customWidth="1"/>
+    <col min="27" max="27" width="24.75" style="316" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="16.5" customHeight="1">
@@ -42794,7 +42797,7 @@
       </c>
       <c r="B9" s="272"/>
       <c r="C9" s="272" t="s">
-        <v>2423</v>
+        <v>2415</v>
       </c>
       <c r="D9" s="185"/>
       <c r="E9" s="185"/>
@@ -43198,7 +43201,7 @@
         <v>2309</v>
       </c>
       <c r="F18" s="272" t="s">
-        <v>2464</v>
+        <v>2452</v>
       </c>
       <c r="G18" s="265" t="s">
         <v>2306</v>
@@ -43207,7 +43210,7 @@
         <v>2305</v>
       </c>
       <c r="I18" s="268" t="s">
-        <v>2475</v>
+        <v>2460</v>
       </c>
       <c r="J18" s="268" t="s">
         <v>2308</v>
@@ -43267,7 +43270,7 @@
         <v>2310</v>
       </c>
       <c r="F19" s="272" t="s">
-        <v>2465</v>
+        <v>2453</v>
       </c>
       <c r="G19" s="186" t="s">
         <v>2306</v>
@@ -43276,7 +43279,7 @@
         <v>2305</v>
       </c>
       <c r="I19" s="185" t="s">
-        <v>2476</v>
+        <v>2461</v>
       </c>
       <c r="J19" s="185" t="s">
         <v>2308</v>
@@ -43454,7 +43457,7 @@
       </c>
       <c r="B23" s="298"/>
       <c r="C23" s="275" t="s">
-        <v>2424</v>
+        <v>2416</v>
       </c>
       <c r="D23" s="266"/>
       <c r="E23" s="266"/>
@@ -44334,27 +44337,27 @@
         <v>2373</v>
       </c>
       <c r="C41" s="274" t="s">
-        <v>2425</v>
+        <v>2417</v>
       </c>
       <c r="D41" s="268">
         <v>1</v>
       </c>
       <c r="E41" s="268" t="s">
-        <v>2393</v>
+        <v>2385</v>
       </c>
       <c r="F41" s="274" t="s">
-        <v>2389</v>
+        <v>2483</v>
       </c>
       <c r="G41" s="265"/>
       <c r="H41" s="268" t="s">
-        <v>2384</v>
+        <v>2383</v>
       </c>
       <c r="I41" s="268"/>
       <c r="J41" s="268"/>
       <c r="K41" s="268"/>
       <c r="L41" s="268"/>
       <c r="M41" s="268" t="s">
-        <v>2385</v>
+        <v>2491</v>
       </c>
       <c r="N41" s="268" t="s">
         <v>2364</v>
@@ -44377,7 +44380,7 @@
       <c r="V41" s="268"/>
       <c r="W41" s="268"/>
       <c r="X41" s="268" t="s">
-        <v>2382</v>
+        <v>2381</v>
       </c>
       <c r="Y41" s="268" t="s">
         <v>2267</v>
@@ -44399,54 +44402,42 @@
         <v>2</v>
       </c>
       <c r="E42" s="185" t="s">
-        <v>2393</v>
+        <v>2485</v>
       </c>
       <c r="F42" s="272" t="s">
-        <v>2381</v>
+        <v>2484</v>
       </c>
       <c r="G42" s="186"/>
       <c r="H42" s="185" t="s">
-        <v>2383</v>
+        <v>2243</v>
       </c>
       <c r="I42" s="185"/>
       <c r="J42" s="185"/>
       <c r="K42" s="185"/>
       <c r="L42" s="185"/>
-      <c r="M42" s="185" t="s">
-        <v>2386</v>
-      </c>
+      <c r="M42" s="185"/>
       <c r="N42" s="185" t="s">
-        <v>1437</v>
-      </c>
-      <c r="O42" s="185" t="s">
-        <v>2307</v>
-      </c>
+        <v>2490</v>
+      </c>
+      <c r="O42" s="185"/>
       <c r="P42" s="185"/>
-      <c r="Q42" s="185">
-        <v>25</v>
-      </c>
+      <c r="Q42" s="185"/>
       <c r="R42" s="185"/>
       <c r="S42" s="185" t="s">
-        <v>2374</v>
-      </c>
-      <c r="T42" s="185" t="s">
-        <v>2380</v>
-      </c>
+        <v>2492</v>
+      </c>
+      <c r="T42" s="185"/>
       <c r="U42" s="185"/>
       <c r="V42" s="185"/>
       <c r="W42" s="185"/>
       <c r="X42" s="185" t="s">
         <v>1443</v>
       </c>
-      <c r="Y42" s="185" t="s">
-        <v>1433</v>
-      </c>
+      <c r="Y42" s="185"/>
       <c r="Z42" s="185" t="s">
         <v>1443</v>
       </c>
-      <c r="AA42" s="293" t="s">
-        <v>1434</v>
-      </c>
+      <c r="AA42" s="293"/>
     </row>
     <row r="43" spans="1:27" ht="16.5" customHeight="1">
       <c r="A43" s="292" t="s">
@@ -44460,21 +44451,21 @@
         <v>1</v>
       </c>
       <c r="E43" s="185" t="s">
-        <v>2394</v>
+        <v>2386</v>
       </c>
       <c r="F43" s="272" t="s">
-        <v>2390</v>
+        <v>2487</v>
       </c>
       <c r="G43" s="186"/>
       <c r="H43" s="185" t="s">
-        <v>2383</v>
+        <v>2382</v>
       </c>
       <c r="I43" s="185"/>
       <c r="J43" s="185"/>
       <c r="K43" s="185"/>
       <c r="L43" s="185"/>
       <c r="M43" s="185" t="s">
-        <v>2385</v>
+        <v>2491</v>
       </c>
       <c r="N43" s="185" t="s">
         <v>1437</v>
@@ -44519,54 +44510,42 @@
         <v>2</v>
       </c>
       <c r="E44" s="185" t="s">
-        <v>2394</v>
+        <v>2486</v>
       </c>
       <c r="F44" s="272" t="s">
-        <v>2387</v>
+        <v>2484</v>
       </c>
       <c r="G44" s="186"/>
       <c r="H44" s="185" t="s">
-        <v>2383</v>
+        <v>2489</v>
       </c>
       <c r="I44" s="185"/>
       <c r="J44" s="185"/>
       <c r="K44" s="185"/>
       <c r="L44" s="185"/>
-      <c r="M44" s="185" t="s">
-        <v>2386</v>
-      </c>
+      <c r="M44" s="185"/>
       <c r="N44" s="185" t="s">
-        <v>1437</v>
-      </c>
-      <c r="O44" s="185" t="s">
-        <v>2307</v>
-      </c>
+        <v>2490</v>
+      </c>
+      <c r="O44" s="185"/>
       <c r="P44" s="185"/>
-      <c r="Q44" s="185">
-        <v>30</v>
-      </c>
+      <c r="Q44" s="185"/>
       <c r="R44" s="185"/>
       <c r="S44" s="185" t="s">
-        <v>2375</v>
-      </c>
-      <c r="T44" s="185" t="s">
-        <v>2380</v>
-      </c>
+        <v>2492</v>
+      </c>
+      <c r="T44" s="185"/>
       <c r="U44" s="185"/>
       <c r="V44" s="185"/>
       <c r="W44" s="185"/>
       <c r="X44" s="185" t="s">
         <v>1443</v>
       </c>
-      <c r="Y44" s="185" t="s">
-        <v>1433</v>
-      </c>
+      <c r="Y44" s="185"/>
       <c r="Z44" s="185" t="s">
         <v>1443</v>
       </c>
-      <c r="AA44" s="293" t="s">
-        <v>1434</v>
-      </c>
+      <c r="AA44" s="293"/>
     </row>
     <row r="45" spans="1:27" ht="16.5" customHeight="1">
       <c r="A45" s="292" t="s">
@@ -44574,16 +44553,16 @@
       </c>
       <c r="B45" s="297"/>
       <c r="C45" s="272" t="s">
-        <v>2392</v>
+        <v>2384</v>
       </c>
       <c r="D45" s="185">
         <v>1</v>
       </c>
       <c r="E45" s="185" t="s">
-        <v>2395</v>
+        <v>2387</v>
       </c>
       <c r="F45" s="272" t="s">
-        <v>2391</v>
+        <v>2488</v>
       </c>
       <c r="G45" s="186"/>
       <c r="H45" s="185" t="s">
@@ -44594,7 +44573,7 @@
       <c r="K45" s="185"/>
       <c r="L45" s="185"/>
       <c r="M45" s="185" t="s">
-        <v>2385</v>
+        <v>2491</v>
       </c>
       <c r="N45" s="185" t="s">
         <v>1437</v>
@@ -44639,54 +44618,42 @@
         <v>2</v>
       </c>
       <c r="E46" s="185" t="s">
-        <v>2395</v>
+        <v>2486</v>
       </c>
       <c r="F46" s="272" t="s">
-        <v>2388</v>
+        <v>2484</v>
       </c>
       <c r="G46" s="186"/>
       <c r="H46" s="185" t="s">
-        <v>2384</v>
+        <v>2489</v>
       </c>
       <c r="I46" s="185"/>
       <c r="J46" s="185"/>
       <c r="K46" s="185"/>
       <c r="L46" s="185"/>
-      <c r="M46" s="185" t="s">
-        <v>2386</v>
-      </c>
+      <c r="M46" s="185"/>
       <c r="N46" s="185" t="s">
-        <v>1437</v>
-      </c>
-      <c r="O46" s="185" t="s">
-        <v>2307</v>
-      </c>
+        <v>2490</v>
+      </c>
+      <c r="O46" s="185"/>
       <c r="P46" s="185"/>
-      <c r="Q46" s="185">
-        <v>35</v>
-      </c>
+      <c r="Q46" s="185"/>
       <c r="R46" s="185"/>
       <c r="S46" s="185" t="s">
-        <v>2379</v>
-      </c>
-      <c r="T46" s="185" t="s">
-        <v>2380</v>
-      </c>
+        <v>2492</v>
+      </c>
+      <c r="T46" s="185"/>
       <c r="U46" s="185"/>
       <c r="V46" s="185"/>
       <c r="W46" s="185"/>
       <c r="X46" s="185" t="s">
         <v>1443</v>
       </c>
-      <c r="Y46" s="185" t="s">
-        <v>1433</v>
-      </c>
+      <c r="Y46" s="185"/>
       <c r="Z46" s="185" t="s">
         <v>1443</v>
       </c>
-      <c r="AA46" s="293" t="s">
-        <v>1434</v>
-      </c>
+      <c r="AA46" s="293"/>
     </row>
     <row r="47" spans="1:27" ht="16.5" customHeight="1">
       <c r="A47" s="292" t="s">
@@ -44717,7 +44684,7 @@
       <c r="V47" s="280"/>
       <c r="W47" s="280"/>
       <c r="X47" s="280" t="s">
-        <v>2382</v>
+        <v>2381</v>
       </c>
       <c r="Y47" s="280"/>
       <c r="Z47" s="280" t="s">
@@ -44725,154 +44692,144 @@
       </c>
       <c r="AA47" s="304"/>
     </row>
-    <row r="48" spans="1:27" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A48" s="294" t="s">
+    <row r="48" spans="1:27" ht="16.5" customHeight="1">
+      <c r="A48" s="292" t="s">
         <v>2380</v>
       </c>
-      <c r="B48" s="298"/>
-      <c r="C48" s="298" t="s">
+      <c r="B48" s="297"/>
+      <c r="C48" s="297" t="s">
         <v>2378</v>
       </c>
-      <c r="D48" s="281"/>
-      <c r="E48" s="281"/>
-      <c r="F48" s="305"/>
-      <c r="G48" s="306"/>
-      <c r="H48" s="266"/>
-      <c r="I48" s="281"/>
-      <c r="J48" s="281"/>
-      <c r="K48" s="281"/>
-      <c r="L48" s="281"/>
-      <c r="M48" s="281"/>
-      <c r="N48" s="281"/>
-      <c r="O48" s="281"/>
-      <c r="P48" s="281"/>
-      <c r="Q48" s="281"/>
-      <c r="R48" s="281"/>
-      <c r="S48" s="281"/>
-      <c r="T48" s="281"/>
-      <c r="U48" s="281"/>
-      <c r="V48" s="281"/>
-      <c r="W48" s="281"/>
-      <c r="X48" s="281" t="s">
+      <c r="D48" s="280"/>
+      <c r="E48" s="280"/>
+      <c r="F48" s="130"/>
+      <c r="G48" s="303"/>
+      <c r="H48" s="185"/>
+      <c r="I48" s="280"/>
+      <c r="J48" s="280"/>
+      <c r="K48" s="280"/>
+      <c r="L48" s="280"/>
+      <c r="M48" s="280"/>
+      <c r="N48" s="280"/>
+      <c r="O48" s="280"/>
+      <c r="P48" s="280"/>
+      <c r="Q48" s="280"/>
+      <c r="R48" s="280"/>
+      <c r="S48" s="280"/>
+      <c r="T48" s="280"/>
+      <c r="U48" s="280"/>
+      <c r="V48" s="280"/>
+      <c r="W48" s="280"/>
+      <c r="X48" s="280" t="s">
         <v>1443</v>
       </c>
-      <c r="Y48" s="281"/>
-      <c r="Z48" s="266" t="s">
+      <c r="Y48" s="280"/>
+      <c r="Z48" s="185" t="s">
         <v>1443</v>
       </c>
-      <c r="AA48" s="295"/>
-    </row>
-    <row r="49" spans="1:27" ht="16.5" customHeight="1">
-      <c r="A49" s="307" t="s">
-        <v>2397</v>
-      </c>
-      <c r="B49" s="308" t="s">
-        <v>2398</v>
-      </c>
-      <c r="C49" s="308" t="s">
-        <v>2413</v>
-      </c>
-      <c r="D49" s="283">
-        <v>1</v>
-      </c>
-      <c r="E49" s="283" t="s">
-        <v>2399</v>
-      </c>
-      <c r="F49" s="308"/>
-      <c r="G49" s="283"/>
-      <c r="H49" s="283" t="s">
+      <c r="AA48" s="293"/>
+    </row>
+    <row r="49" spans="1:27" ht="16.5" customHeight="1" thickBot="1">
+      <c r="A49" s="320" t="s">
+        <v>2492</v>
+      </c>
+      <c r="B49" s="321"/>
+      <c r="C49" s="321" t="s">
+        <v>2493</v>
+      </c>
+      <c r="D49" s="322"/>
+      <c r="E49" s="322"/>
+      <c r="F49" s="323"/>
+      <c r="G49" s="324"/>
+      <c r="H49" s="325"/>
+      <c r="I49" s="322"/>
+      <c r="J49" s="322"/>
+      <c r="K49" s="322"/>
+      <c r="L49" s="322"/>
+      <c r="M49" s="322"/>
+      <c r="N49" s="322"/>
+      <c r="O49" s="322"/>
+      <c r="P49" s="322"/>
+      <c r="Q49" s="322"/>
+      <c r="R49" s="322"/>
+      <c r="S49" s="322"/>
+      <c r="T49" s="322"/>
+      <c r="U49" s="322"/>
+      <c r="V49" s="322"/>
+      <c r="W49" s="322"/>
+      <c r="X49" s="322" t="s">
+        <v>1443</v>
+      </c>
+      <c r="Y49" s="322"/>
+      <c r="Z49" s="325" t="s">
+        <v>1443</v>
+      </c>
+      <c r="AA49" s="326"/>
+    </row>
+    <row r="50" spans="1:27" ht="16.5" customHeight="1">
+      <c r="A50" s="305" t="s">
+        <v>2389</v>
+      </c>
+      <c r="B50" s="306" t="s">
+        <v>2390</v>
+      </c>
+      <c r="C50" s="306" t="s">
+        <v>2405</v>
+      </c>
+      <c r="D50" s="283">
+        <v>1</v>
+      </c>
+      <c r="E50" s="283" t="s">
+        <v>2391</v>
+      </c>
+      <c r="F50" s="306"/>
+      <c r="G50" s="283"/>
+      <c r="H50" s="283" t="s">
         <v>2243</v>
       </c>
-      <c r="I49" s="283"/>
-      <c r="J49" s="283"/>
-      <c r="K49" s="283"/>
-      <c r="L49" s="283"/>
-      <c r="M49" s="283"/>
-      <c r="N49" s="283" t="s">
-        <v>2416</v>
-      </c>
-      <c r="O49" s="283" t="s">
-        <v>2417</v>
-      </c>
-      <c r="P49" s="283"/>
-      <c r="Q49" s="283"/>
-      <c r="R49" s="283"/>
-      <c r="S49" s="283" t="s">
+      <c r="I50" s="283"/>
+      <c r="J50" s="283"/>
+      <c r="K50" s="283"/>
+      <c r="L50" s="283"/>
+      <c r="M50" s="283"/>
+      <c r="N50" s="283" t="s">
+        <v>2408</v>
+      </c>
+      <c r="O50" s="283" t="s">
+        <v>2409</v>
+      </c>
+      <c r="P50" s="283"/>
+      <c r="Q50" s="283"/>
+      <c r="R50" s="283"/>
+      <c r="S50" s="283" t="s">
+        <v>2394</v>
+      </c>
+      <c r="T50" s="283"/>
+      <c r="U50" s="283"/>
+      <c r="V50" s="283"/>
+      <c r="W50" s="283"/>
+      <c r="X50" s="283" t="s">
         <v>2402</v>
       </c>
-      <c r="T49" s="283"/>
-      <c r="U49" s="283"/>
-      <c r="V49" s="283"/>
-      <c r="W49" s="283"/>
-      <c r="X49" s="283" t="s">
-        <v>2410</v>
-      </c>
-      <c r="Y49" s="283"/>
-      <c r="Z49" s="309" t="s">
-        <v>2409</v>
-      </c>
-      <c r="AA49" s="310"/>
-    </row>
-    <row r="50" spans="1:27" ht="16.5" customHeight="1">
-      <c r="A50" s="277" t="s">
-        <v>2396</v>
-      </c>
-      <c r="B50" s="311"/>
-      <c r="C50" s="311"/>
-      <c r="D50" s="284">
-        <v>2</v>
-      </c>
-      <c r="E50" s="284" t="s">
+      <c r="Y50" s="283"/>
+      <c r="Z50" s="307" t="s">
         <v>2401</v>
       </c>
-      <c r="F50" s="311"/>
-      <c r="G50" s="284"/>
-      <c r="H50" s="284" t="s">
-        <v>2243</v>
-      </c>
-      <c r="I50" s="284"/>
-      <c r="J50" s="284"/>
-      <c r="K50" s="284"/>
-      <c r="L50" s="284"/>
-      <c r="M50" s="284"/>
-      <c r="N50" s="284" t="s">
-        <v>2416</v>
-      </c>
-      <c r="O50" s="284" t="s">
-        <v>2418</v>
-      </c>
-      <c r="P50" s="284"/>
-      <c r="Q50" s="284"/>
-      <c r="R50" s="284"/>
-      <c r="S50" s="284" t="s">
-        <v>2402</v>
-      </c>
-      <c r="T50" s="284"/>
-      <c r="U50" s="284"/>
-      <c r="V50" s="284"/>
-      <c r="W50" s="284"/>
-      <c r="X50" s="284" t="s">
-        <v>2409</v>
-      </c>
-      <c r="Y50" s="284"/>
-      <c r="Z50" s="280" t="s">
-        <v>2409</v>
-      </c>
-      <c r="AA50" s="304"/>
+      <c r="AA50" s="308"/>
     </row>
     <row r="51" spans="1:27" ht="16.5" customHeight="1">
       <c r="A51" s="277" t="s">
-        <v>2397</v>
-      </c>
-      <c r="B51" s="311"/>
-      <c r="C51" s="311"/>
+        <v>2388</v>
+      </c>
+      <c r="B51" s="309"/>
+      <c r="C51" s="309"/>
       <c r="D51" s="284">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E51" s="284" t="s">
-        <v>2400</v>
-      </c>
-      <c r="F51" s="311"/>
+        <v>2393</v>
+      </c>
+      <c r="F51" s="309"/>
       <c r="G51" s="284"/>
       <c r="H51" s="284" t="s">
         <v>2243</v>
@@ -44883,47 +44840,43 @@
       <c r="L51" s="284"/>
       <c r="M51" s="284"/>
       <c r="N51" s="284" t="s">
-        <v>2416</v>
+        <v>2408</v>
       </c>
       <c r="O51" s="284" t="s">
-        <v>2419</v>
+        <v>2410</v>
       </c>
       <c r="P51" s="284"/>
       <c r="Q51" s="284"/>
       <c r="R51" s="284"/>
       <c r="S51" s="284" t="s">
-        <v>2402</v>
+        <v>2394</v>
       </c>
       <c r="T51" s="284"/>
       <c r="U51" s="284"/>
       <c r="V51" s="284"/>
       <c r="W51" s="284"/>
       <c r="X51" s="284" t="s">
-        <v>2409</v>
+        <v>2401</v>
       </c>
       <c r="Y51" s="284"/>
       <c r="Z51" s="280" t="s">
-        <v>2409</v>
+        <v>2401</v>
       </c>
       <c r="AA51" s="304"/>
     </row>
     <row r="52" spans="1:27" ht="16.5" customHeight="1">
       <c r="A52" s="277" t="s">
-        <v>2402</v>
-      </c>
-      <c r="B52" s="311"/>
-      <c r="C52" s="311" t="s">
-        <v>2414</v>
-      </c>
+        <v>2389</v>
+      </c>
+      <c r="B52" s="309"/>
+      <c r="C52" s="309"/>
       <c r="D52" s="284">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E52" s="284" t="s">
-        <v>2403</v>
-      </c>
-      <c r="F52" s="311" t="s">
-        <v>2406</v>
-      </c>
+        <v>2392</v>
+      </c>
+      <c r="F52" s="309"/>
       <c r="G52" s="284"/>
       <c r="H52" s="284" t="s">
         <v>2243</v>
@@ -44934,119 +44887,101 @@
       <c r="L52" s="284"/>
       <c r="M52" s="284"/>
       <c r="N52" s="284" t="s">
-        <v>2248</v>
+        <v>2408</v>
       </c>
       <c r="O52" s="284" t="s">
-        <v>2420</v>
+        <v>2411</v>
       </c>
       <c r="P52" s="284"/>
-      <c r="Q52" s="284">
-        <v>5</v>
-      </c>
+      <c r="Q52" s="284"/>
       <c r="R52" s="284"/>
       <c r="S52" s="284" t="s">
-        <v>2412</v>
+        <v>2394</v>
       </c>
       <c r="T52" s="284"/>
       <c r="U52" s="284"/>
       <c r="V52" s="284"/>
       <c r="W52" s="284"/>
       <c r="X52" s="284" t="s">
-        <v>2409</v>
-      </c>
-      <c r="Y52" s="280" t="s">
-        <v>2267</v>
-      </c>
+        <v>2401</v>
+      </c>
+      <c r="Y52" s="284"/>
       <c r="Z52" s="280" t="s">
-        <v>2409</v>
-      </c>
-      <c r="AA52" s="304" t="s">
-        <v>2362</v>
-      </c>
+        <v>2401</v>
+      </c>
+      <c r="AA52" s="304"/>
     </row>
     <row r="53" spans="1:27" s="3" customFormat="1" ht="16.5" customHeight="1">
       <c r="A53" s="277" t="s">
-        <v>2402</v>
-      </c>
-      <c r="B53" s="297"/>
-      <c r="C53" s="297"/>
-      <c r="D53" s="280">
-        <v>2</v>
-      </c>
-      <c r="E53" s="280" t="s">
+        <v>2394</v>
+      </c>
+      <c r="B53" s="309"/>
+      <c r="C53" s="309" t="s">
+        <v>2406</v>
+      </c>
+      <c r="D53" s="284">
+        <v>1</v>
+      </c>
+      <c r="E53" s="284" t="s">
+        <v>2395</v>
+      </c>
+      <c r="F53" s="309" t="s">
+        <v>2398</v>
+      </c>
+      <c r="G53" s="284"/>
+      <c r="H53" s="284" t="s">
+        <v>2243</v>
+      </c>
+      <c r="I53" s="284"/>
+      <c r="J53" s="284"/>
+      <c r="K53" s="284"/>
+      <c r="L53" s="284"/>
+      <c r="M53" s="284"/>
+      <c r="N53" s="284" t="s">
+        <v>2248</v>
+      </c>
+      <c r="O53" s="284" t="s">
+        <v>2412</v>
+      </c>
+      <c r="P53" s="284"/>
+      <c r="Q53" s="284">
+        <v>5</v>
+      </c>
+      <c r="R53" s="284"/>
+      <c r="S53" s="284" t="s">
         <v>2404</v>
       </c>
-      <c r="F53" s="297" t="s">
-        <v>2407</v>
-      </c>
-      <c r="G53" s="297" t="s">
-        <v>2306</v>
-      </c>
-      <c r="H53" s="280" t="s">
-        <v>2305</v>
-      </c>
-      <c r="I53" s="280" t="s">
-        <v>2477</v>
-      </c>
-      <c r="J53" s="280" t="s">
-        <v>2308</v>
-      </c>
-      <c r="K53" s="280" t="s">
-        <v>2247</v>
-      </c>
-      <c r="L53" s="280">
-        <v>20</v>
-      </c>
-      <c r="M53" s="280"/>
-      <c r="N53" s="280" t="s">
-        <v>2258</v>
-      </c>
-      <c r="O53" s="280" t="s">
-        <v>2421</v>
-      </c>
-      <c r="P53" s="280" t="s">
-        <v>2336</v>
-      </c>
-      <c r="Q53" s="280">
-        <v>1</v>
-      </c>
-      <c r="R53" s="280">
-        <v>3</v>
-      </c>
-      <c r="S53" s="280" t="s">
-        <v>2412</v>
-      </c>
-      <c r="T53" s="280"/>
-      <c r="U53" s="280"/>
-      <c r="V53" s="280"/>
-      <c r="W53" s="280"/>
-      <c r="X53" s="280" t="s">
-        <v>2409</v>
-      </c>
-      <c r="Y53" s="185" t="s">
-        <v>2422</v>
+      <c r="T53" s="284"/>
+      <c r="U53" s="284"/>
+      <c r="V53" s="284"/>
+      <c r="W53" s="284"/>
+      <c r="X53" s="284" t="s">
+        <v>2401</v>
+      </c>
+      <c r="Y53" s="280" t="s">
+        <v>2267</v>
       </c>
       <c r="Z53" s="280" t="s">
-        <v>2409</v>
+        <v>2401</v>
       </c>
       <c r="AA53" s="304" t="s">
-        <v>2411</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="54" spans="1:27" s="3" customFormat="1" ht="16.5" customHeight="1">
       <c r="A54" s="277" t="s">
-        <v>2402</v>
+        <v>2394</v>
       </c>
       <c r="B54" s="297"/>
       <c r="C54" s="297"/>
       <c r="D54" s="280">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E54" s="280" t="s">
-        <v>2405</v>
+        <v>2396</v>
       </c>
       <c r="F54" s="297" t="s">
-        <v>2408</v>
+        <v>2399</v>
       </c>
       <c r="G54" s="297" t="s">
         <v>2306</v>
@@ -45055,7 +44990,7 @@
         <v>2305</v>
       </c>
       <c r="I54" s="280" t="s">
-        <v>2478</v>
+        <v>2462</v>
       </c>
       <c r="J54" s="280" t="s">
         <v>2308</v>
@@ -45064,17 +44999,17 @@
         <v>2247</v>
       </c>
       <c r="L54" s="280">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="M54" s="280"/>
       <c r="N54" s="280" t="s">
         <v>2258</v>
       </c>
       <c r="O54" s="280" t="s">
-        <v>2421</v>
+        <v>2413</v>
       </c>
       <c r="P54" s="280" t="s">
-        <v>2337</v>
+        <v>2336</v>
       </c>
       <c r="Q54" s="280">
         <v>1</v>
@@ -45083,190 +45018,204 @@
         <v>3</v>
       </c>
       <c r="S54" s="280" t="s">
-        <v>2412</v>
+        <v>2404</v>
       </c>
       <c r="T54" s="280"/>
       <c r="U54" s="280"/>
       <c r="V54" s="280"/>
       <c r="W54" s="280"/>
       <c r="X54" s="280" t="s">
-        <v>2410</v>
+        <v>2401</v>
       </c>
       <c r="Y54" s="185" t="s">
+        <v>2414</v>
+      </c>
+      <c r="Z54" s="280" t="s">
+        <v>2401</v>
+      </c>
+      <c r="AA54" s="304" t="s">
+        <v>2403</v>
+      </c>
+    </row>
+    <row r="55" spans="1:27" ht="16.5" customHeight="1">
+      <c r="A55" s="277" t="s">
+        <v>2394</v>
+      </c>
+      <c r="B55" s="297"/>
+      <c r="C55" s="297"/>
+      <c r="D55" s="280">
+        <v>3</v>
+      </c>
+      <c r="E55" s="280" t="s">
+        <v>2397</v>
+      </c>
+      <c r="F55" s="297" t="s">
+        <v>2400</v>
+      </c>
+      <c r="G55" s="297" t="s">
+        <v>2306</v>
+      </c>
+      <c r="H55" s="280" t="s">
+        <v>2305</v>
+      </c>
+      <c r="I55" s="280" t="s">
+        <v>2463</v>
+      </c>
+      <c r="J55" s="280" t="s">
+        <v>2308</v>
+      </c>
+      <c r="K55" s="280" t="s">
+        <v>2247</v>
+      </c>
+      <c r="L55" s="280">
+        <v>45</v>
+      </c>
+      <c r="M55" s="280"/>
+      <c r="N55" s="280" t="s">
+        <v>2258</v>
+      </c>
+      <c r="O55" s="280" t="s">
+        <v>2413</v>
+      </c>
+      <c r="P55" s="280" t="s">
+        <v>2337</v>
+      </c>
+      <c r="Q55" s="280">
+        <v>1</v>
+      </c>
+      <c r="R55" s="280">
+        <v>3</v>
+      </c>
+      <c r="S55" s="280" t="s">
+        <v>2404</v>
+      </c>
+      <c r="T55" s="280"/>
+      <c r="U55" s="280"/>
+      <c r="V55" s="280"/>
+      <c r="W55" s="280"/>
+      <c r="X55" s="280" t="s">
+        <v>2402</v>
+      </c>
+      <c r="Y55" s="185" t="s">
         <v>1435</v>
       </c>
-      <c r="Z54" s="280" t="s">
-        <v>2409</v>
-      </c>
-      <c r="AA54" s="304" t="s">
-        <v>2444</v>
-      </c>
-    </row>
-    <row r="55" spans="1:27" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A55" s="278" t="s">
-        <v>2412</v>
-      </c>
-      <c r="B55" s="312"/>
-      <c r="C55" s="312" t="s">
-        <v>2415</v>
-      </c>
-      <c r="D55" s="285"/>
-      <c r="E55" s="285"/>
-      <c r="F55" s="312"/>
-      <c r="G55" s="285"/>
-      <c r="H55" s="285"/>
-      <c r="I55" s="285"/>
-      <c r="J55" s="285"/>
-      <c r="K55" s="285"/>
-      <c r="L55" s="285"/>
-      <c r="M55" s="285"/>
-      <c r="N55" s="285"/>
-      <c r="O55" s="285"/>
-      <c r="P55" s="285"/>
-      <c r="Q55" s="285"/>
-      <c r="R55" s="285"/>
-      <c r="S55" s="285"/>
-      <c r="T55" s="285"/>
-      <c r="U55" s="285"/>
-      <c r="V55" s="285"/>
-      <c r="W55" s="285"/>
-      <c r="X55" s="285" t="s">
-        <v>2410</v>
-      </c>
-      <c r="Y55" s="285"/>
-      <c r="Z55" s="281" t="s">
-        <v>2410</v>
-      </c>
-      <c r="AA55" s="313"/>
-    </row>
-    <row r="56" spans="1:27" ht="16.5" customHeight="1">
-      <c r="A56" s="319" t="s">
-        <v>2426</v>
-      </c>
-      <c r="B56" s="308" t="s">
+      <c r="Z55" s="280" t="s">
+        <v>2401</v>
+      </c>
+      <c r="AA55" s="304" t="s">
+        <v>2436</v>
+      </c>
+    </row>
+    <row r="56" spans="1:27" ht="16.5" customHeight="1" thickBot="1">
+      <c r="A56" s="278" t="s">
+        <v>2404</v>
+      </c>
+      <c r="B56" s="310"/>
+      <c r="C56" s="310" t="s">
+        <v>2407</v>
+      </c>
+      <c r="D56" s="285"/>
+      <c r="E56" s="285"/>
+      <c r="F56" s="310"/>
+      <c r="G56" s="285"/>
+      <c r="H56" s="285"/>
+      <c r="I56" s="285"/>
+      <c r="J56" s="285"/>
+      <c r="K56" s="285"/>
+      <c r="L56" s="285"/>
+      <c r="M56" s="285"/>
+      <c r="N56" s="285"/>
+      <c r="O56" s="285"/>
+      <c r="P56" s="285"/>
+      <c r="Q56" s="285"/>
+      <c r="R56" s="285"/>
+      <c r="S56" s="285"/>
+      <c r="T56" s="285"/>
+      <c r="U56" s="285"/>
+      <c r="V56" s="285"/>
+      <c r="W56" s="285"/>
+      <c r="X56" s="285" t="s">
+        <v>2402</v>
+      </c>
+      <c r="Y56" s="285"/>
+      <c r="Z56" s="281" t="s">
+        <v>2402</v>
+      </c>
+      <c r="AA56" s="311"/>
+    </row>
+    <row r="57" spans="1:27" ht="16.5" customHeight="1">
+      <c r="A57" s="317" t="s">
+        <v>2418</v>
+      </c>
+      <c r="B57" s="306" t="s">
+        <v>2422</v>
+      </c>
+      <c r="C57" s="306" t="s">
+        <v>2423</v>
+      </c>
+      <c r="D57" s="283">
+        <v>1</v>
+      </c>
+      <c r="E57" s="283" t="s">
+        <v>2427</v>
+      </c>
+      <c r="F57" s="306" t="s">
         <v>2430</v>
       </c>
-      <c r="C56" s="308" t="s">
+      <c r="G57" s="283"/>
+      <c r="H57" s="283" t="s">
+        <v>2243</v>
+      </c>
+      <c r="I57" s="283"/>
+      <c r="J57" s="283"/>
+      <c r="K57" s="283"/>
+      <c r="L57" s="283"/>
+      <c r="M57" s="283"/>
+      <c r="N57" s="283" t="s">
+        <v>2433</v>
+      </c>
+      <c r="O57" s="283" t="s">
+        <v>2249</v>
+      </c>
+      <c r="P57" s="283"/>
+      <c r="Q57" s="283">
+        <v>5</v>
+      </c>
+      <c r="R57" s="283"/>
+      <c r="S57" s="283" t="s">
+        <v>2419</v>
+      </c>
+      <c r="T57" s="283"/>
+      <c r="U57" s="283"/>
+      <c r="V57" s="283"/>
+      <c r="W57" s="283"/>
+      <c r="X57" s="283" t="s">
+        <v>2435</v>
+      </c>
+      <c r="Y57" s="283" t="s">
+        <v>2267</v>
+      </c>
+      <c r="Z57" s="307" t="s">
+        <v>1444</v>
+      </c>
+      <c r="AA57" s="308" t="s">
+        <v>2362</v>
+      </c>
+    </row>
+    <row r="58" spans="1:27" ht="16.5" customHeight="1">
+      <c r="A58" s="318" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B58" s="309"/>
+      <c r="C58" s="309"/>
+      <c r="D58" s="284">
+        <v>2</v>
+      </c>
+      <c r="E58" s="284" t="s">
+        <v>2428</v>
+      </c>
+      <c r="F58" s="309" t="s">
         <v>2431</v>
-      </c>
-      <c r="D56" s="283">
-        <v>1</v>
-      </c>
-      <c r="E56" s="283" t="s">
-        <v>2435</v>
-      </c>
-      <c r="F56" s="308" t="s">
-        <v>2438</v>
-      </c>
-      <c r="G56" s="283"/>
-      <c r="H56" s="283" t="s">
-        <v>2243</v>
-      </c>
-      <c r="I56" s="283"/>
-      <c r="J56" s="283"/>
-      <c r="K56" s="283"/>
-      <c r="L56" s="283"/>
-      <c r="M56" s="283"/>
-      <c r="N56" s="283" t="s">
-        <v>2441</v>
-      </c>
-      <c r="O56" s="283" t="s">
-        <v>2249</v>
-      </c>
-      <c r="P56" s="283"/>
-      <c r="Q56" s="283">
-        <v>5</v>
-      </c>
-      <c r="R56" s="283"/>
-      <c r="S56" s="283" t="s">
-        <v>2427</v>
-      </c>
-      <c r="T56" s="283"/>
-      <c r="U56" s="283"/>
-      <c r="V56" s="283"/>
-      <c r="W56" s="283"/>
-      <c r="X56" s="283" t="s">
-        <v>2443</v>
-      </c>
-      <c r="Y56" s="283" t="s">
-        <v>2267</v>
-      </c>
-      <c r="Z56" s="309" t="s">
-        <v>1444</v>
-      </c>
-      <c r="AA56" s="310" t="s">
-        <v>2362</v>
-      </c>
-    </row>
-    <row r="57" spans="1:27" ht="16.5" customHeight="1">
-      <c r="A57" s="320" t="s">
-        <v>1376</v>
-      </c>
-      <c r="B57" s="311"/>
-      <c r="C57" s="311"/>
-      <c r="D57" s="284">
-        <v>2</v>
-      </c>
-      <c r="E57" s="284" t="s">
-        <v>2436</v>
-      </c>
-      <c r="F57" s="311" t="s">
-        <v>2439</v>
-      </c>
-      <c r="G57" s="284"/>
-      <c r="H57" s="284" t="s">
-        <v>2243</v>
-      </c>
-      <c r="I57" s="284"/>
-      <c r="J57" s="284"/>
-      <c r="K57" s="284"/>
-      <c r="L57" s="284"/>
-      <c r="M57" s="284"/>
-      <c r="N57" s="284" t="s">
-        <v>2442</v>
-      </c>
-      <c r="O57" s="284" t="s">
-        <v>2249</v>
-      </c>
-      <c r="P57" s="284"/>
-      <c r="Q57" s="284">
-        <v>2</v>
-      </c>
-      <c r="R57" s="284"/>
-      <c r="S57" s="284" t="s">
-        <v>2428</v>
-      </c>
-      <c r="T57" s="284"/>
-      <c r="U57" s="284"/>
-      <c r="V57" s="284"/>
-      <c r="W57" s="284"/>
-      <c r="X57" s="284" t="s">
-        <v>1444</v>
-      </c>
-      <c r="Y57" s="185" t="s">
-        <v>2422</v>
-      </c>
-      <c r="Z57" s="280" t="s">
-        <v>1444</v>
-      </c>
-      <c r="AA57" s="304" t="s">
-        <v>2411</v>
-      </c>
-    </row>
-    <row r="58" spans="1:27" ht="16.5" customHeight="1">
-      <c r="A58" s="320" t="s">
-        <v>1376</v>
-      </c>
-      <c r="B58" s="311"/>
-      <c r="C58" s="311"/>
-      <c r="D58" s="284">
-        <v>3</v>
-      </c>
-      <c r="E58" s="284" t="s">
-        <v>2437</v>
-      </c>
-      <c r="F58" s="311" t="s">
-        <v>2440</v>
       </c>
       <c r="G58" s="284"/>
       <c r="H58" s="284" t="s">
@@ -45278,18 +45227,18 @@
       <c r="L58" s="284"/>
       <c r="M58" s="284"/>
       <c r="N58" s="284" t="s">
-        <v>2246</v>
+        <v>2434</v>
       </c>
       <c r="O58" s="284" t="s">
-        <v>2247</v>
+        <v>2249</v>
       </c>
       <c r="P58" s="284"/>
       <c r="Q58" s="284">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="R58" s="284"/>
       <c r="S58" s="284" t="s">
-        <v>2429</v>
+        <v>2420</v>
       </c>
       <c r="T58" s="284"/>
       <c r="U58" s="284"/>
@@ -45299,39 +45248,53 @@
         <v>1444</v>
       </c>
       <c r="Y58" s="185" t="s">
-        <v>1435</v>
+        <v>2414</v>
       </c>
       <c r="Z58" s="280" t="s">
         <v>1444</v>
       </c>
       <c r="AA58" s="304" t="s">
-        <v>2444</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="59" spans="1:27" ht="16.5" customHeight="1">
-      <c r="A59" s="320" t="s">
-        <v>2427</v>
-      </c>
-      <c r="B59" s="311"/>
-      <c r="C59" s="311" t="s">
+      <c r="A59" s="318" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B59" s="309"/>
+      <c r="C59" s="309"/>
+      <c r="D59" s="284">
+        <v>3</v>
+      </c>
+      <c r="E59" s="284" t="s">
+        <v>2429</v>
+      </c>
+      <c r="F59" s="309" t="s">
         <v>2432</v>
       </c>
-      <c r="D59" s="284"/>
-      <c r="E59" s="284"/>
-      <c r="F59" s="311"/>
       <c r="G59" s="284"/>
-      <c r="H59" s="284"/>
+      <c r="H59" s="284" t="s">
+        <v>2243</v>
+      </c>
       <c r="I59" s="284"/>
       <c r="J59" s="284"/>
       <c r="K59" s="284"/>
       <c r="L59" s="284"/>
       <c r="M59" s="284"/>
-      <c r="N59" s="284"/>
-      <c r="O59" s="284"/>
+      <c r="N59" s="284" t="s">
+        <v>2246</v>
+      </c>
+      <c r="O59" s="284" t="s">
+        <v>2247</v>
+      </c>
       <c r="P59" s="284"/>
-      <c r="Q59" s="284"/>
+      <c r="Q59" s="284">
+        <v>20</v>
+      </c>
       <c r="R59" s="284"/>
-      <c r="S59" s="284"/>
+      <c r="S59" s="284" t="s">
+        <v>2421</v>
+      </c>
       <c r="T59" s="284"/>
       <c r="U59" s="284"/>
       <c r="V59" s="284"/>
@@ -45339,23 +45302,27 @@
       <c r="X59" s="284" t="s">
         <v>1444</v>
       </c>
-      <c r="Y59" s="284"/>
+      <c r="Y59" s="185" t="s">
+        <v>1435</v>
+      </c>
       <c r="Z59" s="280" t="s">
         <v>1444</v>
       </c>
-      <c r="AA59" s="304"/>
+      <c r="AA59" s="304" t="s">
+        <v>2436</v>
+      </c>
     </row>
     <row r="60" spans="1:27" ht="16.5" customHeight="1">
-      <c r="A60" s="320" t="s">
-        <v>2428</v>
-      </c>
-      <c r="B60" s="311"/>
-      <c r="C60" s="311" t="s">
-        <v>2433</v>
+      <c r="A60" s="318" t="s">
+        <v>2419</v>
+      </c>
+      <c r="B60" s="309"/>
+      <c r="C60" s="309" t="s">
+        <v>2424</v>
       </c>
       <c r="D60" s="284"/>
       <c r="E60" s="284"/>
-      <c r="F60" s="311"/>
+      <c r="F60" s="309"/>
       <c r="G60" s="284"/>
       <c r="H60" s="284"/>
       <c r="I60" s="284"/>
@@ -45374,7 +45341,7 @@
       <c r="V60" s="284"/>
       <c r="W60" s="284"/>
       <c r="X60" s="284" t="s">
-        <v>2443</v>
+        <v>1444</v>
       </c>
       <c r="Y60" s="284"/>
       <c r="Z60" s="280" t="s">
@@ -45382,193 +45349,177 @@
       </c>
       <c r="AA60" s="304"/>
     </row>
-    <row r="61" spans="1:27" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A61" s="321" t="s">
-        <v>2429</v>
-      </c>
-      <c r="B61" s="312"/>
-      <c r="C61" s="312" t="s">
-        <v>2434</v>
-      </c>
-      <c r="D61" s="285"/>
-      <c r="E61" s="285"/>
-      <c r="F61" s="312"/>
-      <c r="G61" s="285"/>
-      <c r="H61" s="285"/>
-      <c r="I61" s="285"/>
-      <c r="J61" s="285"/>
-      <c r="K61" s="285"/>
-      <c r="L61" s="285"/>
-      <c r="M61" s="285"/>
-      <c r="N61" s="285"/>
-      <c r="O61" s="285"/>
-      <c r="P61" s="285"/>
-      <c r="Q61" s="285"/>
-      <c r="R61" s="285"/>
-      <c r="S61" s="285"/>
-      <c r="T61" s="285"/>
-      <c r="U61" s="285"/>
-      <c r="V61" s="285"/>
-      <c r="W61" s="285"/>
-      <c r="X61" s="285" t="s">
+    <row r="61" spans="1:27" ht="16.5" customHeight="1">
+      <c r="A61" s="318" t="s">
+        <v>2420</v>
+      </c>
+      <c r="B61" s="309"/>
+      <c r="C61" s="309" t="s">
+        <v>2425</v>
+      </c>
+      <c r="D61" s="284"/>
+      <c r="E61" s="284"/>
+      <c r="F61" s="309"/>
+      <c r="G61" s="284"/>
+      <c r="H61" s="284"/>
+      <c r="I61" s="284"/>
+      <c r="J61" s="284"/>
+      <c r="K61" s="284"/>
+      <c r="L61" s="284"/>
+      <c r="M61" s="284"/>
+      <c r="N61" s="284"/>
+      <c r="O61" s="284"/>
+      <c r="P61" s="284"/>
+      <c r="Q61" s="284"/>
+      <c r="R61" s="284"/>
+      <c r="S61" s="284"/>
+      <c r="T61" s="284"/>
+      <c r="U61" s="284"/>
+      <c r="V61" s="284"/>
+      <c r="W61" s="284"/>
+      <c r="X61" s="284" t="s">
+        <v>2435</v>
+      </c>
+      <c r="Y61" s="284"/>
+      <c r="Z61" s="280" t="s">
         <v>1444</v>
       </c>
-      <c r="Y61" s="285"/>
-      <c r="Z61" s="281" t="s">
+      <c r="AA61" s="304"/>
+    </row>
+    <row r="62" spans="1:27" ht="16.5" customHeight="1" thickBot="1">
+      <c r="A62" s="319" t="s">
+        <v>2421</v>
+      </c>
+      <c r="B62" s="310"/>
+      <c r="C62" s="310" t="s">
+        <v>2426</v>
+      </c>
+      <c r="D62" s="285"/>
+      <c r="E62" s="285"/>
+      <c r="F62" s="310"/>
+      <c r="G62" s="285"/>
+      <c r="H62" s="285"/>
+      <c r="I62" s="285"/>
+      <c r="J62" s="285"/>
+      <c r="K62" s="285"/>
+      <c r="L62" s="285"/>
+      <c r="M62" s="285"/>
+      <c r="N62" s="285"/>
+      <c r="O62" s="285"/>
+      <c r="P62" s="285"/>
+      <c r="Q62" s="285"/>
+      <c r="R62" s="285"/>
+      <c r="S62" s="285"/>
+      <c r="T62" s="285"/>
+      <c r="U62" s="285"/>
+      <c r="V62" s="285"/>
+      <c r="W62" s="285"/>
+      <c r="X62" s="285" t="s">
         <v>1444</v>
       </c>
-      <c r="AA61" s="313"/>
-    </row>
-    <row r="62" spans="1:27" ht="16.5" customHeight="1">
-      <c r="A62" s="307" t="s">
-        <v>2446</v>
-      </c>
-      <c r="B62" s="308" t="s">
-        <v>2447</v>
-      </c>
-      <c r="C62" s="308" t="s">
-        <v>2480</v>
-      </c>
-      <c r="D62" s="283">
-        <v>1</v>
-      </c>
-      <c r="E62" s="283" t="s">
-        <v>2453</v>
-      </c>
-      <c r="F62" s="308" t="s">
-        <v>2463</v>
-      </c>
-      <c r="G62" s="308" t="s">
-        <v>2473</v>
-      </c>
-      <c r="H62" s="283" t="s">
+      <c r="Y62" s="285"/>
+      <c r="Z62" s="281" t="s">
+        <v>1444</v>
+      </c>
+      <c r="AA62" s="311"/>
+    </row>
+    <row r="63" spans="1:27" ht="16.5" customHeight="1">
+      <c r="A63" s="305" t="s">
+        <v>2438</v>
+      </c>
+      <c r="B63" s="306" t="s">
+        <v>2439</v>
+      </c>
+      <c r="C63" s="306" t="s">
+        <v>2465</v>
+      </c>
+      <c r="D63" s="283">
+        <v>1</v>
+      </c>
+      <c r="E63" s="283" t="s">
+        <v>2444</v>
+      </c>
+      <c r="F63" s="306" t="s">
+        <v>2451</v>
+      </c>
+      <c r="G63" s="306" t="s">
+        <v>2458</v>
+      </c>
+      <c r="H63" s="283" t="s">
         <v>2305</v>
       </c>
-      <c r="I62" s="283" t="s">
-        <v>2474</v>
-      </c>
-      <c r="J62" s="283" t="s">
-        <v>2472</v>
-      </c>
-      <c r="K62" s="283" t="s">
+      <c r="I63" s="283" t="s">
+        <v>2459</v>
+      </c>
+      <c r="J63" s="283" t="s">
+        <v>2457</v>
+      </c>
+      <c r="K63" s="283" t="s">
         <v>2249</v>
       </c>
-      <c r="L62" s="283">
+      <c r="L63" s="283">
         <v>5</v>
       </c>
-      <c r="M62" s="283"/>
-      <c r="N62" s="283" t="s">
+      <c r="M63" s="283"/>
+      <c r="N63" s="283" t="s">
         <v>2244</v>
       </c>
-      <c r="O62" s="283" t="s">
+      <c r="O63" s="283" t="s">
         <v>2245</v>
       </c>
-      <c r="P62" s="283" t="s">
+      <c r="P63" s="283" t="s">
         <v>2313</v>
       </c>
-      <c r="Q62" s="283">
-        <v>1</v>
-      </c>
-      <c r="R62" s="283"/>
-      <c r="S62" s="283" t="s">
-        <v>2449</v>
-      </c>
-      <c r="T62" s="283"/>
-      <c r="U62" s="283"/>
-      <c r="V62" s="283"/>
-      <c r="W62" s="283"/>
-      <c r="X62" s="283" t="s">
-        <v>2471</v>
-      </c>
-      <c r="Y62" s="283" t="s">
+      <c r="Q63" s="283">
+        <v>1</v>
+      </c>
+      <c r="R63" s="283"/>
+      <c r="S63" s="283" t="s">
+        <v>2440</v>
+      </c>
+      <c r="T63" s="283"/>
+      <c r="U63" s="283"/>
+      <c r="V63" s="283"/>
+      <c r="W63" s="283"/>
+      <c r="X63" s="283" t="s">
+        <v>2456</v>
+      </c>
+      <c r="Y63" s="283" t="s">
         <v>2267</v>
       </c>
-      <c r="Z62" s="309" t="s">
-        <v>2470</v>
-      </c>
-      <c r="AA62" s="310" t="s">
+      <c r="Z63" s="307" t="s">
+        <v>2455</v>
+      </c>
+      <c r="AA63" s="308" t="s">
         <v>2362</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="16.5" customHeight="1">
-      <c r="A63" s="320" t="s">
-        <v>2446</v>
-      </c>
-      <c r="B63" s="311"/>
-      <c r="C63" s="311"/>
-      <c r="D63" s="284">
+    <row r="64" spans="1:27" ht="16.5" customHeight="1">
+      <c r="A64" s="318" t="s">
+        <v>2438</v>
+      </c>
+      <c r="B64" s="309"/>
+      <c r="C64" s="309"/>
+      <c r="D64" s="284">
         <v>2</v>
       </c>
-      <c r="E63" s="284" t="s">
-        <v>2454</v>
-      </c>
-      <c r="F63" s="311" t="s">
-        <v>2469</v>
-      </c>
-      <c r="G63" s="284"/>
-      <c r="H63" s="284" t="s">
-        <v>2243</v>
-      </c>
-      <c r="I63" s="284"/>
-      <c r="J63" s="284"/>
-      <c r="K63" s="284"/>
-      <c r="L63" s="284"/>
-      <c r="M63" s="284"/>
-      <c r="N63" s="284"/>
-      <c r="O63" s="284"/>
-      <c r="P63" s="284"/>
-      <c r="Q63" s="284"/>
-      <c r="R63" s="284"/>
-      <c r="S63" s="284" t="s">
-        <v>2448</v>
-      </c>
-      <c r="T63" s="284"/>
-      <c r="U63" s="284"/>
-      <c r="V63" s="284"/>
-      <c r="W63" s="284"/>
-      <c r="X63" s="284" t="s">
-        <v>2470</v>
-      </c>
-      <c r="Y63" s="185" t="s">
-        <v>2422</v>
-      </c>
-      <c r="Z63" s="280" t="s">
-        <v>2470</v>
-      </c>
-      <c r="AA63" s="304" t="s">
-        <v>2411</v>
-      </c>
-    </row>
-    <row r="64" spans="1:27" ht="16.5" customHeight="1">
-      <c r="A64" s="320" t="s">
-        <v>2446</v>
-      </c>
-      <c r="B64" s="311"/>
-      <c r="C64" s="311"/>
-      <c r="D64" s="284">
-        <v>3</v>
-      </c>
       <c r="E64" s="284" t="s">
-        <v>2455</v>
-      </c>
-      <c r="F64" s="311" t="s">
-        <v>2466</v>
+        <v>2445</v>
+      </c>
+      <c r="F64" s="309" t="s">
+        <v>2494</v>
       </c>
       <c r="G64" s="284"/>
       <c r="H64" s="284" t="s">
-        <v>2305</v>
+        <v>2383</v>
       </c>
       <c r="I64" s="284"/>
-      <c r="J64" s="284" t="s">
-        <v>2479</v>
-      </c>
-      <c r="K64" s="284" t="s">
-        <v>2247</v>
-      </c>
-      <c r="L64" s="284">
-        <v>20</v>
-      </c>
-      <c r="M64" s="284"/>
+      <c r="J64" s="284"/>
+      <c r="K64" s="284"/>
+      <c r="L64" s="284"/>
+      <c r="M64" s="284" t="s">
+        <v>2495</v>
+      </c>
       <c r="N64" s="284" t="s">
         <v>2244</v>
       </c>
@@ -45583,53 +45534,57 @@
       </c>
       <c r="R64" s="284"/>
       <c r="S64" s="284" t="s">
-        <v>2452</v>
-      </c>
-      <c r="T64" s="284"/>
+        <v>2441</v>
+      </c>
+      <c r="T64" s="284" t="s">
+        <v>2442</v>
+      </c>
       <c r="U64" s="284"/>
       <c r="V64" s="284"/>
       <c r="W64" s="284"/>
       <c r="X64" s="284" t="s">
-        <v>2470</v>
+        <v>2455</v>
       </c>
       <c r="Y64" s="185" t="s">
-        <v>1435</v>
+        <v>2414</v>
       </c>
       <c r="Z64" s="280" t="s">
-        <v>2470</v>
+        <v>2455</v>
       </c>
       <c r="AA64" s="304" t="s">
-        <v>2444</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="65" spans="1:27" ht="16.5" customHeight="1">
-      <c r="A65" s="320" t="s">
-        <v>2448</v>
-      </c>
-      <c r="B65" s="311"/>
-      <c r="C65" s="311" t="s">
-        <v>2456</v>
-      </c>
+      <c r="A65" s="318" t="s">
+        <v>2438</v>
+      </c>
+      <c r="B65" s="309"/>
+      <c r="C65" s="309"/>
       <c r="D65" s="284">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E65" s="284" t="s">
-        <v>2461</v>
-      </c>
-      <c r="F65" s="311" t="s">
-        <v>2467</v>
+        <v>2446</v>
+      </c>
+      <c r="F65" s="309" t="s">
+        <v>2454</v>
       </c>
       <c r="G65" s="284"/>
       <c r="H65" s="284" t="s">
-        <v>2384</v>
+        <v>2305</v>
       </c>
       <c r="I65" s="284"/>
-      <c r="J65" s="284"/>
-      <c r="K65" s="284"/>
-      <c r="L65" s="284"/>
-      <c r="M65" s="284" t="s">
-        <v>2385</v>
-      </c>
+      <c r="J65" s="284" t="s">
+        <v>2464</v>
+      </c>
+      <c r="K65" s="284" t="s">
+        <v>2247</v>
+      </c>
+      <c r="L65" s="284">
+        <v>20</v>
+      </c>
+      <c r="M65" s="284"/>
       <c r="N65" s="284" t="s">
         <v>2244</v>
       </c>
@@ -45644,99 +45599,73 @@
       </c>
       <c r="R65" s="284"/>
       <c r="S65" s="284" t="s">
-        <v>2450</v>
-      </c>
-      <c r="T65" s="284" t="s">
-        <v>2451</v>
-      </c>
+        <v>2443</v>
+      </c>
+      <c r="T65" s="284"/>
       <c r="U65" s="284"/>
       <c r="V65" s="284"/>
       <c r="W65" s="284"/>
       <c r="X65" s="284" t="s">
-        <v>2470</v>
-      </c>
-      <c r="Y65" s="284" t="s">
-        <v>2267</v>
+        <v>2455</v>
+      </c>
+      <c r="Y65" s="185" t="s">
+        <v>1435</v>
       </c>
       <c r="Z65" s="280" t="s">
-        <v>2470</v>
+        <v>2455</v>
       </c>
       <c r="AA65" s="304" t="s">
-        <v>2362</v>
+        <v>2436</v>
       </c>
     </row>
     <row r="66" spans="1:27" ht="16.5" customHeight="1">
-      <c r="A66" s="320" t="s">
-        <v>2448</v>
-      </c>
-      <c r="B66" s="311"/>
-      <c r="C66" s="311"/>
-      <c r="D66" s="284">
-        <v>2</v>
-      </c>
-      <c r="E66" s="284" t="s">
-        <v>2462</v>
-      </c>
-      <c r="F66" s="311" t="s">
-        <v>2468</v>
-      </c>
+      <c r="A66" s="318" t="s">
+        <v>2440</v>
+      </c>
+      <c r="B66" s="309"/>
+      <c r="C66" s="309" t="s">
+        <v>2447</v>
+      </c>
+      <c r="D66" s="284"/>
+      <c r="E66" s="284"/>
+      <c r="F66" s="309"/>
       <c r="G66" s="284"/>
-      <c r="H66" s="284" t="s">
-        <v>2384</v>
-      </c>
+      <c r="H66" s="284"/>
       <c r="I66" s="284"/>
       <c r="J66" s="284"/>
       <c r="K66" s="284"/>
       <c r="L66" s="284"/>
-      <c r="M66" s="284" t="s">
-        <v>2386</v>
-      </c>
-      <c r="N66" s="284" t="s">
-        <v>2244</v>
-      </c>
-      <c r="O66" s="284" t="s">
-        <v>2245</v>
-      </c>
-      <c r="P66" s="284" t="s">
-        <v>2336</v>
-      </c>
-      <c r="Q66" s="284">
-        <v>1</v>
-      </c>
+      <c r="M66" s="284"/>
+      <c r="N66" s="284"/>
+      <c r="O66" s="284"/>
+      <c r="P66" s="284"/>
+      <c r="Q66" s="284"/>
       <c r="R66" s="284"/>
-      <c r="S66" s="284" t="s">
-        <v>2450</v>
-      </c>
-      <c r="T66" s="284" t="s">
-        <v>2451</v>
-      </c>
+      <c r="S66" s="284"/>
+      <c r="T66" s="284"/>
       <c r="U66" s="284"/>
       <c r="V66" s="284"/>
       <c r="W66" s="284"/>
       <c r="X66" s="284" t="s">
-        <v>2470</v>
-      </c>
-      <c r="Y66" s="284" t="s">
-        <v>2422</v>
-      </c>
+        <v>2455</v>
+      </c>
+      <c r="Y66" s="284"/>
       <c r="Z66" s="280" t="s">
-        <v>2470</v>
-      </c>
-      <c r="AA66" s="304" t="s">
-        <v>2411</v>
-      </c>
+        <v>2455</v>
+      </c>
+      <c r="AA66" s="304"/>
     </row>
     <row r="67" spans="1:27" ht="16.5" customHeight="1">
-      <c r="A67" s="320" t="s">
+      <c r="A67" s="318" t="s">
+        <v>2441</v>
+      </c>
+      <c r="B67" s="309"/>
+      <c r="C67" s="309" t="s">
         <v>2449</v>
-      </c>
-      <c r="B67" s="311"/>
-      <c r="C67" s="311" t="s">
-        <v>2457</v>
       </c>
       <c r="D67" s="284"/>
       <c r="E67" s="284"/>
-      <c r="F67" s="311"/>
+      <c r="F67" s="309"/>
       <c r="G67" s="284"/>
       <c r="H67" s="284"/>
       <c r="I67" s="284"/>
@@ -45755,25 +45684,25 @@
       <c r="V67" s="284"/>
       <c r="W67" s="284"/>
       <c r="X67" s="284" t="s">
-        <v>2470</v>
+        <v>2455</v>
       </c>
       <c r="Y67" s="284"/>
       <c r="Z67" s="280" t="s">
-        <v>2470</v>
+        <v>2455</v>
       </c>
       <c r="AA67" s="304"/>
     </row>
     <row r="68" spans="1:27" ht="16.5" customHeight="1">
-      <c r="A68" s="320" t="s">
+      <c r="A68" s="318" t="s">
+        <v>2442</v>
+      </c>
+      <c r="B68" s="309"/>
+      <c r="C68" s="309" t="s">
         <v>2450</v>
-      </c>
-      <c r="B68" s="311"/>
-      <c r="C68" s="311" t="s">
-        <v>2459</v>
       </c>
       <c r="D68" s="284"/>
       <c r="E68" s="284"/>
-      <c r="F68" s="311"/>
+      <c r="F68" s="309"/>
       <c r="G68" s="284"/>
       <c r="H68" s="284"/>
       <c r="I68" s="284"/>
@@ -45792,132 +45721,124 @@
       <c r="V68" s="284"/>
       <c r="W68" s="284"/>
       <c r="X68" s="284" t="s">
-        <v>2470</v>
+        <v>2455</v>
       </c>
       <c r="Y68" s="284"/>
       <c r="Z68" s="280" t="s">
-        <v>2470</v>
+        <v>2455</v>
       </c>
       <c r="AA68" s="304"/>
     </row>
-    <row r="69" spans="1:27" ht="16.5" customHeight="1">
-      <c r="A69" s="320" t="s">
-        <v>2451</v>
-      </c>
-      <c r="B69" s="311"/>
-      <c r="C69" s="311" t="s">
-        <v>2460</v>
-      </c>
-      <c r="D69" s="284"/>
-      <c r="E69" s="284"/>
-      <c r="F69" s="311"/>
-      <c r="G69" s="284"/>
-      <c r="H69" s="284"/>
-      <c r="I69" s="284"/>
-      <c r="J69" s="284"/>
-      <c r="K69" s="284"/>
-      <c r="L69" s="284"/>
-      <c r="M69" s="284"/>
-      <c r="N69" s="284"/>
-      <c r="O69" s="284"/>
-      <c r="P69" s="284"/>
-      <c r="Q69" s="284"/>
-      <c r="R69" s="284"/>
-      <c r="S69" s="284"/>
-      <c r="T69" s="284"/>
-      <c r="U69" s="284"/>
-      <c r="V69" s="284"/>
-      <c r="W69" s="284"/>
-      <c r="X69" s="284" t="s">
-        <v>2470</v>
-      </c>
-      <c r="Y69" s="284"/>
-      <c r="Z69" s="280" t="s">
-        <v>2470</v>
-      </c>
-      <c r="AA69" s="304"/>
-    </row>
-    <row r="70" spans="1:27" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A70" s="321" t="s">
-        <v>2452</v>
-      </c>
-      <c r="B70" s="312"/>
-      <c r="C70" s="312" t="s">
-        <v>2458</v>
-      </c>
-      <c r="D70" s="285"/>
-      <c r="E70" s="285"/>
+    <row r="69" spans="1:27" ht="16.5" customHeight="1" thickBot="1">
+      <c r="A69" s="319" t="s">
+        <v>2443</v>
+      </c>
+      <c r="B69" s="310"/>
+      <c r="C69" s="310" t="s">
+        <v>2448</v>
+      </c>
+      <c r="D69" s="285"/>
+      <c r="E69" s="285"/>
+      <c r="F69" s="310"/>
+      <c r="G69" s="285"/>
+      <c r="H69" s="285"/>
+      <c r="I69" s="285"/>
+      <c r="J69" s="285"/>
+      <c r="K69" s="285"/>
+      <c r="L69" s="285"/>
+      <c r="M69" s="285"/>
+      <c r="N69" s="285"/>
+      <c r="O69" s="285"/>
+      <c r="P69" s="285"/>
+      <c r="Q69" s="285"/>
+      <c r="R69" s="285"/>
+      <c r="S69" s="285"/>
+      <c r="T69" s="285"/>
+      <c r="U69" s="285"/>
+      <c r="V69" s="285"/>
+      <c r="W69" s="285"/>
+      <c r="X69" s="285" t="s">
+        <v>2455</v>
+      </c>
+      <c r="Y69" s="285"/>
+      <c r="Z69" s="281" t="s">
+        <v>2455</v>
+      </c>
+      <c r="AA69" s="311"/>
+    </row>
+    <row r="70" spans="1:27" ht="16.5" customHeight="1">
+      <c r="A70" s="312" t="s">
+        <v>2481</v>
+      </c>
+      <c r="B70" s="312" t="s">
+        <v>2481</v>
+      </c>
+      <c r="C70" s="312"/>
+      <c r="D70" s="286"/>
+      <c r="E70" s="286"/>
       <c r="F70" s="312"/>
-      <c r="G70" s="285"/>
-      <c r="H70" s="285"/>
-      <c r="I70" s="285"/>
-      <c r="J70" s="285"/>
-      <c r="K70" s="285"/>
-      <c r="L70" s="285"/>
-      <c r="M70" s="285"/>
-      <c r="N70" s="285"/>
-      <c r="O70" s="285"/>
-      <c r="P70" s="285"/>
-      <c r="Q70" s="285"/>
-      <c r="R70" s="285"/>
-      <c r="S70" s="285"/>
-      <c r="T70" s="285"/>
-      <c r="U70" s="285"/>
-      <c r="V70" s="285"/>
-      <c r="W70" s="285"/>
-      <c r="X70" s="285" t="s">
-        <v>2470</v>
-      </c>
-      <c r="Y70" s="285"/>
-      <c r="Z70" s="281" t="s">
-        <v>2470</v>
-      </c>
+      <c r="G70" s="286"/>
+      <c r="H70" s="286"/>
+      <c r="I70" s="286"/>
+      <c r="J70" s="286"/>
+      <c r="K70" s="286"/>
+      <c r="L70" s="286"/>
+      <c r="M70" s="286"/>
+      <c r="N70" s="286"/>
+      <c r="O70" s="286"/>
+      <c r="P70" s="286"/>
+      <c r="Q70" s="286"/>
+      <c r="R70" s="286"/>
+      <c r="S70" s="286"/>
+      <c r="T70" s="286"/>
+      <c r="U70" s="286"/>
+      <c r="V70" s="286"/>
+      <c r="W70" s="286"/>
+      <c r="X70" s="286"/>
+      <c r="Y70" s="286"/>
+      <c r="Z70" s="313"/>
       <c r="AA70" s="313"/>
     </row>
     <row r="71" spans="1:27" ht="16.5" customHeight="1">
-      <c r="A71" s="314" t="s">
-        <v>2496</v>
-      </c>
-      <c r="B71" s="314" t="s">
-        <v>2496</v>
-      </c>
-      <c r="C71" s="314"/>
-      <c r="D71" s="286"/>
-      <c r="E71" s="286"/>
-      <c r="F71" s="314"/>
-      <c r="G71" s="286"/>
-      <c r="H71" s="286"/>
-      <c r="I71" s="286"/>
-      <c r="J71" s="286"/>
-      <c r="K71" s="286"/>
-      <c r="L71" s="286"/>
-      <c r="M71" s="286"/>
-      <c r="N71" s="286"/>
-      <c r="O71" s="286"/>
-      <c r="P71" s="286"/>
-      <c r="Q71" s="286"/>
-      <c r="R71" s="286"/>
-      <c r="S71" s="286"/>
-      <c r="T71" s="286"/>
-      <c r="U71" s="286"/>
-      <c r="V71" s="286"/>
-      <c r="W71" s="286"/>
-      <c r="X71" s="286"/>
-      <c r="Y71" s="286"/>
-      <c r="Z71" s="315"/>
-      <c r="AA71" s="315"/>
+      <c r="A71" s="312" t="s">
+        <v>2482</v>
+      </c>
+      <c r="B71" s="309" t="s">
+        <v>2482</v>
+      </c>
+      <c r="C71" s="309"/>
+      <c r="D71" s="284"/>
+      <c r="E71" s="284"/>
+      <c r="F71" s="309"/>
+      <c r="G71" s="284"/>
+      <c r="H71" s="284"/>
+      <c r="I71" s="284"/>
+      <c r="J71" s="284"/>
+      <c r="K71" s="284"/>
+      <c r="L71" s="284"/>
+      <c r="M71" s="284"/>
+      <c r="N71" s="284"/>
+      <c r="O71" s="284"/>
+      <c r="P71" s="284"/>
+      <c r="Q71" s="284"/>
+      <c r="R71" s="284"/>
+      <c r="S71" s="284"/>
+      <c r="T71" s="284"/>
+      <c r="U71" s="284"/>
+      <c r="V71" s="284"/>
+      <c r="W71" s="284"/>
+      <c r="X71" s="284"/>
+      <c r="Y71" s="284"/>
+      <c r="Z71" s="280"/>
+      <c r="AA71" s="280"/>
     </row>
     <row r="72" spans="1:27" ht="16.5" customHeight="1">
-      <c r="A72" s="314" t="s">
-        <v>2497</v>
-      </c>
-      <c r="B72" s="311" t="s">
-        <v>2497</v>
-      </c>
-      <c r="C72" s="311"/>
+      <c r="A72" s="309"/>
+      <c r="B72" s="309"/>
+      <c r="C72" s="309"/>
       <c r="D72" s="284"/>
       <c r="E72" s="284"/>
-      <c r="F72" s="311"/>
+      <c r="F72" s="309"/>
       <c r="G72" s="284"/>
       <c r="H72" s="284"/>
       <c r="I72" s="284"/>
@@ -45940,35 +45861,6 @@
       <c r="Z72" s="280"/>
       <c r="AA72" s="280"/>
     </row>
-    <row r="73" spans="1:27" ht="16.5" customHeight="1">
-      <c r="A73" s="311"/>
-      <c r="B73" s="311"/>
-      <c r="C73" s="311"/>
-      <c r="D73" s="284"/>
-      <c r="E73" s="284"/>
-      <c r="F73" s="311"/>
-      <c r="G73" s="284"/>
-      <c r="H73" s="284"/>
-      <c r="I73" s="284"/>
-      <c r="J73" s="284"/>
-      <c r="K73" s="284"/>
-      <c r="L73" s="284"/>
-      <c r="M73" s="284"/>
-      <c r="N73" s="284"/>
-      <c r="O73" s="284"/>
-      <c r="P73" s="284"/>
-      <c r="Q73" s="284"/>
-      <c r="R73" s="284"/>
-      <c r="S73" s="284"/>
-      <c r="T73" s="284"/>
-      <c r="U73" s="284"/>
-      <c r="V73" s="284"/>
-      <c r="W73" s="284"/>
-      <c r="X73" s="284"/>
-      <c r="Y73" s="284"/>
-      <c r="Z73" s="280"/>
-      <c r="AA73" s="280"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="40" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erang\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{443C0138-FC4E-430E-B995-F0E46DED9C66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F49D8547-2060-4C9F-B345-EA48C3118980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5078" uniqueCount="2496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5081" uniqueCount="2499">
   <si>
     <t>캐릭터ID</t>
   </si>
@@ -12840,18 +12840,6 @@
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
   <si>
-    <t>주사위 6 이상, 무작위 일반~레어 유물 획득</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>주사위 8 이상, 무작위 레어~에픽 유물 획득</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>주사위 10 이상, 무작위 에픽~유니크 유물 획득</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
     <t>Event_05_A</t>
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
@@ -12996,18 +12984,6 @@
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
   <si>
-    <t>주사위 6 이상, 레드 더스티움 30 획득</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>주사위 14 이상, 무작위 에픽 유물 획득</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>주사위 10 이상, 레드 더스티움 50 획득</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
     <t>event6</t>
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
@@ -13126,18 +13102,6 @@
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
   <si>
-    <t>{Party1Name}{이가} 만진다.</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>{Party3Name}{이가} 만진다.</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>{Party2Name}{이가} 만진다.</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
     <t>Event_08_A</t>
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
@@ -13158,14 +13122,6 @@
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
   <si>
-    <t>레드 더스티움 20 소모, 레어~에픽 기억 발현</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>레드 더스티움 45 소모, 에픽~유니크 기억 발현</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
     <t>event8</t>
   </si>
   <si>
@@ -13281,10 +13237,6 @@
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
   <si>
-    <t>모든 파티원 최대 생명력 5 증가</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
     <t>모든 파티원 최대 마나 2 증가</t>
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
@@ -13364,22 +13316,6 @@
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
   <si>
-    <t>전체 생명력 5감소, 무작위 레어~유니크 유물 획득</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>레드 더스티움 15 소모, 무작위 일반~에픽 기억 발현</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>레드 더스티움 30 소모, 무작위 레어~유니크 기억 발현</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>침식도 20 증가, 무작위 일반~유니크 유물 획득</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
     <t>event10</t>
   </si>
   <si>
@@ -13482,10 +13418,6 @@
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
   <si>
-    <t>예측 성공 시, 레드 더스티움 25 획득</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
     <t>이벤트 종료</t>
   </si>
   <si>
@@ -13497,14 +13429,6 @@
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
   <si>
-    <t>예측 성공 시, 레드 더스티움 30 획득</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>예측 성공 시, 레드 더스티움 35 획득</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
     <t>Immediate</t>
   </si>
   <si>
@@ -13522,11 +13446,118 @@
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
   <si>
-    <t>예측 성공 시, 무작위 유물 획득</t>
+    <t>PlayerChoice</t>
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
   <si>
-    <t>PlayerChoice</t>
+    <t>{Party1Name}의 생명력 회복 또는 기억 발현</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Party2Name}의 생명력 회복 또는 기억 발현</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Party3Name}의 생명력 회복 또는 기억 발현</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 파티원 최대 생명력 10 증가</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Party1Name}{이가} 다가간다.</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Party2Name}{이가} 다가간다.</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>{Party3Name}{이가} 다가간다.</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>레드 더스티움 15 소모
+무작위 일반~에픽 기억 발현</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>레드 더스티움 30 소모
+무작위 레어~유니크 기억 발현</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>주사위 6 이상
+무작위 일반~레어 유물 획득</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>주사위 8 이상
+무작위 레어~에픽 유물 획득</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>주사위 10 이상
+무작위 에픽~유니크 유물 획득</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>주사위 6 이상
+레드 더스티움 30 획득
+실패 : 생명력 5 감소</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>주사위 10 이상
+레드 더스티움 50 획득
+실패 : 생명력 5 감소</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>주사위 14 이상
+무작위 에픽 유물 획득
+실패 : 생명력 5 감소</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>예측 : 앞면 or 뒷면
+레드 더스티움 25 획득</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>예측 : 앞면 or 뒷면
+레드 더스티움 30 획득</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>예측 : 앞면 or 뒷면
+레드 더스티움 35 획득</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>레드 더스티움 20 소모
+레어~에픽 기억 발현</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>레드 더스티움 45 소모
+에픽~유니크 기억 발현</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>전체 생명력 5 감소
+무작위 레어~유니크 유물 획득</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>예측 : 앞면 or 뒷면
+무작위 유물 획득</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>침식도 20 증가
+무작위 일반~유니크 유물 획득</t>
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
 </sst>
@@ -14466,7 +14497,7 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="327">
+  <cellXfs count="329">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -15432,6 +15463,12 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Normal" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
@@ -39844,7 +39881,7 @@
         <v>216</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>2473</v>
+        <v>2457</v>
       </c>
       <c r="E11" s="16">
         <v>0</v>
@@ -39870,7 +39907,7 @@
         <v>216</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>2475</v>
+        <v>2459</v>
       </c>
       <c r="E12" s="16">
         <v>0</v>
@@ -40202,7 +40239,7 @@
         <v>1371</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>2466</v>
+        <v>2450</v>
       </c>
       <c r="C25" s="16" t="s">
         <v>1356</v>
@@ -40211,7 +40248,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>2388</v>
+        <v>2382</v>
       </c>
       <c r="F25" s="16" t="s">
         <v>1314</v>
@@ -40225,7 +40262,7 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="16" t="s">
-        <v>2472</v>
+        <v>2456</v>
       </c>
       <c r="B26" s="16" t="s">
         <v>1372</v>
@@ -40254,7 +40291,7 @@
         <v>1374</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>2467</v>
+        <v>2451</v>
       </c>
       <c r="C27" s="16" t="s">
         <v>1356</v>
@@ -40263,7 +40300,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>2437</v>
+        <v>2425</v>
       </c>
       <c r="F27" s="16" t="s">
         <v>1314</v>
@@ -40280,7 +40317,7 @@
         <v>1377</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>2468</v>
+        <v>2452</v>
       </c>
       <c r="C28" s="16" t="s">
         <v>1356</v>
@@ -40289,7 +40326,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>2470</v>
+        <v>2454</v>
       </c>
       <c r="F28" s="16" t="s">
         <v>1314</v>
@@ -40306,7 +40343,7 @@
         <v>1379</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>2469</v>
+        <v>2453</v>
       </c>
       <c r="C29" s="16" t="s">
         <v>1356</v>
@@ -40315,7 +40352,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>2471</v>
+        <v>2455</v>
       </c>
       <c r="F29" s="16" t="s">
         <v>1314</v>
@@ -40449,7 +40486,7 @@
         <v>0</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>2481</v>
+        <v>2465</v>
       </c>
       <c r="F36" s="16" t="s">
         <v>1314</v>
@@ -41469,7 +41506,7 @@
     </row>
     <row r="24" spans="1:26" ht="17.25" customHeight="1">
       <c r="A24" s="258" t="s">
-        <v>2474</v>
+        <v>2458</v>
       </c>
       <c r="B24" s="212" t="s">
         <v>214</v>
@@ -41528,7 +41565,7 @@
     </row>
     <row r="25" spans="1:26" ht="17.25" thickBot="1">
       <c r="A25" s="163" t="s">
-        <v>2474</v>
+        <v>2458</v>
       </c>
       <c r="B25" s="164" t="s">
         <v>178</v>
@@ -41567,7 +41604,7 @@
     </row>
     <row r="26" spans="1:26">
       <c r="A26" s="156" t="s">
-        <v>2476</v>
+        <v>2460</v>
       </c>
       <c r="B26" s="157" t="s">
         <v>214</v>
@@ -41626,7 +41663,7 @@
     </row>
     <row r="27" spans="1:26" ht="17.25" customHeight="1" thickBot="1">
       <c r="A27" s="163" t="s">
-        <v>2476</v>
+        <v>2460</v>
       </c>
       <c r="B27" s="164" t="s">
         <v>185</v>
@@ -41665,7 +41702,7 @@
     </row>
     <row r="28" spans="1:26" ht="17.25" thickBot="1">
       <c r="A28" s="168" t="s">
-        <v>2477</v>
+        <v>2461</v>
       </c>
       <c r="B28" s="169" t="s">
         <v>222</v>
@@ -41719,7 +41756,7 @@
     </row>
     <row r="29" spans="1:26">
       <c r="A29" s="156" t="s">
-        <v>2478</v>
+        <v>2462</v>
       </c>
       <c r="B29" s="157" t="s">
         <v>202</v>
@@ -41773,7 +41810,7 @@
     </row>
     <row r="30" spans="1:26" ht="17.25" customHeight="1" thickBot="1">
       <c r="A30" s="163" t="s">
-        <v>2478</v>
+        <v>2462</v>
       </c>
       <c r="B30" s="164" t="s">
         <v>229</v>
@@ -41808,7 +41845,7 @@
     </row>
     <row r="31" spans="1:26">
       <c r="A31" s="156" t="s">
-        <v>2479</v>
+        <v>2463</v>
       </c>
       <c r="B31" s="157" t="s">
         <v>208</v>
@@ -41867,7 +41904,7 @@
     </row>
     <row r="32" spans="1:26" ht="17.25" customHeight="1" thickBot="1">
       <c r="A32" s="163" t="s">
-        <v>2479</v>
+        <v>2463</v>
       </c>
       <c r="B32" s="164" t="s">
         <v>229</v>
@@ -41906,7 +41943,7 @@
     </row>
     <row r="33" spans="1:26" ht="17.25" thickBot="1">
       <c r="A33" s="168" t="s">
-        <v>2480</v>
+        <v>2464</v>
       </c>
       <c r="B33" s="169" t="s">
         <v>2127</v>
@@ -42271,7 +42308,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:AA72"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="54.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.5" style="314" customWidth="1"/>
     <col min="2" max="2" width="22.5" style="314" customWidth="1"/>
@@ -42297,7 +42334,7 @@
     <col min="27" max="27" width="24.75" style="316" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="16.5" customHeight="1">
+    <row r="1" spans="1:27" ht="54.95" customHeight="1">
       <c r="A1" s="276" t="s">
         <v>2186</v>
       </c>
@@ -42359,13 +42396,13 @@
         <v>2284</v>
       </c>
       <c r="U1" s="184" t="s">
-        <v>2367</v>
+        <v>2361</v>
       </c>
       <c r="V1" s="184" t="s">
-        <v>2368</v>
+        <v>2362</v>
       </c>
       <c r="W1" s="184" t="s">
-        <v>2369</v>
+        <v>2363</v>
       </c>
       <c r="X1" s="184" t="s">
         <v>2226</v>
@@ -42380,7 +42417,7 @@
         <v>2229</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="16.5" customHeight="1" thickBot="1">
+    <row r="2" spans="1:27" ht="54.95" customHeight="1" thickBot="1">
       <c r="A2" s="288" t="s">
         <v>2185</v>
       </c>
@@ -42445,10 +42482,10 @@
         <v>2219</v>
       </c>
       <c r="V2" s="279" t="s">
-        <v>2365</v>
+        <v>2359</v>
       </c>
       <c r="W2" s="279" t="s">
-        <v>2366</v>
+        <v>2360</v>
       </c>
       <c r="X2" s="279" t="s">
         <v>2222</v>
@@ -42463,7 +42500,7 @@
         <v>2224</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="16.5" customHeight="1">
+    <row r="3" spans="1:27" ht="54.95" customHeight="1">
       <c r="A3" s="290" t="s">
         <v>2183</v>
       </c>
@@ -42526,7 +42563,7 @@
         <v>2267</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="16.5" customHeight="1">
+    <row r="4" spans="1:27" ht="54.95" customHeight="1">
       <c r="A4" s="292" t="s">
         <v>2183</v>
       </c>
@@ -42585,7 +42622,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="16.5" customHeight="1">
+    <row r="5" spans="1:27" ht="54.95" customHeight="1">
       <c r="A5" s="292" t="s">
         <v>2183</v>
       </c>
@@ -42644,7 +42681,7 @@
         <v>1435</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="16.5" customHeight="1" thickBot="1">
+    <row r="6" spans="1:27" ht="54.95" customHeight="1" thickBot="1">
       <c r="A6" s="294" t="s">
         <v>2238</v>
       </c>
@@ -42681,7 +42718,7 @@
       </c>
       <c r="AA6" s="295"/>
     </row>
-    <row r="7" spans="1:27" ht="16.5" customHeight="1">
+    <row r="7" spans="1:27" ht="54.95" customHeight="1">
       <c r="A7" s="290" t="s">
         <v>2250</v>
       </c>
@@ -42740,7 +42777,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="16.5" customHeight="1">
+    <row r="8" spans="1:27" ht="54.95" customHeight="1">
       <c r="A8" s="292" t="s">
         <v>2250</v>
       </c>
@@ -42791,13 +42828,13 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="16.5" customHeight="1">
+    <row r="9" spans="1:27" ht="54.95" customHeight="1">
       <c r="A9" s="292" t="s">
         <v>2251</v>
       </c>
       <c r="B9" s="272"/>
       <c r="C9" s="272" t="s">
-        <v>2415</v>
+        <v>2404</v>
       </c>
       <c r="D9" s="185"/>
       <c r="E9" s="185"/>
@@ -42828,7 +42865,7 @@
       </c>
       <c r="AA9" s="293"/>
     </row>
-    <row r="10" spans="1:27" ht="16.5" customHeight="1">
+    <row r="10" spans="1:27" ht="54.95" customHeight="1">
       <c r="A10" s="292" t="s">
         <v>2239</v>
       </c>
@@ -42865,7 +42902,7 @@
       </c>
       <c r="AA10" s="293"/>
     </row>
-    <row r="11" spans="1:27" ht="16.5" customHeight="1" thickBot="1">
+    <row r="11" spans="1:27" ht="54.95" customHeight="1" thickBot="1">
       <c r="A11" s="292" t="s">
         <v>2252</v>
       </c>
@@ -42902,7 +42939,7 @@
       </c>
       <c r="AA11" s="293"/>
     </row>
-    <row r="12" spans="1:27" ht="16.5" customHeight="1">
+    <row r="12" spans="1:27" ht="54.95" customHeight="1">
       <c r="A12" s="290" t="s">
         <v>2289</v>
       </c>
@@ -42963,7 +43000,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="16.5" customHeight="1">
+    <row r="13" spans="1:27" ht="54.95" customHeight="1">
       <c r="A13" s="292" t="s">
         <v>2289</v>
       </c>
@@ -43018,7 +43055,7 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="16.5" customHeight="1">
+    <row r="14" spans="1:27" ht="54.95" customHeight="1">
       <c r="A14" s="292" t="s">
         <v>2289</v>
       </c>
@@ -43073,7 +43110,7 @@
         <v>1436</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="16.5" customHeight="1">
+    <row r="15" spans="1:27" ht="54.95" customHeight="1">
       <c r="A15" s="292" t="s">
         <v>2279</v>
       </c>
@@ -43110,7 +43147,7 @@
       </c>
       <c r="AA15" s="293"/>
     </row>
-    <row r="16" spans="1:27" ht="16.5" customHeight="1">
+    <row r="16" spans="1:27" ht="54.95" customHeight="1">
       <c r="A16" s="292" t="s">
         <v>2280</v>
       </c>
@@ -43147,7 +43184,7 @@
       </c>
       <c r="AA16" s="293"/>
     </row>
-    <row r="17" spans="1:27" ht="16.5" customHeight="1" thickBot="1">
+    <row r="17" spans="1:27" ht="54.95" customHeight="1" thickBot="1">
       <c r="A17" s="294" t="s">
         <v>2281</v>
       </c>
@@ -43184,7 +43221,7 @@
       </c>
       <c r="AA17" s="295"/>
     </row>
-    <row r="18" spans="1:27" ht="16.5" customHeight="1">
+    <row r="18" spans="1:27" ht="54.95" customHeight="1">
       <c r="A18" s="290" t="s">
         <v>2290</v>
       </c>
@@ -43201,7 +43238,7 @@
         <v>2309</v>
       </c>
       <c r="F18" s="272" t="s">
-        <v>2452</v>
+        <v>2483</v>
       </c>
       <c r="G18" s="265" t="s">
         <v>2306</v>
@@ -43210,7 +43247,7 @@
         <v>2305</v>
       </c>
       <c r="I18" s="268" t="s">
-        <v>2460</v>
+        <v>2444</v>
       </c>
       <c r="J18" s="268" t="s">
         <v>2308</v>
@@ -43254,10 +43291,10 @@
         <v>1440</v>
       </c>
       <c r="AA18" s="291" t="s">
-        <v>2362</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="16.5" customHeight="1">
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" ht="54.95" customHeight="1">
       <c r="A19" s="292" t="s">
         <v>1364</v>
       </c>
@@ -43270,7 +43307,7 @@
         <v>2310</v>
       </c>
       <c r="F19" s="272" t="s">
-        <v>2453</v>
+        <v>2484</v>
       </c>
       <c r="G19" s="186" t="s">
         <v>2306</v>
@@ -43279,7 +43316,7 @@
         <v>2305</v>
       </c>
       <c r="I19" s="185" t="s">
-        <v>2461</v>
+        <v>2445</v>
       </c>
       <c r="J19" s="185" t="s">
         <v>2308</v>
@@ -43326,7 +43363,7 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="16.5" customHeight="1">
+    <row r="20" spans="1:27" ht="54.95" customHeight="1">
       <c r="A20" s="292" t="s">
         <v>1364</v>
       </c>
@@ -43377,7 +43414,7 @@
         <v>1436</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="16.5" customHeight="1">
+    <row r="21" spans="1:27" ht="54.95" customHeight="1">
       <c r="A21" s="292" t="s">
         <v>2292</v>
       </c>
@@ -43414,7 +43451,7 @@
       </c>
       <c r="AA21" s="293"/>
     </row>
-    <row r="22" spans="1:27" ht="16.5" customHeight="1">
+    <row r="22" spans="1:27" ht="54.95" customHeight="1">
       <c r="A22" s="292" t="s">
         <v>2293</v>
       </c>
@@ -43451,13 +43488,13 @@
       </c>
       <c r="AA22" s="293"/>
     </row>
-    <row r="23" spans="1:27" ht="16.5" customHeight="1" thickBot="1">
+    <row r="23" spans="1:27" ht="54.95" customHeight="1" thickBot="1">
       <c r="A23" s="294" t="s">
         <v>2294</v>
       </c>
       <c r="B23" s="298"/>
       <c r="C23" s="275" t="s">
-        <v>2416</v>
+        <v>2405</v>
       </c>
       <c r="D23" s="266"/>
       <c r="E23" s="266"/>
@@ -43488,7 +43525,7 @@
       </c>
       <c r="AA23" s="295"/>
     </row>
-    <row r="24" spans="1:27" ht="16.5" customHeight="1">
+    <row r="24" spans="1:27" ht="54.95" customHeight="1">
       <c r="A24" s="290" t="s">
         <v>2314</v>
       </c>
@@ -43496,7 +43533,7 @@
         <v>2315</v>
       </c>
       <c r="C24" s="274" t="s">
-        <v>2330</v>
+        <v>2327</v>
       </c>
       <c r="D24" s="268">
         <v>1</v>
@@ -43505,18 +43542,18 @@
         <v>2316</v>
       </c>
       <c r="F24" s="274" t="s">
-        <v>2319</v>
+        <v>2485</v>
       </c>
       <c r="G24" s="265"/>
       <c r="H24" s="268" t="s">
-        <v>2331</v>
+        <v>2328</v>
       </c>
       <c r="I24" s="268"/>
       <c r="J24" s="268"/>
       <c r="K24" s="268"/>
       <c r="L24" s="268"/>
       <c r="M24" s="268" t="s">
-        <v>2332</v>
+        <v>2329</v>
       </c>
       <c r="N24" s="268" t="s">
         <v>2244</v>
@@ -43532,28 +43569,28 @@
       </c>
       <c r="R24" s="268"/>
       <c r="S24" s="268" t="s">
+        <v>2319</v>
+      </c>
+      <c r="T24" s="268" t="s">
         <v>2322</v>
-      </c>
-      <c r="T24" s="268" t="s">
-        <v>2325</v>
       </c>
       <c r="U24" s="268"/>
       <c r="V24" s="268"/>
       <c r="W24" s="268"/>
       <c r="X24" s="268" t="s">
-        <v>2335</v>
+        <v>2332</v>
       </c>
       <c r="Y24" s="268" t="s">
         <v>2267</v>
       </c>
       <c r="Z24" s="268" t="s">
-        <v>2335</v>
+        <v>2332</v>
       </c>
       <c r="AA24" s="291" t="s">
-        <v>2362</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" ht="16.5" customHeight="1">
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" ht="54.95" customHeight="1">
       <c r="A25" s="292" t="s">
         <v>2314</v>
       </c>
@@ -43566,18 +43603,18 @@
         <v>2317</v>
       </c>
       <c r="F25" s="272" t="s">
-        <v>2320</v>
+        <v>2486</v>
       </c>
       <c r="G25" s="186"/>
       <c r="H25" s="185" t="s">
-        <v>2331</v>
+        <v>2328</v>
       </c>
       <c r="I25" s="185"/>
       <c r="J25" s="185"/>
       <c r="K25" s="185"/>
       <c r="L25" s="185"/>
       <c r="M25" s="185" t="s">
-        <v>2333</v>
+        <v>2330</v>
       </c>
       <c r="N25" s="185" t="s">
         <v>2244</v>
@@ -43586,35 +43623,35 @@
         <v>2245</v>
       </c>
       <c r="P25" s="185" t="s">
-        <v>2336</v>
+        <v>2333</v>
       </c>
       <c r="Q25" s="185">
         <v>1</v>
       </c>
       <c r="R25" s="185"/>
       <c r="S25" s="185" t="s">
-        <v>2323</v>
+        <v>2320</v>
       </c>
       <c r="T25" s="185" t="s">
-        <v>2325</v>
+        <v>2322</v>
       </c>
       <c r="U25" s="185"/>
       <c r="V25" s="185"/>
       <c r="W25" s="185"/>
       <c r="X25" s="185" t="s">
-        <v>2335</v>
+        <v>2332</v>
       </c>
       <c r="Y25" s="185" t="s">
         <v>1433</v>
       </c>
       <c r="Z25" s="185" t="s">
-        <v>2335</v>
+        <v>2332</v>
       </c>
       <c r="AA25" s="293" t="s">
         <v>1434</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="16.5" customHeight="1">
+    <row r="26" spans="1:27" ht="54.95" customHeight="1">
       <c r="A26" s="292" t="s">
         <v>2314</v>
       </c>
@@ -43627,18 +43664,18 @@
         <v>2318</v>
       </c>
       <c r="F26" s="272" t="s">
-        <v>2321</v>
+        <v>2487</v>
       </c>
       <c r="G26" s="186"/>
       <c r="H26" s="185" t="s">
-        <v>2331</v>
+        <v>2328</v>
       </c>
       <c r="I26" s="185"/>
       <c r="J26" s="185"/>
       <c r="K26" s="185"/>
       <c r="L26" s="185"/>
       <c r="M26" s="185" t="s">
-        <v>2334</v>
+        <v>2331</v>
       </c>
       <c r="N26" s="185" t="s">
         <v>2244</v>
@@ -43647,41 +43684,41 @@
         <v>2245</v>
       </c>
       <c r="P26" s="185" t="s">
-        <v>2337</v>
+        <v>2334</v>
       </c>
       <c r="Q26" s="185">
         <v>1</v>
       </c>
       <c r="R26" s="185"/>
       <c r="S26" s="185" t="s">
-        <v>2324</v>
+        <v>2321</v>
       </c>
       <c r="T26" s="185" t="s">
-        <v>2325</v>
+        <v>2322</v>
       </c>
       <c r="U26" s="185"/>
       <c r="V26" s="185"/>
       <c r="W26" s="185"/>
       <c r="X26" s="185" t="s">
-        <v>2335</v>
+        <v>2332</v>
       </c>
       <c r="Y26" s="185" t="s">
         <v>1435</v>
       </c>
       <c r="Z26" s="185" t="s">
-        <v>2335</v>
+        <v>2332</v>
       </c>
       <c r="AA26" s="293" t="s">
         <v>1436</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="16.5" customHeight="1">
+    <row r="27" spans="1:27" ht="54.95" customHeight="1">
       <c r="A27" s="292" t="s">
-        <v>2322</v>
+        <v>2319</v>
       </c>
       <c r="B27" s="297"/>
       <c r="C27" s="272" t="s">
-        <v>2327</v>
+        <v>2324</v>
       </c>
       <c r="D27" s="185"/>
       <c r="E27" s="185"/>
@@ -43712,13 +43749,13 @@
       </c>
       <c r="AA27" s="293"/>
     </row>
-    <row r="28" spans="1:27" ht="16.5" customHeight="1">
+    <row r="28" spans="1:27" ht="54.95" customHeight="1">
       <c r="A28" s="292" t="s">
-        <v>2323</v>
+        <v>2320</v>
       </c>
       <c r="B28" s="297"/>
       <c r="C28" s="272" t="s">
-        <v>2328</v>
+        <v>2325</v>
       </c>
       <c r="D28" s="185"/>
       <c r="E28" s="185"/>
@@ -43749,13 +43786,13 @@
       </c>
       <c r="AA28" s="293"/>
     </row>
-    <row r="29" spans="1:27" ht="16.5" customHeight="1">
+    <row r="29" spans="1:27" ht="54.95" customHeight="1">
       <c r="A29" s="292" t="s">
-        <v>2324</v>
+        <v>2321</v>
       </c>
       <c r="B29" s="297"/>
       <c r="C29" s="272" t="s">
-        <v>2329</v>
+        <v>2326</v>
       </c>
       <c r="D29" s="185"/>
       <c r="E29" s="185"/>
@@ -43786,13 +43823,13 @@
       </c>
       <c r="AA29" s="293"/>
     </row>
-    <row r="30" spans="1:27" ht="16.5" customHeight="1" thickBot="1">
+    <row r="30" spans="1:27" ht="54.95" customHeight="1" thickBot="1">
       <c r="A30" s="294" t="s">
-        <v>2325</v>
+        <v>2322</v>
       </c>
       <c r="B30" s="298"/>
       <c r="C30" s="275" t="s">
-        <v>2326</v>
+        <v>2323</v>
       </c>
       <c r="D30" s="266"/>
       <c r="E30" s="266"/>
@@ -43823,38 +43860,38 @@
       </c>
       <c r="AA30" s="295"/>
     </row>
-    <row r="31" spans="1:27" ht="16.5" customHeight="1">
+    <row r="31" spans="1:27" ht="54.95" customHeight="1">
       <c r="A31" s="290" t="s">
-        <v>2338</v>
+        <v>2335</v>
       </c>
       <c r="B31" s="296" t="s">
-        <v>2339</v>
+        <v>2336</v>
       </c>
       <c r="C31" s="274" t="s">
-        <v>2351</v>
+        <v>2348</v>
       </c>
       <c r="D31" s="268">
         <v>1</v>
       </c>
       <c r="E31" s="268" t="s">
-        <v>2340</v>
+        <v>2337</v>
       </c>
       <c r="F31" s="274" t="s">
-        <v>2358</v>
+        <v>2488</v>
       </c>
       <c r="G31" s="265"/>
       <c r="H31" s="268" t="s">
-        <v>2331</v>
+        <v>2328</v>
       </c>
       <c r="I31" s="268"/>
       <c r="J31" s="268"/>
       <c r="K31" s="268"/>
       <c r="L31" s="268"/>
       <c r="M31" s="268" t="s">
-        <v>2332</v>
+        <v>2329</v>
       </c>
       <c r="N31" s="268" t="s">
-        <v>2364</v>
+        <v>2358</v>
       </c>
       <c r="O31" s="268" t="s">
         <v>2308</v>
@@ -43865,13 +43902,13 @@
       </c>
       <c r="R31" s="268"/>
       <c r="S31" s="268" t="s">
-        <v>2342</v>
+        <v>2339</v>
       </c>
       <c r="T31" s="268" t="s">
-        <v>2348</v>
+        <v>2345</v>
       </c>
       <c r="U31" s="268" t="s">
-        <v>2370</v>
+        <v>2364</v>
       </c>
       <c r="V31" s="268" t="s">
         <v>2249</v>
@@ -43880,7 +43917,7 @@
         <v>5</v>
       </c>
       <c r="X31" s="268" t="s">
-        <v>2361</v>
+        <v>2355</v>
       </c>
       <c r="Y31" s="268" t="s">
         <v>2267</v>
@@ -43889,12 +43926,12 @@
         <v>1442</v>
       </c>
       <c r="AA31" s="291" t="s">
-        <v>2362</v>
-      </c>
-    </row>
-    <row r="32" spans="1:27" ht="16.5" customHeight="1">
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27" ht="54.95" customHeight="1">
       <c r="A32" s="292" t="s">
-        <v>2338</v>
+        <v>2335</v>
       </c>
       <c r="B32" s="297"/>
       <c r="C32" s="272"/>
@@ -43902,7 +43939,7 @@
         <v>2</v>
       </c>
       <c r="E32" s="185" t="s">
-        <v>2341</v>
+        <v>2338</v>
       </c>
       <c r="F32" s="272" t="s">
         <v>2299</v>
@@ -43924,7 +43961,7 @@
       <c r="Q32" s="185"/>
       <c r="R32" s="185"/>
       <c r="S32" s="185" t="s">
-        <v>2349</v>
+        <v>2346</v>
       </c>
       <c r="T32" s="185"/>
       <c r="U32" s="185"/>
@@ -43943,36 +43980,36 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="16.5" customHeight="1">
+    <row r="33" spans="1:27" ht="54.95" customHeight="1">
       <c r="A33" s="292" t="s">
-        <v>2342</v>
+        <v>2339</v>
       </c>
       <c r="B33" s="297"/>
       <c r="C33" s="272" t="s">
-        <v>2352</v>
+        <v>2349</v>
       </c>
       <c r="D33" s="185">
         <v>1</v>
       </c>
       <c r="E33" s="185" t="s">
-        <v>2344</v>
+        <v>2341</v>
       </c>
       <c r="F33" s="272" t="s">
-        <v>2360</v>
+        <v>2489</v>
       </c>
       <c r="G33" s="186"/>
       <c r="H33" s="185" t="s">
-        <v>2331</v>
+        <v>2328</v>
       </c>
       <c r="I33" s="185"/>
       <c r="J33" s="185"/>
       <c r="K33" s="185"/>
       <c r="L33" s="185"/>
       <c r="M33" s="185" t="s">
-        <v>2334</v>
+        <v>2331</v>
       </c>
       <c r="N33" s="185" t="s">
-        <v>2364</v>
+        <v>2358</v>
       </c>
       <c r="O33" s="185" t="s">
         <v>2308</v>
@@ -43983,13 +44020,13 @@
       </c>
       <c r="R33" s="185"/>
       <c r="S33" s="185" t="s">
-        <v>2343</v>
+        <v>2340</v>
       </c>
       <c r="T33" s="185" t="s">
-        <v>2348</v>
+        <v>2345</v>
       </c>
       <c r="U33" s="185" t="s">
-        <v>2370</v>
+        <v>2364</v>
       </c>
       <c r="V33" s="185" t="s">
         <v>2249</v>
@@ -44007,12 +44044,12 @@
         <v>1442</v>
       </c>
       <c r="AA33" s="293" t="s">
-        <v>2362</v>
-      </c>
-    </row>
-    <row r="34" spans="1:27" ht="16.5" customHeight="1">
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="34" spans="1:27" ht="54.95" customHeight="1">
       <c r="A34" s="292" t="s">
-        <v>2342</v>
+        <v>2339</v>
       </c>
       <c r="B34" s="272"/>
       <c r="C34" s="272"/>
@@ -44020,7 +44057,7 @@
         <v>2</v>
       </c>
       <c r="E34" s="185" t="s">
-        <v>2345</v>
+        <v>2342</v>
       </c>
       <c r="F34" s="272" t="s">
         <v>2299</v>
@@ -44042,7 +44079,7 @@
       <c r="Q34" s="185"/>
       <c r="R34" s="185"/>
       <c r="S34" s="185" t="s">
-        <v>2350</v>
+        <v>2347</v>
       </c>
       <c r="T34" s="185"/>
       <c r="U34" s="185"/>
@@ -44061,33 +44098,33 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="16.5" customHeight="1">
+    <row r="35" spans="1:27" ht="54.95" customHeight="1">
       <c r="A35" s="292" t="s">
-        <v>2343</v>
+        <v>2340</v>
       </c>
       <c r="B35" s="272"/>
       <c r="C35" s="272" t="s">
-        <v>2353</v>
+        <v>2350</v>
       </c>
       <c r="D35" s="185">
         <v>1</v>
       </c>
       <c r="E35" s="185" t="s">
-        <v>2347</v>
+        <v>2344</v>
       </c>
       <c r="F35" s="272" t="s">
-        <v>2359</v>
+        <v>2490</v>
       </c>
       <c r="G35" s="186"/>
       <c r="H35" s="185" t="s">
-        <v>2331</v>
+        <v>2328</v>
       </c>
       <c r="I35" s="185"/>
       <c r="J35" s="185"/>
       <c r="K35" s="185"/>
       <c r="L35" s="185"/>
       <c r="M35" s="185" t="s">
-        <v>2363</v>
+        <v>2357</v>
       </c>
       <c r="N35" s="185" t="s">
         <v>2244</v>
@@ -44096,20 +44133,20 @@
         <v>2245</v>
       </c>
       <c r="P35" s="185" t="s">
-        <v>2371</v>
+        <v>2365</v>
       </c>
       <c r="Q35" s="185">
         <v>1</v>
       </c>
       <c r="R35" s="185"/>
       <c r="S35" s="185" t="s">
-        <v>2346</v>
+        <v>2343</v>
       </c>
       <c r="T35" s="185" t="s">
-        <v>2348</v>
+        <v>2345</v>
       </c>
       <c r="U35" s="185" t="s">
-        <v>2370</v>
+        <v>2364</v>
       </c>
       <c r="V35" s="185" t="s">
         <v>2249</v>
@@ -44127,12 +44164,12 @@
         <v>1442</v>
       </c>
       <c r="AA35" s="293" t="s">
-        <v>2362</v>
-      </c>
-    </row>
-    <row r="36" spans="1:27" ht="16.5" customHeight="1">
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="36" spans="1:27" ht="54.95" customHeight="1">
       <c r="A36" s="292" t="s">
-        <v>2343</v>
+        <v>2340</v>
       </c>
       <c r="B36" s="272"/>
       <c r="C36" s="272"/>
@@ -44140,7 +44177,7 @@
         <v>2</v>
       </c>
       <c r="E36" s="185" t="s">
-        <v>2345</v>
+        <v>2342</v>
       </c>
       <c r="F36" s="272" t="s">
         <v>2299</v>
@@ -44162,14 +44199,14 @@
       <c r="Q36" s="185"/>
       <c r="R36" s="185"/>
       <c r="S36" s="185" t="s">
-        <v>2350</v>
+        <v>2347</v>
       </c>
       <c r="T36" s="185"/>
       <c r="U36" s="185"/>
       <c r="V36" s="185"/>
       <c r="W36" s="185"/>
       <c r="X36" s="185" t="s">
-        <v>2361</v>
+        <v>2355</v>
       </c>
       <c r="Y36" s="185" t="s">
         <v>1433</v>
@@ -44181,13 +44218,13 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="16.5" customHeight="1">
+    <row r="37" spans="1:27" ht="54.95" customHeight="1">
       <c r="A37" s="292" t="s">
-        <v>2346</v>
+        <v>2343</v>
       </c>
       <c r="B37" s="272"/>
       <c r="C37" s="272" t="s">
-        <v>2354</v>
+        <v>2351</v>
       </c>
       <c r="D37" s="185"/>
       <c r="E37" s="185"/>
@@ -44218,13 +44255,13 @@
       </c>
       <c r="AA37" s="293"/>
     </row>
-    <row r="38" spans="1:27" ht="16.5" customHeight="1">
+    <row r="38" spans="1:27" ht="54.95" customHeight="1">
       <c r="A38" s="292" t="s">
-        <v>2348</v>
+        <v>2345</v>
       </c>
       <c r="B38" s="272"/>
       <c r="C38" s="272" t="s">
-        <v>2355</v>
+        <v>2352</v>
       </c>
       <c r="D38" s="185"/>
       <c r="E38" s="185"/>
@@ -44255,13 +44292,13 @@
       </c>
       <c r="AA38" s="293"/>
     </row>
-    <row r="39" spans="1:27" ht="16.5" customHeight="1">
+    <row r="39" spans="1:27" ht="54.95" customHeight="1">
       <c r="A39" s="292" t="s">
-        <v>2349</v>
+        <v>2346</v>
       </c>
       <c r="B39" s="272"/>
       <c r="C39" s="272" t="s">
-        <v>2356</v>
+        <v>2353</v>
       </c>
       <c r="D39" s="185"/>
       <c r="E39" s="185"/>
@@ -44292,13 +44329,13 @@
       </c>
       <c r="AA39" s="293"/>
     </row>
-    <row r="40" spans="1:27" ht="16.5" customHeight="1" thickBot="1">
+    <row r="40" spans="1:27" ht="54.95" customHeight="1" thickBot="1">
       <c r="A40" s="299" t="s">
-        <v>2350</v>
+        <v>2347</v>
       </c>
       <c r="B40" s="300"/>
       <c r="C40" s="273" t="s">
-        <v>2357</v>
+        <v>2354</v>
       </c>
       <c r="D40" s="270"/>
       <c r="E40" s="270"/>
@@ -44329,38 +44366,38 @@
       </c>
       <c r="AA40" s="301"/>
     </row>
-    <row r="41" spans="1:27" ht="16.5" customHeight="1">
+    <row r="41" spans="1:27" ht="54.95" customHeight="1">
       <c r="A41" s="290" t="s">
-        <v>2372</v>
+        <v>2366</v>
       </c>
       <c r="B41" s="274" t="s">
-        <v>2373</v>
+        <v>2367</v>
       </c>
       <c r="C41" s="274" t="s">
-        <v>2417</v>
+        <v>2406</v>
       </c>
       <c r="D41" s="268">
         <v>1</v>
       </c>
       <c r="E41" s="268" t="s">
-        <v>2385</v>
+        <v>2379</v>
       </c>
       <c r="F41" s="274" t="s">
-        <v>2483</v>
+        <v>2491</v>
       </c>
       <c r="G41" s="265"/>
       <c r="H41" s="268" t="s">
-        <v>2383</v>
+        <v>2377</v>
       </c>
       <c r="I41" s="268"/>
       <c r="J41" s="268"/>
       <c r="K41" s="268"/>
       <c r="L41" s="268"/>
       <c r="M41" s="268" t="s">
-        <v>2491</v>
+        <v>2472</v>
       </c>
       <c r="N41" s="268" t="s">
-        <v>2364</v>
+        <v>2358</v>
       </c>
       <c r="O41" s="268" t="s">
         <v>2308</v>
@@ -44371,16 +44408,16 @@
       </c>
       <c r="R41" s="268"/>
       <c r="S41" s="268" t="s">
+        <v>2368</v>
+      </c>
+      <c r="T41" s="268" t="s">
         <v>2374</v>
-      </c>
-      <c r="T41" s="268" t="s">
-        <v>2380</v>
       </c>
       <c r="U41" s="268"/>
       <c r="V41" s="268"/>
       <c r="W41" s="268"/>
       <c r="X41" s="268" t="s">
-        <v>2381</v>
+        <v>2375</v>
       </c>
       <c r="Y41" s="268" t="s">
         <v>2267</v>
@@ -44389,12 +44426,12 @@
         <v>1443</v>
       </c>
       <c r="AA41" s="291" t="s">
-        <v>2362</v>
-      </c>
-    </row>
-    <row r="42" spans="1:27" ht="16.5" customHeight="1">
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="42" spans="1:27" ht="54.95" customHeight="1">
       <c r="A42" s="292" t="s">
-        <v>2372</v>
+        <v>2366</v>
       </c>
       <c r="B42" s="272"/>
       <c r="C42" s="272"/>
@@ -44402,10 +44439,10 @@
         <v>2</v>
       </c>
       <c r="E42" s="185" t="s">
-        <v>2485</v>
+        <v>2468</v>
       </c>
       <c r="F42" s="272" t="s">
-        <v>2484</v>
+        <v>2467</v>
       </c>
       <c r="G42" s="186"/>
       <c r="H42" s="185" t="s">
@@ -44417,14 +44454,14 @@
       <c r="L42" s="185"/>
       <c r="M42" s="185"/>
       <c r="N42" s="185" t="s">
-        <v>2490</v>
+        <v>2471</v>
       </c>
       <c r="O42" s="185"/>
       <c r="P42" s="185"/>
       <c r="Q42" s="185"/>
       <c r="R42" s="185"/>
       <c r="S42" s="185" t="s">
-        <v>2492</v>
+        <v>2473</v>
       </c>
       <c r="T42" s="185"/>
       <c r="U42" s="185"/>
@@ -44439,33 +44476,33 @@
       </c>
       <c r="AA42" s="293"/>
     </row>
-    <row r="43" spans="1:27" ht="16.5" customHeight="1">
+    <row r="43" spans="1:27" ht="54.95" customHeight="1">
       <c r="A43" s="292" t="s">
-        <v>2374</v>
+        <v>2368</v>
       </c>
       <c r="B43" s="297"/>
       <c r="C43" s="272" t="s">
-        <v>2376</v>
+        <v>2370</v>
       </c>
       <c r="D43" s="185">
         <v>1</v>
       </c>
       <c r="E43" s="185" t="s">
-        <v>2386</v>
+        <v>2380</v>
       </c>
       <c r="F43" s="272" t="s">
-        <v>2487</v>
+        <v>2492</v>
       </c>
       <c r="G43" s="186"/>
       <c r="H43" s="185" t="s">
-        <v>2382</v>
+        <v>2376</v>
       </c>
       <c r="I43" s="185"/>
       <c r="J43" s="185"/>
       <c r="K43" s="185"/>
       <c r="L43" s="185"/>
       <c r="M43" s="185" t="s">
-        <v>2491</v>
+        <v>2472</v>
       </c>
       <c r="N43" s="185" t="s">
         <v>1437</v>
@@ -44479,10 +44516,10 @@
       </c>
       <c r="R43" s="185"/>
       <c r="S43" s="185" t="s">
-        <v>2375</v>
+        <v>2369</v>
       </c>
       <c r="T43" s="185" t="s">
-        <v>2380</v>
+        <v>2374</v>
       </c>
       <c r="U43" s="185"/>
       <c r="V43" s="185"/>
@@ -44497,12 +44534,12 @@
         <v>1443</v>
       </c>
       <c r="AA43" s="293" t="s">
-        <v>2362</v>
-      </c>
-    </row>
-    <row r="44" spans="1:27" ht="16.5" customHeight="1">
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="44" spans="1:27" ht="54.95" customHeight="1">
       <c r="A44" s="292" t="s">
-        <v>2374</v>
+        <v>2368</v>
       </c>
       <c r="B44" s="297"/>
       <c r="C44" s="272"/>
@@ -44510,14 +44547,14 @@
         <v>2</v>
       </c>
       <c r="E44" s="185" t="s">
-        <v>2486</v>
+        <v>2469</v>
       </c>
       <c r="F44" s="272" t="s">
-        <v>2484</v>
+        <v>2467</v>
       </c>
       <c r="G44" s="186"/>
       <c r="H44" s="185" t="s">
-        <v>2489</v>
+        <v>2470</v>
       </c>
       <c r="I44" s="185"/>
       <c r="J44" s="185"/>
@@ -44525,14 +44562,14 @@
       <c r="L44" s="185"/>
       <c r="M44" s="185"/>
       <c r="N44" s="185" t="s">
-        <v>2490</v>
+        <v>2471</v>
       </c>
       <c r="O44" s="185"/>
       <c r="P44" s="185"/>
       <c r="Q44" s="185"/>
       <c r="R44" s="185"/>
       <c r="S44" s="185" t="s">
-        <v>2492</v>
+        <v>2473</v>
       </c>
       <c r="T44" s="185"/>
       <c r="U44" s="185"/>
@@ -44547,33 +44584,33 @@
       </c>
       <c r="AA44" s="293"/>
     </row>
-    <row r="45" spans="1:27" ht="16.5" customHeight="1">
+    <row r="45" spans="1:27" ht="54.95" customHeight="1">
       <c r="A45" s="292" t="s">
-        <v>2375</v>
+        <v>2369</v>
       </c>
       <c r="B45" s="297"/>
       <c r="C45" s="272" t="s">
-        <v>2384</v>
+        <v>2378</v>
       </c>
       <c r="D45" s="185">
         <v>1</v>
       </c>
       <c r="E45" s="185" t="s">
-        <v>2387</v>
+        <v>2381</v>
       </c>
       <c r="F45" s="272" t="s">
-        <v>2488</v>
+        <v>2493</v>
       </c>
       <c r="G45" s="186"/>
       <c r="H45" s="185" t="s">
-        <v>2383</v>
+        <v>2377</v>
       </c>
       <c r="I45" s="185"/>
       <c r="J45" s="185"/>
       <c r="K45" s="185"/>
       <c r="L45" s="185"/>
       <c r="M45" s="185" t="s">
-        <v>2491</v>
+        <v>2472</v>
       </c>
       <c r="N45" s="185" t="s">
         <v>1437</v>
@@ -44587,10 +44624,10 @@
       </c>
       <c r="R45" s="185"/>
       <c r="S45" s="185" t="s">
-        <v>2379</v>
+        <v>2373</v>
       </c>
       <c r="T45" s="185" t="s">
-        <v>2380</v>
+        <v>2374</v>
       </c>
       <c r="U45" s="185"/>
       <c r="V45" s="185"/>
@@ -44605,12 +44642,12 @@
         <v>1443</v>
       </c>
       <c r="AA45" s="293" t="s">
-        <v>2362</v>
-      </c>
-    </row>
-    <row r="46" spans="1:27" ht="16.5" customHeight="1">
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="46" spans="1:27" ht="54.95" customHeight="1">
       <c r="A46" s="292" t="s">
-        <v>2375</v>
+        <v>2369</v>
       </c>
       <c r="B46" s="297"/>
       <c r="C46" s="272"/>
@@ -44618,14 +44655,14 @@
         <v>2</v>
       </c>
       <c r="E46" s="185" t="s">
-        <v>2486</v>
+        <v>2469</v>
       </c>
       <c r="F46" s="272" t="s">
-        <v>2484</v>
+        <v>2467</v>
       </c>
       <c r="G46" s="186"/>
       <c r="H46" s="185" t="s">
-        <v>2489</v>
+        <v>2470</v>
       </c>
       <c r="I46" s="185"/>
       <c r="J46" s="185"/>
@@ -44633,14 +44670,14 @@
       <c r="L46" s="185"/>
       <c r="M46" s="185"/>
       <c r="N46" s="185" t="s">
-        <v>2490</v>
+        <v>2471</v>
       </c>
       <c r="O46" s="185"/>
       <c r="P46" s="185"/>
       <c r="Q46" s="185"/>
       <c r="R46" s="185"/>
       <c r="S46" s="185" t="s">
-        <v>2492</v>
+        <v>2473</v>
       </c>
       <c r="T46" s="185"/>
       <c r="U46" s="185"/>
@@ -44655,13 +44692,13 @@
       </c>
       <c r="AA46" s="293"/>
     </row>
-    <row r="47" spans="1:27" ht="16.5" customHeight="1">
+    <row r="47" spans="1:27" ht="54.95" customHeight="1">
       <c r="A47" s="292" t="s">
-        <v>2379</v>
+        <v>2373</v>
       </c>
       <c r="B47" s="297"/>
       <c r="C47" s="272" t="s">
-        <v>2377</v>
+        <v>2371</v>
       </c>
       <c r="D47" s="280"/>
       <c r="E47" s="280"/>
@@ -44684,7 +44721,7 @@
       <c r="V47" s="280"/>
       <c r="W47" s="280"/>
       <c r="X47" s="280" t="s">
-        <v>2381</v>
+        <v>2375</v>
       </c>
       <c r="Y47" s="280"/>
       <c r="Z47" s="280" t="s">
@@ -44692,13 +44729,13 @@
       </c>
       <c r="AA47" s="304"/>
     </row>
-    <row r="48" spans="1:27" ht="16.5" customHeight="1">
+    <row r="48" spans="1:27" ht="54.95" customHeight="1">
       <c r="A48" s="292" t="s">
-        <v>2380</v>
+        <v>2374</v>
       </c>
       <c r="B48" s="297"/>
       <c r="C48" s="297" t="s">
-        <v>2378</v>
+        <v>2372</v>
       </c>
       <c r="D48" s="280"/>
       <c r="E48" s="280"/>
@@ -44729,13 +44766,13 @@
       </c>
       <c r="AA48" s="293"/>
     </row>
-    <row r="49" spans="1:27" ht="16.5" customHeight="1" thickBot="1">
+    <row r="49" spans="1:27" ht="54.95" customHeight="1" thickBot="1">
       <c r="A49" s="320" t="s">
-        <v>2492</v>
+        <v>2473</v>
       </c>
       <c r="B49" s="321"/>
       <c r="C49" s="321" t="s">
-        <v>2493</v>
+        <v>2474</v>
       </c>
       <c r="D49" s="322"/>
       <c r="E49" s="322"/>
@@ -44766,23 +44803,25 @@
       </c>
       <c r="AA49" s="326"/>
     </row>
-    <row r="50" spans="1:27" ht="16.5" customHeight="1">
+    <row r="50" spans="1:27" ht="54.95" customHeight="1">
       <c r="A50" s="305" t="s">
-        <v>2389</v>
+        <v>2383</v>
       </c>
       <c r="B50" s="306" t="s">
-        <v>2390</v>
+        <v>2384</v>
       </c>
       <c r="C50" s="306" t="s">
-        <v>2405</v>
+        <v>2394</v>
       </c>
       <c r="D50" s="283">
         <v>1</v>
       </c>
       <c r="E50" s="283" t="s">
-        <v>2391</v>
-      </c>
-      <c r="F50" s="306"/>
+        <v>2480</v>
+      </c>
+      <c r="F50" s="306" t="s">
+        <v>2476</v>
+      </c>
       <c r="G50" s="283"/>
       <c r="H50" s="283" t="s">
         <v>2243</v>
@@ -44793,33 +44832,33 @@
       <c r="L50" s="283"/>
       <c r="M50" s="283"/>
       <c r="N50" s="283" t="s">
-        <v>2408</v>
+        <v>2397</v>
       </c>
       <c r="O50" s="283" t="s">
-        <v>2409</v>
+        <v>2398</v>
       </c>
       <c r="P50" s="283"/>
       <c r="Q50" s="283"/>
       <c r="R50" s="283"/>
       <c r="S50" s="283" t="s">
-        <v>2394</v>
+        <v>2385</v>
       </c>
       <c r="T50" s="283"/>
       <c r="U50" s="283"/>
       <c r="V50" s="283"/>
       <c r="W50" s="283"/>
       <c r="X50" s="283" t="s">
-        <v>2402</v>
+        <v>2391</v>
       </c>
       <c r="Y50" s="283"/>
       <c r="Z50" s="307" t="s">
-        <v>2401</v>
+        <v>2390</v>
       </c>
       <c r="AA50" s="308"/>
     </row>
-    <row r="51" spans="1:27" ht="16.5" customHeight="1">
+    <row r="51" spans="1:27" ht="54.95" customHeight="1">
       <c r="A51" s="277" t="s">
-        <v>2388</v>
+        <v>2382</v>
       </c>
       <c r="B51" s="309"/>
       <c r="C51" s="309"/>
@@ -44827,9 +44866,11 @@
         <v>2</v>
       </c>
       <c r="E51" s="284" t="s">
-        <v>2393</v>
-      </c>
-      <c r="F51" s="309"/>
+        <v>2481</v>
+      </c>
+      <c r="F51" s="309" t="s">
+        <v>2477</v>
+      </c>
       <c r="G51" s="284"/>
       <c r="H51" s="284" t="s">
         <v>2243</v>
@@ -44840,33 +44881,33 @@
       <c r="L51" s="284"/>
       <c r="M51" s="284"/>
       <c r="N51" s="284" t="s">
-        <v>2408</v>
+        <v>2397</v>
       </c>
       <c r="O51" s="284" t="s">
-        <v>2410</v>
+        <v>2399</v>
       </c>
       <c r="P51" s="284"/>
       <c r="Q51" s="284"/>
       <c r="R51" s="284"/>
       <c r="S51" s="284" t="s">
-        <v>2394</v>
+        <v>2385</v>
       </c>
       <c r="T51" s="284"/>
       <c r="U51" s="284"/>
       <c r="V51" s="284"/>
       <c r="W51" s="284"/>
       <c r="X51" s="284" t="s">
-        <v>2401</v>
+        <v>2390</v>
       </c>
       <c r="Y51" s="284"/>
       <c r="Z51" s="280" t="s">
-        <v>2401</v>
+        <v>2390</v>
       </c>
       <c r="AA51" s="304"/>
     </row>
-    <row r="52" spans="1:27" ht="16.5" customHeight="1">
+    <row r="52" spans="1:27" ht="54.95" customHeight="1">
       <c r="A52" s="277" t="s">
-        <v>2389</v>
+        <v>2383</v>
       </c>
       <c r="B52" s="309"/>
       <c r="C52" s="309"/>
@@ -44874,9 +44915,11 @@
         <v>3</v>
       </c>
       <c r="E52" s="284" t="s">
-        <v>2392</v>
-      </c>
-      <c r="F52" s="309"/>
+        <v>2482</v>
+      </c>
+      <c r="F52" s="309" t="s">
+        <v>2478</v>
+      </c>
       <c r="G52" s="284"/>
       <c r="H52" s="284" t="s">
         <v>2243</v>
@@ -44887,46 +44930,46 @@
       <c r="L52" s="284"/>
       <c r="M52" s="284"/>
       <c r="N52" s="284" t="s">
-        <v>2408</v>
+        <v>2397</v>
       </c>
       <c r="O52" s="284" t="s">
-        <v>2411</v>
+        <v>2400</v>
       </c>
       <c r="P52" s="284"/>
       <c r="Q52" s="284"/>
       <c r="R52" s="284"/>
       <c r="S52" s="284" t="s">
-        <v>2394</v>
+        <v>2385</v>
       </c>
       <c r="T52" s="284"/>
       <c r="U52" s="284"/>
       <c r="V52" s="284"/>
       <c r="W52" s="284"/>
       <c r="X52" s="284" t="s">
-        <v>2401</v>
+        <v>2390</v>
       </c>
       <c r="Y52" s="284"/>
       <c r="Z52" s="280" t="s">
-        <v>2401</v>
+        <v>2390</v>
       </c>
       <c r="AA52" s="304"/>
     </row>
-    <row r="53" spans="1:27" s="3" customFormat="1" ht="16.5" customHeight="1">
+    <row r="53" spans="1:27" s="3" customFormat="1" ht="54.95" customHeight="1">
       <c r="A53" s="277" t="s">
-        <v>2394</v>
+        <v>2385</v>
       </c>
       <c r="B53" s="309"/>
       <c r="C53" s="309" t="s">
-        <v>2406</v>
+        <v>2395</v>
       </c>
       <c r="D53" s="284">
         <v>1</v>
       </c>
       <c r="E53" s="284" t="s">
-        <v>2395</v>
+        <v>2386</v>
       </c>
       <c r="F53" s="309" t="s">
-        <v>2398</v>
+        <v>2389</v>
       </c>
       <c r="G53" s="284"/>
       <c r="H53" s="284" t="s">
@@ -44941,7 +44984,7 @@
         <v>2248</v>
       </c>
       <c r="O53" s="284" t="s">
-        <v>2412</v>
+        <v>2401</v>
       </c>
       <c r="P53" s="284"/>
       <c r="Q53" s="284">
@@ -44949,28 +44992,28 @@
       </c>
       <c r="R53" s="284"/>
       <c r="S53" s="284" t="s">
-        <v>2404</v>
+        <v>2393</v>
       </c>
       <c r="T53" s="284"/>
       <c r="U53" s="284"/>
       <c r="V53" s="284"/>
       <c r="W53" s="284"/>
       <c r="X53" s="284" t="s">
-        <v>2401</v>
+        <v>2390</v>
       </c>
       <c r="Y53" s="280" t="s">
         <v>2267</v>
       </c>
       <c r="Z53" s="280" t="s">
-        <v>2401</v>
+        <v>2390</v>
       </c>
       <c r="AA53" s="304" t="s">
-        <v>2362</v>
-      </c>
-    </row>
-    <row r="54" spans="1:27" s="3" customFormat="1" ht="16.5" customHeight="1">
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="54" spans="1:27" s="3" customFormat="1" ht="54.95" customHeight="1">
       <c r="A54" s="277" t="s">
-        <v>2394</v>
+        <v>2385</v>
       </c>
       <c r="B54" s="297"/>
       <c r="C54" s="297"/>
@@ -44978,10 +45021,10 @@
         <v>2</v>
       </c>
       <c r="E54" s="280" t="s">
-        <v>2396</v>
-      </c>
-      <c r="F54" s="297" t="s">
-        <v>2399</v>
+        <v>2387</v>
+      </c>
+      <c r="F54" s="130" t="s">
+        <v>2494</v>
       </c>
       <c r="G54" s="297" t="s">
         <v>2306</v>
@@ -44990,7 +45033,7 @@
         <v>2305</v>
       </c>
       <c r="I54" s="280" t="s">
-        <v>2462</v>
+        <v>2446</v>
       </c>
       <c r="J54" s="280" t="s">
         <v>2308</v>
@@ -45006,10 +45049,10 @@
         <v>2258</v>
       </c>
       <c r="O54" s="280" t="s">
-        <v>2413</v>
+        <v>2402</v>
       </c>
       <c r="P54" s="280" t="s">
-        <v>2336</v>
+        <v>2333</v>
       </c>
       <c r="Q54" s="280">
         <v>1</v>
@@ -45018,28 +45061,28 @@
         <v>3</v>
       </c>
       <c r="S54" s="280" t="s">
-        <v>2404</v>
+        <v>2393</v>
       </c>
       <c r="T54" s="280"/>
       <c r="U54" s="280"/>
       <c r="V54" s="280"/>
       <c r="W54" s="280"/>
       <c r="X54" s="280" t="s">
-        <v>2401</v>
+        <v>2390</v>
       </c>
       <c r="Y54" s="185" t="s">
-        <v>2414</v>
+        <v>2403</v>
       </c>
       <c r="Z54" s="280" t="s">
-        <v>2401</v>
+        <v>2390</v>
       </c>
       <c r="AA54" s="304" t="s">
-        <v>2403</v>
-      </c>
-    </row>
-    <row r="55" spans="1:27" ht="16.5" customHeight="1">
+        <v>2392</v>
+      </c>
+    </row>
+    <row r="55" spans="1:27" ht="54.95" customHeight="1">
       <c r="A55" s="277" t="s">
-        <v>2394</v>
+        <v>2385</v>
       </c>
       <c r="B55" s="297"/>
       <c r="C55" s="297"/>
@@ -45047,10 +45090,10 @@
         <v>3</v>
       </c>
       <c r="E55" s="280" t="s">
-        <v>2397</v>
-      </c>
-      <c r="F55" s="297" t="s">
-        <v>2400</v>
+        <v>2388</v>
+      </c>
+      <c r="F55" s="130" t="s">
+        <v>2495</v>
       </c>
       <c r="G55" s="297" t="s">
         <v>2306</v>
@@ -45059,7 +45102,7 @@
         <v>2305</v>
       </c>
       <c r="I55" s="280" t="s">
-        <v>2463</v>
+        <v>2447</v>
       </c>
       <c r="J55" s="280" t="s">
         <v>2308</v>
@@ -45075,10 +45118,10 @@
         <v>2258</v>
       </c>
       <c r="O55" s="280" t="s">
-        <v>2413</v>
+        <v>2402</v>
       </c>
       <c r="P55" s="280" t="s">
-        <v>2337</v>
+        <v>2334</v>
       </c>
       <c r="Q55" s="280">
         <v>1</v>
@@ -45087,32 +45130,32 @@
         <v>3</v>
       </c>
       <c r="S55" s="280" t="s">
-        <v>2404</v>
+        <v>2393</v>
       </c>
       <c r="T55" s="280"/>
       <c r="U55" s="280"/>
       <c r="V55" s="280"/>
       <c r="W55" s="280"/>
       <c r="X55" s="280" t="s">
-        <v>2402</v>
+        <v>2391</v>
       </c>
       <c r="Y55" s="185" t="s">
         <v>1435</v>
       </c>
       <c r="Z55" s="280" t="s">
-        <v>2401</v>
+        <v>2390</v>
       </c>
       <c r="AA55" s="304" t="s">
-        <v>2436</v>
-      </c>
-    </row>
-    <row r="56" spans="1:27" ht="16.5" customHeight="1" thickBot="1">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="56" spans="1:27" ht="54.95" customHeight="1" thickBot="1">
       <c r="A56" s="278" t="s">
-        <v>2404</v>
+        <v>2393</v>
       </c>
       <c r="B56" s="310"/>
       <c r="C56" s="310" t="s">
-        <v>2407</v>
+        <v>2396</v>
       </c>
       <c r="D56" s="285"/>
       <c r="E56" s="285"/>
@@ -45135,32 +45178,32 @@
       <c r="V56" s="285"/>
       <c r="W56" s="285"/>
       <c r="X56" s="285" t="s">
-        <v>2402</v>
+        <v>2391</v>
       </c>
       <c r="Y56" s="285"/>
       <c r="Z56" s="281" t="s">
-        <v>2402</v>
+        <v>2391</v>
       </c>
       <c r="AA56" s="311"/>
     </row>
-    <row r="57" spans="1:27" ht="16.5" customHeight="1">
+    <row r="57" spans="1:27" ht="54.95" customHeight="1">
       <c r="A57" s="317" t="s">
-        <v>2418</v>
+        <v>2407</v>
       </c>
       <c r="B57" s="306" t="s">
-        <v>2422</v>
+        <v>2411</v>
       </c>
       <c r="C57" s="306" t="s">
-        <v>2423</v>
+        <v>2412</v>
       </c>
       <c r="D57" s="283">
         <v>1</v>
       </c>
       <c r="E57" s="283" t="s">
-        <v>2427</v>
+        <v>2416</v>
       </c>
       <c r="F57" s="306" t="s">
-        <v>2430</v>
+        <v>2479</v>
       </c>
       <c r="G57" s="283"/>
       <c r="H57" s="283" t="s">
@@ -45172,25 +45215,25 @@
       <c r="L57" s="283"/>
       <c r="M57" s="283"/>
       <c r="N57" s="283" t="s">
-        <v>2433</v>
+        <v>2421</v>
       </c>
       <c r="O57" s="283" t="s">
         <v>2249</v>
       </c>
       <c r="P57" s="283"/>
       <c r="Q57" s="283">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R57" s="283"/>
       <c r="S57" s="283" t="s">
-        <v>2419</v>
+        <v>2408</v>
       </c>
       <c r="T57" s="283"/>
       <c r="U57" s="283"/>
       <c r="V57" s="283"/>
       <c r="W57" s="283"/>
       <c r="X57" s="283" t="s">
-        <v>2435</v>
+        <v>2423</v>
       </c>
       <c r="Y57" s="283" t="s">
         <v>2267</v>
@@ -45199,10 +45242,10 @@
         <v>1444</v>
       </c>
       <c r="AA57" s="308" t="s">
-        <v>2362</v>
-      </c>
-    </row>
-    <row r="58" spans="1:27" ht="16.5" customHeight="1">
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="58" spans="1:27" ht="54.95" customHeight="1">
       <c r="A58" s="318" t="s">
         <v>1376</v>
       </c>
@@ -45212,10 +45255,10 @@
         <v>2</v>
       </c>
       <c r="E58" s="284" t="s">
-        <v>2428</v>
+        <v>2417</v>
       </c>
       <c r="F58" s="309" t="s">
-        <v>2431</v>
+        <v>2419</v>
       </c>
       <c r="G58" s="284"/>
       <c r="H58" s="284" t="s">
@@ -45227,7 +45270,7 @@
       <c r="L58" s="284"/>
       <c r="M58" s="284"/>
       <c r="N58" s="284" t="s">
-        <v>2434</v>
+        <v>2422</v>
       </c>
       <c r="O58" s="284" t="s">
         <v>2249</v>
@@ -45238,7 +45281,7 @@
       </c>
       <c r="R58" s="284"/>
       <c r="S58" s="284" t="s">
-        <v>2420</v>
+        <v>2409</v>
       </c>
       <c r="T58" s="284"/>
       <c r="U58" s="284"/>
@@ -45248,16 +45291,16 @@
         <v>1444</v>
       </c>
       <c r="Y58" s="185" t="s">
-        <v>2414</v>
+        <v>2403</v>
       </c>
       <c r="Z58" s="280" t="s">
         <v>1444</v>
       </c>
       <c r="AA58" s="304" t="s">
-        <v>2403</v>
-      </c>
-    </row>
-    <row r="59" spans="1:27" ht="16.5" customHeight="1">
+        <v>2392</v>
+      </c>
+    </row>
+    <row r="59" spans="1:27" ht="54.95" customHeight="1">
       <c r="A59" s="318" t="s">
         <v>1376</v>
       </c>
@@ -45267,10 +45310,10 @@
         <v>3</v>
       </c>
       <c r="E59" s="284" t="s">
-        <v>2429</v>
+        <v>2418</v>
       </c>
       <c r="F59" s="309" t="s">
-        <v>2432</v>
+        <v>2420</v>
       </c>
       <c r="G59" s="284"/>
       <c r="H59" s="284" t="s">
@@ -45293,7 +45336,7 @@
       </c>
       <c r="R59" s="284"/>
       <c r="S59" s="284" t="s">
-        <v>2421</v>
+        <v>2410</v>
       </c>
       <c r="T59" s="284"/>
       <c r="U59" s="284"/>
@@ -45309,16 +45352,16 @@
         <v>1444</v>
       </c>
       <c r="AA59" s="304" t="s">
-        <v>2436</v>
-      </c>
-    </row>
-    <row r="60" spans="1:27" ht="16.5" customHeight="1">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="60" spans="1:27" ht="54.95" customHeight="1">
       <c r="A60" s="318" t="s">
-        <v>2419</v>
+        <v>2408</v>
       </c>
       <c r="B60" s="309"/>
       <c r="C60" s="309" t="s">
-        <v>2424</v>
+        <v>2413</v>
       </c>
       <c r="D60" s="284"/>
       <c r="E60" s="284"/>
@@ -45349,13 +45392,13 @@
       </c>
       <c r="AA60" s="304"/>
     </row>
-    <row r="61" spans="1:27" ht="16.5" customHeight="1">
+    <row r="61" spans="1:27" ht="54.95" customHeight="1">
       <c r="A61" s="318" t="s">
-        <v>2420</v>
+        <v>2409</v>
       </c>
       <c r="B61" s="309"/>
       <c r="C61" s="309" t="s">
-        <v>2425</v>
+        <v>2414</v>
       </c>
       <c r="D61" s="284"/>
       <c r="E61" s="284"/>
@@ -45378,7 +45421,7 @@
       <c r="V61" s="284"/>
       <c r="W61" s="284"/>
       <c r="X61" s="284" t="s">
-        <v>2435</v>
+        <v>2423</v>
       </c>
       <c r="Y61" s="284"/>
       <c r="Z61" s="280" t="s">
@@ -45386,13 +45429,13 @@
       </c>
       <c r="AA61" s="304"/>
     </row>
-    <row r="62" spans="1:27" ht="16.5" customHeight="1" thickBot="1">
+    <row r="62" spans="1:27" ht="54.95" customHeight="1" thickBot="1">
       <c r="A62" s="319" t="s">
-        <v>2421</v>
+        <v>2410</v>
       </c>
       <c r="B62" s="310"/>
       <c r="C62" s="310" t="s">
-        <v>2426</v>
+        <v>2415</v>
       </c>
       <c r="D62" s="285"/>
       <c r="E62" s="285"/>
@@ -45423,36 +45466,36 @@
       </c>
       <c r="AA62" s="311"/>
     </row>
-    <row r="63" spans="1:27" ht="16.5" customHeight="1">
+    <row r="63" spans="1:27" ht="54.95" customHeight="1">
       <c r="A63" s="305" t="s">
-        <v>2438</v>
+        <v>2426</v>
       </c>
       <c r="B63" s="306" t="s">
-        <v>2439</v>
+        <v>2427</v>
       </c>
       <c r="C63" s="306" t="s">
-        <v>2465</v>
+        <v>2449</v>
       </c>
       <c r="D63" s="283">
         <v>1</v>
       </c>
       <c r="E63" s="283" t="s">
-        <v>2444</v>
-      </c>
-      <c r="F63" s="306" t="s">
-        <v>2451</v>
+        <v>2432</v>
+      </c>
+      <c r="F63" s="327" t="s">
+        <v>2496</v>
       </c>
       <c r="G63" s="306" t="s">
-        <v>2458</v>
+        <v>2442</v>
       </c>
       <c r="H63" s="283" t="s">
         <v>2305</v>
       </c>
       <c r="I63" s="283" t="s">
-        <v>2459</v>
+        <v>2443</v>
       </c>
       <c r="J63" s="283" t="s">
-        <v>2457</v>
+        <v>2441</v>
       </c>
       <c r="K63" s="283" t="s">
         <v>2249</v>
@@ -45475,28 +45518,28 @@
       </c>
       <c r="R63" s="283"/>
       <c r="S63" s="283" t="s">
-        <v>2440</v>
+        <v>2428</v>
       </c>
       <c r="T63" s="283"/>
       <c r="U63" s="283"/>
       <c r="V63" s="283"/>
       <c r="W63" s="283"/>
       <c r="X63" s="283" t="s">
-        <v>2456</v>
+        <v>2440</v>
       </c>
       <c r="Y63" s="283" t="s">
         <v>2267</v>
       </c>
       <c r="Z63" s="307" t="s">
-        <v>2455</v>
+        <v>2439</v>
       </c>
       <c r="AA63" s="308" t="s">
-        <v>2362</v>
-      </c>
-    </row>
-    <row r="64" spans="1:27" ht="16.5" customHeight="1">
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="64" spans="1:27" ht="54.95" customHeight="1">
       <c r="A64" s="318" t="s">
-        <v>2438</v>
+        <v>2426</v>
       </c>
       <c r="B64" s="309"/>
       <c r="C64" s="309"/>
@@ -45504,21 +45547,21 @@
         <v>2</v>
       </c>
       <c r="E64" s="284" t="s">
-        <v>2445</v>
-      </c>
-      <c r="F64" s="309" t="s">
-        <v>2494</v>
+        <v>2433</v>
+      </c>
+      <c r="F64" s="328" t="s">
+        <v>2497</v>
       </c>
       <c r="G64" s="284"/>
       <c r="H64" s="284" t="s">
-        <v>2383</v>
+        <v>2377</v>
       </c>
       <c r="I64" s="284"/>
       <c r="J64" s="284"/>
       <c r="K64" s="284"/>
       <c r="L64" s="284"/>
       <c r="M64" s="284" t="s">
-        <v>2495</v>
+        <v>2475</v>
       </c>
       <c r="N64" s="284" t="s">
         <v>2244</v>
@@ -45534,30 +45577,30 @@
       </c>
       <c r="R64" s="284"/>
       <c r="S64" s="284" t="s">
-        <v>2441</v>
+        <v>2429</v>
       </c>
       <c r="T64" s="284" t="s">
-        <v>2442</v>
+        <v>2430</v>
       </c>
       <c r="U64" s="284"/>
       <c r="V64" s="284"/>
       <c r="W64" s="284"/>
       <c r="X64" s="284" t="s">
-        <v>2455</v>
+        <v>2439</v>
       </c>
       <c r="Y64" s="185" t="s">
-        <v>2414</v>
+        <v>2403</v>
       </c>
       <c r="Z64" s="280" t="s">
-        <v>2455</v>
+        <v>2439</v>
       </c>
       <c r="AA64" s="304" t="s">
-        <v>2403</v>
-      </c>
-    </row>
-    <row r="65" spans="1:27" ht="16.5" customHeight="1">
+        <v>2392</v>
+      </c>
+    </row>
+    <row r="65" spans="1:27" ht="54.95" customHeight="1">
       <c r="A65" s="318" t="s">
-        <v>2438</v>
+        <v>2426</v>
       </c>
       <c r="B65" s="309"/>
       <c r="C65" s="309"/>
@@ -45565,10 +45608,10 @@
         <v>3</v>
       </c>
       <c r="E65" s="284" t="s">
-        <v>2446</v>
-      </c>
-      <c r="F65" s="309" t="s">
-        <v>2454</v>
+        <v>2434</v>
+      </c>
+      <c r="F65" s="328" t="s">
+        <v>2498</v>
       </c>
       <c r="G65" s="284"/>
       <c r="H65" s="284" t="s">
@@ -45576,7 +45619,7 @@
       </c>
       <c r="I65" s="284"/>
       <c r="J65" s="284" t="s">
-        <v>2464</v>
+        <v>2448</v>
       </c>
       <c r="K65" s="284" t="s">
         <v>2247</v>
@@ -45599,32 +45642,32 @@
       </c>
       <c r="R65" s="284"/>
       <c r="S65" s="284" t="s">
-        <v>2443</v>
+        <v>2431</v>
       </c>
       <c r="T65" s="284"/>
       <c r="U65" s="284"/>
       <c r="V65" s="284"/>
       <c r="W65" s="284"/>
       <c r="X65" s="284" t="s">
-        <v>2455</v>
+        <v>2439</v>
       </c>
       <c r="Y65" s="185" t="s">
         <v>1435</v>
       </c>
       <c r="Z65" s="280" t="s">
-        <v>2455</v>
+        <v>2439</v>
       </c>
       <c r="AA65" s="304" t="s">
-        <v>2436</v>
-      </c>
-    </row>
-    <row r="66" spans="1:27" ht="16.5" customHeight="1">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="66" spans="1:27" ht="54.95" customHeight="1">
       <c r="A66" s="318" t="s">
-        <v>2440</v>
+        <v>2428</v>
       </c>
       <c r="B66" s="309"/>
       <c r="C66" s="309" t="s">
-        <v>2447</v>
+        <v>2435</v>
       </c>
       <c r="D66" s="284"/>
       <c r="E66" s="284"/>
@@ -45647,21 +45690,21 @@
       <c r="V66" s="284"/>
       <c r="W66" s="284"/>
       <c r="X66" s="284" t="s">
-        <v>2455</v>
+        <v>2439</v>
       </c>
       <c r="Y66" s="284"/>
       <c r="Z66" s="280" t="s">
-        <v>2455</v>
+        <v>2439</v>
       </c>
       <c r="AA66" s="304"/>
     </row>
-    <row r="67" spans="1:27" ht="16.5" customHeight="1">
+    <row r="67" spans="1:27" ht="54.95" customHeight="1">
       <c r="A67" s="318" t="s">
-        <v>2441</v>
+        <v>2429</v>
       </c>
       <c r="B67" s="309"/>
       <c r="C67" s="309" t="s">
-        <v>2449</v>
+        <v>2437</v>
       </c>
       <c r="D67" s="284"/>
       <c r="E67" s="284"/>
@@ -45684,21 +45727,21 @@
       <c r="V67" s="284"/>
       <c r="W67" s="284"/>
       <c r="X67" s="284" t="s">
-        <v>2455</v>
+        <v>2439</v>
       </c>
       <c r="Y67" s="284"/>
       <c r="Z67" s="280" t="s">
-        <v>2455</v>
+        <v>2439</v>
       </c>
       <c r="AA67" s="304"/>
     </row>
-    <row r="68" spans="1:27" ht="16.5" customHeight="1">
+    <row r="68" spans="1:27" ht="54.95" customHeight="1">
       <c r="A68" s="318" t="s">
-        <v>2442</v>
+        <v>2430</v>
       </c>
       <c r="B68" s="309"/>
       <c r="C68" s="309" t="s">
-        <v>2450</v>
+        <v>2438</v>
       </c>
       <c r="D68" s="284"/>
       <c r="E68" s="284"/>
@@ -45721,21 +45764,21 @@
       <c r="V68" s="284"/>
       <c r="W68" s="284"/>
       <c r="X68" s="284" t="s">
-        <v>2455</v>
+        <v>2439</v>
       </c>
       <c r="Y68" s="284"/>
       <c r="Z68" s="280" t="s">
-        <v>2455</v>
+        <v>2439</v>
       </c>
       <c r="AA68" s="304"/>
     </row>
-    <row r="69" spans="1:27" ht="16.5" customHeight="1" thickBot="1">
+    <row r="69" spans="1:27" ht="54.95" customHeight="1" thickBot="1">
       <c r="A69" s="319" t="s">
-        <v>2443</v>
+        <v>2431</v>
       </c>
       <c r="B69" s="310"/>
       <c r="C69" s="310" t="s">
-        <v>2448</v>
+        <v>2436</v>
       </c>
       <c r="D69" s="285"/>
       <c r="E69" s="285"/>
@@ -45758,20 +45801,20 @@
       <c r="V69" s="285"/>
       <c r="W69" s="285"/>
       <c r="X69" s="285" t="s">
-        <v>2455</v>
+        <v>2439</v>
       </c>
       <c r="Y69" s="285"/>
       <c r="Z69" s="281" t="s">
-        <v>2455</v>
+        <v>2439</v>
       </c>
       <c r="AA69" s="311"/>
     </row>
-    <row r="70" spans="1:27" ht="16.5" customHeight="1">
+    <row r="70" spans="1:27" ht="54.95" customHeight="1">
       <c r="A70" s="312" t="s">
-        <v>2481</v>
+        <v>2465</v>
       </c>
       <c r="B70" s="312" t="s">
-        <v>2481</v>
+        <v>2465</v>
       </c>
       <c r="C70" s="312"/>
       <c r="D70" s="286"/>
@@ -45799,12 +45842,12 @@
       <c r="Z70" s="313"/>
       <c r="AA70" s="313"/>
     </row>
-    <row r="71" spans="1:27" ht="16.5" customHeight="1">
+    <row r="71" spans="1:27" ht="54.95" customHeight="1">
       <c r="A71" s="312" t="s">
-        <v>2482</v>
+        <v>2466</v>
       </c>
       <c r="B71" s="309" t="s">
-        <v>2482</v>
+        <v>2466</v>
       </c>
       <c r="C71" s="309"/>
       <c r="D71" s="284"/>
@@ -45832,7 +45875,7 @@
       <c r="Z71" s="280"/>
       <c r="AA71" s="280"/>
     </row>
-    <row r="72" spans="1:27" ht="16.5" customHeight="1">
+    <row r="72" spans="1:27" ht="54.95" customHeight="1">
       <c r="A72" s="309"/>
       <c r="B72" s="309"/>
       <c r="C72" s="309"/>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erang\Desktop\RELIC\Assets\ExcelSource\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k2104200063\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3DA499C-67AF-4ABC-8A8F-DC9E5CB48BC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58490897-2F25-4FC2-9454-D67C8909E240}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -32,17 +32,6 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -13747,15 +13736,15 @@
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
   <si>
-    <t>"거점으로 향하는 길목, 한 탐사자가 작은 모닥불 앞에 앉아 있다."</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
     <t>"잠시 휴식을 취한 일행은 기운을 되찾았다."</t>
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
   <si>
     <t>event_tutorial</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>"거점으로 향하는 길목, 한 탐사자가 휴식하고 있다."</t>
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
 </sst>
@@ -27246,6 +27235,7 @@
   </sheetData>
   <phoneticPr fontId="40" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -45713,7 +45703,7 @@
         <v>2539</v>
       </c>
       <c r="C70" s="256" t="s">
-        <v>2551</v>
+        <v>2553</v>
       </c>
       <c r="D70" s="256">
         <v>1</v>
@@ -45752,13 +45742,13 @@
       <c r="V70" s="256"/>
       <c r="W70" s="256"/>
       <c r="X70" s="256" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
       <c r="Y70" s="256" t="s">
         <v>2248</v>
       </c>
       <c r="Z70" s="256" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
       <c r="AA70" s="256" t="s">
         <v>2337</v>
@@ -45770,7 +45760,7 @@
       </c>
       <c r="B71" s="244"/>
       <c r="C71" s="244" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
       <c r="D71" s="244"/>
       <c r="E71" s="244"/>
@@ -45793,11 +45783,11 @@
       <c r="V71" s="244"/>
       <c r="W71" s="244"/>
       <c r="X71" s="244" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
       <c r="Y71" s="244"/>
       <c r="Z71" s="244" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
       <c r="AA71" s="244"/>
     </row>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k2104200063\Desktop\RELIC\Assets\ExcelSource\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erang\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58490897-2F25-4FC2-9454-D67C8909E240}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD468700-BB88-41A0-B5B2-5D50DC59AB53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5196" uniqueCount="2554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5196" uniqueCount="2555">
   <si>
     <t>캐릭터ID</t>
   </si>
@@ -13745,6 +13745,10 @@
   </si>
   <si>
     <t>"거점으로 향하는 길목, 한 탐사자가 휴식하고 있다."</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>Common:47,Rare:38,Epic:12,Unique:3</t>
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
 </sst>
@@ -16063,7 +16067,7 @@
         <v>47</v>
       </c>
       <c r="C3" s="8">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="D3" s="7">
         <v>10</v>
@@ -16134,7 +16138,7 @@
         <v>64</v>
       </c>
       <c r="C4" s="12">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="D4" s="11">
         <v>12</v>
@@ -16205,7 +16209,7 @@
         <v>80</v>
       </c>
       <c r="C5" s="12">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="D5" s="11">
         <v>14</v>
@@ -16276,7 +16280,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="12">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="D6" s="11">
         <v>11</v>
@@ -42421,7 +42425,7 @@
         <v>2240</v>
       </c>
       <c r="P3" s="241" t="s">
-        <v>2249</v>
+        <v>2554</v>
       </c>
       <c r="Q3" s="241">
         <v>1</v>
@@ -42480,7 +42484,7 @@
         <v>2241</v>
       </c>
       <c r="P4" s="161" t="s">
-        <v>2249</v>
+        <v>2554</v>
       </c>
       <c r="Q4" s="161">
         <v>1</v>
@@ -42539,7 +42543,7 @@
         <v>2242</v>
       </c>
       <c r="P5" s="161" t="s">
-        <v>2249</v>
+        <v>2554</v>
       </c>
       <c r="Q5" s="161">
         <v>1</v>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k2104200063\Desktop\RELIC\Assets\ExcelSource\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ydjh1\Desktop\ProjectDustium\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58490897-2F25-4FC2-9454-D67C8909E240}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC3DABA-0798-4510-A819-FDDC0049D5E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -31,16 +31,11 @@
     <sheet name="Tutorial" sheetId="16" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5196" uniqueCount="2554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5196" uniqueCount="2557">
   <si>
     <t>캐릭터ID</t>
   </si>
@@ -13745,6 +13740,18 @@
   </si>
   <si>
     <t>"거점으로 향하는 길목, 한 탐사자가 휴식하고 있다."</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>event_choice_04_success</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>event_choice_04_failure</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>event_choice_03_success</t>
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
 </sst>
@@ -14609,7 +14616,7 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="285">
+  <cellXfs count="284">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -15391,9 +15398,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -15894,23 +15898,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="4" customWidth="1"/>
-    <col min="2" max="2" width="7.25" style="4" customWidth="1"/>
-    <col min="3" max="3" width="11.625" style="4" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="7.19921875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="11.59765625" style="4" customWidth="1"/>
     <col min="4" max="4" width="13" style="4" customWidth="1"/>
-    <col min="5" max="5" width="17.625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="13.75" style="4" customWidth="1"/>
-    <col min="7" max="7" width="13.125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="17.59765625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="13.69921875" style="4" customWidth="1"/>
+    <col min="7" max="7" width="13.09765625" style="4" customWidth="1"/>
     <col min="8" max="8" width="17" style="4" customWidth="1"/>
-    <col min="9" max="9" width="16.25" style="4" customWidth="1"/>
-    <col min="10" max="11" width="12.125" style="4" customWidth="1"/>
-    <col min="12" max="13" width="12.25" style="4" customWidth="1"/>
+    <col min="9" max="9" width="16.19921875" style="4" customWidth="1"/>
+    <col min="10" max="11" width="12.09765625" style="4" customWidth="1"/>
+    <col min="12" max="13" width="12.19921875" style="4" customWidth="1"/>
     <col min="14" max="15" width="14.5" style="4" customWidth="1"/>
-    <col min="16" max="17" width="14.125" style="4" customWidth="1"/>
+    <col min="16" max="17" width="14.09765625" style="4" customWidth="1"/>
     <col min="18" max="22" width="8.5" style="4" customWidth="1"/>
-    <col min="23" max="23" width="44.75" style="4" customWidth="1"/>
+    <col min="23" max="23" width="44.69921875" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="16.5" customHeight="1">
@@ -16537,11 +16541,11 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:AK56"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="1" max="1" width="19.5" style="4" customWidth="1"/>
-    <col min="2" max="2" width="20.25" style="4" customWidth="1"/>
-    <col min="3" max="32" width="9.125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="20.19921875" style="4" customWidth="1"/>
+    <col min="3" max="32" width="9.09765625" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="16.5" customHeight="1">
@@ -19399,7 +19403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:32" ht="16.149999999999999" customHeight="1">
+    <row r="30" spans="1:32" ht="16.2" customHeight="1">
       <c r="A30" s="176" t="s">
         <v>1524</v>
       </c>
@@ -19497,7 +19501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:32" ht="16.149999999999999" customHeight="1" thickBot="1">
+    <row r="31" spans="1:32" ht="16.2" customHeight="1" thickBot="1">
       <c r="A31" s="177" t="s">
         <v>1527</v>
       </c>
@@ -21082,18 +21086,18 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:K47"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="1" max="1" width="9" style="3" customWidth="1"/>
-    <col min="2" max="2" width="21.625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="18.625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="44.25" style="4" customWidth="1"/>
-    <col min="5" max="5" width="79.75" style="4" customWidth="1"/>
-    <col min="6" max="6" width="14.25" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.75" style="4" customWidth="1"/>
-    <col min="8" max="8" width="17.75" style="4" customWidth="1"/>
+    <col min="2" max="2" width="21.59765625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="18.59765625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="44.19921875" style="4" customWidth="1"/>
+    <col min="5" max="5" width="79.69921875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="14.19921875" style="4" customWidth="1"/>
+    <col min="7" max="7" width="14.69921875" style="4" customWidth="1"/>
+    <col min="8" max="8" width="17.69921875" style="4" customWidth="1"/>
     <col min="9" max="9" width="12.5" style="4" customWidth="1"/>
-    <col min="10" max="10" width="95.625" style="4" customWidth="1"/>
+    <col min="10" max="10" width="95.59765625" style="4" customWidth="1"/>
     <col min="11" max="11" width="12.5" style="4" customWidth="1"/>
   </cols>
   <sheetData>
@@ -22751,17 +22755,17 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:P70"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="11.625" style="85" customWidth="1"/>
-    <col min="2" max="2" width="22.75" style="85" customWidth="1"/>
-    <col min="3" max="3" width="67.75" style="85" customWidth="1"/>
-    <col min="4" max="4" width="20.125" style="78" customWidth="1"/>
-    <col min="5" max="5" width="18.625" style="78" customWidth="1"/>
-    <col min="6" max="6" width="111.25" style="85" customWidth="1"/>
-    <col min="7" max="7" width="19.75" style="78" customWidth="1"/>
-    <col min="8" max="8" width="17.75" style="16" customWidth="1"/>
-    <col min="9" max="9" width="17.125" style="16" customWidth="1"/>
+    <col min="1" max="1" width="11.59765625" style="85" customWidth="1"/>
+    <col min="2" max="2" width="22.69921875" style="85" customWidth="1"/>
+    <col min="3" max="3" width="67.69921875" style="85" customWidth="1"/>
+    <col min="4" max="4" width="20.09765625" style="78" customWidth="1"/>
+    <col min="5" max="5" width="18.59765625" style="78" customWidth="1"/>
+    <col min="6" max="6" width="111.19921875" style="85" customWidth="1"/>
+    <col min="7" max="7" width="19.69921875" style="78" customWidth="1"/>
+    <col min="8" max="8" width="17.69921875" style="16" customWidth="1"/>
+    <col min="9" max="9" width="17.09765625" style="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -24828,17 +24832,17 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:L17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="1" max="1" width="15" style="74" customWidth="1"/>
-    <col min="2" max="2" width="18.625" style="14" customWidth="1"/>
-    <col min="3" max="3" width="18.625" style="74" customWidth="1"/>
-    <col min="4" max="4" width="33.625" style="74" customWidth="1"/>
-    <col min="5" max="5" width="10.625" style="74" customWidth="1"/>
-    <col min="6" max="6" width="11.25" style="74" customWidth="1"/>
-    <col min="7" max="7" width="11.75" style="74" customWidth="1"/>
-    <col min="8" max="8" width="10.25" style="74" customWidth="1"/>
-    <col min="9" max="9" width="117.25" style="74" customWidth="1"/>
+    <col min="2" max="2" width="18.59765625" style="14" customWidth="1"/>
+    <col min="3" max="3" width="18.59765625" style="74" customWidth="1"/>
+    <col min="4" max="4" width="33.59765625" style="74" customWidth="1"/>
+    <col min="5" max="5" width="10.59765625" style="74" customWidth="1"/>
+    <col min="6" max="6" width="11.19921875" style="74" customWidth="1"/>
+    <col min="7" max="7" width="11.69921875" style="74" customWidth="1"/>
+    <col min="8" max="8" width="10.19921875" style="74" customWidth="1"/>
+    <col min="9" max="9" width="117.19921875" style="74" customWidth="1"/>
     <col min="10" max="12" width="12" style="74" customWidth="1"/>
   </cols>
   <sheetData>
@@ -25497,11 +25501,11 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:E34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="2" width="9.25" style="4" customWidth="1"/>
+    <col min="1" max="2" width="9.19921875" style="4" customWidth="1"/>
     <col min="3" max="3" width="17.5" style="4" customWidth="1"/>
-    <col min="4" max="4" width="96.25" style="4" customWidth="1"/>
+    <col min="4" max="4" width="96.19921875" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -25718,19 +25722,19 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:L26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="2" width="17.75" style="74" customWidth="1"/>
+    <col min="1" max="2" width="17.69921875" style="74" customWidth="1"/>
     <col min="3" max="3" width="13.5" style="74" customWidth="1"/>
-    <col min="4" max="4" width="11.25" style="74" customWidth="1"/>
-    <col min="5" max="5" width="12.125" style="74" customWidth="1"/>
+    <col min="4" max="4" width="11.19921875" style="74" customWidth="1"/>
+    <col min="5" max="5" width="12.09765625" style="74" customWidth="1"/>
     <col min="6" max="6" width="16.5" style="74" customWidth="1"/>
-    <col min="7" max="7" width="15.25" style="74" customWidth="1"/>
-    <col min="8" max="8" width="35.75" style="74" customWidth="1"/>
-    <col min="9" max="9" width="27.75" style="74" customWidth="1"/>
+    <col min="7" max="7" width="15.19921875" style="74" customWidth="1"/>
+    <col min="8" max="8" width="35.69921875" style="74" customWidth="1"/>
+    <col min="9" max="9" width="27.69921875" style="74" customWidth="1"/>
     <col min="10" max="10" width="16.5" style="74" customWidth="1"/>
-    <col min="11" max="11" width="13.625" style="74" customWidth="1"/>
-    <col min="12" max="12" width="43.625" style="74" customWidth="1"/>
+    <col min="11" max="11" width="13.59765625" style="74" customWidth="1"/>
+    <col min="12" max="12" width="43.59765625" style="74" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -26707,126 +26711,126 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BEBF3C2-6F22-465F-9281-A2A155740600}">
   <dimension ref="A1:P13"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="16.625" customWidth="1"/>
-    <col min="2" max="2" width="11.375" customWidth="1"/>
-    <col min="4" max="4" width="21.75" customWidth="1"/>
-    <col min="5" max="5" width="17.875" customWidth="1"/>
-    <col min="6" max="6" width="21.375" customWidth="1"/>
-    <col min="7" max="7" width="14.875" customWidth="1"/>
+    <col min="1" max="1" width="16.59765625" customWidth="1"/>
+    <col min="2" max="2" width="11.3984375" customWidth="1"/>
+    <col min="4" max="4" width="21.69921875" customWidth="1"/>
+    <col min="5" max="5" width="17.8984375" customWidth="1"/>
+    <col min="6" max="6" width="21.3984375" customWidth="1"/>
+    <col min="7" max="7" width="14.8984375" customWidth="1"/>
     <col min="8" max="8" width="21" customWidth="1"/>
-    <col min="9" max="9" width="16.875" customWidth="1"/>
-    <col min="10" max="10" width="19.875" customWidth="1"/>
-    <col min="11" max="11" width="25.125" customWidth="1"/>
-    <col min="12" max="12" width="78.375" style="141" customWidth="1"/>
-    <col min="13" max="13" width="18.25" customWidth="1"/>
+    <col min="9" max="9" width="16.8984375" customWidth="1"/>
+    <col min="10" max="10" width="19.8984375" customWidth="1"/>
+    <col min="11" max="11" width="25.09765625" customWidth="1"/>
+    <col min="12" max="12" width="78.3984375" style="141" customWidth="1"/>
+    <col min="13" max="13" width="18.19921875" customWidth="1"/>
     <col min="14" max="14" width="19.5" customWidth="1"/>
     <col min="15" max="15" width="27.5" customWidth="1"/>
-    <col min="16" max="16" width="40.625" customWidth="1"/>
+    <col min="16" max="16" width="40.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="263" customFormat="1">
-      <c r="A1" s="264" t="s">
+    <row r="1" spans="1:16">
+      <c r="A1" s="263" t="s">
         <v>2486</v>
       </c>
-      <c r="B1" s="264" t="s">
+      <c r="B1" s="263" t="s">
         <v>2487</v>
       </c>
-      <c r="C1" s="264" t="s">
+      <c r="C1" s="263" t="s">
         <v>1299</v>
       </c>
-      <c r="D1" s="264" t="s">
+      <c r="D1" s="263" t="s">
         <v>2488</v>
       </c>
-      <c r="E1" s="264" t="s">
+      <c r="E1" s="263" t="s">
         <v>2489</v>
       </c>
-      <c r="F1" s="264" t="s">
+      <c r="F1" s="263" t="s">
         <v>2490</v>
       </c>
-      <c r="G1" s="264" t="s">
+      <c r="G1" s="263" t="s">
         <v>2491</v>
       </c>
-      <c r="H1" s="264" t="s">
+      <c r="H1" s="263" t="s">
         <v>1956</v>
       </c>
-      <c r="I1" s="264" t="s">
+      <c r="I1" s="263" t="s">
         <v>2492</v>
       </c>
-      <c r="J1" s="264" t="s">
+      <c r="J1" s="263" t="s">
         <v>2528</v>
       </c>
-      <c r="K1" s="264" t="s">
+      <c r="K1" s="263" t="s">
         <v>2493</v>
       </c>
-      <c r="L1" s="265" t="s">
+      <c r="L1" s="264" t="s">
         <v>2494</v>
       </c>
-      <c r="M1" s="264" t="s">
+      <c r="M1" s="263" t="s">
         <v>2495</v>
       </c>
-      <c r="N1" s="264" t="s">
+      <c r="N1" s="263" t="s">
         <v>2496</v>
       </c>
-      <c r="O1" s="264" t="s">
+      <c r="O1" s="263" t="s">
         <v>2546</v>
       </c>
-      <c r="P1" s="264" t="s">
+      <c r="P1" s="263" t="s">
         <v>2548</v>
       </c>
     </row>
-    <row r="2" spans="1:16" s="263" customFormat="1">
-      <c r="A2" s="264" t="s">
+    <row r="2" spans="1:16">
+      <c r="A2" s="263" t="s">
         <v>2497</v>
       </c>
-      <c r="B2" s="264" t="s">
+      <c r="B2" s="263" t="s">
         <v>2498</v>
       </c>
-      <c r="C2" s="264" t="s">
+      <c r="C2" s="263" t="s">
         <v>1305</v>
       </c>
-      <c r="D2" s="264" t="s">
+      <c r="D2" s="263" t="s">
         <v>2499</v>
       </c>
-      <c r="E2" s="264" t="s">
+      <c r="E2" s="263" t="s">
         <v>2500</v>
       </c>
-      <c r="F2" s="264" t="s">
+      <c r="F2" s="263" t="s">
         <v>2501</v>
       </c>
-      <c r="G2" s="264" t="s">
+      <c r="G2" s="263" t="s">
         <v>2502</v>
       </c>
-      <c r="H2" s="264" t="s">
+      <c r="H2" s="263" t="s">
         <v>147</v>
       </c>
-      <c r="I2" s="264" t="s">
+      <c r="I2" s="263" t="s">
         <v>2503</v>
       </c>
-      <c r="J2" s="264" t="s">
+      <c r="J2" s="263" t="s">
         <v>2529</v>
       </c>
-      <c r="K2" s="264" t="s">
+      <c r="K2" s="263" t="s">
         <v>2504</v>
       </c>
-      <c r="L2" s="265" t="s">
+      <c r="L2" s="264" t="s">
         <v>2505</v>
       </c>
-      <c r="M2" s="264" t="s">
+      <c r="M2" s="263" t="s">
         <v>2506</v>
       </c>
-      <c r="N2" s="264" t="s">
+      <c r="N2" s="263" t="s">
         <v>2507</v>
       </c>
-      <c r="O2" s="264" t="s">
+      <c r="O2" s="263" t="s">
         <v>2547</v>
       </c>
-      <c r="P2" s="264" t="s">
+      <c r="P2" s="263" t="s">
         <v>2549</v>
       </c>
     </row>
-    <row r="3" spans="1:16" s="263" customFormat="1">
+    <row r="3" spans="1:16">
       <c r="A3" s="140" t="s">
         <v>2508</v>
       </c>
@@ -26865,10 +26869,8 @@
         <v>2513</v>
       </c>
       <c r="N3" s="140"/>
-      <c r="O3"/>
-      <c r="P3"/>
-    </row>
-    <row r="4" spans="1:16" s="263" customFormat="1">
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" s="140" t="s">
         <v>2508</v>
       </c>
@@ -26908,7 +26910,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="5" spans="1:16" s="263" customFormat="1">
+    <row r="5" spans="1:16">
       <c r="A5" s="140" t="s">
         <v>2508</v>
       </c>
@@ -26948,7 +26950,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="6" spans="1:16" s="263" customFormat="1">
+    <row r="6" spans="1:16">
       <c r="A6" s="140" t="s">
         <v>2508</v>
       </c>
@@ -26988,7 +26990,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="7" spans="1:16" s="263" customFormat="1">
+    <row r="7" spans="1:16">
       <c r="A7" s="140" t="s">
         <v>2508</v>
       </c>
@@ -27028,7 +27030,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="8" spans="1:16" s="263" customFormat="1" ht="33">
+    <row r="8" spans="1:16" ht="34.799999999999997">
       <c r="A8" s="140" t="s">
         <v>2508</v>
       </c>
@@ -27052,7 +27054,7 @@
       <c r="K8" s="140" t="s">
         <v>2522</v>
       </c>
-      <c r="L8" s="266" t="s">
+      <c r="L8" s="265" t="s">
         <v>2543</v>
       </c>
       <c r="M8" s="140" t="s">
@@ -27068,7 +27070,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="9" spans="1:16" s="263" customFormat="1" ht="33">
+    <row r="9" spans="1:16" ht="34.799999999999997">
       <c r="A9" s="140" t="s">
         <v>2508</v>
       </c>
@@ -27092,7 +27094,7 @@
       <c r="K9" s="140" t="s">
         <v>2523</v>
       </c>
-      <c r="L9" s="266" t="s">
+      <c r="L9" s="265" t="s">
         <v>2544</v>
       </c>
       <c r="M9" s="140" t="s">
@@ -27108,7 +27110,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="10" spans="1:16" s="263" customFormat="1">
+    <row r="10" spans="1:16">
       <c r="A10" s="140" t="s">
         <v>2508</v>
       </c>
@@ -27128,15 +27130,12 @@
       <c r="I10" s="140"/>
       <c r="J10" s="140"/>
       <c r="K10" s="140"/>
-      <c r="L10" s="141"/>
       <c r="M10" s="140" t="s">
         <v>2513</v>
       </c>
       <c r="N10" s="140"/>
-      <c r="O10"/>
-      <c r="P10"/>
-    </row>
-    <row r="11" spans="1:16" s="263" customFormat="1">
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" s="140" t="s">
         <v>2508</v>
       </c>
@@ -27176,7 +27175,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="12" spans="1:16" s="263" customFormat="1">
+    <row r="12" spans="1:16">
       <c r="A12" s="140" t="s">
         <v>2508</v>
       </c>
@@ -27216,7 +27215,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="13" spans="1:16" s="263" customFormat="1">
+    <row r="13" spans="1:16">
       <c r="A13" s="140"/>
       <c r="B13" s="140"/>
       <c r="C13" s="140"/>
@@ -27228,7 +27227,6 @@
       <c r="I13" s="140"/>
       <c r="J13" s="140"/>
       <c r="K13" s="140"/>
-      <c r="L13" s="141"/>
       <c r="M13" s="140"/>
       <c r="N13" s="140"/>
     </row>
@@ -27242,20 +27240,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:U38"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="2" width="10.625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="17.25" style="4" customWidth="1"/>
-    <col min="4" max="4" width="9.625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="7.25" style="4" customWidth="1"/>
-    <col min="6" max="6" width="19.125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="13.625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="18.125" style="4" customWidth="1"/>
-    <col min="9" max="9" width="19.75" style="4" customWidth="1"/>
-    <col min="10" max="10" width="19.125" style="4" customWidth="1"/>
-    <col min="11" max="19" width="15.625" style="4" customWidth="1"/>
+    <col min="1" max="2" width="10.59765625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="17.19921875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="7.19921875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="19.09765625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="13.59765625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="18.09765625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="19.69921875" style="4" customWidth="1"/>
+    <col min="10" max="10" width="19.09765625" style="4" customWidth="1"/>
+    <col min="11" max="19" width="15.59765625" style="4" customWidth="1"/>
     <col min="20" max="20" width="14.5" style="4" customWidth="1"/>
-    <col min="21" max="21" width="16.125" style="4" customWidth="1"/>
+    <col min="21" max="21" width="16.09765625" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21">
@@ -28771,27 +28769,27 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:R73"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="1" max="1" width="15.5" style="19" customWidth="1"/>
     <col min="2" max="2" width="20" style="19" customWidth="1"/>
     <col min="3" max="3" width="11.5" style="19" customWidth="1"/>
-    <col min="4" max="4" width="16.25" style="16" customWidth="1"/>
+    <col min="4" max="4" width="16.19921875" style="16" customWidth="1"/>
     <col min="5" max="5" width="18.5" style="19" customWidth="1"/>
     <col min="6" max="6" width="16.5" style="19" customWidth="1"/>
-    <col min="7" max="8" width="9.625" style="19" customWidth="1"/>
-    <col min="9" max="9" width="15.625" style="19" customWidth="1"/>
-    <col min="10" max="10" width="20.75" style="19" customWidth="1"/>
-    <col min="11" max="11" width="36.75" style="19" customWidth="1"/>
+    <col min="7" max="8" width="9.59765625" style="19" customWidth="1"/>
+    <col min="9" max="9" width="15.59765625" style="19" customWidth="1"/>
+    <col min="10" max="10" width="20.69921875" style="19" customWidth="1"/>
+    <col min="11" max="11" width="36.69921875" style="19" customWidth="1"/>
     <col min="12" max="12" width="11" style="20" customWidth="1"/>
     <col min="13" max="13" width="11.5" style="20" customWidth="1"/>
     <col min="14" max="14" width="22" style="20" customWidth="1"/>
-    <col min="15" max="15" width="18.25" style="20" customWidth="1"/>
-    <col min="16" max="16" width="13.25" style="21" customWidth="1"/>
-    <col min="17" max="17" width="98.75" style="22" customWidth="1"/>
+    <col min="15" max="15" width="18.19921875" style="20" customWidth="1"/>
+    <col min="16" max="16" width="13.19921875" style="21" customWidth="1"/>
+    <col min="17" max="17" width="98.69921875" style="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="1" spans="1:17" ht="19.95" customHeight="1">
       <c r="A1" s="23" t="s">
         <v>247</v>
       </c>
@@ -28844,7 +28842,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="19.899999999999999" customHeight="1" thickBot="1">
+    <row r="2" spans="1:17" ht="19.95" customHeight="1" thickBot="1">
       <c r="A2" s="25" t="s">
         <v>262</v>
       </c>
@@ -28897,7 +28895,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="3" spans="1:17" ht="19.95" customHeight="1">
       <c r="A3" s="27" t="s">
         <v>278</v>
       </c>
@@ -28950,7 +28948,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="4" spans="1:17" ht="19.95" customHeight="1">
       <c r="A4" s="31" t="s">
         <v>49</v>
       </c>
@@ -29003,7 +29001,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="5" spans="1:17" ht="19.95" customHeight="1">
       <c r="A5" s="31" t="s">
         <v>50</v>
       </c>
@@ -29056,7 +29054,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="6" spans="1:17" ht="19.95" customHeight="1">
       <c r="A6" s="31" t="s">
         <v>65</v>
       </c>
@@ -29109,7 +29107,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="7" spans="1:17" ht="19.95" customHeight="1">
       <c r="A7" s="31" t="s">
         <v>66</v>
       </c>
@@ -29162,7 +29160,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="8" spans="1:17" ht="19.95" customHeight="1">
       <c r="A8" s="31" t="s">
         <v>81</v>
       </c>
@@ -29215,7 +29213,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="9" spans="1:17" ht="19.95" customHeight="1">
       <c r="A9" s="31" t="s">
         <v>82</v>
       </c>
@@ -29268,7 +29266,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="10" spans="1:17" ht="19.95" customHeight="1">
       <c r="A10" s="31" t="s">
         <v>97</v>
       </c>
@@ -29321,7 +29319,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="11" spans="1:17" ht="19.95" customHeight="1">
       <c r="A11" s="31" t="s">
         <v>98</v>
       </c>
@@ -29374,7 +29372,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="12" spans="1:17" ht="19.95" customHeight="1">
       <c r="A12" s="31" t="s">
         <v>112</v>
       </c>
@@ -29427,7 +29425,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="19.899999999999999" customHeight="1" thickBot="1">
+    <row r="13" spans="1:17" ht="19.95" customHeight="1" thickBot="1">
       <c r="A13" s="35" t="s">
         <v>113</v>
       </c>
@@ -29480,7 +29478,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="14" spans="1:17" ht="19.95" customHeight="1">
       <c r="A14" s="38" t="s">
         <v>51</v>
       </c>
@@ -29533,7 +29531,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="15" spans="1:17" ht="19.95" customHeight="1">
       <c r="A15" s="31" t="s">
         <v>52</v>
       </c>
@@ -29586,7 +29584,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="16" spans="1:17" ht="19.95" customHeight="1">
       <c r="A16" s="31" t="s">
         <v>67</v>
       </c>
@@ -29639,7 +29637,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="17" spans="1:17" ht="19.95" customHeight="1">
       <c r="A17" s="31" t="s">
         <v>68</v>
       </c>
@@ -29692,7 +29690,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="18" spans="1:17" ht="19.95" customHeight="1">
       <c r="A18" s="31" t="s">
         <v>83</v>
       </c>
@@ -29745,7 +29743,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="19" spans="1:17" ht="19.95" customHeight="1">
       <c r="A19" s="31" t="s">
         <v>84</v>
       </c>
@@ -29798,7 +29796,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="20" spans="1:17" ht="19.95" customHeight="1">
       <c r="A20" s="31" t="s">
         <v>99</v>
       </c>
@@ -29851,7 +29849,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="21" spans="1:17" ht="19.95" customHeight="1">
       <c r="A21" s="31" t="s">
         <v>100</v>
       </c>
@@ -29904,7 +29902,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="22" spans="1:17" ht="19.95" customHeight="1">
       <c r="A22" s="31" t="s">
         <v>114</v>
       </c>
@@ -29957,7 +29955,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="19.899999999999999" customHeight="1" thickBot="1">
+    <row r="23" spans="1:17" ht="19.95" customHeight="1" thickBot="1">
       <c r="A23" s="35" t="s">
         <v>115</v>
       </c>
@@ -30010,7 +30008,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="24" spans="1:17" ht="19.95" customHeight="1">
       <c r="A24" s="38" t="s">
         <v>53</v>
       </c>
@@ -30063,7 +30061,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="1" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="25" spans="1:17" s="1" customFormat="1" ht="19.95" customHeight="1">
       <c r="A25" s="31" t="s">
         <v>54</v>
       </c>
@@ -30116,7 +30114,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="26" spans="1:17" ht="19.95" customHeight="1">
       <c r="A26" s="31" t="s">
         <v>69</v>
       </c>
@@ -30169,7 +30167,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="1" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="27" spans="1:17" s="1" customFormat="1" ht="19.95" customHeight="1">
       <c r="A27" s="31" t="s">
         <v>70</v>
       </c>
@@ -30222,7 +30220,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="28" spans="1:17" ht="19.95" customHeight="1">
       <c r="A28" s="31" t="s">
         <v>85</v>
       </c>
@@ -30275,7 +30273,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="1" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="29" spans="1:17" s="1" customFormat="1" ht="19.95" customHeight="1">
       <c r="A29" s="31" t="s">
         <v>86</v>
       </c>
@@ -30328,7 +30326,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="30" spans="1:17" ht="19.95" customHeight="1">
       <c r="A30" s="31" t="s">
         <v>101</v>
       </c>
@@ -30381,7 +30379,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="1" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="31" spans="1:17" s="1" customFormat="1" ht="19.95" customHeight="1">
       <c r="A31" s="31" t="s">
         <v>102</v>
       </c>
@@ -30434,7 +30432,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="32" spans="1:17" ht="19.95" customHeight="1">
       <c r="A32" s="31" t="s">
         <v>116</v>
       </c>
@@ -30487,7 +30485,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="1" customFormat="1" ht="19.899999999999999" customHeight="1" thickBot="1">
+    <row r="33" spans="1:17" s="1" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A33" s="35" t="s">
         <v>117</v>
       </c>
@@ -30540,7 +30538,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="34" spans="1:17" ht="19.95" customHeight="1">
       <c r="A34" s="43" t="s">
         <v>389</v>
       </c>
@@ -30593,7 +30591,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="1" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="35" spans="1:17" s="1" customFormat="1" ht="19.95" customHeight="1">
       <c r="A35" s="46" t="s">
         <v>394</v>
       </c>
@@ -30646,7 +30644,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="36" spans="1:17" ht="19.95" customHeight="1">
       <c r="A36" s="46" t="s">
         <v>398</v>
       </c>
@@ -30699,7 +30697,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="1" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="37" spans="1:17" s="1" customFormat="1" ht="19.95" customHeight="1">
       <c r="A37" s="46" t="s">
         <v>402</v>
       </c>
@@ -30752,7 +30750,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="38" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="38" spans="1:17" ht="19.95" customHeight="1">
       <c r="A38" s="46" t="s">
         <v>406</v>
       </c>
@@ -30805,7 +30803,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="39" spans="1:17" s="1" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="39" spans="1:17" s="1" customFormat="1" ht="19.95" customHeight="1">
       <c r="A39" s="46" t="s">
         <v>410</v>
       </c>
@@ -30858,7 +30856,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="40" spans="1:17" ht="19.95" customHeight="1">
       <c r="A40" s="46" t="s">
         <v>414</v>
       </c>
@@ -30911,7 +30909,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="41" spans="1:17" s="1" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="41" spans="1:17" s="1" customFormat="1" ht="19.95" customHeight="1">
       <c r="A41" s="46" t="s">
         <v>421</v>
       </c>
@@ -30964,7 +30962,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="42" spans="1:17" ht="19.95" customHeight="1">
       <c r="A42" s="46" t="s">
         <v>426</v>
       </c>
@@ -31017,7 +31015,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="43" spans="1:17" s="1" customFormat="1" ht="19.899999999999999" customHeight="1" thickBot="1">
+    <row r="43" spans="1:17" s="1" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A43" s="50" t="s">
         <v>431</v>
       </c>
@@ -31070,7 +31068,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="44" spans="1:17" s="2" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="44" spans="1:17" s="2" customFormat="1" ht="19.95" customHeight="1">
       <c r="A44" s="53" t="s">
         <v>437</v>
       </c>
@@ -31123,7 +31121,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="45" spans="1:17" s="1" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="45" spans="1:17" s="1" customFormat="1" ht="19.95" customHeight="1">
       <c r="A45" s="57" t="s">
         <v>441</v>
       </c>
@@ -31176,7 +31174,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="46" spans="1:17" s="2" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="46" spans="1:17" s="2" customFormat="1" ht="19.95" customHeight="1">
       <c r="A46" s="57" t="s">
         <v>446</v>
       </c>
@@ -31229,7 +31227,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="47" spans="1:17" s="1" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="47" spans="1:17" s="1" customFormat="1" ht="19.95" customHeight="1">
       <c r="A47" s="57" t="s">
         <v>451</v>
       </c>
@@ -31282,7 +31280,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="48" spans="1:17" s="2" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="48" spans="1:17" s="2" customFormat="1" ht="19.95" customHeight="1">
       <c r="A48" s="57" t="s">
         <v>455</v>
       </c>
@@ -31335,7 +31333,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="1" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="49" spans="1:18" s="1" customFormat="1" ht="19.95" customHeight="1">
       <c r="A49" s="57" t="s">
         <v>459</v>
       </c>
@@ -31388,7 +31386,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="2" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="50" spans="1:18" s="2" customFormat="1" ht="19.95" customHeight="1">
       <c r="A50" s="57" t="s">
         <v>461</v>
       </c>
@@ -31441,7 +31439,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="1" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="51" spans="1:18" s="1" customFormat="1" ht="19.95" customHeight="1">
       <c r="A51" s="57" t="s">
         <v>467</v>
       </c>
@@ -31494,7 +31492,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="2" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="52" spans="1:18" s="2" customFormat="1" ht="19.95" customHeight="1">
       <c r="A52" s="57" t="s">
         <v>471</v>
       </c>
@@ -31547,7 +31545,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="1" customFormat="1" ht="19.899999999999999" customHeight="1" thickBot="1">
+    <row r="53" spans="1:18" s="1" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A53" s="63" t="s">
         <v>476</v>
       </c>
@@ -31600,7 +31598,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="2" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="54" spans="1:18" s="2" customFormat="1" ht="19.95" customHeight="1">
       <c r="A54" s="53" t="s">
         <v>481</v>
       </c>
@@ -31653,7 +31651,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="55" spans="1:18" s="1" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="55" spans="1:18" s="1" customFormat="1" ht="19.95" customHeight="1">
       <c r="A55" s="57" t="s">
         <v>484</v>
       </c>
@@ -31706,7 +31704,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="56" spans="1:18" s="2" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="56" spans="1:18" s="2" customFormat="1" ht="19.95" customHeight="1">
       <c r="A56" s="57" t="s">
         <v>488</v>
       </c>
@@ -31760,7 +31758,7 @@
       </c>
       <c r="R56"/>
     </row>
-    <row r="57" spans="1:18" s="1" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="57" spans="1:18" s="1" customFormat="1" ht="19.95" customHeight="1">
       <c r="A57" s="57" t="s">
         <v>490</v>
       </c>
@@ -31814,7 +31812,7 @@
       </c>
       <c r="R57"/>
     </row>
-    <row r="58" spans="1:18" s="2" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="58" spans="1:18" s="2" customFormat="1" ht="19.95" customHeight="1">
       <c r="A58" s="57" t="s">
         <v>495</v>
       </c>
@@ -31868,7 +31866,7 @@
       </c>
       <c r="R58"/>
     </row>
-    <row r="59" spans="1:18" s="1" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="59" spans="1:18" s="1" customFormat="1" ht="19.95" customHeight="1">
       <c r="A59" s="57" t="s">
         <v>500</v>
       </c>
@@ -31921,7 +31919,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="60" spans="1:18" s="2" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="60" spans="1:18" s="2" customFormat="1" ht="19.95" customHeight="1">
       <c r="A60" s="57" t="s">
         <v>506</v>
       </c>
@@ -31974,7 +31972,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="61" spans="1:18" s="1" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="61" spans="1:18" s="1" customFormat="1" ht="19.95" customHeight="1">
       <c r="A61" s="57" t="s">
         <v>511</v>
       </c>
@@ -32027,7 +32025,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="62" spans="1:18" s="2" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="62" spans="1:18" s="2" customFormat="1" ht="19.95" customHeight="1">
       <c r="A62" s="57" t="s">
         <v>515</v>
       </c>
@@ -32080,7 +32078,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="63" spans="1:18" s="1" customFormat="1" ht="19.899999999999999" customHeight="1" thickBot="1">
+    <row r="63" spans="1:18" s="1" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A63" s="63" t="s">
         <v>518</v>
       </c>
@@ -32133,7 +32131,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="64" spans="1:18" s="2" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="64" spans="1:18" s="2" customFormat="1" ht="19.95" customHeight="1">
       <c r="A64" s="53" t="s">
         <v>523</v>
       </c>
@@ -32186,7 +32184,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="65" spans="1:17" s="1" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="65" spans="1:17" s="1" customFormat="1" ht="19.95" customHeight="1">
       <c r="A65" s="57" t="s">
         <v>530</v>
       </c>
@@ -32239,7 +32237,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="66" spans="1:17" s="2" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="66" spans="1:17" s="2" customFormat="1" ht="19.95" customHeight="1">
       <c r="A66" s="57" t="s">
         <v>534</v>
       </c>
@@ -32292,7 +32290,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="67" spans="1:17" s="1" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="67" spans="1:17" s="1" customFormat="1" ht="19.95" customHeight="1">
       <c r="A67" s="57" t="s">
         <v>539</v>
       </c>
@@ -32345,7 +32343,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="68" spans="1:17" s="2" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="68" spans="1:17" s="2" customFormat="1" ht="19.95" customHeight="1">
       <c r="A68" s="57" t="s">
         <v>543</v>
       </c>
@@ -32398,7 +32396,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="69" spans="1:17" s="1" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="69" spans="1:17" s="1" customFormat="1" ht="19.95" customHeight="1">
       <c r="A69" s="57" t="s">
         <v>548</v>
       </c>
@@ -32451,7 +32449,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="70" spans="1:17" s="2" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="70" spans="1:17" s="2" customFormat="1" ht="19.95" customHeight="1">
       <c r="A70" s="57" t="s">
         <v>553</v>
       </c>
@@ -32504,7 +32502,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="71" spans="1:17" s="1" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="71" spans="1:17" s="1" customFormat="1" ht="19.95" customHeight="1">
       <c r="A71" s="57" t="s">
         <v>557</v>
       </c>
@@ -32557,7 +32555,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="72" spans="1:17" s="2" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="72" spans="1:17" s="2" customFormat="1" ht="19.95" customHeight="1">
       <c r="A72" s="57" t="s">
         <v>562</v>
       </c>
@@ -32610,7 +32608,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="73" spans="1:17" s="1" customFormat="1" ht="19.899999999999999" customHeight="1" thickBot="1">
+    <row r="73" spans="1:17" s="1" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A73" s="63" t="s">
         <v>566</v>
       </c>
@@ -32672,20 +32670,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:N49"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="13.25" style="4" customWidth="1"/>
-    <col min="2" max="2" width="20.125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="13.19921875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="20.09765625" style="4" customWidth="1"/>
     <col min="3" max="3" width="11.5" style="4" customWidth="1"/>
-    <col min="4" max="4" width="17.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.25" style="4" customWidth="1"/>
-    <col min="6" max="7" width="14.25" style="4" customWidth="1"/>
-    <col min="8" max="8" width="11.25" style="4" customWidth="1"/>
-    <col min="9" max="9" width="19.125" style="4" customWidth="1"/>
-    <col min="10" max="10" width="17.75" style="4" customWidth="1"/>
-    <col min="11" max="11" width="87.25" style="4" customWidth="1"/>
-    <col min="12" max="12" width="18.75" style="4" customWidth="1"/>
-    <col min="13" max="13" width="16.75" style="4" customWidth="1"/>
+    <col min="4" max="4" width="17.19921875" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.19921875" style="4" customWidth="1"/>
+    <col min="6" max="7" width="14.19921875" style="4" customWidth="1"/>
+    <col min="8" max="8" width="11.19921875" style="4" customWidth="1"/>
+    <col min="9" max="9" width="19.09765625" style="4" customWidth="1"/>
+    <col min="10" max="10" width="17.69921875" style="4" customWidth="1"/>
+    <col min="11" max="11" width="87.19921875" style="4" customWidth="1"/>
+    <col min="12" max="12" width="18.69921875" style="4" customWidth="1"/>
+    <col min="13" max="13" width="16.69921875" style="4" customWidth="1"/>
     <col min="14" max="14" width="18" style="74" customWidth="1"/>
   </cols>
   <sheetData>
@@ -34482,17 +34480,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:L16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="25.75" style="4" customWidth="1"/>
-    <col min="3" max="3" width="7.625" style="4" customWidth="1"/>
+    <col min="1" max="1" width="25.69921875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="7.59765625" style="4" customWidth="1"/>
     <col min="4" max="4" width="11.5" style="4" customWidth="1"/>
-    <col min="5" max="5" width="15.125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="15.09765625" style="4" customWidth="1"/>
     <col min="8" max="8" width="11.5" style="4" customWidth="1"/>
-    <col min="9" max="9" width="13.125" style="4" customWidth="1"/>
+    <col min="9" max="9" width="13.09765625" style="4" customWidth="1"/>
     <col min="10" max="10" width="13.5" style="4" customWidth="1"/>
-    <col min="11" max="11" width="12.125" style="4" customWidth="1"/>
-    <col min="12" max="12" width="63.75" style="4" customWidth="1"/>
+    <col min="11" max="11" width="12.09765625" style="4" customWidth="1"/>
+    <col min="12" max="12" width="63.69921875" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -34972,14 +34970,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F372"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="49.25" style="87" customWidth="1"/>
-    <col min="2" max="2" width="69.375" style="14" customWidth="1"/>
-    <col min="3" max="3" width="30.25" style="14" customWidth="1"/>
-    <col min="4" max="4" width="17.25" style="14" customWidth="1"/>
+    <col min="1" max="1" width="49.19921875" style="87" customWidth="1"/>
+    <col min="2" max="2" width="69.3984375" style="14" customWidth="1"/>
+    <col min="3" max="3" width="30.19921875" style="14" customWidth="1"/>
+    <col min="4" max="4" width="17.19921875" style="14" customWidth="1"/>
     <col min="5" max="5" width="106" style="87" customWidth="1"/>
-    <col min="6" max="6" width="17.25" style="14" customWidth="1"/>
+    <col min="6" max="6" width="17.19921875" style="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="16.5" customHeight="1">
@@ -39658,15 +39656,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:H30"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="2" max="2" width="16" style="4" customWidth="1"/>
-    <col min="3" max="3" width="10.75" style="4" customWidth="1"/>
-    <col min="4" max="4" width="16.25" style="4" customWidth="1"/>
+    <col min="3" max="3" width="10.69921875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="16.19921875" style="4" customWidth="1"/>
     <col min="5" max="5" width="12" style="4" customWidth="1"/>
-    <col min="6" max="6" width="13.625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="13.59765625" style="4" customWidth="1"/>
     <col min="7" max="7" width="14.5" style="4" customWidth="1"/>
-    <col min="8" max="8" width="17.75" style="74" customWidth="1"/>
+    <col min="8" max="8" width="17.69921875" style="74" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -40458,18 +40456,18 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:AA49"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="16.375" style="4" customWidth="1"/>
-    <col min="2" max="2" width="11.25" style="4" customWidth="1"/>
-    <col min="3" max="6" width="14.625" style="4" customWidth="1"/>
-    <col min="7" max="7" width="28.125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="20.75" style="4" customWidth="1"/>
+    <col min="1" max="1" width="16.3984375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="11.19921875" style="4" customWidth="1"/>
+    <col min="3" max="6" width="14.59765625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="28.09765625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="20.69921875" style="4" customWidth="1"/>
     <col min="9" max="9" width="21.5" style="4" customWidth="1"/>
-    <col min="10" max="10" width="16.75" style="4" customWidth="1"/>
-    <col min="11" max="11" width="16.25" style="4" customWidth="1"/>
-    <col min="12" max="12" width="19.25" style="14" customWidth="1"/>
-    <col min="13" max="13" width="25.125" style="74" customWidth="1"/>
+    <col min="10" max="10" width="16.69921875" style="4" customWidth="1"/>
+    <col min="11" max="11" width="16.19921875" style="4" customWidth="1"/>
+    <col min="12" max="12" width="19.19921875" style="14" customWidth="1"/>
+    <col min="13" max="13" width="25.09765625" style="74" customWidth="1"/>
     <col min="14" max="14" width="20.5" style="74" customWidth="1"/>
     <col min="15" max="15" width="20" style="74" customWidth="1"/>
     <col min="16" max="16" width="23" style="74" customWidth="1"/>
@@ -41267,7 +41265,7 @@
       <c r="R19" s="141"/>
       <c r="S19" s="141"/>
     </row>
-    <row r="20" spans="1:26" ht="17.25" thickBot="1">
+    <row r="20" spans="1:26" ht="18" thickBot="1">
       <c r="A20" s="151" t="s">
         <v>2128</v>
       </c>
@@ -41390,7 +41388,7 @@
       <c r="Y22" s="141"/>
       <c r="Z22" s="141"/>
     </row>
-    <row r="23" spans="1:26" ht="17.25" thickBot="1">
+    <row r="23" spans="1:26" ht="18" thickBot="1">
       <c r="A23" s="151" t="s">
         <v>2129</v>
       </c>
@@ -41488,7 +41486,7 @@
       <c r="Y24" s="141"/>
       <c r="Z24" s="141"/>
     </row>
-    <row r="25" spans="1:26" ht="17.25" thickBot="1">
+    <row r="25" spans="1:26" ht="18" thickBot="1">
       <c r="A25" s="151" t="s">
         <v>2435</v>
       </c>
@@ -41625,7 +41623,7 @@
       <c r="Y27" s="141"/>
       <c r="Z27" s="141"/>
     </row>
-    <row r="28" spans="1:26" ht="17.25" thickBot="1">
+    <row r="28" spans="1:26" ht="18" thickBot="1">
       <c r="A28" s="156" t="s">
         <v>2438</v>
       </c>
@@ -41866,7 +41864,7 @@
       <c r="Y32" s="141"/>
       <c r="Z32" s="141"/>
     </row>
-    <row r="33" spans="1:26" ht="17.25" thickBot="1">
+    <row r="33" spans="1:26" ht="18" thickBot="1">
       <c r="A33" s="156" t="s">
         <v>2441</v>
       </c>
@@ -42194,34 +42192,34 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:AA72"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="54.95" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="54.9" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.5" style="257" customWidth="1"/>
     <col min="2" max="2" width="22.5" style="257" customWidth="1"/>
-    <col min="3" max="3" width="90.25" style="257" customWidth="1"/>
-    <col min="4" max="4" width="13.25" style="247" customWidth="1"/>
-    <col min="5" max="5" width="31.875" style="247" customWidth="1"/>
-    <col min="6" max="6" width="58.625" style="257" customWidth="1"/>
-    <col min="7" max="7" width="58.625" style="258" customWidth="1"/>
-    <col min="8" max="8" width="13.75" style="247" customWidth="1"/>
-    <col min="9" max="9" width="26.625" style="247" customWidth="1"/>
+    <col min="3" max="3" width="90.19921875" style="257" customWidth="1"/>
+    <col min="4" max="4" width="13.19921875" style="247" customWidth="1"/>
+    <col min="5" max="5" width="31.8984375" style="247" customWidth="1"/>
+    <col min="6" max="6" width="58.59765625" style="257" customWidth="1"/>
+    <col min="7" max="7" width="58.59765625" style="258" customWidth="1"/>
+    <col min="8" max="8" width="13.69921875" style="247" customWidth="1"/>
+    <col min="9" max="9" width="26.59765625" style="247" customWidth="1"/>
     <col min="10" max="10" width="15.5" style="247" customWidth="1"/>
-    <col min="11" max="11" width="21.75" style="247" customWidth="1"/>
-    <col min="12" max="12" width="13.125" style="247" customWidth="1"/>
-    <col min="13" max="13" width="20.25" style="247" customWidth="1"/>
-    <col min="14" max="14" width="19.25" style="247" customWidth="1"/>
-    <col min="15" max="15" width="29.125" style="247" customWidth="1"/>
-    <col min="16" max="16" width="37.625" style="247" customWidth="1"/>
-    <col min="17" max="18" width="15.75" style="247" customWidth="1"/>
-    <col min="19" max="23" width="17.75" style="247" customWidth="1"/>
+    <col min="11" max="11" width="21.69921875" style="247" customWidth="1"/>
+    <col min="12" max="12" width="13.09765625" style="247" customWidth="1"/>
+    <col min="13" max="13" width="20.19921875" style="247" customWidth="1"/>
+    <col min="14" max="14" width="19.19921875" style="247" customWidth="1"/>
+    <col min="15" max="15" width="29.09765625" style="247" customWidth="1"/>
+    <col min="16" max="16" width="37.59765625" style="247" customWidth="1"/>
+    <col min="17" max="18" width="15.69921875" style="247" customWidth="1"/>
+    <col min="19" max="23" width="17.69921875" style="247" customWidth="1"/>
     <col min="24" max="24" width="33.5" style="247" customWidth="1"/>
-    <col min="25" max="25" width="43.875" style="247" customWidth="1"/>
-    <col min="26" max="26" width="26.75" style="259" customWidth="1"/>
-    <col min="27" max="27" width="24.75" style="259" customWidth="1"/>
+    <col min="25" max="25" width="43.8984375" style="247" customWidth="1"/>
+    <col min="26" max="26" width="26.69921875" style="259" customWidth="1"/>
+    <col min="27" max="27" width="24.69921875" style="259" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A1" s="267" t="s">
+    <row r="1" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A1" s="266" t="s">
         <v>2167</v>
       </c>
       <c r="B1" s="160" t="s">
@@ -42303,8 +42301,8 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="54.95" customHeight="1" thickBot="1">
-      <c r="A2" s="268" t="s">
+    <row r="2" spans="1:27" ht="54.9" customHeight="1" thickBot="1">
+      <c r="A2" s="267" t="s">
         <v>2166</v>
       </c>
       <c r="B2" s="243" t="s">
@@ -42386,8 +42384,8 @@
         <v>2205</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A3" s="269" t="s">
+    <row r="3" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A3" s="268" t="s">
         <v>2164</v>
       </c>
       <c r="B3" s="241" t="s">
@@ -42449,8 +42447,8 @@
         <v>2248</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A4" s="270" t="s">
+    <row r="4" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A4" s="269" t="s">
         <v>2164</v>
       </c>
       <c r="B4" s="161"/>
@@ -42508,8 +42506,8 @@
         <v>1414</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A5" s="270" t="s">
+    <row r="5" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A5" s="269" t="s">
         <v>2164</v>
       </c>
       <c r="B5" s="161"/>
@@ -42567,8 +42565,8 @@
         <v>1416</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="54.95" customHeight="1" thickBot="1">
-      <c r="A6" s="271" t="s">
+    <row r="6" spans="1:27" ht="54.9" customHeight="1" thickBot="1">
+      <c r="A6" s="270" t="s">
         <v>2219</v>
       </c>
       <c r="B6" s="240"/>
@@ -42604,8 +42602,8 @@
       </c>
       <c r="AA6" s="250"/>
     </row>
-    <row r="7" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A7" s="269" t="s">
+    <row r="7" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A7" s="268" t="s">
         <v>2231</v>
       </c>
       <c r="B7" s="241" t="s">
@@ -42663,8 +42661,8 @@
         <v>1413</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A8" s="270" t="s">
+    <row r="8" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A8" s="269" t="s">
         <v>2231</v>
       </c>
       <c r="B8" s="161"/>
@@ -42714,8 +42712,8 @@
         <v>1415</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A9" s="270" t="s">
+    <row r="9" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A9" s="269" t="s">
         <v>2232</v>
       </c>
       <c r="B9" s="161"/>
@@ -42751,8 +42749,8 @@
       </c>
       <c r="AA9" s="249"/>
     </row>
-    <row r="10" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A10" s="270" t="s">
+    <row r="10" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A10" s="269" t="s">
         <v>2220</v>
       </c>
       <c r="B10" s="161"/>
@@ -42788,8 +42786,8 @@
       </c>
       <c r="AA10" s="249"/>
     </row>
-    <row r="11" spans="1:27" ht="54.95" customHeight="1" thickBot="1">
-      <c r="A11" s="270" t="s">
+    <row r="11" spans="1:27" ht="54.9" customHeight="1" thickBot="1">
+      <c r="A11" s="269" t="s">
         <v>2233</v>
       </c>
       <c r="B11" s="161"/>
@@ -42825,8 +42823,8 @@
       </c>
       <c r="AA11" s="249"/>
     </row>
-    <row r="12" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A12" s="269" t="s">
+    <row r="12" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A12" s="268" t="s">
         <v>2270</v>
       </c>
       <c r="B12" s="241" t="s">
@@ -42886,8 +42884,8 @@
         <v>1413</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A13" s="270" t="s">
+    <row r="13" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A13" s="269" t="s">
         <v>2270</v>
       </c>
       <c r="B13" s="161"/>
@@ -42941,8 +42939,8 @@
         <v>1415</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A14" s="270" t="s">
+    <row r="14" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A14" s="269" t="s">
         <v>2270</v>
       </c>
       <c r="B14" s="161"/>
@@ -42996,8 +42994,8 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A15" s="270" t="s">
+    <row r="15" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A15" s="269" t="s">
         <v>2260</v>
       </c>
       <c r="B15" s="161"/>
@@ -43033,8 +43031,8 @@
       </c>
       <c r="AA15" s="249"/>
     </row>
-    <row r="16" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A16" s="270" t="s">
+    <row r="16" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A16" s="269" t="s">
         <v>2261</v>
       </c>
       <c r="B16" s="161"/>
@@ -43070,8 +43068,8 @@
       </c>
       <c r="AA16" s="249"/>
     </row>
-    <row r="17" spans="1:27" ht="54.95" customHeight="1" thickBot="1">
-      <c r="A17" s="271" t="s">
+    <row r="17" spans="1:27" ht="54.9" customHeight="1" thickBot="1">
+      <c r="A17" s="270" t="s">
         <v>2262</v>
       </c>
       <c r="B17" s="240"/>
@@ -43107,8 +43105,8 @@
       </c>
       <c r="AA17" s="250"/>
     </row>
-    <row r="18" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A18" s="269" t="s">
+    <row r="18" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A18" s="268" t="s">
         <v>2271</v>
       </c>
       <c r="B18" s="253" t="s">
@@ -43180,8 +43178,8 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A19" s="270" t="s">
+    <row r="19" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A19" s="269" t="s">
         <v>1364</v>
       </c>
       <c r="B19" s="244"/>
@@ -43249,8 +43247,8 @@
         <v>1415</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A20" s="270" t="s">
+    <row r="20" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A20" s="269" t="s">
         <v>1364</v>
       </c>
       <c r="B20" s="244"/>
@@ -43300,8 +43298,8 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A21" s="270" t="s">
+    <row r="21" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A21" s="269" t="s">
         <v>2273</v>
       </c>
       <c r="B21" s="244"/>
@@ -43337,8 +43335,8 @@
       </c>
       <c r="AA21" s="249"/>
     </row>
-    <row r="22" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A22" s="270" t="s">
+    <row r="22" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A22" s="269" t="s">
         <v>2274</v>
       </c>
       <c r="B22" s="244"/>
@@ -43374,8 +43372,8 @@
       </c>
       <c r="AA22" s="249"/>
     </row>
-    <row r="23" spans="1:27" ht="54.95" customHeight="1" thickBot="1">
-      <c r="A23" s="271" t="s">
+    <row r="23" spans="1:27" ht="54.9" customHeight="1" thickBot="1">
+      <c r="A23" s="270" t="s">
         <v>2275</v>
       </c>
       <c r="B23" s="245"/>
@@ -43411,8 +43409,8 @@
       </c>
       <c r="AA23" s="250"/>
     </row>
-    <row r="24" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A24" s="269" t="s">
+    <row r="24" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A24" s="268" t="s">
         <v>2295</v>
       </c>
       <c r="B24" s="253" t="s">
@@ -43476,8 +43474,8 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A25" s="270" t="s">
+    <row r="25" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A25" s="269" t="s">
         <v>2295</v>
       </c>
       <c r="B25" s="244"/>
@@ -43537,8 +43535,8 @@
         <v>1415</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A26" s="270" t="s">
+    <row r="26" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A26" s="269" t="s">
         <v>2295</v>
       </c>
       <c r="B26" s="244"/>
@@ -43598,8 +43596,8 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A27" s="270" t="s">
+    <row r="27" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A27" s="269" t="s">
         <v>2300</v>
       </c>
       <c r="B27" s="244"/>
@@ -43635,8 +43633,8 @@
       </c>
       <c r="AA27" s="249"/>
     </row>
-    <row r="28" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A28" s="270" t="s">
+    <row r="28" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A28" s="269" t="s">
         <v>2301</v>
       </c>
       <c r="B28" s="244"/>
@@ -43672,8 +43670,8 @@
       </c>
       <c r="AA28" s="249"/>
     </row>
-    <row r="29" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A29" s="270" t="s">
+    <row r="29" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A29" s="269" t="s">
         <v>2302</v>
       </c>
       <c r="B29" s="244"/>
@@ -43709,8 +43707,8 @@
       </c>
       <c r="AA29" s="249"/>
     </row>
-    <row r="30" spans="1:27" ht="54.95" customHeight="1" thickBot="1">
-      <c r="A30" s="271" t="s">
+    <row r="30" spans="1:27" ht="54.9" customHeight="1" thickBot="1">
+      <c r="A30" s="270" t="s">
         <v>2303</v>
       </c>
       <c r="B30" s="245"/>
@@ -43746,8 +43744,8 @@
       </c>
       <c r="AA30" s="250"/>
     </row>
-    <row r="31" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A31" s="269" t="s">
+    <row r="31" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A31" s="268" t="s">
         <v>2316</v>
       </c>
       <c r="B31" s="253" t="s">
@@ -43815,8 +43813,8 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A32" s="270" t="s">
+    <row r="32" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A32" s="269" t="s">
         <v>2316</v>
       </c>
       <c r="B32" s="244"/>
@@ -43857,17 +43855,17 @@
         <v>1423</v>
       </c>
       <c r="Y32" s="161" t="s">
-        <v>1414</v>
+        <v>2554</v>
       </c>
       <c r="Z32" s="161" t="s">
         <v>1423</v>
       </c>
       <c r="AA32" s="249" t="s">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="33" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A33" s="270" t="s">
+        <v>2555</v>
+      </c>
+    </row>
+    <row r="33" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A33" s="269" t="s">
         <v>2320</v>
       </c>
       <c r="B33" s="244"/>
@@ -43924,17 +43922,17 @@
         <v>1423</v>
       </c>
       <c r="Y33" s="161" t="s">
-        <v>1412</v>
+        <v>2384</v>
       </c>
       <c r="Z33" s="161" t="s">
         <v>1423</v>
       </c>
       <c r="AA33" s="249" t="s">
-        <v>2337</v>
-      </c>
-    </row>
-    <row r="34" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A34" s="270" t="s">
+        <v>2373</v>
+      </c>
+    </row>
+    <row r="34" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A34" s="269" t="s">
         <v>2320</v>
       </c>
       <c r="B34" s="161"/>
@@ -43975,17 +43973,17 @@
         <v>1423</v>
       </c>
       <c r="Y34" s="161" t="s">
-        <v>1414</v>
+        <v>2554</v>
       </c>
       <c r="Z34" s="161" t="s">
         <v>1423</v>
       </c>
       <c r="AA34" s="249" t="s">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="35" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A35" s="270" t="s">
+        <v>2555</v>
+      </c>
+    </row>
+    <row r="35" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A35" s="269" t="s">
         <v>2321</v>
       </c>
       <c r="B35" s="161"/>
@@ -44044,17 +44042,17 @@
         <v>1423</v>
       </c>
       <c r="Y35" s="161" t="s">
-        <v>1412</v>
+        <v>2556</v>
       </c>
       <c r="Z35" s="161" t="s">
         <v>1423</v>
       </c>
       <c r="AA35" s="249" t="s">
-        <v>2337</v>
-      </c>
-    </row>
-    <row r="36" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A36" s="270" t="s">
+        <v>2405</v>
+      </c>
+    </row>
+    <row r="36" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A36" s="269" t="s">
         <v>2321</v>
       </c>
       <c r="B36" s="161"/>
@@ -44095,17 +44093,17 @@
         <v>2336</v>
       </c>
       <c r="Y36" s="161" t="s">
-        <v>1414</v>
+        <v>2554</v>
       </c>
       <c r="Z36" s="161" t="s">
         <v>1423</v>
       </c>
       <c r="AA36" s="249" t="s">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="37" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A37" s="270" t="s">
+        <v>2555</v>
+      </c>
+    </row>
+    <row r="37" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A37" s="269" t="s">
         <v>2324</v>
       </c>
       <c r="B37" s="161"/>
@@ -44141,8 +44139,8 @@
       </c>
       <c r="AA37" s="249"/>
     </row>
-    <row r="38" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A38" s="270" t="s">
+    <row r="38" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A38" s="269" t="s">
         <v>2326</v>
       </c>
       <c r="B38" s="161"/>
@@ -44178,8 +44176,8 @@
       </c>
       <c r="AA38" s="249"/>
     </row>
-    <row r="39" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A39" s="270" t="s">
+    <row r="39" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A39" s="269" t="s">
         <v>2327</v>
       </c>
       <c r="B39" s="161"/>
@@ -44215,8 +44213,8 @@
       </c>
       <c r="AA39" s="249"/>
     </row>
-    <row r="40" spans="1:27" ht="54.95" customHeight="1" thickBot="1">
-      <c r="A40" s="272" t="s">
+    <row r="40" spans="1:27" ht="54.9" customHeight="1" thickBot="1">
+      <c r="A40" s="271" t="s">
         <v>2328</v>
       </c>
       <c r="B40" s="246"/>
@@ -44252,8 +44250,8 @@
       </c>
       <c r="AA40" s="251"/>
     </row>
-    <row r="41" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A41" s="269" t="s">
+    <row r="41" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A41" s="268" t="s">
         <v>2347</v>
       </c>
       <c r="B41" s="241" t="s">
@@ -44315,8 +44313,8 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="42" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A42" s="270" t="s">
+    <row r="42" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A42" s="269" t="s">
         <v>2347</v>
       </c>
       <c r="B42" s="161"/>
@@ -44362,8 +44360,8 @@
       </c>
       <c r="AA42" s="249"/>
     </row>
-    <row r="43" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A43" s="270" t="s">
+    <row r="43" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A43" s="269" t="s">
         <v>2349</v>
       </c>
       <c r="B43" s="244"/>
@@ -44423,8 +44421,8 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A44" s="270" t="s">
+    <row r="44" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A44" s="269" t="s">
         <v>2349</v>
       </c>
       <c r="B44" s="244"/>
@@ -44470,8 +44468,8 @@
       </c>
       <c r="AA44" s="249"/>
     </row>
-    <row r="45" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A45" s="270" t="s">
+    <row r="45" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A45" s="269" t="s">
         <v>2350</v>
       </c>
       <c r="B45" s="244"/>
@@ -44531,8 +44529,8 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A46" s="270" t="s">
+    <row r="46" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A46" s="269" t="s">
         <v>2350</v>
       </c>
       <c r="B46" s="244"/>
@@ -44578,8 +44576,8 @@
       </c>
       <c r="AA46" s="249"/>
     </row>
-    <row r="47" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A47" s="270" t="s">
+    <row r="47" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A47" s="269" t="s">
         <v>2354</v>
       </c>
       <c r="B47" s="244"/>
@@ -44588,7 +44586,7 @@
       </c>
       <c r="D47" s="244"/>
       <c r="E47" s="244"/>
-      <c r="F47" s="273"/>
+      <c r="F47" s="272"/>
       <c r="G47" s="244"/>
       <c r="H47" s="244"/>
       <c r="I47" s="244"/>
@@ -44615,8 +44613,8 @@
       </c>
       <c r="AA47" s="252"/>
     </row>
-    <row r="48" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A48" s="270" t="s">
+    <row r="48" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A48" s="269" t="s">
         <v>2355</v>
       </c>
       <c r="B48" s="244"/>
@@ -44625,7 +44623,7 @@
       </c>
       <c r="D48" s="244"/>
       <c r="E48" s="244"/>
-      <c r="F48" s="274"/>
+      <c r="F48" s="273"/>
       <c r="G48" s="244"/>
       <c r="H48" s="161"/>
       <c r="I48" s="244"/>
@@ -44652,8 +44650,8 @@
       </c>
       <c r="AA48" s="249"/>
     </row>
-    <row r="49" spans="1:27" ht="54.95" customHeight="1" thickBot="1">
-      <c r="A49" s="275" t="s">
+    <row r="49" spans="1:27" ht="54.9" customHeight="1" thickBot="1">
+      <c r="A49" s="274" t="s">
         <v>2449</v>
       </c>
       <c r="B49" s="260"/>
@@ -44662,7 +44660,7 @@
       </c>
       <c r="D49" s="260"/>
       <c r="E49" s="260"/>
-      <c r="F49" s="276"/>
+      <c r="F49" s="275"/>
       <c r="G49" s="260"/>
       <c r="H49" s="261"/>
       <c r="I49" s="260"/>
@@ -44689,8 +44687,8 @@
       </c>
       <c r="AA49" s="262"/>
     </row>
-    <row r="50" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A50" s="277" t="s">
+    <row r="50" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A50" s="276" t="s">
         <v>2364</v>
       </c>
       <c r="B50" s="253" t="s">
@@ -44742,8 +44740,8 @@
       </c>
       <c r="AA50" s="254"/>
     </row>
-    <row r="51" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A51" s="278" t="s">
+    <row r="51" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A51" s="277" t="s">
         <v>2363</v>
       </c>
       <c r="B51" s="244"/>
@@ -44791,8 +44789,8 @@
       </c>
       <c r="AA51" s="252"/>
     </row>
-    <row r="52" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A52" s="278" t="s">
+    <row r="52" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A52" s="277" t="s">
         <v>2364</v>
       </c>
       <c r="B52" s="244"/>
@@ -44840,8 +44838,8 @@
       </c>
       <c r="AA52" s="252"/>
     </row>
-    <row r="53" spans="1:27" s="3" customFormat="1" ht="54.95" customHeight="1">
-      <c r="A53" s="278" t="s">
+    <row r="53" spans="1:27" s="3" customFormat="1" ht="54.9" customHeight="1">
+      <c r="A53" s="277" t="s">
         <v>2366</v>
       </c>
       <c r="B53" s="244"/>
@@ -44897,8 +44895,8 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="54" spans="1:27" s="3" customFormat="1" ht="54.95" customHeight="1">
-      <c r="A54" s="278" t="s">
+    <row r="54" spans="1:27" s="3" customFormat="1" ht="54.9" customHeight="1">
+      <c r="A54" s="277" t="s">
         <v>2366</v>
       </c>
       <c r="B54" s="244"/>
@@ -44909,7 +44907,7 @@
       <c r="E54" s="244" t="s">
         <v>2368</v>
       </c>
-      <c r="F54" s="274" t="s">
+      <c r="F54" s="273" t="s">
         <v>2470</v>
       </c>
       <c r="G54" s="244" t="s">
@@ -44966,8 +44964,8 @@
         <v>2373</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A55" s="278" t="s">
+    <row r="55" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A55" s="277" t="s">
         <v>2366</v>
       </c>
       <c r="B55" s="244"/>
@@ -44978,7 +44976,7 @@
       <c r="E55" s="244" t="s">
         <v>2369</v>
       </c>
-      <c r="F55" s="274" t="s">
+      <c r="F55" s="273" t="s">
         <v>2471</v>
       </c>
       <c r="G55" s="244" t="s">
@@ -45035,8 +45033,8 @@
         <v>2405</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="54.95" customHeight="1" thickBot="1">
-      <c r="A56" s="279" t="s">
+    <row r="56" spans="1:27" ht="54.9" customHeight="1" thickBot="1">
+      <c r="A56" s="278" t="s">
         <v>2374</v>
       </c>
       <c r="B56" s="245"/>
@@ -45072,8 +45070,8 @@
       </c>
       <c r="AA56" s="255"/>
     </row>
-    <row r="57" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A57" s="280" t="s">
+    <row r="57" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A57" s="279" t="s">
         <v>2388</v>
       </c>
       <c r="B57" s="253" t="s">
@@ -45131,8 +45129,8 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A58" s="281" t="s">
+    <row r="58" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A58" s="280" t="s">
         <v>1375</v>
       </c>
       <c r="B58" s="244"/>
@@ -45186,8 +45184,8 @@
         <v>2373</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A59" s="281" t="s">
+    <row r="59" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A59" s="280" t="s">
         <v>1375</v>
       </c>
       <c r="B59" s="244"/>
@@ -45241,8 +45239,8 @@
         <v>2405</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A60" s="281" t="s">
+    <row r="60" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A60" s="280" t="s">
         <v>2389</v>
       </c>
       <c r="B60" s="244"/>
@@ -45278,8 +45276,8 @@
       </c>
       <c r="AA60" s="252"/>
     </row>
-    <row r="61" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A61" s="281" t="s">
+    <row r="61" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A61" s="280" t="s">
         <v>2390</v>
       </c>
       <c r="B61" s="244"/>
@@ -45315,8 +45313,8 @@
       </c>
       <c r="AA61" s="252"/>
     </row>
-    <row r="62" spans="1:27" ht="54.95" customHeight="1" thickBot="1">
-      <c r="A62" s="282" t="s">
+    <row r="62" spans="1:27" ht="54.9" customHeight="1" thickBot="1">
+      <c r="A62" s="281" t="s">
         <v>2391</v>
       </c>
       <c r="B62" s="245"/>
@@ -45352,8 +45350,8 @@
       </c>
       <c r="AA62" s="255"/>
     </row>
-    <row r="63" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A63" s="277" t="s">
+    <row r="63" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A63" s="276" t="s">
         <v>2407</v>
       </c>
       <c r="B63" s="253" t="s">
@@ -45368,7 +45366,7 @@
       <c r="E63" s="253" t="s">
         <v>2413</v>
       </c>
-      <c r="F63" s="283" t="s">
+      <c r="F63" s="282" t="s">
         <v>2472</v>
       </c>
       <c r="G63" s="253" t="s">
@@ -45423,8 +45421,8 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A64" s="281" t="s">
+    <row r="64" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A64" s="280" t="s">
         <v>2407</v>
       </c>
       <c r="B64" s="244"/>
@@ -45435,7 +45433,7 @@
       <c r="E64" s="244" t="s">
         <v>2414</v>
       </c>
-      <c r="F64" s="274" t="s">
+      <c r="F64" s="273" t="s">
         <v>2473</v>
       </c>
       <c r="G64" s="244"/>
@@ -45484,8 +45482,8 @@
         <v>2373</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A65" s="281" t="s">
+    <row r="65" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A65" s="280" t="s">
         <v>2407</v>
       </c>
       <c r="B65" s="244"/>
@@ -45496,7 +45494,7 @@
       <c r="E65" s="244" t="s">
         <v>2415</v>
       </c>
-      <c r="F65" s="274" t="s">
+      <c r="F65" s="273" t="s">
         <v>2474</v>
       </c>
       <c r="G65" s="244"/>
@@ -45547,8 +45545,8 @@
         <v>2405</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A66" s="281" t="s">
+    <row r="66" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A66" s="280" t="s">
         <v>2409</v>
       </c>
       <c r="B66" s="244"/>
@@ -45584,8 +45582,8 @@
       </c>
       <c r="AA66" s="252"/>
     </row>
-    <row r="67" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A67" s="281" t="s">
+    <row r="67" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A67" s="280" t="s">
         <v>2410</v>
       </c>
       <c r="B67" s="244"/>
@@ -45621,8 +45619,8 @@
       </c>
       <c r="AA67" s="252"/>
     </row>
-    <row r="68" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A68" s="281" t="s">
+    <row r="68" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A68" s="280" t="s">
         <v>2411</v>
       </c>
       <c r="B68" s="244"/>
@@ -45658,8 +45656,8 @@
       </c>
       <c r="AA68" s="252"/>
     </row>
-    <row r="69" spans="1:27" ht="54.95" customHeight="1" thickBot="1">
-      <c r="A69" s="282" t="s">
+    <row r="69" spans="1:27" ht="54.9" customHeight="1" thickBot="1">
+      <c r="A69" s="281" t="s">
         <v>2412</v>
       </c>
       <c r="B69" s="245"/>
@@ -45695,7 +45693,7 @@
       </c>
       <c r="AA69" s="255"/>
     </row>
-    <row r="70" spans="1:27" ht="54.95" customHeight="1">
+    <row r="70" spans="1:27" ht="54.9" customHeight="1">
       <c r="A70" s="256" t="s">
         <v>2442</v>
       </c>
@@ -45711,7 +45709,7 @@
       <c r="E70" s="256" t="s">
         <v>2540</v>
       </c>
-      <c r="F70" s="284" t="s">
+      <c r="F70" s="283" t="s">
         <v>2541</v>
       </c>
       <c r="G70" s="256"/>
@@ -45754,7 +45752,7 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="54.95" customHeight="1">
+    <row r="71" spans="1:27" ht="54.9" customHeight="1">
       <c r="A71" s="256" t="s">
         <v>2542</v>
       </c>
@@ -45791,7 +45789,7 @@
       </c>
       <c r="AA71" s="244"/>
     </row>
-    <row r="72" spans="1:27" ht="54.95" customHeight="1">
+    <row r="72" spans="1:27" ht="54.9" customHeight="1">
       <c r="A72" s="244"/>
       <c r="B72" s="244"/>
       <c r="C72" s="244"/>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erang\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD468700-BB88-41A0-B5B2-5D50DC59AB53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{802B94A5-B772-4EA9-91E0-F7A10E12BECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5196" uniqueCount="2555">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5870" uniqueCount="2558">
   <si>
     <t>캐릭터ID</t>
   </si>
@@ -13749,6 +13749,18 @@
   </si>
   <si>
     <t>Common:47,Rare:38,Epic:12,Unique:3</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>event_choice_04_success</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>event_choice_03_success</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>event_choice_04_failure</t>
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
 </sst>
@@ -43861,13 +43873,13 @@
         <v>1423</v>
       </c>
       <c r="Y32" s="161" t="s">
-        <v>1414</v>
+        <v>2555</v>
       </c>
       <c r="Z32" s="161" t="s">
         <v>1423</v>
       </c>
       <c r="AA32" s="249" t="s">
-        <v>1415</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="33" spans="1:27" ht="54.95" customHeight="1">
@@ -43928,13 +43940,13 @@
         <v>1423</v>
       </c>
       <c r="Y33" s="161" t="s">
-        <v>1412</v>
+        <v>2384</v>
       </c>
       <c r="Z33" s="161" t="s">
         <v>1423</v>
       </c>
       <c r="AA33" s="249" t="s">
-        <v>2337</v>
+        <v>2373</v>
       </c>
     </row>
     <row r="34" spans="1:27" ht="54.95" customHeight="1">
@@ -43979,13 +43991,13 @@
         <v>1423</v>
       </c>
       <c r="Y34" s="161" t="s">
-        <v>1414</v>
+        <v>2555</v>
       </c>
       <c r="Z34" s="161" t="s">
         <v>1423</v>
       </c>
       <c r="AA34" s="249" t="s">
-        <v>1415</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="35" spans="1:27" ht="54.95" customHeight="1">
@@ -44048,13 +44060,13 @@
         <v>1423</v>
       </c>
       <c r="Y35" s="161" t="s">
-        <v>1412</v>
+        <v>2556</v>
       </c>
       <c r="Z35" s="161" t="s">
         <v>1423</v>
       </c>
       <c r="AA35" s="249" t="s">
-        <v>2337</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="36" spans="1:27" ht="54.95" customHeight="1">
@@ -44099,13 +44111,13 @@
         <v>2336</v>
       </c>
       <c r="Y36" s="161" t="s">
-        <v>1414</v>
+        <v>2555</v>
       </c>
       <c r="Z36" s="161" t="s">
         <v>1423</v>
       </c>
       <c r="AA36" s="249" t="s">
-        <v>1415</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="37" spans="1:27" ht="54.95" customHeight="1">

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erang\Desktop\RELIC\Assets\ExcelSource\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ydjh1\Desktop\ProjectDustium\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{802B94A5-B772-4EA9-91E0-F7A10E12BECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0541D42C-4A8F-495D-8DF6-5F34B32F40C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -31,16 +31,11 @@
     <sheet name="Tutorial" sheetId="16" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5870" uniqueCount="2558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5196" uniqueCount="2558">
   <si>
     <t>캐릭터ID</t>
   </si>
@@ -14625,7 +14620,7 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="285">
+  <cellXfs count="284">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -15407,9 +15402,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -15910,23 +15902,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="4" customWidth="1"/>
-    <col min="2" max="2" width="7.25" style="4" customWidth="1"/>
-    <col min="3" max="3" width="11.625" style="4" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="7.19921875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="11.59765625" style="4" customWidth="1"/>
     <col min="4" max="4" width="13" style="4" customWidth="1"/>
-    <col min="5" max="5" width="17.625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="13.75" style="4" customWidth="1"/>
-    <col min="7" max="7" width="13.125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="17.59765625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="13.69921875" style="4" customWidth="1"/>
+    <col min="7" max="7" width="13.09765625" style="4" customWidth="1"/>
     <col min="8" max="8" width="17" style="4" customWidth="1"/>
-    <col min="9" max="9" width="16.25" style="4" customWidth="1"/>
-    <col min="10" max="11" width="12.125" style="4" customWidth="1"/>
-    <col min="12" max="13" width="12.25" style="4" customWidth="1"/>
+    <col min="9" max="9" width="16.19921875" style="4" customWidth="1"/>
+    <col min="10" max="11" width="12.09765625" style="4" customWidth="1"/>
+    <col min="12" max="13" width="12.19921875" style="4" customWidth="1"/>
     <col min="14" max="15" width="14.5" style="4" customWidth="1"/>
-    <col min="16" max="17" width="14.125" style="4" customWidth="1"/>
+    <col min="16" max="17" width="14.09765625" style="4" customWidth="1"/>
     <col min="18" max="22" width="8.5" style="4" customWidth="1"/>
-    <col min="23" max="23" width="44.75" style="4" customWidth="1"/>
+    <col min="23" max="23" width="44.69921875" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="16.5" customHeight="1">
@@ -16553,11 +16545,11 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:AK56"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="1" max="1" width="19.5" style="4" customWidth="1"/>
-    <col min="2" max="2" width="20.25" style="4" customWidth="1"/>
-    <col min="3" max="32" width="9.125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="20.19921875" style="4" customWidth="1"/>
+    <col min="3" max="32" width="9.09765625" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="16.5" customHeight="1">
@@ -19415,7 +19407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:32" ht="16.149999999999999" customHeight="1">
+    <row r="30" spans="1:32" ht="16.2" customHeight="1">
       <c r="A30" s="176" t="s">
         <v>1524</v>
       </c>
@@ -19513,7 +19505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:32" ht="16.149999999999999" customHeight="1" thickBot="1">
+    <row r="31" spans="1:32" ht="16.2" customHeight="1" thickBot="1">
       <c r="A31" s="177" t="s">
         <v>1527</v>
       </c>
@@ -21098,18 +21090,18 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:K47"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="1" max="1" width="9" style="3" customWidth="1"/>
-    <col min="2" max="2" width="21.625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="18.625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="44.25" style="4" customWidth="1"/>
-    <col min="5" max="5" width="79.75" style="4" customWidth="1"/>
-    <col min="6" max="6" width="14.25" style="4" customWidth="1"/>
-    <col min="7" max="7" width="14.75" style="4" customWidth="1"/>
-    <col min="8" max="8" width="17.75" style="4" customWidth="1"/>
+    <col min="2" max="2" width="21.59765625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="18.59765625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="44.19921875" style="4" customWidth="1"/>
+    <col min="5" max="5" width="79.69921875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="14.19921875" style="4" customWidth="1"/>
+    <col min="7" max="7" width="14.69921875" style="4" customWidth="1"/>
+    <col min="8" max="8" width="17.69921875" style="4" customWidth="1"/>
     <col min="9" max="9" width="12.5" style="4" customWidth="1"/>
-    <col min="10" max="10" width="95.625" style="4" customWidth="1"/>
+    <col min="10" max="10" width="95.59765625" style="4" customWidth="1"/>
     <col min="11" max="11" width="12.5" style="4" customWidth="1"/>
   </cols>
   <sheetData>
@@ -22767,17 +22759,17 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:P70"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="11.625" style="85" customWidth="1"/>
-    <col min="2" max="2" width="22.75" style="85" customWidth="1"/>
-    <col min="3" max="3" width="67.75" style="85" customWidth="1"/>
-    <col min="4" max="4" width="20.125" style="78" customWidth="1"/>
-    <col min="5" max="5" width="18.625" style="78" customWidth="1"/>
-    <col min="6" max="6" width="111.25" style="85" customWidth="1"/>
-    <col min="7" max="7" width="19.75" style="78" customWidth="1"/>
-    <col min="8" max="8" width="17.75" style="16" customWidth="1"/>
-    <col min="9" max="9" width="17.125" style="16" customWidth="1"/>
+    <col min="1" max="1" width="11.59765625" style="85" customWidth="1"/>
+    <col min="2" max="2" width="22.69921875" style="85" customWidth="1"/>
+    <col min="3" max="3" width="67.69921875" style="85" customWidth="1"/>
+    <col min="4" max="4" width="20.09765625" style="78" customWidth="1"/>
+    <col min="5" max="5" width="18.59765625" style="78" customWidth="1"/>
+    <col min="6" max="6" width="111.19921875" style="85" customWidth="1"/>
+    <col min="7" max="7" width="19.69921875" style="78" customWidth="1"/>
+    <col min="8" max="8" width="17.69921875" style="16" customWidth="1"/>
+    <col min="9" max="9" width="17.09765625" style="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -24844,17 +24836,17 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:L17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="1" max="1" width="15" style="74" customWidth="1"/>
-    <col min="2" max="2" width="18.625" style="14" customWidth="1"/>
-    <col min="3" max="3" width="18.625" style="74" customWidth="1"/>
-    <col min="4" max="4" width="33.625" style="74" customWidth="1"/>
-    <col min="5" max="5" width="10.625" style="74" customWidth="1"/>
-    <col min="6" max="6" width="11.25" style="74" customWidth="1"/>
-    <col min="7" max="7" width="11.75" style="74" customWidth="1"/>
-    <col min="8" max="8" width="10.25" style="74" customWidth="1"/>
-    <col min="9" max="9" width="117.25" style="74" customWidth="1"/>
+    <col min="2" max="2" width="18.59765625" style="14" customWidth="1"/>
+    <col min="3" max="3" width="18.59765625" style="74" customWidth="1"/>
+    <col min="4" max="4" width="33.59765625" style="74" customWidth="1"/>
+    <col min="5" max="5" width="10.59765625" style="74" customWidth="1"/>
+    <col min="6" max="6" width="11.19921875" style="74" customWidth="1"/>
+    <col min="7" max="7" width="11.69921875" style="74" customWidth="1"/>
+    <col min="8" max="8" width="10.19921875" style="74" customWidth="1"/>
+    <col min="9" max="9" width="117.19921875" style="74" customWidth="1"/>
     <col min="10" max="12" width="12" style="74" customWidth="1"/>
   </cols>
   <sheetData>
@@ -25513,11 +25505,11 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:E34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="2" width="9.25" style="4" customWidth="1"/>
+    <col min="1" max="2" width="9.19921875" style="4" customWidth="1"/>
     <col min="3" max="3" width="17.5" style="4" customWidth="1"/>
-    <col min="4" max="4" width="96.25" style="4" customWidth="1"/>
+    <col min="4" max="4" width="96.19921875" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -25734,19 +25726,19 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:L26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="2" width="17.75" style="74" customWidth="1"/>
+    <col min="1" max="2" width="17.69921875" style="74" customWidth="1"/>
     <col min="3" max="3" width="13.5" style="74" customWidth="1"/>
-    <col min="4" max="4" width="11.25" style="74" customWidth="1"/>
-    <col min="5" max="5" width="12.125" style="74" customWidth="1"/>
+    <col min="4" max="4" width="11.19921875" style="74" customWidth="1"/>
+    <col min="5" max="5" width="12.09765625" style="74" customWidth="1"/>
     <col min="6" max="6" width="16.5" style="74" customWidth="1"/>
-    <col min="7" max="7" width="15.25" style="74" customWidth="1"/>
-    <col min="8" max="8" width="35.75" style="74" customWidth="1"/>
-    <col min="9" max="9" width="27.75" style="74" customWidth="1"/>
+    <col min="7" max="7" width="15.19921875" style="74" customWidth="1"/>
+    <col min="8" max="8" width="35.69921875" style="74" customWidth="1"/>
+    <col min="9" max="9" width="27.69921875" style="74" customWidth="1"/>
     <col min="10" max="10" width="16.5" style="74" customWidth="1"/>
-    <col min="11" max="11" width="13.625" style="74" customWidth="1"/>
-    <col min="12" max="12" width="43.625" style="74" customWidth="1"/>
+    <col min="11" max="11" width="13.59765625" style="74" customWidth="1"/>
+    <col min="12" max="12" width="43.59765625" style="74" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -26723,126 +26715,126 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BEBF3C2-6F22-465F-9281-A2A155740600}">
   <dimension ref="A1:P13"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="16.625" customWidth="1"/>
-    <col min="2" max="2" width="11.375" customWidth="1"/>
-    <col min="4" max="4" width="21.75" customWidth="1"/>
-    <col min="5" max="5" width="17.875" customWidth="1"/>
-    <col min="6" max="6" width="21.375" customWidth="1"/>
-    <col min="7" max="7" width="14.875" customWidth="1"/>
+    <col min="1" max="1" width="16.59765625" customWidth="1"/>
+    <col min="2" max="2" width="11.3984375" customWidth="1"/>
+    <col min="4" max="4" width="21.69921875" customWidth="1"/>
+    <col min="5" max="5" width="17.8984375" customWidth="1"/>
+    <col min="6" max="6" width="21.3984375" customWidth="1"/>
+    <col min="7" max="7" width="14.8984375" customWidth="1"/>
     <col min="8" max="8" width="21" customWidth="1"/>
-    <col min="9" max="9" width="16.875" customWidth="1"/>
-    <col min="10" max="10" width="19.875" customWidth="1"/>
-    <col min="11" max="11" width="25.125" customWidth="1"/>
-    <col min="12" max="12" width="78.375" style="141" customWidth="1"/>
-    <col min="13" max="13" width="18.25" customWidth="1"/>
+    <col min="9" max="9" width="16.8984375" customWidth="1"/>
+    <col min="10" max="10" width="19.8984375" customWidth="1"/>
+    <col min="11" max="11" width="25.09765625" customWidth="1"/>
+    <col min="12" max="12" width="78.3984375" style="141" customWidth="1"/>
+    <col min="13" max="13" width="18.19921875" customWidth="1"/>
     <col min="14" max="14" width="19.5" customWidth="1"/>
     <col min="15" max="15" width="27.5" customWidth="1"/>
-    <col min="16" max="16" width="40.625" customWidth="1"/>
+    <col min="16" max="16" width="40.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="263" customFormat="1">
-      <c r="A1" s="264" t="s">
+    <row r="1" spans="1:16">
+      <c r="A1" s="263" t="s">
         <v>2486</v>
       </c>
-      <c r="B1" s="264" t="s">
+      <c r="B1" s="263" t="s">
         <v>2487</v>
       </c>
-      <c r="C1" s="264" t="s">
+      <c r="C1" s="263" t="s">
         <v>1299</v>
       </c>
-      <c r="D1" s="264" t="s">
+      <c r="D1" s="263" t="s">
         <v>2488</v>
       </c>
-      <c r="E1" s="264" t="s">
+      <c r="E1" s="263" t="s">
         <v>2489</v>
       </c>
-      <c r="F1" s="264" t="s">
+      <c r="F1" s="263" t="s">
         <v>2490</v>
       </c>
-      <c r="G1" s="264" t="s">
+      <c r="G1" s="263" t="s">
         <v>2491</v>
       </c>
-      <c r="H1" s="264" t="s">
+      <c r="H1" s="263" t="s">
         <v>1956</v>
       </c>
-      <c r="I1" s="264" t="s">
+      <c r="I1" s="263" t="s">
         <v>2492</v>
       </c>
-      <c r="J1" s="264" t="s">
+      <c r="J1" s="263" t="s">
         <v>2528</v>
       </c>
-      <c r="K1" s="264" t="s">
+      <c r="K1" s="263" t="s">
         <v>2493</v>
       </c>
-      <c r="L1" s="265" t="s">
+      <c r="L1" s="264" t="s">
         <v>2494</v>
       </c>
-      <c r="M1" s="264" t="s">
+      <c r="M1" s="263" t="s">
         <v>2495</v>
       </c>
-      <c r="N1" s="264" t="s">
+      <c r="N1" s="263" t="s">
         <v>2496</v>
       </c>
-      <c r="O1" s="264" t="s">
+      <c r="O1" s="263" t="s">
         <v>2546</v>
       </c>
-      <c r="P1" s="264" t="s">
+      <c r="P1" s="263" t="s">
         <v>2548</v>
       </c>
     </row>
-    <row r="2" spans="1:16" s="263" customFormat="1">
-      <c r="A2" s="264" t="s">
+    <row r="2" spans="1:16">
+      <c r="A2" s="263" t="s">
         <v>2497</v>
       </c>
-      <c r="B2" s="264" t="s">
+      <c r="B2" s="263" t="s">
         <v>2498</v>
       </c>
-      <c r="C2" s="264" t="s">
+      <c r="C2" s="263" t="s">
         <v>1305</v>
       </c>
-      <c r="D2" s="264" t="s">
+      <c r="D2" s="263" t="s">
         <v>2499</v>
       </c>
-      <c r="E2" s="264" t="s">
+      <c r="E2" s="263" t="s">
         <v>2500</v>
       </c>
-      <c r="F2" s="264" t="s">
+      <c r="F2" s="263" t="s">
         <v>2501</v>
       </c>
-      <c r="G2" s="264" t="s">
+      <c r="G2" s="263" t="s">
         <v>2502</v>
       </c>
-      <c r="H2" s="264" t="s">
+      <c r="H2" s="263" t="s">
         <v>147</v>
       </c>
-      <c r="I2" s="264" t="s">
+      <c r="I2" s="263" t="s">
         <v>2503</v>
       </c>
-      <c r="J2" s="264" t="s">
+      <c r="J2" s="263" t="s">
         <v>2529</v>
       </c>
-      <c r="K2" s="264" t="s">
+      <c r="K2" s="263" t="s">
         <v>2504</v>
       </c>
-      <c r="L2" s="265" t="s">
+      <c r="L2" s="264" t="s">
         <v>2505</v>
       </c>
-      <c r="M2" s="264" t="s">
+      <c r="M2" s="263" t="s">
         <v>2506</v>
       </c>
-      <c r="N2" s="264" t="s">
+      <c r="N2" s="263" t="s">
         <v>2507</v>
       </c>
-      <c r="O2" s="264" t="s">
+      <c r="O2" s="263" t="s">
         <v>2547</v>
       </c>
-      <c r="P2" s="264" t="s">
+      <c r="P2" s="263" t="s">
         <v>2549</v>
       </c>
     </row>
-    <row r="3" spans="1:16" s="263" customFormat="1">
+    <row r="3" spans="1:16">
       <c r="A3" s="140" t="s">
         <v>2508</v>
       </c>
@@ -26881,10 +26873,8 @@
         <v>2513</v>
       </c>
       <c r="N3" s="140"/>
-      <c r="O3"/>
-      <c r="P3"/>
-    </row>
-    <row r="4" spans="1:16" s="263" customFormat="1">
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" s="140" t="s">
         <v>2508</v>
       </c>
@@ -26924,7 +26914,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="5" spans="1:16" s="263" customFormat="1">
+    <row r="5" spans="1:16">
       <c r="A5" s="140" t="s">
         <v>2508</v>
       </c>
@@ -26964,7 +26954,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="6" spans="1:16" s="263" customFormat="1">
+    <row r="6" spans="1:16">
       <c r="A6" s="140" t="s">
         <v>2508</v>
       </c>
@@ -27004,7 +26994,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="7" spans="1:16" s="263" customFormat="1">
+    <row r="7" spans="1:16">
       <c r="A7" s="140" t="s">
         <v>2508</v>
       </c>
@@ -27044,7 +27034,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="8" spans="1:16" s="263" customFormat="1" ht="33">
+    <row r="8" spans="1:16" ht="34.799999999999997">
       <c r="A8" s="140" t="s">
         <v>2508</v>
       </c>
@@ -27068,7 +27058,7 @@
       <c r="K8" s="140" t="s">
         <v>2522</v>
       </c>
-      <c r="L8" s="266" t="s">
+      <c r="L8" s="265" t="s">
         <v>2543</v>
       </c>
       <c r="M8" s="140" t="s">
@@ -27084,7 +27074,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="9" spans="1:16" s="263" customFormat="1" ht="33">
+    <row r="9" spans="1:16" ht="34.799999999999997">
       <c r="A9" s="140" t="s">
         <v>2508</v>
       </c>
@@ -27108,7 +27098,7 @@
       <c r="K9" s="140" t="s">
         <v>2523</v>
       </c>
-      <c r="L9" s="266" t="s">
+      <c r="L9" s="265" t="s">
         <v>2544</v>
       </c>
       <c r="M9" s="140" t="s">
@@ -27124,7 +27114,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="10" spans="1:16" s="263" customFormat="1">
+    <row r="10" spans="1:16">
       <c r="A10" s="140" t="s">
         <v>2508</v>
       </c>
@@ -27144,15 +27134,12 @@
       <c r="I10" s="140"/>
       <c r="J10" s="140"/>
       <c r="K10" s="140"/>
-      <c r="L10" s="141"/>
       <c r="M10" s="140" t="s">
         <v>2513</v>
       </c>
       <c r="N10" s="140"/>
-      <c r="O10"/>
-      <c r="P10"/>
-    </row>
-    <row r="11" spans="1:16" s="263" customFormat="1">
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" s="140" t="s">
         <v>2508</v>
       </c>
@@ -27192,7 +27179,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="12" spans="1:16" s="263" customFormat="1">
+    <row r="12" spans="1:16">
       <c r="A12" s="140" t="s">
         <v>2508</v>
       </c>
@@ -27232,7 +27219,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="13" spans="1:16" s="263" customFormat="1">
+    <row r="13" spans="1:16">
       <c r="A13" s="140"/>
       <c r="B13" s="140"/>
       <c r="C13" s="140"/>
@@ -27244,7 +27231,6 @@
       <c r="I13" s="140"/>
       <c r="J13" s="140"/>
       <c r="K13" s="140"/>
-      <c r="L13" s="141"/>
       <c r="M13" s="140"/>
       <c r="N13" s="140"/>
     </row>
@@ -27258,20 +27244,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:U38"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="2" width="10.625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="17.25" style="4" customWidth="1"/>
-    <col min="4" max="4" width="9.625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="7.25" style="4" customWidth="1"/>
-    <col min="6" max="6" width="19.125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="13.625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="18.125" style="4" customWidth="1"/>
-    <col min="9" max="9" width="19.75" style="4" customWidth="1"/>
-    <col min="10" max="10" width="19.125" style="4" customWidth="1"/>
-    <col min="11" max="19" width="15.625" style="4" customWidth="1"/>
+    <col min="1" max="2" width="10.59765625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="17.19921875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="7.19921875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="19.09765625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="13.59765625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="18.09765625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="19.69921875" style="4" customWidth="1"/>
+    <col min="10" max="10" width="19.09765625" style="4" customWidth="1"/>
+    <col min="11" max="19" width="15.59765625" style="4" customWidth="1"/>
     <col min="20" max="20" width="14.5" style="4" customWidth="1"/>
-    <col min="21" max="21" width="16.125" style="4" customWidth="1"/>
+    <col min="21" max="21" width="16.09765625" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21">
@@ -28787,27 +28773,27 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:R73"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="1" max="1" width="15.5" style="19" customWidth="1"/>
     <col min="2" max="2" width="20" style="19" customWidth="1"/>
     <col min="3" max="3" width="11.5" style="19" customWidth="1"/>
-    <col min="4" max="4" width="16.25" style="16" customWidth="1"/>
+    <col min="4" max="4" width="16.19921875" style="16" customWidth="1"/>
     <col min="5" max="5" width="18.5" style="19" customWidth="1"/>
     <col min="6" max="6" width="16.5" style="19" customWidth="1"/>
-    <col min="7" max="8" width="9.625" style="19" customWidth="1"/>
-    <col min="9" max="9" width="15.625" style="19" customWidth="1"/>
-    <col min="10" max="10" width="20.75" style="19" customWidth="1"/>
-    <col min="11" max="11" width="36.75" style="19" customWidth="1"/>
+    <col min="7" max="8" width="9.59765625" style="19" customWidth="1"/>
+    <col min="9" max="9" width="15.59765625" style="19" customWidth="1"/>
+    <col min="10" max="10" width="20.69921875" style="19" customWidth="1"/>
+    <col min="11" max="11" width="36.69921875" style="19" customWidth="1"/>
     <col min="12" max="12" width="11" style="20" customWidth="1"/>
     <col min="13" max="13" width="11.5" style="20" customWidth="1"/>
     <col min="14" max="14" width="22" style="20" customWidth="1"/>
-    <col min="15" max="15" width="18.25" style="20" customWidth="1"/>
-    <col min="16" max="16" width="13.25" style="21" customWidth="1"/>
-    <col min="17" max="17" width="98.75" style="22" customWidth="1"/>
+    <col min="15" max="15" width="18.19921875" style="20" customWidth="1"/>
+    <col min="16" max="16" width="13.19921875" style="21" customWidth="1"/>
+    <col min="17" max="17" width="98.69921875" style="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="1" spans="1:17" ht="19.95" customHeight="1">
       <c r="A1" s="23" t="s">
         <v>247</v>
       </c>
@@ -28860,7 +28846,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="19.899999999999999" customHeight="1" thickBot="1">
+    <row r="2" spans="1:17" ht="19.95" customHeight="1" thickBot="1">
       <c r="A2" s="25" t="s">
         <v>262</v>
       </c>
@@ -28913,7 +28899,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="3" spans="1:17" ht="19.95" customHeight="1">
       <c r="A3" s="27" t="s">
         <v>278</v>
       </c>
@@ -28966,7 +28952,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="4" spans="1:17" ht="19.95" customHeight="1">
       <c r="A4" s="31" t="s">
         <v>49</v>
       </c>
@@ -29019,7 +29005,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="5" spans="1:17" ht="19.95" customHeight="1">
       <c r="A5" s="31" t="s">
         <v>50</v>
       </c>
@@ -29072,7 +29058,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="6" spans="1:17" ht="19.95" customHeight="1">
       <c r="A6" s="31" t="s">
         <v>65</v>
       </c>
@@ -29125,7 +29111,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="7" spans="1:17" ht="19.95" customHeight="1">
       <c r="A7" s="31" t="s">
         <v>66</v>
       </c>
@@ -29178,7 +29164,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="8" spans="1:17" ht="19.95" customHeight="1">
       <c r="A8" s="31" t="s">
         <v>81</v>
       </c>
@@ -29231,7 +29217,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="9" spans="1:17" ht="19.95" customHeight="1">
       <c r="A9" s="31" t="s">
         <v>82</v>
       </c>
@@ -29284,7 +29270,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="10" spans="1:17" ht="19.95" customHeight="1">
       <c r="A10" s="31" t="s">
         <v>97</v>
       </c>
@@ -29337,7 +29323,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="11" spans="1:17" ht="19.95" customHeight="1">
       <c r="A11" s="31" t="s">
         <v>98</v>
       </c>
@@ -29390,7 +29376,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="12" spans="1:17" ht="19.95" customHeight="1">
       <c r="A12" s="31" t="s">
         <v>112</v>
       </c>
@@ -29443,7 +29429,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="19.899999999999999" customHeight="1" thickBot="1">
+    <row r="13" spans="1:17" ht="19.95" customHeight="1" thickBot="1">
       <c r="A13" s="35" t="s">
         <v>113</v>
       </c>
@@ -29496,7 +29482,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="14" spans="1:17" ht="19.95" customHeight="1">
       <c r="A14" s="38" t="s">
         <v>51</v>
       </c>
@@ -29549,7 +29535,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="15" spans="1:17" ht="19.95" customHeight="1">
       <c r="A15" s="31" t="s">
         <v>52</v>
       </c>
@@ -29602,7 +29588,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="16" spans="1:17" ht="19.95" customHeight="1">
       <c r="A16" s="31" t="s">
         <v>67</v>
       </c>
@@ -29655,7 +29641,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="17" spans="1:17" ht="19.95" customHeight="1">
       <c r="A17" s="31" t="s">
         <v>68</v>
       </c>
@@ -29708,7 +29694,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="18" spans="1:17" ht="19.95" customHeight="1">
       <c r="A18" s="31" t="s">
         <v>83</v>
       </c>
@@ -29761,7 +29747,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="19" spans="1:17" ht="19.95" customHeight="1">
       <c r="A19" s="31" t="s">
         <v>84</v>
       </c>
@@ -29814,7 +29800,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="20" spans="1:17" ht="19.95" customHeight="1">
       <c r="A20" s="31" t="s">
         <v>99</v>
       </c>
@@ -29867,7 +29853,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="21" spans="1:17" ht="19.95" customHeight="1">
       <c r="A21" s="31" t="s">
         <v>100</v>
       </c>
@@ -29920,7 +29906,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="22" spans="1:17" ht="19.95" customHeight="1">
       <c r="A22" s="31" t="s">
         <v>114</v>
       </c>
@@ -29973,7 +29959,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="19.899999999999999" customHeight="1" thickBot="1">
+    <row r="23" spans="1:17" ht="19.95" customHeight="1" thickBot="1">
       <c r="A23" s="35" t="s">
         <v>115</v>
       </c>
@@ -30026,7 +30012,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="24" spans="1:17" ht="19.95" customHeight="1">
       <c r="A24" s="38" t="s">
         <v>53</v>
       </c>
@@ -30079,7 +30065,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="1" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="25" spans="1:17" s="1" customFormat="1" ht="19.95" customHeight="1">
       <c r="A25" s="31" t="s">
         <v>54</v>
       </c>
@@ -30132,7 +30118,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="26" spans="1:17" ht="19.95" customHeight="1">
       <c r="A26" s="31" t="s">
         <v>69</v>
       </c>
@@ -30185,7 +30171,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="1" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="27" spans="1:17" s="1" customFormat="1" ht="19.95" customHeight="1">
       <c r="A27" s="31" t="s">
         <v>70</v>
       </c>
@@ -30238,7 +30224,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="28" spans="1:17" ht="19.95" customHeight="1">
       <c r="A28" s="31" t="s">
         <v>85</v>
       </c>
@@ -30291,7 +30277,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="1" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="29" spans="1:17" s="1" customFormat="1" ht="19.95" customHeight="1">
       <c r="A29" s="31" t="s">
         <v>86</v>
       </c>
@@ -30344,7 +30330,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="30" spans="1:17" ht="19.95" customHeight="1">
       <c r="A30" s="31" t="s">
         <v>101</v>
       </c>
@@ -30397,7 +30383,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="1" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="31" spans="1:17" s="1" customFormat="1" ht="19.95" customHeight="1">
       <c r="A31" s="31" t="s">
         <v>102</v>
       </c>
@@ -30450,7 +30436,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="32" spans="1:17" ht="19.95" customHeight="1">
       <c r="A32" s="31" t="s">
         <v>116</v>
       </c>
@@ -30503,7 +30489,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="1" customFormat="1" ht="19.899999999999999" customHeight="1" thickBot="1">
+    <row r="33" spans="1:17" s="1" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A33" s="35" t="s">
         <v>117</v>
       </c>
@@ -30556,7 +30542,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="34" spans="1:17" ht="19.95" customHeight="1">
       <c r="A34" s="43" t="s">
         <v>389</v>
       </c>
@@ -30609,7 +30595,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="1" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="35" spans="1:17" s="1" customFormat="1" ht="19.95" customHeight="1">
       <c r="A35" s="46" t="s">
         <v>394</v>
       </c>
@@ -30662,7 +30648,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="36" spans="1:17" ht="19.95" customHeight="1">
       <c r="A36" s="46" t="s">
         <v>398</v>
       </c>
@@ -30715,7 +30701,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="1" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="37" spans="1:17" s="1" customFormat="1" ht="19.95" customHeight="1">
       <c r="A37" s="46" t="s">
         <v>402</v>
       </c>
@@ -30768,7 +30754,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="38" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="38" spans="1:17" ht="19.95" customHeight="1">
       <c r="A38" s="46" t="s">
         <v>406</v>
       </c>
@@ -30821,7 +30807,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="39" spans="1:17" s="1" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="39" spans="1:17" s="1" customFormat="1" ht="19.95" customHeight="1">
       <c r="A39" s="46" t="s">
         <v>410</v>
       </c>
@@ -30874,7 +30860,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="40" spans="1:17" ht="19.95" customHeight="1">
       <c r="A40" s="46" t="s">
         <v>414</v>
       </c>
@@ -30927,7 +30913,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="41" spans="1:17" s="1" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="41" spans="1:17" s="1" customFormat="1" ht="19.95" customHeight="1">
       <c r="A41" s="46" t="s">
         <v>421</v>
       </c>
@@ -30980,7 +30966,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="19.899999999999999" customHeight="1">
+    <row r="42" spans="1:17" ht="19.95" customHeight="1">
       <c r="A42" s="46" t="s">
         <v>426</v>
       </c>
@@ -31033,7 +31019,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="43" spans="1:17" s="1" customFormat="1" ht="19.899999999999999" customHeight="1" thickBot="1">
+    <row r="43" spans="1:17" s="1" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A43" s="50" t="s">
         <v>431</v>
       </c>
@@ -31086,7 +31072,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="44" spans="1:17" s="2" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="44" spans="1:17" s="2" customFormat="1" ht="19.95" customHeight="1">
       <c r="A44" s="53" t="s">
         <v>437</v>
       </c>
@@ -31139,7 +31125,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="45" spans="1:17" s="1" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="45" spans="1:17" s="1" customFormat="1" ht="19.95" customHeight="1">
       <c r="A45" s="57" t="s">
         <v>441</v>
       </c>
@@ -31192,7 +31178,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="46" spans="1:17" s="2" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="46" spans="1:17" s="2" customFormat="1" ht="19.95" customHeight="1">
       <c r="A46" s="57" t="s">
         <v>446</v>
       </c>
@@ -31245,7 +31231,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="47" spans="1:17" s="1" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="47" spans="1:17" s="1" customFormat="1" ht="19.95" customHeight="1">
       <c r="A47" s="57" t="s">
         <v>451</v>
       </c>
@@ -31298,7 +31284,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="48" spans="1:17" s="2" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="48" spans="1:17" s="2" customFormat="1" ht="19.95" customHeight="1">
       <c r="A48" s="57" t="s">
         <v>455</v>
       </c>
@@ -31351,7 +31337,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="1" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="49" spans="1:18" s="1" customFormat="1" ht="19.95" customHeight="1">
       <c r="A49" s="57" t="s">
         <v>459</v>
       </c>
@@ -31404,7 +31390,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="2" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="50" spans="1:18" s="2" customFormat="1" ht="19.95" customHeight="1">
       <c r="A50" s="57" t="s">
         <v>461</v>
       </c>
@@ -31457,7 +31443,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="1" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="51" spans="1:18" s="1" customFormat="1" ht="19.95" customHeight="1">
       <c r="A51" s="57" t="s">
         <v>467</v>
       </c>
@@ -31510,7 +31496,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="2" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="52" spans="1:18" s="2" customFormat="1" ht="19.95" customHeight="1">
       <c r="A52" s="57" t="s">
         <v>471</v>
       </c>
@@ -31563,7 +31549,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="1" customFormat="1" ht="19.899999999999999" customHeight="1" thickBot="1">
+    <row r="53" spans="1:18" s="1" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A53" s="63" t="s">
         <v>476</v>
       </c>
@@ -31616,7 +31602,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="2" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="54" spans="1:18" s="2" customFormat="1" ht="19.95" customHeight="1">
       <c r="A54" s="53" t="s">
         <v>481</v>
       </c>
@@ -31669,7 +31655,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="55" spans="1:18" s="1" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="55" spans="1:18" s="1" customFormat="1" ht="19.95" customHeight="1">
       <c r="A55" s="57" t="s">
         <v>484</v>
       </c>
@@ -31722,7 +31708,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="56" spans="1:18" s="2" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="56" spans="1:18" s="2" customFormat="1" ht="19.95" customHeight="1">
       <c r="A56" s="57" t="s">
         <v>488</v>
       </c>
@@ -31776,7 +31762,7 @@
       </c>
       <c r="R56"/>
     </row>
-    <row r="57" spans="1:18" s="1" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="57" spans="1:18" s="1" customFormat="1" ht="19.95" customHeight="1">
       <c r="A57" s="57" t="s">
         <v>490</v>
       </c>
@@ -31830,7 +31816,7 @@
       </c>
       <c r="R57"/>
     </row>
-    <row r="58" spans="1:18" s="2" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="58" spans="1:18" s="2" customFormat="1" ht="19.95" customHeight="1">
       <c r="A58" s="57" t="s">
         <v>495</v>
       </c>
@@ -31884,7 +31870,7 @@
       </c>
       <c r="R58"/>
     </row>
-    <row r="59" spans="1:18" s="1" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="59" spans="1:18" s="1" customFormat="1" ht="19.95" customHeight="1">
       <c r="A59" s="57" t="s">
         <v>500</v>
       </c>
@@ -31937,7 +31923,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="60" spans="1:18" s="2" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="60" spans="1:18" s="2" customFormat="1" ht="19.95" customHeight="1">
       <c r="A60" s="57" t="s">
         <v>506</v>
       </c>
@@ -31990,7 +31976,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="61" spans="1:18" s="1" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="61" spans="1:18" s="1" customFormat="1" ht="19.95" customHeight="1">
       <c r="A61" s="57" t="s">
         <v>511</v>
       </c>
@@ -32043,7 +32029,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="62" spans="1:18" s="2" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="62" spans="1:18" s="2" customFormat="1" ht="19.95" customHeight="1">
       <c r="A62" s="57" t="s">
         <v>515</v>
       </c>
@@ -32096,7 +32082,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="63" spans="1:18" s="1" customFormat="1" ht="19.899999999999999" customHeight="1" thickBot="1">
+    <row r="63" spans="1:18" s="1" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A63" s="63" t="s">
         <v>518</v>
       </c>
@@ -32149,7 +32135,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="64" spans="1:18" s="2" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="64" spans="1:18" s="2" customFormat="1" ht="19.95" customHeight="1">
       <c r="A64" s="53" t="s">
         <v>523</v>
       </c>
@@ -32202,7 +32188,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="65" spans="1:17" s="1" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="65" spans="1:17" s="1" customFormat="1" ht="19.95" customHeight="1">
       <c r="A65" s="57" t="s">
         <v>530</v>
       </c>
@@ -32255,7 +32241,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="66" spans="1:17" s="2" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="66" spans="1:17" s="2" customFormat="1" ht="19.95" customHeight="1">
       <c r="A66" s="57" t="s">
         <v>534</v>
       </c>
@@ -32308,7 +32294,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="67" spans="1:17" s="1" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="67" spans="1:17" s="1" customFormat="1" ht="19.95" customHeight="1">
       <c r="A67" s="57" t="s">
         <v>539</v>
       </c>
@@ -32361,7 +32347,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="68" spans="1:17" s="2" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="68" spans="1:17" s="2" customFormat="1" ht="19.95" customHeight="1">
       <c r="A68" s="57" t="s">
         <v>543</v>
       </c>
@@ -32414,7 +32400,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="69" spans="1:17" s="1" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="69" spans="1:17" s="1" customFormat="1" ht="19.95" customHeight="1">
       <c r="A69" s="57" t="s">
         <v>548</v>
       </c>
@@ -32467,7 +32453,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="70" spans="1:17" s="2" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="70" spans="1:17" s="2" customFormat="1" ht="19.95" customHeight="1">
       <c r="A70" s="57" t="s">
         <v>553</v>
       </c>
@@ -32520,7 +32506,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="71" spans="1:17" s="1" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="71" spans="1:17" s="1" customFormat="1" ht="19.95" customHeight="1">
       <c r="A71" s="57" t="s">
         <v>557</v>
       </c>
@@ -32573,7 +32559,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="72" spans="1:17" s="2" customFormat="1" ht="19.899999999999999" customHeight="1">
+    <row r="72" spans="1:17" s="2" customFormat="1" ht="19.95" customHeight="1">
       <c r="A72" s="57" t="s">
         <v>562</v>
       </c>
@@ -32626,7 +32612,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="73" spans="1:17" s="1" customFormat="1" ht="19.899999999999999" customHeight="1" thickBot="1">
+    <row r="73" spans="1:17" s="1" customFormat="1" ht="19.95" customHeight="1" thickBot="1">
       <c r="A73" s="63" t="s">
         <v>566</v>
       </c>
@@ -32688,20 +32674,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:N49"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="13.25" style="4" customWidth="1"/>
-    <col min="2" max="2" width="20.125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="13.19921875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="20.09765625" style="4" customWidth="1"/>
     <col min="3" max="3" width="11.5" style="4" customWidth="1"/>
-    <col min="4" max="4" width="17.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.25" style="4" customWidth="1"/>
-    <col min="6" max="7" width="14.25" style="4" customWidth="1"/>
-    <col min="8" max="8" width="11.25" style="4" customWidth="1"/>
-    <col min="9" max="9" width="19.125" style="4" customWidth="1"/>
-    <col min="10" max="10" width="17.75" style="4" customWidth="1"/>
-    <col min="11" max="11" width="87.25" style="4" customWidth="1"/>
-    <col min="12" max="12" width="18.75" style="4" customWidth="1"/>
-    <col min="13" max="13" width="16.75" style="4" customWidth="1"/>
+    <col min="4" max="4" width="17.19921875" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.19921875" style="4" customWidth="1"/>
+    <col min="6" max="7" width="14.19921875" style="4" customWidth="1"/>
+    <col min="8" max="8" width="11.19921875" style="4" customWidth="1"/>
+    <col min="9" max="9" width="19.09765625" style="4" customWidth="1"/>
+    <col min="10" max="10" width="17.69921875" style="4" customWidth="1"/>
+    <col min="11" max="11" width="87.19921875" style="4" customWidth="1"/>
+    <col min="12" max="12" width="18.69921875" style="4" customWidth="1"/>
+    <col min="13" max="13" width="16.69921875" style="4" customWidth="1"/>
     <col min="14" max="14" width="18" style="74" customWidth="1"/>
   </cols>
   <sheetData>
@@ -34498,17 +34484,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:L16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="25.75" style="4" customWidth="1"/>
-    <col min="3" max="3" width="7.625" style="4" customWidth="1"/>
+    <col min="1" max="1" width="25.69921875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="7.59765625" style="4" customWidth="1"/>
     <col min="4" max="4" width="11.5" style="4" customWidth="1"/>
-    <col min="5" max="5" width="15.125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="15.09765625" style="4" customWidth="1"/>
     <col min="8" max="8" width="11.5" style="4" customWidth="1"/>
-    <col min="9" max="9" width="13.125" style="4" customWidth="1"/>
+    <col min="9" max="9" width="13.09765625" style="4" customWidth="1"/>
     <col min="10" max="10" width="13.5" style="4" customWidth="1"/>
-    <col min="11" max="11" width="12.125" style="4" customWidth="1"/>
-    <col min="12" max="12" width="63.75" style="4" customWidth="1"/>
+    <col min="11" max="11" width="12.09765625" style="4" customWidth="1"/>
+    <col min="12" max="12" width="63.69921875" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -34988,14 +34974,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F372"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="49.25" style="87" customWidth="1"/>
-    <col min="2" max="2" width="69.375" style="14" customWidth="1"/>
-    <col min="3" max="3" width="30.25" style="14" customWidth="1"/>
-    <col min="4" max="4" width="17.25" style="14" customWidth="1"/>
+    <col min="1" max="1" width="49.19921875" style="87" customWidth="1"/>
+    <col min="2" max="2" width="69.3984375" style="14" customWidth="1"/>
+    <col min="3" max="3" width="30.19921875" style="14" customWidth="1"/>
+    <col min="4" max="4" width="17.19921875" style="14" customWidth="1"/>
     <col min="5" max="5" width="106" style="87" customWidth="1"/>
-    <col min="6" max="6" width="17.25" style="14" customWidth="1"/>
+    <col min="6" max="6" width="17.19921875" style="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="16.5" customHeight="1">
@@ -39674,15 +39660,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:H30"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="2" max="2" width="16" style="4" customWidth="1"/>
-    <col min="3" max="3" width="10.75" style="4" customWidth="1"/>
-    <col min="4" max="4" width="16.25" style="4" customWidth="1"/>
+    <col min="3" max="3" width="10.69921875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="16.19921875" style="4" customWidth="1"/>
     <col min="5" max="5" width="12" style="4" customWidth="1"/>
-    <col min="6" max="6" width="13.625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="13.59765625" style="4" customWidth="1"/>
     <col min="7" max="7" width="14.5" style="4" customWidth="1"/>
-    <col min="8" max="8" width="17.75" style="74" customWidth="1"/>
+    <col min="8" max="8" width="17.69921875" style="74" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -40474,18 +40460,18 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:AA49"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="16.375" style="4" customWidth="1"/>
-    <col min="2" max="2" width="11.25" style="4" customWidth="1"/>
-    <col min="3" max="6" width="14.625" style="4" customWidth="1"/>
-    <col min="7" max="7" width="28.125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="20.75" style="4" customWidth="1"/>
+    <col min="1" max="1" width="16.3984375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="11.19921875" style="4" customWidth="1"/>
+    <col min="3" max="6" width="14.59765625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="28.09765625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="20.69921875" style="4" customWidth="1"/>
     <col min="9" max="9" width="21.5" style="4" customWidth="1"/>
-    <col min="10" max="10" width="16.75" style="4" customWidth="1"/>
-    <col min="11" max="11" width="16.25" style="4" customWidth="1"/>
-    <col min="12" max="12" width="19.25" style="14" customWidth="1"/>
-    <col min="13" max="13" width="25.125" style="74" customWidth="1"/>
+    <col min="10" max="10" width="16.69921875" style="4" customWidth="1"/>
+    <col min="11" max="11" width="16.19921875" style="4" customWidth="1"/>
+    <col min="12" max="12" width="19.19921875" style="14" customWidth="1"/>
+    <col min="13" max="13" width="25.09765625" style="74" customWidth="1"/>
     <col min="14" max="14" width="20.5" style="74" customWidth="1"/>
     <col min="15" max="15" width="20" style="74" customWidth="1"/>
     <col min="16" max="16" width="23" style="74" customWidth="1"/>
@@ -41283,7 +41269,7 @@
       <c r="R19" s="141"/>
       <c r="S19" s="141"/>
     </row>
-    <row r="20" spans="1:26" ht="17.25" thickBot="1">
+    <row r="20" spans="1:26" ht="18" thickBot="1">
       <c r="A20" s="151" t="s">
         <v>2128</v>
       </c>
@@ -41406,7 +41392,7 @@
       <c r="Y22" s="141"/>
       <c r="Z22" s="141"/>
     </row>
-    <row r="23" spans="1:26" ht="17.25" thickBot="1">
+    <row r="23" spans="1:26" ht="18" thickBot="1">
       <c r="A23" s="151" t="s">
         <v>2129</v>
       </c>
@@ -41504,7 +41490,7 @@
       <c r="Y24" s="141"/>
       <c r="Z24" s="141"/>
     </row>
-    <row r="25" spans="1:26" ht="17.25" thickBot="1">
+    <row r="25" spans="1:26" ht="18" thickBot="1">
       <c r="A25" s="151" t="s">
         <v>2435</v>
       </c>
@@ -41641,7 +41627,7 @@
       <c r="Y27" s="141"/>
       <c r="Z27" s="141"/>
     </row>
-    <row r="28" spans="1:26" ht="17.25" thickBot="1">
+    <row r="28" spans="1:26" ht="18" thickBot="1">
       <c r="A28" s="156" t="s">
         <v>2438</v>
       </c>
@@ -41882,7 +41868,7 @@
       <c r="Y32" s="141"/>
       <c r="Z32" s="141"/>
     </row>
-    <row r="33" spans="1:26" ht="17.25" thickBot="1">
+    <row r="33" spans="1:26" ht="18" thickBot="1">
       <c r="A33" s="156" t="s">
         <v>2441</v>
       </c>
@@ -42210,34 +42196,34 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:AA72"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="54.95" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="54.9" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.5" style="257" customWidth="1"/>
     <col min="2" max="2" width="22.5" style="257" customWidth="1"/>
-    <col min="3" max="3" width="90.25" style="257" customWidth="1"/>
-    <col min="4" max="4" width="13.25" style="247" customWidth="1"/>
-    <col min="5" max="5" width="31.875" style="247" customWidth="1"/>
-    <col min="6" max="6" width="58.625" style="257" customWidth="1"/>
-    <col min="7" max="7" width="58.625" style="258" customWidth="1"/>
-    <col min="8" max="8" width="13.75" style="247" customWidth="1"/>
-    <col min="9" max="9" width="26.625" style="247" customWidth="1"/>
+    <col min="3" max="3" width="90.19921875" style="257" customWidth="1"/>
+    <col min="4" max="4" width="13.19921875" style="247" customWidth="1"/>
+    <col min="5" max="5" width="31.8984375" style="247" customWidth="1"/>
+    <col min="6" max="6" width="58.59765625" style="257" customWidth="1"/>
+    <col min="7" max="7" width="58.59765625" style="258" customWidth="1"/>
+    <col min="8" max="8" width="13.69921875" style="247" customWidth="1"/>
+    <col min="9" max="9" width="26.59765625" style="247" customWidth="1"/>
     <col min="10" max="10" width="15.5" style="247" customWidth="1"/>
-    <col min="11" max="11" width="21.75" style="247" customWidth="1"/>
-    <col min="12" max="12" width="13.125" style="247" customWidth="1"/>
-    <col min="13" max="13" width="20.25" style="247" customWidth="1"/>
-    <col min="14" max="14" width="19.25" style="247" customWidth="1"/>
-    <col min="15" max="15" width="29.125" style="247" customWidth="1"/>
-    <col min="16" max="16" width="37.625" style="247" customWidth="1"/>
-    <col min="17" max="18" width="15.75" style="247" customWidth="1"/>
-    <col min="19" max="23" width="17.75" style="247" customWidth="1"/>
+    <col min="11" max="11" width="21.69921875" style="247" customWidth="1"/>
+    <col min="12" max="12" width="13.09765625" style="247" customWidth="1"/>
+    <col min="13" max="13" width="20.19921875" style="247" customWidth="1"/>
+    <col min="14" max="14" width="19.19921875" style="247" customWidth="1"/>
+    <col min="15" max="15" width="29.09765625" style="247" customWidth="1"/>
+    <col min="16" max="16" width="37.59765625" style="247" customWidth="1"/>
+    <col min="17" max="18" width="15.69921875" style="247" customWidth="1"/>
+    <col min="19" max="23" width="17.69921875" style="247" customWidth="1"/>
     <col min="24" max="24" width="33.5" style="247" customWidth="1"/>
-    <col min="25" max="25" width="43.875" style="247" customWidth="1"/>
-    <col min="26" max="26" width="26.75" style="259" customWidth="1"/>
-    <col min="27" max="27" width="24.75" style="259" customWidth="1"/>
+    <col min="25" max="25" width="43.8984375" style="247" customWidth="1"/>
+    <col min="26" max="26" width="26.69921875" style="259" customWidth="1"/>
+    <col min="27" max="27" width="24.69921875" style="259" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A1" s="267" t="s">
+    <row r="1" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A1" s="266" t="s">
         <v>2167</v>
       </c>
       <c r="B1" s="160" t="s">
@@ -42319,8 +42305,8 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="54.95" customHeight="1" thickBot="1">
-      <c r="A2" s="268" t="s">
+    <row r="2" spans="1:27" ht="54.9" customHeight="1" thickBot="1">
+      <c r="A2" s="267" t="s">
         <v>2166</v>
       </c>
       <c r="B2" s="243" t="s">
@@ -42402,8 +42388,8 @@
         <v>2205</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A3" s="269" t="s">
+    <row r="3" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A3" s="268" t="s">
         <v>2164</v>
       </c>
       <c r="B3" s="241" t="s">
@@ -42465,8 +42451,8 @@
         <v>2248</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A4" s="270" t="s">
+    <row r="4" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A4" s="269" t="s">
         <v>2164</v>
       </c>
       <c r="B4" s="161"/>
@@ -42524,8 +42510,8 @@
         <v>1414</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A5" s="270" t="s">
+    <row r="5" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A5" s="269" t="s">
         <v>2164</v>
       </c>
       <c r="B5" s="161"/>
@@ -42583,8 +42569,8 @@
         <v>1416</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="54.95" customHeight="1" thickBot="1">
-      <c r="A6" s="271" t="s">
+    <row r="6" spans="1:27" ht="54.9" customHeight="1" thickBot="1">
+      <c r="A6" s="270" t="s">
         <v>2219</v>
       </c>
       <c r="B6" s="240"/>
@@ -42620,8 +42606,8 @@
       </c>
       <c r="AA6" s="250"/>
     </row>
-    <row r="7" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A7" s="269" t="s">
+    <row r="7" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A7" s="268" t="s">
         <v>2231</v>
       </c>
       <c r="B7" s="241" t="s">
@@ -42679,8 +42665,8 @@
         <v>1413</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A8" s="270" t="s">
+    <row r="8" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A8" s="269" t="s">
         <v>2231</v>
       </c>
       <c r="B8" s="161"/>
@@ -42730,8 +42716,8 @@
         <v>1415</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A9" s="270" t="s">
+    <row r="9" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A9" s="269" t="s">
         <v>2232</v>
       </c>
       <c r="B9" s="161"/>
@@ -42767,8 +42753,8 @@
       </c>
       <c r="AA9" s="249"/>
     </row>
-    <row r="10" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A10" s="270" t="s">
+    <row r="10" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A10" s="269" t="s">
         <v>2220</v>
       </c>
       <c r="B10" s="161"/>
@@ -42804,8 +42790,8 @@
       </c>
       <c r="AA10" s="249"/>
     </row>
-    <row r="11" spans="1:27" ht="54.95" customHeight="1" thickBot="1">
-      <c r="A11" s="270" t="s">
+    <row r="11" spans="1:27" ht="54.9" customHeight="1" thickBot="1">
+      <c r="A11" s="269" t="s">
         <v>2233</v>
       </c>
       <c r="B11" s="161"/>
@@ -42841,8 +42827,8 @@
       </c>
       <c r="AA11" s="249"/>
     </row>
-    <row r="12" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A12" s="269" t="s">
+    <row r="12" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A12" s="268" t="s">
         <v>2270</v>
       </c>
       <c r="B12" s="241" t="s">
@@ -42902,8 +42888,8 @@
         <v>1413</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A13" s="270" t="s">
+    <row r="13" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A13" s="269" t="s">
         <v>2270</v>
       </c>
       <c r="B13" s="161"/>
@@ -42957,8 +42943,8 @@
         <v>1415</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A14" s="270" t="s">
+    <row r="14" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A14" s="269" t="s">
         <v>2270</v>
       </c>
       <c r="B14" s="161"/>
@@ -43012,8 +42998,8 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A15" s="270" t="s">
+    <row r="15" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A15" s="269" t="s">
         <v>2260</v>
       </c>
       <c r="B15" s="161"/>
@@ -43049,8 +43035,8 @@
       </c>
       <c r="AA15" s="249"/>
     </row>
-    <row r="16" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A16" s="270" t="s">
+    <row r="16" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A16" s="269" t="s">
         <v>2261</v>
       </c>
       <c r="B16" s="161"/>
@@ -43086,8 +43072,8 @@
       </c>
       <c r="AA16" s="249"/>
     </row>
-    <row r="17" spans="1:27" ht="54.95" customHeight="1" thickBot="1">
-      <c r="A17" s="271" t="s">
+    <row r="17" spans="1:27" ht="54.9" customHeight="1" thickBot="1">
+      <c r="A17" s="270" t="s">
         <v>2262</v>
       </c>
       <c r="B17" s="240"/>
@@ -43123,8 +43109,8 @@
       </c>
       <c r="AA17" s="250"/>
     </row>
-    <row r="18" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A18" s="269" t="s">
+    <row r="18" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A18" s="268" t="s">
         <v>2271</v>
       </c>
       <c r="B18" s="253" t="s">
@@ -43196,8 +43182,8 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A19" s="270" t="s">
+    <row r="19" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A19" s="269" t="s">
         <v>1364</v>
       </c>
       <c r="B19" s="244"/>
@@ -43265,8 +43251,8 @@
         <v>1415</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A20" s="270" t="s">
+    <row r="20" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A20" s="269" t="s">
         <v>1364</v>
       </c>
       <c r="B20" s="244"/>
@@ -43316,8 +43302,8 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A21" s="270" t="s">
+    <row r="21" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A21" s="269" t="s">
         <v>2273</v>
       </c>
       <c r="B21" s="244"/>
@@ -43353,8 +43339,8 @@
       </c>
       <c r="AA21" s="249"/>
     </row>
-    <row r="22" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A22" s="270" t="s">
+    <row r="22" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A22" s="269" t="s">
         <v>2274</v>
       </c>
       <c r="B22" s="244"/>
@@ -43390,8 +43376,8 @@
       </c>
       <c r="AA22" s="249"/>
     </row>
-    <row r="23" spans="1:27" ht="54.95" customHeight="1" thickBot="1">
-      <c r="A23" s="271" t="s">
+    <row r="23" spans="1:27" ht="54.9" customHeight="1" thickBot="1">
+      <c r="A23" s="270" t="s">
         <v>2275</v>
       </c>
       <c r="B23" s="245"/>
@@ -43427,8 +43413,8 @@
       </c>
       <c r="AA23" s="250"/>
     </row>
-    <row r="24" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A24" s="269" t="s">
+    <row r="24" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A24" s="268" t="s">
         <v>2295</v>
       </c>
       <c r="B24" s="253" t="s">
@@ -43492,8 +43478,8 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A25" s="270" t="s">
+    <row r="25" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A25" s="269" t="s">
         <v>2295</v>
       </c>
       <c r="B25" s="244"/>
@@ -43553,8 +43539,8 @@
         <v>1415</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A26" s="270" t="s">
+    <row r="26" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A26" s="269" t="s">
         <v>2295</v>
       </c>
       <c r="B26" s="244"/>
@@ -43614,8 +43600,8 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A27" s="270" t="s">
+    <row r="27" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A27" s="269" t="s">
         <v>2300</v>
       </c>
       <c r="B27" s="244"/>
@@ -43651,8 +43637,8 @@
       </c>
       <c r="AA27" s="249"/>
     </row>
-    <row r="28" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A28" s="270" t="s">
+    <row r="28" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A28" s="269" t="s">
         <v>2301</v>
       </c>
       <c r="B28" s="244"/>
@@ -43688,8 +43674,8 @@
       </c>
       <c r="AA28" s="249"/>
     </row>
-    <row r="29" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A29" s="270" t="s">
+    <row r="29" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A29" s="269" t="s">
         <v>2302</v>
       </c>
       <c r="B29" s="244"/>
@@ -43725,8 +43711,8 @@
       </c>
       <c r="AA29" s="249"/>
     </row>
-    <row r="30" spans="1:27" ht="54.95" customHeight="1" thickBot="1">
-      <c r="A30" s="271" t="s">
+    <row r="30" spans="1:27" ht="54.9" customHeight="1" thickBot="1">
+      <c r="A30" s="270" t="s">
         <v>2303</v>
       </c>
       <c r="B30" s="245"/>
@@ -43762,8 +43748,8 @@
       </c>
       <c r="AA30" s="250"/>
     </row>
-    <row r="31" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A31" s="269" t="s">
+    <row r="31" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A31" s="268" t="s">
         <v>2316</v>
       </c>
       <c r="B31" s="253" t="s">
@@ -43831,8 +43817,8 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A32" s="270" t="s">
+    <row r="32" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A32" s="269" t="s">
         <v>2316</v>
       </c>
       <c r="B32" s="244"/>
@@ -43882,8 +43868,8 @@
         <v>2557</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A33" s="270" t="s">
+    <row r="33" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A33" s="269" t="s">
         <v>2320</v>
       </c>
       <c r="B33" s="244"/>
@@ -43946,11 +43932,11 @@
         <v>1423</v>
       </c>
       <c r="AA33" s="249" t="s">
-        <v>2373</v>
-      </c>
-    </row>
-    <row r="34" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A34" s="270" t="s">
+        <v>2337</v>
+      </c>
+    </row>
+    <row r="34" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A34" s="269" t="s">
         <v>2320</v>
       </c>
       <c r="B34" s="161"/>
@@ -44000,8 +43986,8 @@
         <v>2557</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A35" s="270" t="s">
+    <row r="35" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A35" s="269" t="s">
         <v>2321</v>
       </c>
       <c r="B35" s="161"/>
@@ -44066,11 +44052,11 @@
         <v>1423</v>
       </c>
       <c r="AA35" s="249" t="s">
-        <v>2405</v>
-      </c>
-    </row>
-    <row r="36" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A36" s="270" t="s">
+        <v>2337</v>
+      </c>
+    </row>
+    <row r="36" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A36" s="269" t="s">
         <v>2321</v>
       </c>
       <c r="B36" s="161"/>
@@ -44120,8 +44106,8 @@
         <v>2557</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A37" s="270" t="s">
+    <row r="37" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A37" s="269" t="s">
         <v>2324</v>
       </c>
       <c r="B37" s="161"/>
@@ -44157,8 +44143,8 @@
       </c>
       <c r="AA37" s="249"/>
     </row>
-    <row r="38" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A38" s="270" t="s">
+    <row r="38" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A38" s="269" t="s">
         <v>2326</v>
       </c>
       <c r="B38" s="161"/>
@@ -44194,8 +44180,8 @@
       </c>
       <c r="AA38" s="249"/>
     </row>
-    <row r="39" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A39" s="270" t="s">
+    <row r="39" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A39" s="269" t="s">
         <v>2327</v>
       </c>
       <c r="B39" s="161"/>
@@ -44231,8 +44217,8 @@
       </c>
       <c r="AA39" s="249"/>
     </row>
-    <row r="40" spans="1:27" ht="54.95" customHeight="1" thickBot="1">
-      <c r="A40" s="272" t="s">
+    <row r="40" spans="1:27" ht="54.9" customHeight="1" thickBot="1">
+      <c r="A40" s="271" t="s">
         <v>2328</v>
       </c>
       <c r="B40" s="246"/>
@@ -44268,8 +44254,8 @@
       </c>
       <c r="AA40" s="251"/>
     </row>
-    <row r="41" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A41" s="269" t="s">
+    <row r="41" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A41" s="268" t="s">
         <v>2347</v>
       </c>
       <c r="B41" s="241" t="s">
@@ -44331,8 +44317,8 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="42" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A42" s="270" t="s">
+    <row r="42" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A42" s="269" t="s">
         <v>2347</v>
       </c>
       <c r="B42" s="161"/>
@@ -44378,8 +44364,8 @@
       </c>
       <c r="AA42" s="249"/>
     </row>
-    <row r="43" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A43" s="270" t="s">
+    <row r="43" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A43" s="269" t="s">
         <v>2349</v>
       </c>
       <c r="B43" s="244"/>
@@ -44439,8 +44425,8 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A44" s="270" t="s">
+    <row r="44" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A44" s="269" t="s">
         <v>2349</v>
       </c>
       <c r="B44" s="244"/>
@@ -44486,8 +44472,8 @@
       </c>
       <c r="AA44" s="249"/>
     </row>
-    <row r="45" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A45" s="270" t="s">
+    <row r="45" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A45" s="269" t="s">
         <v>2350</v>
       </c>
       <c r="B45" s="244"/>
@@ -44547,8 +44533,8 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A46" s="270" t="s">
+    <row r="46" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A46" s="269" t="s">
         <v>2350</v>
       </c>
       <c r="B46" s="244"/>
@@ -44594,8 +44580,8 @@
       </c>
       <c r="AA46" s="249"/>
     </row>
-    <row r="47" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A47" s="270" t="s">
+    <row r="47" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A47" s="269" t="s">
         <v>2354</v>
       </c>
       <c r="B47" s="244"/>
@@ -44604,7 +44590,7 @@
       </c>
       <c r="D47" s="244"/>
       <c r="E47" s="244"/>
-      <c r="F47" s="273"/>
+      <c r="F47" s="272"/>
       <c r="G47" s="244"/>
       <c r="H47" s="244"/>
       <c r="I47" s="244"/>
@@ -44631,8 +44617,8 @@
       </c>
       <c r="AA47" s="252"/>
     </row>
-    <row r="48" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A48" s="270" t="s">
+    <row r="48" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A48" s="269" t="s">
         <v>2355</v>
       </c>
       <c r="B48" s="244"/>
@@ -44641,7 +44627,7 @@
       </c>
       <c r="D48" s="244"/>
       <c r="E48" s="244"/>
-      <c r="F48" s="274"/>
+      <c r="F48" s="273"/>
       <c r="G48" s="244"/>
       <c r="H48" s="161"/>
       <c r="I48" s="244"/>
@@ -44668,8 +44654,8 @@
       </c>
       <c r="AA48" s="249"/>
     </row>
-    <row r="49" spans="1:27" ht="54.95" customHeight="1" thickBot="1">
-      <c r="A49" s="275" t="s">
+    <row r="49" spans="1:27" ht="54.9" customHeight="1" thickBot="1">
+      <c r="A49" s="274" t="s">
         <v>2449</v>
       </c>
       <c r="B49" s="260"/>
@@ -44678,7 +44664,7 @@
       </c>
       <c r="D49" s="260"/>
       <c r="E49" s="260"/>
-      <c r="F49" s="276"/>
+      <c r="F49" s="275"/>
       <c r="G49" s="260"/>
       <c r="H49" s="261"/>
       <c r="I49" s="260"/>
@@ -44705,8 +44691,8 @@
       </c>
       <c r="AA49" s="262"/>
     </row>
-    <row r="50" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A50" s="277" t="s">
+    <row r="50" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A50" s="276" t="s">
         <v>2364</v>
       </c>
       <c r="B50" s="253" t="s">
@@ -44758,8 +44744,8 @@
       </c>
       <c r="AA50" s="254"/>
     </row>
-    <row r="51" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A51" s="278" t="s">
+    <row r="51" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A51" s="277" t="s">
         <v>2363</v>
       </c>
       <c r="B51" s="244"/>
@@ -44807,8 +44793,8 @@
       </c>
       <c r="AA51" s="252"/>
     </row>
-    <row r="52" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A52" s="278" t="s">
+    <row r="52" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A52" s="277" t="s">
         <v>2364</v>
       </c>
       <c r="B52" s="244"/>
@@ -44856,8 +44842,8 @@
       </c>
       <c r="AA52" s="252"/>
     </row>
-    <row r="53" spans="1:27" s="3" customFormat="1" ht="54.95" customHeight="1">
-      <c r="A53" s="278" t="s">
+    <row r="53" spans="1:27" s="3" customFormat="1" ht="54.9" customHeight="1">
+      <c r="A53" s="277" t="s">
         <v>2366</v>
       </c>
       <c r="B53" s="244"/>
@@ -44913,8 +44899,8 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="54" spans="1:27" s="3" customFormat="1" ht="54.95" customHeight="1">
-      <c r="A54" s="278" t="s">
+    <row r="54" spans="1:27" s="3" customFormat="1" ht="54.9" customHeight="1">
+      <c r="A54" s="277" t="s">
         <v>2366</v>
       </c>
       <c r="B54" s="244"/>
@@ -44925,7 +44911,7 @@
       <c r="E54" s="244" t="s">
         <v>2368</v>
       </c>
-      <c r="F54" s="274" t="s">
+      <c r="F54" s="273" t="s">
         <v>2470</v>
       </c>
       <c r="G54" s="244" t="s">
@@ -44982,8 +44968,8 @@
         <v>2373</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A55" s="278" t="s">
+    <row r="55" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A55" s="277" t="s">
         <v>2366</v>
       </c>
       <c r="B55" s="244"/>
@@ -44994,7 +44980,7 @@
       <c r="E55" s="244" t="s">
         <v>2369</v>
       </c>
-      <c r="F55" s="274" t="s">
+      <c r="F55" s="273" t="s">
         <v>2471</v>
       </c>
       <c r="G55" s="244" t="s">
@@ -45051,8 +45037,8 @@
         <v>2405</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="54.95" customHeight="1" thickBot="1">
-      <c r="A56" s="279" t="s">
+    <row r="56" spans="1:27" ht="54.9" customHeight="1" thickBot="1">
+      <c r="A56" s="278" t="s">
         <v>2374</v>
       </c>
       <c r="B56" s="245"/>
@@ -45088,8 +45074,8 @@
       </c>
       <c r="AA56" s="255"/>
     </row>
-    <row r="57" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A57" s="280" t="s">
+    <row r="57" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A57" s="279" t="s">
         <v>2388</v>
       </c>
       <c r="B57" s="253" t="s">
@@ -45147,8 +45133,8 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A58" s="281" t="s">
+    <row r="58" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A58" s="280" t="s">
         <v>1375</v>
       </c>
       <c r="B58" s="244"/>
@@ -45202,8 +45188,8 @@
         <v>2373</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A59" s="281" t="s">
+    <row r="59" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A59" s="280" t="s">
         <v>1375</v>
       </c>
       <c r="B59" s="244"/>
@@ -45257,8 +45243,8 @@
         <v>2405</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A60" s="281" t="s">
+    <row r="60" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A60" s="280" t="s">
         <v>2389</v>
       </c>
       <c r="B60" s="244"/>
@@ -45294,8 +45280,8 @@
       </c>
       <c r="AA60" s="252"/>
     </row>
-    <row r="61" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A61" s="281" t="s">
+    <row r="61" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A61" s="280" t="s">
         <v>2390</v>
       </c>
       <c r="B61" s="244"/>
@@ -45331,8 +45317,8 @@
       </c>
       <c r="AA61" s="252"/>
     </row>
-    <row r="62" spans="1:27" ht="54.95" customHeight="1" thickBot="1">
-      <c r="A62" s="282" t="s">
+    <row r="62" spans="1:27" ht="54.9" customHeight="1" thickBot="1">
+      <c r="A62" s="281" t="s">
         <v>2391</v>
       </c>
       <c r="B62" s="245"/>
@@ -45368,8 +45354,8 @@
       </c>
       <c r="AA62" s="255"/>
     </row>
-    <row r="63" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A63" s="277" t="s">
+    <row r="63" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A63" s="276" t="s">
         <v>2407</v>
       </c>
       <c r="B63" s="253" t="s">
@@ -45384,7 +45370,7 @@
       <c r="E63" s="253" t="s">
         <v>2413</v>
       </c>
-      <c r="F63" s="283" t="s">
+      <c r="F63" s="282" t="s">
         <v>2472</v>
       </c>
       <c r="G63" s="253" t="s">
@@ -45439,8 +45425,8 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A64" s="281" t="s">
+    <row r="64" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A64" s="280" t="s">
         <v>2407</v>
       </c>
       <c r="B64" s="244"/>
@@ -45451,7 +45437,7 @@
       <c r="E64" s="244" t="s">
         <v>2414</v>
       </c>
-      <c r="F64" s="274" t="s">
+      <c r="F64" s="273" t="s">
         <v>2473</v>
       </c>
       <c r="G64" s="244"/>
@@ -45500,8 +45486,8 @@
         <v>2373</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A65" s="281" t="s">
+    <row r="65" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A65" s="280" t="s">
         <v>2407</v>
       </c>
       <c r="B65" s="244"/>
@@ -45512,7 +45498,7 @@
       <c r="E65" s="244" t="s">
         <v>2415</v>
       </c>
-      <c r="F65" s="274" t="s">
+      <c r="F65" s="273" t="s">
         <v>2474</v>
       </c>
       <c r="G65" s="244"/>
@@ -45563,8 +45549,8 @@
         <v>2405</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A66" s="281" t="s">
+    <row r="66" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A66" s="280" t="s">
         <v>2409</v>
       </c>
       <c r="B66" s="244"/>
@@ -45600,8 +45586,8 @@
       </c>
       <c r="AA66" s="252"/>
     </row>
-    <row r="67" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A67" s="281" t="s">
+    <row r="67" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A67" s="280" t="s">
         <v>2410</v>
       </c>
       <c r="B67" s="244"/>
@@ -45637,8 +45623,8 @@
       </c>
       <c r="AA67" s="252"/>
     </row>
-    <row r="68" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A68" s="281" t="s">
+    <row r="68" spans="1:27" ht="54.9" customHeight="1">
+      <c r="A68" s="280" t="s">
         <v>2411</v>
       </c>
       <c r="B68" s="244"/>
@@ -45674,8 +45660,8 @@
       </c>
       <c r="AA68" s="252"/>
     </row>
-    <row r="69" spans="1:27" ht="54.95" customHeight="1" thickBot="1">
-      <c r="A69" s="282" t="s">
+    <row r="69" spans="1:27" ht="54.9" customHeight="1" thickBot="1">
+      <c r="A69" s="281" t="s">
         <v>2412</v>
       </c>
       <c r="B69" s="245"/>
@@ -45711,7 +45697,7 @@
       </c>
       <c r="AA69" s="255"/>
     </row>
-    <row r="70" spans="1:27" ht="54.95" customHeight="1">
+    <row r="70" spans="1:27" ht="54.9" customHeight="1">
       <c r="A70" s="256" t="s">
         <v>2442</v>
       </c>
@@ -45727,7 +45713,7 @@
       <c r="E70" s="256" t="s">
         <v>2540</v>
       </c>
-      <c r="F70" s="284" t="s">
+      <c r="F70" s="283" t="s">
         <v>2541</v>
       </c>
       <c r="G70" s="256"/>
@@ -45770,7 +45756,7 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="54.95" customHeight="1">
+    <row r="71" spans="1:27" ht="54.9" customHeight="1">
       <c r="A71" s="256" t="s">
         <v>2542</v>
       </c>
@@ -45807,7 +45793,7 @@
       </c>
       <c r="AA71" s="244"/>
     </row>
-    <row r="72" spans="1:27" ht="54.95" customHeight="1">
+    <row r="72" spans="1:27" ht="54.9" customHeight="1">
       <c r="A72" s="244"/>
       <c r="B72" s="244"/>
       <c r="C72" s="244"/>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erang\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64ABE3F6-2A0B-4E17-BA8F-9448823AF3FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{126D2177-7889-4AE9-83B3-929CF329F742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -12922,10 +12922,6 @@
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
   <si>
-    <t>14~18</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
     <t>Gain</t>
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
@@ -13429,339 +13425,343 @@
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
   <si>
-    <t>주사위 14 이상
+    <t>예측 : 앞면 or 뒷면
+레드 더스티움 25 획득</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>예측 : 앞면 or 뒷면
+레드 더스티움 30 획득</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>예측 : 앞면 or 뒷면
+레드 더스티움 35 획득</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>레드 더스티움 20 소모
+레어~에픽 기억 발현</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>레드 더스티움 45 소모
+에픽~유니크 기억 발현</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>전체 생명력 5 감소
+무작위 레어~유니크 유물 획득</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>예측 : 앞면 or 뒷면
+무작위 유물 획득</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>침식도 20 증가
+무작위 일반~유니크 유물 획득</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>Battlemap_T_01</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>Map_25</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>Map_26</t>
+  </si>
+  <si>
+    <t>Map_26</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tutorial1</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tutorial</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>Map_27</t>
+  </si>
+  <si>
+    <t>Tutorial2</t>
+  </si>
+  <si>
+    <t>Tutorial3</t>
+  </si>
+  <si>
+    <t>Battlemap_T_02</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>튜토리얼(드라우그, 블라이트)</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>튜토리얼ID</t>
+  </si>
+  <si>
+    <t>진행순서</t>
+  </si>
+  <si>
+    <t>시작 파티</t>
+  </si>
+  <si>
+    <t>시작 침식도</t>
+  </si>
+  <si>
+    <t>시작 생명력(%)</t>
+  </si>
+  <si>
+    <t>몬스터 생성 지연</t>
+  </si>
+  <si>
+    <t>대화 캐릭터ID</t>
+  </si>
+  <si>
+    <t>문구 키</t>
+  </si>
+  <si>
+    <t>한국어 대사/안내</t>
+  </si>
+  <si>
+    <t>넘김 방식</t>
+  </si>
+  <si>
+    <t>강조 UI</t>
+  </si>
+  <si>
+    <t>TutorialId</t>
+  </si>
+  <si>
+    <t>Order</t>
+  </si>
+  <si>
+    <t>StartParty</t>
+  </si>
+  <si>
+    <t>InitialErosion</t>
+  </si>
+  <si>
+    <t>InitialHpPercent</t>
+  </si>
+  <si>
+    <t>DeferMonsterSpawn</t>
+  </si>
+  <si>
+    <t>SpeakerId</t>
+  </si>
+  <si>
+    <t>TextKey</t>
+  </si>
+  <si>
+    <t>TextKO</t>
+  </si>
+  <si>
+    <t>Advance</t>
+  </si>
+  <si>
+    <t>HighlightTarget</t>
+  </si>
+  <si>
+    <t>Tutorial_01</t>
+  </si>
+  <si>
+    <t>Char_01,Char_02</t>
+  </si>
+  <si>
+    <t>Arrival</t>
+  </si>
+  <si>
+    <t>tutorial.t01.arrival</t>
+  </si>
+  <si>
+    <t>거점으로 향하는 길</t>
+  </si>
+  <si>
+    <t>Auto</t>
+  </si>
+  <si>
+    <t>Dialogue</t>
+  </si>
+  <si>
+    <t>tutorial.t01.dialogue.01</t>
+  </si>
+  <si>
+    <t>ClickAny</t>
+  </si>
+  <si>
+    <t>tutorial.t01.dialogue.02</t>
+  </si>
+  <si>
+    <t>tutorial.t01.dialogue.03</t>
+  </si>
+  <si>
+    <t>Guide</t>
+  </si>
+  <si>
+    <t>tutorial.t01.erosion.01</t>
+  </si>
+  <si>
+    <t>Erosion</t>
+  </si>
+  <si>
+    <t>tutorial.t01.erosion.02</t>
+  </si>
+  <si>
+    <t>tutorial.t01.erosion.03</t>
+  </si>
+  <si>
+    <t>SpawnMonsters</t>
+  </si>
+  <si>
+    <t>tutorial.t01.dialogue.04</t>
+  </si>
+  <si>
+    <t>tutorial.t01.dialogue.05</t>
+  </si>
+  <si>
+    <t>70,65</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>출력</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>Text output</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialogbox</t>
+  </si>
+  <si>
+    <t>TutorialTooltip</t>
+  </si>
+  <si>
+    <t>BattleMapIntroText</t>
+  </si>
+  <si>
+    <t>탐사 중에는 침식도가 누적됩니다.</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>하하, 이러다 거점에 도착하기도 전에 지치겠어!</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>불필요한 체력 소모는 피하시죠. 거점까지 얼마 남지 않았습니다.</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>후아! 생각보다 먼 길인데? 슬슬 몸이 무거워지는걸.</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>변이체군요. 아무래도 그냥 지나가긴 어렵겠습니다.</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>좋아! 그럼 녀석부터 처리하고 가자!</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>뜻밖의 합류</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>함께 휴식한다.</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>전체 생명력 15 회복
+헤이즈 합류</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>Event_T_01_A</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>새로운 방에 진입하면 3, 피해를 받으면 1,
+전투불능이 되면 10의 침식도가 증가합니다.</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>침식도가 최대치인 100에 도달하면
+매 턴 생명력이 10씩 감소합니다.</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>tutorial.prompt.click_any</t>
+  </si>
+  <si>
+    <t>완료 안내 키</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>CompleteTextKey</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>완료 안내</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>CompleteTextKO</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>아무 곳이나 클릭하여 계속</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>"잠시 휴식을 취한 일행은 기운을 되찾았다."</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>event_tutorial</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>"거점으로 향하는 길목, 한 탐사자가 휴식하고 있다."</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>Common:47,Rare:38,Epic:12,Unique:3</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>event_choice_04_success</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>event_choice_03_success</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>event_choice_04_failure</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>MemoryDropChance</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>주사위 12 이상
 무작위 에픽 유물 획득
 실패 : 생명력 5 감소</t>
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
   <si>
-    <t>예측 : 앞면 or 뒷면
-레드 더스티움 25 획득</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>예측 : 앞면 or 뒷면
-레드 더스티움 30 획득</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>예측 : 앞면 or 뒷면
-레드 더스티움 35 획득</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>레드 더스티움 20 소모
-레어~에픽 기억 발현</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>레드 더스티움 45 소모
-에픽~유니크 기억 발현</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>전체 생명력 5 감소
-무작위 레어~유니크 유물 획득</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>예측 : 앞면 or 뒷면
-무작위 유물 획득</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>침식도 20 증가
-무작위 일반~유니크 유물 획득</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>Battlemap_T_01</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>Map_25</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>Map_26</t>
-  </si>
-  <si>
-    <t>Map_26</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tutorial1</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tutorial</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>Map_27</t>
-  </si>
-  <si>
-    <t>Tutorial2</t>
-  </si>
-  <si>
-    <t>Tutorial3</t>
-  </si>
-  <si>
-    <t>Battlemap_T_02</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>튜토리얼(드라우그, 블라이트)</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>튜토리얼ID</t>
-  </si>
-  <si>
-    <t>진행순서</t>
-  </si>
-  <si>
-    <t>시작 파티</t>
-  </si>
-  <si>
-    <t>시작 침식도</t>
-  </si>
-  <si>
-    <t>시작 생명력(%)</t>
-  </si>
-  <si>
-    <t>몬스터 생성 지연</t>
-  </si>
-  <si>
-    <t>대화 캐릭터ID</t>
-  </si>
-  <si>
-    <t>문구 키</t>
-  </si>
-  <si>
-    <t>한국어 대사/안내</t>
-  </si>
-  <si>
-    <t>넘김 방식</t>
-  </si>
-  <si>
-    <t>강조 UI</t>
-  </si>
-  <si>
-    <t>TutorialId</t>
-  </si>
-  <si>
-    <t>Order</t>
-  </si>
-  <si>
-    <t>StartParty</t>
-  </si>
-  <si>
-    <t>InitialErosion</t>
-  </si>
-  <si>
-    <t>InitialHpPercent</t>
-  </si>
-  <si>
-    <t>DeferMonsterSpawn</t>
-  </si>
-  <si>
-    <t>SpeakerId</t>
-  </si>
-  <si>
-    <t>TextKey</t>
-  </si>
-  <si>
-    <t>TextKO</t>
-  </si>
-  <si>
-    <t>Advance</t>
-  </si>
-  <si>
-    <t>HighlightTarget</t>
-  </si>
-  <si>
-    <t>Tutorial_01</t>
-  </si>
-  <si>
-    <t>Char_01,Char_02</t>
-  </si>
-  <si>
-    <t>Arrival</t>
-  </si>
-  <si>
-    <t>tutorial.t01.arrival</t>
-  </si>
-  <si>
-    <t>거점으로 향하는 길</t>
-  </si>
-  <si>
-    <t>Auto</t>
-  </si>
-  <si>
-    <t>Dialogue</t>
-  </si>
-  <si>
-    <t>tutorial.t01.dialogue.01</t>
-  </si>
-  <si>
-    <t>ClickAny</t>
-  </si>
-  <si>
-    <t>tutorial.t01.dialogue.02</t>
-  </si>
-  <si>
-    <t>tutorial.t01.dialogue.03</t>
-  </si>
-  <si>
-    <t>Guide</t>
-  </si>
-  <si>
-    <t>tutorial.t01.erosion.01</t>
-  </si>
-  <si>
-    <t>Erosion</t>
-  </si>
-  <si>
-    <t>tutorial.t01.erosion.02</t>
-  </si>
-  <si>
-    <t>tutorial.t01.erosion.03</t>
-  </si>
-  <si>
-    <t>SpawnMonsters</t>
-  </si>
-  <si>
-    <t>tutorial.t01.dialogue.04</t>
-  </si>
-  <si>
-    <t>tutorial.t01.dialogue.05</t>
-  </si>
-  <si>
-    <t>70,65</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>출력</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>Text output</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dialogbox</t>
-  </si>
-  <si>
-    <t>TutorialTooltip</t>
-  </si>
-  <si>
-    <t>BattleMapIntroText</t>
-  </si>
-  <si>
-    <t>탐사 중에는 침식도가 누적됩니다.</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>하하, 이러다 거점에 도착하기도 전에 지치겠어!</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>불필요한 체력 소모는 피하시죠. 거점까지 얼마 남지 않았습니다.</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>후아! 생각보다 먼 길인데? 슬슬 몸이 무거워지는걸.</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>변이체군요. 아무래도 그냥 지나가긴 어렵겠습니다.</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>좋아! 그럼 녀석부터 처리하고 가자!</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>뜻밖의 합류</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>함께 휴식한다.</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>전체 생명력 15 회복
-헤이즈 합류</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>Event_T_01_A</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>새로운 방에 진입하면 3, 피해를 받으면 1,
-전투불능이 되면 10의 침식도가 증가합니다.</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>침식도가 최대치인 100에 도달하면
-매 턴 생명력이 10씩 감소합니다.</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>tutorial.prompt.click_any</t>
-  </si>
-  <si>
-    <t>완료 안내 키</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>CompleteTextKey</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>완료 안내</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>CompleteTextKO</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>아무 곳이나 클릭하여 계속</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>"잠시 휴식을 취한 일행은 기운을 되찾았다."</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>event_tutorial</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>"거점으로 향하는 길목, 한 탐사자가 휴식하고 있다."</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>Common:47,Rare:38,Epic:12,Unique:3</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>event_choice_04_success</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>event_choice_03_success</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>event_choice_04_failure</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>MemoryDropChance</t>
+    <t>12~18</t>
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
 </sst>
@@ -26742,487 +26742,487 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="263" t="s">
-        <v>2485</v>
+        <v>2483</v>
       </c>
       <c r="B1" s="263" t="s">
-        <v>2486</v>
+        <v>2484</v>
       </c>
       <c r="C1" s="263" t="s">
         <v>1299</v>
       </c>
       <c r="D1" s="263" t="s">
+        <v>2485</v>
+      </c>
+      <c r="E1" s="263" t="s">
+        <v>2486</v>
+      </c>
+      <c r="F1" s="263" t="s">
         <v>2487</v>
       </c>
-      <c r="E1" s="263" t="s">
+      <c r="G1" s="263" t="s">
         <v>2488</v>
-      </c>
-      <c r="F1" s="263" t="s">
-        <v>2489</v>
-      </c>
-      <c r="G1" s="263" t="s">
-        <v>2490</v>
       </c>
       <c r="H1" s="263" t="s">
         <v>1955</v>
       </c>
       <c r="I1" s="263" t="s">
+        <v>2489</v>
+      </c>
+      <c r="J1" s="263" t="s">
+        <v>2525</v>
+      </c>
+      <c r="K1" s="263" t="s">
+        <v>2490</v>
+      </c>
+      <c r="L1" s="264" t="s">
         <v>2491</v>
       </c>
-      <c r="J1" s="263" t="s">
-        <v>2527</v>
-      </c>
-      <c r="K1" s="263" t="s">
+      <c r="M1" s="263" t="s">
         <v>2492</v>
       </c>
-      <c r="L1" s="264" t="s">
+      <c r="N1" s="263" t="s">
         <v>2493</v>
       </c>
-      <c r="M1" s="263" t="s">
-        <v>2494</v>
-      </c>
-      <c r="N1" s="263" t="s">
-        <v>2495</v>
-      </c>
       <c r="O1" s="263" t="s">
+        <v>2543</v>
+      </c>
+      <c r="P1" s="263" t="s">
         <v>2545</v>
-      </c>
-      <c r="P1" s="263" t="s">
-        <v>2547</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="263" t="s">
-        <v>2496</v>
+        <v>2494</v>
       </c>
       <c r="B2" s="263" t="s">
-        <v>2497</v>
+        <v>2495</v>
       </c>
       <c r="C2" s="263" t="s">
         <v>1305</v>
       </c>
       <c r="D2" s="263" t="s">
+        <v>2496</v>
+      </c>
+      <c r="E2" s="263" t="s">
+        <v>2497</v>
+      </c>
+      <c r="F2" s="263" t="s">
         <v>2498</v>
       </c>
-      <c r="E2" s="263" t="s">
+      <c r="G2" s="263" t="s">
         <v>2499</v>
-      </c>
-      <c r="F2" s="263" t="s">
-        <v>2500</v>
-      </c>
-      <c r="G2" s="263" t="s">
-        <v>2501</v>
       </c>
       <c r="H2" s="263" t="s">
         <v>147</v>
       </c>
       <c r="I2" s="263" t="s">
+        <v>2500</v>
+      </c>
+      <c r="J2" s="263" t="s">
+        <v>2526</v>
+      </c>
+      <c r="K2" s="263" t="s">
+        <v>2501</v>
+      </c>
+      <c r="L2" s="264" t="s">
         <v>2502</v>
       </c>
-      <c r="J2" s="263" t="s">
-        <v>2528</v>
-      </c>
-      <c r="K2" s="263" t="s">
+      <c r="M2" s="263" t="s">
         <v>2503</v>
       </c>
-      <c r="L2" s="264" t="s">
+      <c r="N2" s="263" t="s">
         <v>2504</v>
       </c>
-      <c r="M2" s="263" t="s">
-        <v>2505</v>
-      </c>
-      <c r="N2" s="263" t="s">
-        <v>2506</v>
-      </c>
       <c r="O2" s="263" t="s">
+        <v>2544</v>
+      </c>
+      <c r="P2" s="263" t="s">
         <v>2546</v>
-      </c>
-      <c r="P2" s="263" t="s">
-        <v>2548</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="140" t="s">
-        <v>2507</v>
+        <v>2505</v>
       </c>
       <c r="B3" s="140">
         <v>1</v>
       </c>
       <c r="C3" s="140" t="s">
-        <v>2476</v>
+        <v>2474</v>
       </c>
       <c r="D3" s="140" t="s">
-        <v>2508</v>
+        <v>2506</v>
       </c>
       <c r="E3" s="140">
         <v>42</v>
       </c>
       <c r="F3" s="140" t="s">
-        <v>2526</v>
+        <v>2524</v>
       </c>
       <c r="G3" s="140">
         <v>1</v>
       </c>
       <c r="H3" s="140" t="s">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="I3" s="140"/>
       <c r="J3" s="140" t="s">
-        <v>2531</v>
+        <v>2529</v>
       </c>
       <c r="K3" s="140" t="s">
+        <v>2508</v>
+      </c>
+      <c r="L3" s="141" t="s">
+        <v>2509</v>
+      </c>
+      <c r="M3" s="140" t="s">
         <v>2510</v>
-      </c>
-      <c r="L3" s="141" t="s">
-        <v>2511</v>
-      </c>
-      <c r="M3" s="140" t="s">
-        <v>2512</v>
       </c>
       <c r="N3" s="140"/>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="140" t="s">
-        <v>2507</v>
+        <v>2505</v>
       </c>
       <c r="B4" s="140">
         <v>2</v>
       </c>
       <c r="C4" s="140" t="s">
-        <v>2476</v>
+        <v>2474</v>
       </c>
       <c r="D4" s="140"/>
       <c r="E4" s="140"/>
       <c r="F4" s="140"/>
       <c r="G4" s="140"/>
       <c r="H4" s="140" t="s">
-        <v>2513</v>
+        <v>2511</v>
       </c>
       <c r="I4" s="140" t="s">
         <v>46</v>
       </c>
       <c r="J4" s="140" t="s">
-        <v>2529</v>
+        <v>2527</v>
       </c>
       <c r="K4" s="140" t="s">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="L4" s="141" t="s">
-        <v>2535</v>
+        <v>2533</v>
       </c>
       <c r="M4" s="140" t="s">
-        <v>2515</v>
+        <v>2513</v>
       </c>
       <c r="N4" s="140"/>
       <c r="O4" t="s">
-        <v>2544</v>
+        <v>2542</v>
       </c>
       <c r="P4" t="s">
-        <v>2549</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="140" t="s">
-        <v>2507</v>
+        <v>2505</v>
       </c>
       <c r="B5" s="140">
         <v>3</v>
       </c>
       <c r="C5" s="140" t="s">
-        <v>2476</v>
+        <v>2474</v>
       </c>
       <c r="D5" s="140"/>
       <c r="E5" s="140"/>
       <c r="F5" s="140"/>
       <c r="G5" s="140"/>
       <c r="H5" s="140" t="s">
-        <v>2513</v>
+        <v>2511</v>
       </c>
       <c r="I5" s="140" t="s">
         <v>46</v>
       </c>
       <c r="J5" s="140" t="s">
-        <v>2529</v>
+        <v>2527</v>
       </c>
       <c r="K5" s="140" t="s">
-        <v>2516</v>
+        <v>2514</v>
       </c>
       <c r="L5" s="141" t="s">
-        <v>2533</v>
+        <v>2531</v>
       </c>
       <c r="M5" s="140" t="s">
-        <v>2515</v>
+        <v>2513</v>
       </c>
       <c r="N5" s="140"/>
       <c r="O5" t="s">
-        <v>2544</v>
+        <v>2542</v>
       </c>
       <c r="P5" t="s">
-        <v>2549</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="140" t="s">
-        <v>2507</v>
+        <v>2505</v>
       </c>
       <c r="B6" s="140">
         <v>4</v>
       </c>
       <c r="C6" s="140" t="s">
-        <v>2476</v>
+        <v>2474</v>
       </c>
       <c r="D6" s="140"/>
       <c r="E6" s="140"/>
       <c r="F6" s="140"/>
       <c r="G6" s="140"/>
       <c r="H6" s="140" t="s">
-        <v>2513</v>
+        <v>2511</v>
       </c>
       <c r="I6" s="140" t="s">
         <v>63</v>
       </c>
       <c r="J6" s="140" t="s">
-        <v>2529</v>
+        <v>2527</v>
       </c>
       <c r="K6" s="140" t="s">
-        <v>2517</v>
+        <v>2515</v>
       </c>
       <c r="L6" s="141" t="s">
-        <v>2534</v>
+        <v>2532</v>
       </c>
       <c r="M6" s="140" t="s">
-        <v>2515</v>
+        <v>2513</v>
       </c>
       <c r="N6" s="140"/>
       <c r="O6" t="s">
-        <v>2544</v>
+        <v>2542</v>
       </c>
       <c r="P6" t="s">
-        <v>2549</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="140" t="s">
-        <v>2507</v>
+        <v>2505</v>
       </c>
       <c r="B7" s="140">
         <v>5</v>
       </c>
       <c r="C7" s="140" t="s">
-        <v>2476</v>
+        <v>2474</v>
       </c>
       <c r="D7" s="140"/>
       <c r="E7" s="140"/>
       <c r="F7" s="140"/>
       <c r="G7" s="140"/>
       <c r="H7" s="140" t="s">
-        <v>2518</v>
+        <v>2516</v>
       </c>
       <c r="I7" s="140"/>
       <c r="J7" s="140" t="s">
+        <v>2528</v>
+      </c>
+      <c r="K7" s="140" t="s">
+        <v>2517</v>
+      </c>
+      <c r="L7" s="141" t="s">
         <v>2530</v>
       </c>
-      <c r="K7" s="140" t="s">
-        <v>2519</v>
-      </c>
-      <c r="L7" s="141" t="s">
-        <v>2532</v>
-      </c>
       <c r="M7" s="140" t="s">
-        <v>2515</v>
+        <v>2513</v>
       </c>
       <c r="N7" s="140" t="s">
-        <v>2520</v>
+        <v>2518</v>
       </c>
       <c r="O7" t="s">
-        <v>2544</v>
+        <v>2542</v>
       </c>
       <c r="P7" t="s">
-        <v>2549</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="33">
       <c r="A8" s="140" t="s">
-        <v>2507</v>
+        <v>2505</v>
       </c>
       <c r="B8" s="140">
         <v>6</v>
       </c>
       <c r="C8" s="140" t="s">
-        <v>2476</v>
+        <v>2474</v>
       </c>
       <c r="D8" s="140"/>
       <c r="E8" s="140"/>
       <c r="F8" s="140"/>
       <c r="G8" s="140"/>
       <c r="H8" s="140" t="s">
-        <v>2518</v>
+        <v>2516</v>
       </c>
       <c r="I8" s="140"/>
       <c r="J8" s="140" t="s">
-        <v>2530</v>
+        <v>2528</v>
       </c>
       <c r="K8" s="140" t="s">
-        <v>2521</v>
+        <v>2519</v>
       </c>
       <c r="L8" s="265" t="s">
+        <v>2540</v>
+      </c>
+      <c r="M8" s="140" t="s">
+        <v>2513</v>
+      </c>
+      <c r="N8" s="140" t="s">
+        <v>2518</v>
+      </c>
+      <c r="O8" t="s">
         <v>2542</v>
       </c>
-      <c r="M8" s="140" t="s">
-        <v>2515</v>
-      </c>
-      <c r="N8" s="140" t="s">
-        <v>2520</v>
-      </c>
-      <c r="O8" t="s">
-        <v>2544</v>
-      </c>
       <c r="P8" t="s">
-        <v>2549</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="33">
       <c r="A9" s="140" t="s">
-        <v>2507</v>
+        <v>2505</v>
       </c>
       <c r="B9" s="140">
         <v>7</v>
       </c>
       <c r="C9" s="140" t="s">
-        <v>2476</v>
+        <v>2474</v>
       </c>
       <c r="D9" s="140"/>
       <c r="E9" s="140"/>
       <c r="F9" s="140"/>
       <c r="G9" s="140"/>
       <c r="H9" s="140" t="s">
-        <v>2518</v>
+        <v>2516</v>
       </c>
       <c r="I9" s="140"/>
       <c r="J9" s="140" t="s">
-        <v>2530</v>
+        <v>2528</v>
       </c>
       <c r="K9" s="140" t="s">
-        <v>2522</v>
+        <v>2520</v>
       </c>
       <c r="L9" s="265" t="s">
-        <v>2543</v>
+        <v>2541</v>
       </c>
       <c r="M9" s="140" t="s">
-        <v>2515</v>
+        <v>2513</v>
       </c>
       <c r="N9" s="140" t="s">
-        <v>2520</v>
+        <v>2518</v>
       </c>
       <c r="O9" t="s">
-        <v>2544</v>
+        <v>2542</v>
       </c>
       <c r="P9" t="s">
-        <v>2549</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="140" t="s">
-        <v>2507</v>
+        <v>2505</v>
       </c>
       <c r="B10" s="140">
         <v>8</v>
       </c>
       <c r="C10" s="140" t="s">
-        <v>2476</v>
+        <v>2474</v>
       </c>
       <c r="D10" s="140"/>
       <c r="E10" s="140"/>
       <c r="F10" s="140"/>
       <c r="G10" s="140"/>
       <c r="H10" s="140" t="s">
-        <v>2523</v>
+        <v>2521</v>
       </c>
       <c r="I10" s="140"/>
       <c r="J10" s="140"/>
       <c r="K10" s="140"/>
       <c r="M10" s="140" t="s">
-        <v>2512</v>
+        <v>2510</v>
       </c>
       <c r="N10" s="140"/>
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="140" t="s">
-        <v>2507</v>
+        <v>2505</v>
       </c>
       <c r="B11" s="140">
         <v>9</v>
       </c>
       <c r="C11" s="140" t="s">
-        <v>2476</v>
+        <v>2474</v>
       </c>
       <c r="D11" s="140"/>
       <c r="E11" s="140"/>
       <c r="F11" s="140"/>
       <c r="G11" s="140"/>
       <c r="H11" s="140" t="s">
-        <v>2513</v>
+        <v>2511</v>
       </c>
       <c r="I11" s="140" t="s">
         <v>63</v>
       </c>
       <c r="J11" s="140" t="s">
-        <v>2529</v>
+        <v>2527</v>
       </c>
       <c r="K11" s="140" t="s">
-        <v>2524</v>
+        <v>2522</v>
       </c>
       <c r="L11" s="141" t="s">
-        <v>2536</v>
+        <v>2534</v>
       </c>
       <c r="M11" s="140" t="s">
-        <v>2515</v>
+        <v>2513</v>
       </c>
       <c r="N11" s="140"/>
       <c r="O11" t="s">
-        <v>2544</v>
+        <v>2542</v>
       </c>
       <c r="P11" t="s">
-        <v>2549</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="140" t="s">
-        <v>2507</v>
+        <v>2505</v>
       </c>
       <c r="B12" s="140">
         <v>10</v>
       </c>
       <c r="C12" s="140" t="s">
-        <v>2476</v>
+        <v>2474</v>
       </c>
       <c r="D12" s="140"/>
       <c r="E12" s="140"/>
       <c r="F12" s="140"/>
       <c r="G12" s="140"/>
       <c r="H12" s="140" t="s">
-        <v>2513</v>
+        <v>2511</v>
       </c>
       <c r="I12" s="140" t="s">
         <v>46</v>
       </c>
       <c r="J12" s="140" t="s">
-        <v>2529</v>
+        <v>2527</v>
       </c>
       <c r="K12" s="140" t="s">
-        <v>2525</v>
+        <v>2523</v>
       </c>
       <c r="L12" s="141" t="s">
-        <v>2537</v>
+        <v>2535</v>
       </c>
       <c r="M12" s="140" t="s">
-        <v>2515</v>
+        <v>2513</v>
       </c>
       <c r="N12" s="140"/>
       <c r="O12" t="s">
-        <v>2544</v>
+        <v>2542</v>
       </c>
       <c r="P12" t="s">
-        <v>2549</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -39948,7 +39948,7 @@
         <v>216</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>2433</v>
+        <v>2432</v>
       </c>
       <c r="E11" s="16">
         <v>0</v>
@@ -39974,7 +39974,7 @@
         <v>216</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>2435</v>
+        <v>2434</v>
       </c>
       <c r="E12" s="16">
         <v>0</v>
@@ -40306,7 +40306,7 @@
         <v>1371</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>2430</v>
+        <v>2429</v>
       </c>
       <c r="C25" s="16" t="s">
         <v>1356</v>
@@ -40315,7 +40315,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>2362</v>
+        <v>2361</v>
       </c>
       <c r="F25" s="16" t="s">
         <v>1314</v>
@@ -40329,7 +40329,7 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="16" t="s">
-        <v>2432</v>
+        <v>2431</v>
       </c>
       <c r="B26" s="16" t="s">
         <v>1372</v>
@@ -40355,10 +40355,10 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="16" t="s">
-        <v>2475</v>
+        <v>2473</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>2431</v>
+        <v>2430</v>
       </c>
       <c r="C27" s="16" t="s">
         <v>1356</v>
@@ -40367,7 +40367,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>2405</v>
+        <v>2404</v>
       </c>
       <c r="F27" s="16" t="s">
         <v>1314</v>
@@ -40381,16 +40381,16 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="16" t="s">
+        <v>2475</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>2476</v>
+      </c>
+      <c r="C28" s="16" t="s">
         <v>2477</v>
       </c>
-      <c r="B28" s="16" t="s">
-        <v>2478</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>2479</v>
-      </c>
       <c r="D28" s="16" t="s">
-        <v>2474</v>
+        <v>2472</v>
       </c>
       <c r="E28" s="16">
         <v>0</v>
@@ -40407,16 +40407,16 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="16" t="s">
-        <v>2480</v>
+        <v>2478</v>
       </c>
       <c r="B29" s="16" t="s">
+        <v>2479</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>2477</v>
+      </c>
+      <c r="D29" s="16" t="s">
         <v>2481</v>
-      </c>
-      <c r="C29" s="16" t="s">
-        <v>2479</v>
-      </c>
-      <c r="D29" s="16" t="s">
-        <v>2483</v>
       </c>
       <c r="E29" s="16">
         <v>0</v>
@@ -40436,16 +40436,16 @@
         <v>1377</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>2482</v>
+        <v>2480</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>2479</v>
+        <v>2477</v>
       </c>
       <c r="D30" s="16">
         <v>0</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>2441</v>
+        <v>2440</v>
       </c>
       <c r="F30" s="16" t="s">
         <v>1314</v>
@@ -40556,7 +40556,7 @@
         <v>1396</v>
       </c>
       <c r="H2" s="143" t="s">
-        <v>2557</v>
+        <v>2555</v>
       </c>
       <c r="I2" s="143" t="s">
         <v>1397</v>
@@ -41439,7 +41439,7 @@
     </row>
     <row r="24" spans="1:26" ht="17.25" customHeight="1">
       <c r="A24" s="233" t="s">
-        <v>2434</v>
+        <v>2433</v>
       </c>
       <c r="B24" s="187" t="s">
         <v>214</v>
@@ -41498,7 +41498,7 @@
     </row>
     <row r="25" spans="1:26" ht="17.25" thickBot="1">
       <c r="A25" s="151" t="s">
-        <v>2434</v>
+        <v>2433</v>
       </c>
       <c r="B25" s="152" t="s">
         <v>178</v>
@@ -41537,7 +41537,7 @@
     </row>
     <row r="26" spans="1:26">
       <c r="A26" s="144" t="s">
-        <v>2436</v>
+        <v>2435</v>
       </c>
       <c r="B26" s="145" t="s">
         <v>214</v>
@@ -41596,7 +41596,7 @@
     </row>
     <row r="27" spans="1:26" ht="17.25" customHeight="1" thickBot="1">
       <c r="A27" s="151" t="s">
-        <v>2436</v>
+        <v>2435</v>
       </c>
       <c r="B27" s="152" t="s">
         <v>185</v>
@@ -41635,7 +41635,7 @@
     </row>
     <row r="28" spans="1:26" ht="17.25" thickBot="1">
       <c r="A28" s="156" t="s">
-        <v>2437</v>
+        <v>2436</v>
       </c>
       <c r="B28" s="157" t="s">
         <v>222</v>
@@ -41689,7 +41689,7 @@
     </row>
     <row r="29" spans="1:26">
       <c r="A29" s="144" t="s">
-        <v>2438</v>
+        <v>2437</v>
       </c>
       <c r="B29" s="145" t="s">
         <v>202</v>
@@ -41743,7 +41743,7 @@
     </row>
     <row r="30" spans="1:26" ht="17.25" customHeight="1" thickBot="1">
       <c r="A30" s="151" t="s">
-        <v>2438</v>
+        <v>2437</v>
       </c>
       <c r="B30" s="152" t="s">
         <v>229</v>
@@ -41778,7 +41778,7 @@
     </row>
     <row r="31" spans="1:26">
       <c r="A31" s="144" t="s">
-        <v>2439</v>
+        <v>2438</v>
       </c>
       <c r="B31" s="145" t="s">
         <v>208</v>
@@ -41837,7 +41837,7 @@
     </row>
     <row r="32" spans="1:26" ht="17.25" customHeight="1" thickBot="1">
       <c r="A32" s="151" t="s">
-        <v>2439</v>
+        <v>2438</v>
       </c>
       <c r="B32" s="152" t="s">
         <v>229</v>
@@ -41876,7 +41876,7 @@
     </row>
     <row r="33" spans="1:26" ht="17.25" thickBot="1">
       <c r="A33" s="156" t="s">
-        <v>2440</v>
+        <v>2439</v>
       </c>
       <c r="B33" s="157" t="s">
         <v>2107</v>
@@ -41935,7 +41935,7 @@
     </row>
     <row r="34" spans="1:26" ht="17.25" customHeight="1">
       <c r="A34" s="187" t="s">
-        <v>2474</v>
+        <v>2472</v>
       </c>
       <c r="B34" s="187" t="s">
         <v>2110</v>
@@ -41994,7 +41994,7 @@
     </row>
     <row r="35" spans="1:26" ht="17.25" customHeight="1">
       <c r="A35" s="16" t="s">
-        <v>2483</v>
+        <v>2481</v>
       </c>
       <c r="B35" s="16" t="s">
         <v>2116</v>
@@ -42012,7 +42012,7 @@
         <v>-1</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>2484</v>
+        <v>2482</v>
       </c>
       <c r="H35" s="17">
         <v>0</v>
@@ -42053,7 +42053,7 @@
     </row>
     <row r="36" spans="1:26">
       <c r="A36" s="16" t="s">
-        <v>2483</v>
+        <v>2481</v>
       </c>
       <c r="B36" s="16" t="s">
         <v>2113</v>
@@ -42290,13 +42290,13 @@
         <v>2264</v>
       </c>
       <c r="U1" s="160" t="s">
+        <v>2340</v>
+      </c>
+      <c r="V1" s="160" t="s">
         <v>2341</v>
       </c>
-      <c r="V1" s="160" t="s">
+      <c r="W1" s="160" t="s">
         <v>2342</v>
-      </c>
-      <c r="W1" s="160" t="s">
-        <v>2343</v>
       </c>
       <c r="X1" s="160" t="s">
         <v>2206</v>
@@ -42376,10 +42376,10 @@
         <v>2199</v>
       </c>
       <c r="V2" s="243" t="s">
+        <v>2338</v>
+      </c>
+      <c r="W2" s="243" t="s">
         <v>2339</v>
-      </c>
-      <c r="W2" s="243" t="s">
-        <v>2340</v>
       </c>
       <c r="X2" s="243" t="s">
         <v>2202</v>
@@ -42429,7 +42429,7 @@
         <v>2239</v>
       </c>
       <c r="P3" s="241" t="s">
-        <v>2553</v>
+        <v>2551</v>
       </c>
       <c r="Q3" s="241">
         <v>1</v>
@@ -42488,7 +42488,7 @@
         <v>2240</v>
       </c>
       <c r="P4" s="161" t="s">
-        <v>2553</v>
+        <v>2551</v>
       </c>
       <c r="Q4" s="161">
         <v>1</v>
@@ -42547,7 +42547,7 @@
         <v>2241</v>
       </c>
       <c r="P5" s="161" t="s">
-        <v>2553</v>
+        <v>2551</v>
       </c>
       <c r="Q5" s="161">
         <v>1</v>
@@ -42728,7 +42728,7 @@
       </c>
       <c r="B9" s="161"/>
       <c r="C9" s="161" t="s">
-        <v>2384</v>
+        <v>2383</v>
       </c>
       <c r="D9" s="161"/>
       <c r="E9" s="161"/>
@@ -43132,7 +43132,7 @@
         <v>2289</v>
       </c>
       <c r="F18" s="161" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="G18" s="241" t="s">
         <v>2286</v>
@@ -43141,7 +43141,7 @@
         <v>2285</v>
       </c>
       <c r="I18" s="241" t="s">
-        <v>2424</v>
+        <v>2423</v>
       </c>
       <c r="J18" s="241" t="s">
         <v>2288</v>
@@ -43201,7 +43201,7 @@
         <v>2290</v>
       </c>
       <c r="F19" s="161" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
       <c r="G19" s="161" t="s">
         <v>2286</v>
@@ -43210,7 +43210,7 @@
         <v>2285</v>
       </c>
       <c r="I19" s="161" t="s">
-        <v>2425</v>
+        <v>2424</v>
       </c>
       <c r="J19" s="161" t="s">
         <v>2288</v>
@@ -43388,7 +43388,7 @@
       </c>
       <c r="B23" s="245"/>
       <c r="C23" s="240" t="s">
-        <v>2385</v>
+        <v>2384</v>
       </c>
       <c r="D23" s="240"/>
       <c r="E23" s="240"/>
@@ -43436,7 +43436,7 @@
         <v>2296</v>
       </c>
       <c r="F24" s="241" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
       <c r="G24" s="241"/>
       <c r="H24" s="241" t="s">
@@ -43497,7 +43497,7 @@
         <v>2297</v>
       </c>
       <c r="F25" s="161" t="s">
-        <v>2461</v>
+        <v>2460</v>
       </c>
       <c r="G25" s="161"/>
       <c r="H25" s="161" t="s">
@@ -43558,7 +43558,7 @@
         <v>2298</v>
       </c>
       <c r="F26" s="161" t="s">
-        <v>2462</v>
+        <v>2461</v>
       </c>
       <c r="G26" s="161"/>
       <c r="H26" s="161" t="s">
@@ -43771,7 +43771,7 @@
         <v>2317</v>
       </c>
       <c r="F31" s="241" t="s">
-        <v>2463</v>
+        <v>2462</v>
       </c>
       <c r="G31" s="241"/>
       <c r="H31" s="241" t="s">
@@ -43785,7 +43785,7 @@
         <v>2309</v>
       </c>
       <c r="N31" s="241" t="s">
-        <v>2338</v>
+        <v>2337</v>
       </c>
       <c r="O31" s="241" t="s">
         <v>2288</v>
@@ -43802,7 +43802,7 @@
         <v>2325</v>
       </c>
       <c r="U31" s="241" t="s">
-        <v>2344</v>
+        <v>2343</v>
       </c>
       <c r="V31" s="241" t="s">
         <v>2229</v>
@@ -43865,13 +43865,13 @@
         <v>1422</v>
       </c>
       <c r="Y32" s="161" t="s">
-        <v>2554</v>
+        <v>2552</v>
       </c>
       <c r="Z32" s="161" t="s">
         <v>1422</v>
       </c>
       <c r="AA32" s="249" t="s">
-        <v>2556</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="33" spans="1:27" ht="54.95" customHeight="1">
@@ -43889,7 +43889,7 @@
         <v>2321</v>
       </c>
       <c r="F33" s="161" t="s">
-        <v>2464</v>
+        <v>2463</v>
       </c>
       <c r="G33" s="161"/>
       <c r="H33" s="161" t="s">
@@ -43903,7 +43903,7 @@
         <v>2311</v>
       </c>
       <c r="N33" s="161" t="s">
-        <v>2338</v>
+        <v>2337</v>
       </c>
       <c r="O33" s="161" t="s">
         <v>2288</v>
@@ -43920,7 +43920,7 @@
         <v>2325</v>
       </c>
       <c r="U33" s="161" t="s">
-        <v>2344</v>
+        <v>2343</v>
       </c>
       <c r="V33" s="161" t="s">
         <v>2229</v>
@@ -43932,7 +43932,7 @@
         <v>1422</v>
       </c>
       <c r="Y33" s="161" t="s">
-        <v>2383</v>
+        <v>2382</v>
       </c>
       <c r="Z33" s="161" t="s">
         <v>1422</v>
@@ -43983,13 +43983,13 @@
         <v>1422</v>
       </c>
       <c r="Y34" s="161" t="s">
-        <v>2554</v>
+        <v>2552</v>
       </c>
       <c r="Z34" s="161" t="s">
         <v>1422</v>
       </c>
       <c r="AA34" s="249" t="s">
-        <v>2556</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="35" spans="1:27" ht="54.95" customHeight="1">
@@ -44007,7 +44007,7 @@
         <v>2324</v>
       </c>
       <c r="F35" s="161" t="s">
-        <v>2465</v>
+        <v>2556</v>
       </c>
       <c r="G35" s="161"/>
       <c r="H35" s="161" t="s">
@@ -44018,7 +44018,7 @@
       <c r="K35" s="161"/>
       <c r="L35" s="161"/>
       <c r="M35" s="161" t="s">
-        <v>2337</v>
+        <v>2557</v>
       </c>
       <c r="N35" s="161" t="s">
         <v>2224</v>
@@ -44027,7 +44027,7 @@
         <v>2225</v>
       </c>
       <c r="P35" s="161" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
       <c r="Q35" s="161">
         <v>1</v>
@@ -44040,7 +44040,7 @@
         <v>2325</v>
       </c>
       <c r="U35" s="161" t="s">
-        <v>2344</v>
+        <v>2343</v>
       </c>
       <c r="V35" s="161" t="s">
         <v>2229</v>
@@ -44052,7 +44052,7 @@
         <v>1422</v>
       </c>
       <c r="Y35" s="161" t="s">
-        <v>2555</v>
+        <v>2553</v>
       </c>
       <c r="Z35" s="161" t="s">
         <v>1422</v>
@@ -44103,13 +44103,13 @@
         <v>2335</v>
       </c>
       <c r="Y36" s="161" t="s">
-        <v>2554</v>
+        <v>2552</v>
       </c>
       <c r="Z36" s="161" t="s">
         <v>1422</v>
       </c>
       <c r="AA36" s="249" t="s">
-        <v>2556</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="37" spans="1:27" ht="54.95" customHeight="1">
@@ -44262,36 +44262,36 @@
     </row>
     <row r="41" spans="1:27" ht="54.95" customHeight="1">
       <c r="A41" s="268" t="s">
+        <v>2345</v>
+      </c>
+      <c r="B41" s="241" t="s">
         <v>2346</v>
       </c>
-      <c r="B41" s="241" t="s">
-        <v>2347</v>
-      </c>
       <c r="C41" s="241" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="D41" s="241">
         <v>1</v>
       </c>
       <c r="E41" s="241" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="F41" s="241" t="s">
-        <v>2466</v>
+        <v>2464</v>
       </c>
       <c r="G41" s="241"/>
       <c r="H41" s="241" t="s">
-        <v>2357</v>
+        <v>2356</v>
       </c>
       <c r="I41" s="241"/>
       <c r="J41" s="241"/>
       <c r="K41" s="241"/>
       <c r="L41" s="241"/>
       <c r="M41" s="241" t="s">
-        <v>2447</v>
+        <v>2446</v>
       </c>
       <c r="N41" s="241" t="s">
-        <v>2338</v>
+        <v>2337</v>
       </c>
       <c r="O41" s="241" t="s">
         <v>2288</v>
@@ -44302,16 +44302,16 @@
       </c>
       <c r="R41" s="241"/>
       <c r="S41" s="241" t="s">
-        <v>2348</v>
+        <v>2347</v>
       </c>
       <c r="T41" s="241" t="s">
-        <v>2354</v>
+        <v>2353</v>
       </c>
       <c r="U41" s="241"/>
       <c r="V41" s="241"/>
       <c r="W41" s="241"/>
       <c r="X41" s="241" t="s">
-        <v>2355</v>
+        <v>2354</v>
       </c>
       <c r="Y41" s="241" t="s">
         <v>2247</v>
@@ -44325,7 +44325,7 @@
     </row>
     <row r="42" spans="1:27" ht="54.95" customHeight="1">
       <c r="A42" s="269" t="s">
-        <v>2346</v>
+        <v>2345</v>
       </c>
       <c r="B42" s="161"/>
       <c r="C42" s="161"/>
@@ -44333,10 +44333,10 @@
         <v>2</v>
       </c>
       <c r="E42" s="161" t="s">
-        <v>2443</v>
+        <v>2442</v>
       </c>
       <c r="F42" s="161" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="G42" s="161"/>
       <c r="H42" s="161" t="s">
@@ -44355,7 +44355,7 @@
       <c r="Q42" s="161"/>
       <c r="R42" s="161"/>
       <c r="S42" s="161" t="s">
-        <v>2448</v>
+        <v>2447</v>
       </c>
       <c r="T42" s="161"/>
       <c r="U42" s="161"/>
@@ -44372,31 +44372,31 @@
     </row>
     <row r="43" spans="1:27" ht="54.95" customHeight="1">
       <c r="A43" s="269" t="s">
-        <v>2348</v>
+        <v>2347</v>
       </c>
       <c r="B43" s="244"/>
       <c r="C43" s="161" t="s">
-        <v>2350</v>
+        <v>2349</v>
       </c>
       <c r="D43" s="161">
         <v>1</v>
       </c>
       <c r="E43" s="161" t="s">
-        <v>2360</v>
+        <v>2359</v>
       </c>
       <c r="F43" s="161" t="s">
-        <v>2467</v>
+        <v>2465</v>
       </c>
       <c r="G43" s="161"/>
       <c r="H43" s="161" t="s">
-        <v>2356</v>
+        <v>2355</v>
       </c>
       <c r="I43" s="161"/>
       <c r="J43" s="161"/>
       <c r="K43" s="161"/>
       <c r="L43" s="161"/>
       <c r="M43" s="161" t="s">
-        <v>2447</v>
+        <v>2446</v>
       </c>
       <c r="N43" s="161" t="s">
         <v>1417</v>
@@ -44410,10 +44410,10 @@
       </c>
       <c r="R43" s="161"/>
       <c r="S43" s="161" t="s">
-        <v>2349</v>
+        <v>2348</v>
       </c>
       <c r="T43" s="161" t="s">
-        <v>2354</v>
+        <v>2353</v>
       </c>
       <c r="U43" s="161"/>
       <c r="V43" s="161"/>
@@ -44433,7 +44433,7 @@
     </row>
     <row r="44" spans="1:27" ht="54.95" customHeight="1">
       <c r="A44" s="269" t="s">
-        <v>2348</v>
+        <v>2347</v>
       </c>
       <c r="B44" s="244"/>
       <c r="C44" s="161"/>
@@ -44441,14 +44441,14 @@
         <v>2</v>
       </c>
       <c r="E44" s="161" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
       <c r="F44" s="161" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="G44" s="161"/>
       <c r="H44" s="161" t="s">
-        <v>2445</v>
+        <v>2444</v>
       </c>
       <c r="I44" s="161"/>
       <c r="J44" s="161"/>
@@ -44456,14 +44456,14 @@
       <c r="L44" s="161"/>
       <c r="M44" s="161"/>
       <c r="N44" s="161" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="O44" s="161"/>
       <c r="P44" s="161"/>
       <c r="Q44" s="161"/>
       <c r="R44" s="161"/>
       <c r="S44" s="161" t="s">
-        <v>2448</v>
+        <v>2447</v>
       </c>
       <c r="T44" s="161"/>
       <c r="U44" s="161"/>
@@ -44480,31 +44480,31 @@
     </row>
     <row r="45" spans="1:27" ht="54.95" customHeight="1">
       <c r="A45" s="269" t="s">
-        <v>2349</v>
+        <v>2348</v>
       </c>
       <c r="B45" s="244"/>
       <c r="C45" s="161" t="s">
-        <v>2358</v>
+        <v>2357</v>
       </c>
       <c r="D45" s="161">
         <v>1</v>
       </c>
       <c r="E45" s="161" t="s">
-        <v>2361</v>
+        <v>2360</v>
       </c>
       <c r="F45" s="161" t="s">
-        <v>2468</v>
+        <v>2466</v>
       </c>
       <c r="G45" s="161"/>
       <c r="H45" s="161" t="s">
-        <v>2357</v>
+        <v>2356</v>
       </c>
       <c r="I45" s="161"/>
       <c r="J45" s="161"/>
       <c r="K45" s="161"/>
       <c r="L45" s="161"/>
       <c r="M45" s="161" t="s">
-        <v>2447</v>
+        <v>2446</v>
       </c>
       <c r="N45" s="161" t="s">
         <v>1417</v>
@@ -44518,10 +44518,10 @@
       </c>
       <c r="R45" s="161"/>
       <c r="S45" s="161" t="s">
+        <v>2352</v>
+      </c>
+      <c r="T45" s="161" t="s">
         <v>2353</v>
-      </c>
-      <c r="T45" s="161" t="s">
-        <v>2354</v>
       </c>
       <c r="U45" s="161"/>
       <c r="V45" s="161"/>
@@ -44541,7 +44541,7 @@
     </row>
     <row r="46" spans="1:27" ht="54.95" customHeight="1">
       <c r="A46" s="269" t="s">
-        <v>2349</v>
+        <v>2348</v>
       </c>
       <c r="B46" s="244"/>
       <c r="C46" s="161"/>
@@ -44549,14 +44549,14 @@
         <v>2</v>
       </c>
       <c r="E46" s="161" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
       <c r="F46" s="161" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="G46" s="161"/>
       <c r="H46" s="161" t="s">
-        <v>2445</v>
+        <v>2444</v>
       </c>
       <c r="I46" s="161"/>
       <c r="J46" s="161"/>
@@ -44564,14 +44564,14 @@
       <c r="L46" s="161"/>
       <c r="M46" s="161"/>
       <c r="N46" s="161" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="O46" s="161"/>
       <c r="P46" s="161"/>
       <c r="Q46" s="161"/>
       <c r="R46" s="161"/>
       <c r="S46" s="161" t="s">
-        <v>2448</v>
+        <v>2447</v>
       </c>
       <c r="T46" s="161"/>
       <c r="U46" s="161"/>
@@ -44588,11 +44588,11 @@
     </row>
     <row r="47" spans="1:27" ht="54.95" customHeight="1">
       <c r="A47" s="269" t="s">
-        <v>2353</v>
+        <v>2352</v>
       </c>
       <c r="B47" s="244"/>
       <c r="C47" s="161" t="s">
-        <v>2351</v>
+        <v>2350</v>
       </c>
       <c r="D47" s="244"/>
       <c r="E47" s="244"/>
@@ -44615,7 +44615,7 @@
       <c r="V47" s="244"/>
       <c r="W47" s="244"/>
       <c r="X47" s="244" t="s">
-        <v>2355</v>
+        <v>2354</v>
       </c>
       <c r="Y47" s="244"/>
       <c r="Z47" s="244" t="s">
@@ -44625,11 +44625,11 @@
     </row>
     <row r="48" spans="1:27" ht="54.95" customHeight="1">
       <c r="A48" s="269" t="s">
-        <v>2354</v>
+        <v>2353</v>
       </c>
       <c r="B48" s="244"/>
       <c r="C48" s="244" t="s">
-        <v>2352</v>
+        <v>2351</v>
       </c>
       <c r="D48" s="244"/>
       <c r="E48" s="244"/>
@@ -44662,11 +44662,11 @@
     </row>
     <row r="49" spans="1:27" ht="54.95" customHeight="1" thickBot="1">
       <c r="A49" s="274" t="s">
-        <v>2448</v>
+        <v>2447</v>
       </c>
       <c r="B49" s="260"/>
       <c r="C49" s="260" t="s">
-        <v>2449</v>
+        <v>2448</v>
       </c>
       <c r="D49" s="260"/>
       <c r="E49" s="260"/>
@@ -44699,22 +44699,22 @@
     </row>
     <row r="50" spans="1:27" ht="54.95" customHeight="1">
       <c r="A50" s="276" t="s">
+        <v>2362</v>
+      </c>
+      <c r="B50" s="253" t="s">
         <v>2363</v>
       </c>
-      <c r="B50" s="253" t="s">
-        <v>2364</v>
-      </c>
       <c r="C50" s="253" t="s">
-        <v>2374</v>
+        <v>2373</v>
       </c>
       <c r="D50" s="253">
         <v>1</v>
       </c>
       <c r="E50" s="253" t="s">
-        <v>2455</v>
+        <v>2454</v>
       </c>
       <c r="F50" s="253" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="G50" s="253"/>
       <c r="H50" s="253" t="s">
@@ -44726,33 +44726,33 @@
       <c r="L50" s="253"/>
       <c r="M50" s="253"/>
       <c r="N50" s="253" t="s">
+        <v>2376</v>
+      </c>
+      <c r="O50" s="253" t="s">
         <v>2377</v>
-      </c>
-      <c r="O50" s="253" t="s">
-        <v>2378</v>
       </c>
       <c r="P50" s="253"/>
       <c r="Q50" s="253"/>
       <c r="R50" s="253"/>
       <c r="S50" s="253" t="s">
-        <v>2365</v>
+        <v>2364</v>
       </c>
       <c r="T50" s="253"/>
       <c r="U50" s="253"/>
       <c r="V50" s="253"/>
       <c r="W50" s="253"/>
       <c r="X50" s="253" t="s">
-        <v>2371</v>
+        <v>2370</v>
       </c>
       <c r="Y50" s="253"/>
       <c r="Z50" s="253" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="AA50" s="254"/>
     </row>
     <row r="51" spans="1:27" ht="54.95" customHeight="1">
       <c r="A51" s="277" t="s">
-        <v>2362</v>
+        <v>2361</v>
       </c>
       <c r="B51" s="244"/>
       <c r="C51" s="244"/>
@@ -44760,10 +44760,10 @@
         <v>2</v>
       </c>
       <c r="E51" s="244" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
       <c r="F51" s="244" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
       <c r="G51" s="244"/>
       <c r="H51" s="244" t="s">
@@ -44775,33 +44775,33 @@
       <c r="L51" s="244"/>
       <c r="M51" s="244"/>
       <c r="N51" s="244" t="s">
-        <v>2377</v>
+        <v>2376</v>
       </c>
       <c r="O51" s="244" t="s">
-        <v>2379</v>
+        <v>2378</v>
       </c>
       <c r="P51" s="244"/>
       <c r="Q51" s="244"/>
       <c r="R51" s="244"/>
       <c r="S51" s="244" t="s">
-        <v>2365</v>
+        <v>2364</v>
       </c>
       <c r="T51" s="244"/>
       <c r="U51" s="244"/>
       <c r="V51" s="244"/>
       <c r="W51" s="244"/>
       <c r="X51" s="244" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="Y51" s="244"/>
       <c r="Z51" s="244" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="AA51" s="252"/>
     </row>
     <row r="52" spans="1:27" ht="54.95" customHeight="1">
       <c r="A52" s="277" t="s">
-        <v>2363</v>
+        <v>2362</v>
       </c>
       <c r="B52" s="244"/>
       <c r="C52" s="244"/>
@@ -44809,10 +44809,10 @@
         <v>3</v>
       </c>
       <c r="E52" s="244" t="s">
-        <v>2457</v>
+        <v>2456</v>
       </c>
       <c r="F52" s="244" t="s">
-        <v>2453</v>
+        <v>2452</v>
       </c>
       <c r="G52" s="244"/>
       <c r="H52" s="244" t="s">
@@ -44824,46 +44824,46 @@
       <c r="L52" s="244"/>
       <c r="M52" s="244"/>
       <c r="N52" s="244" t="s">
-        <v>2377</v>
+        <v>2376</v>
       </c>
       <c r="O52" s="244" t="s">
-        <v>2380</v>
+        <v>2379</v>
       </c>
       <c r="P52" s="244"/>
       <c r="Q52" s="244"/>
       <c r="R52" s="244"/>
       <c r="S52" s="244" t="s">
-        <v>2365</v>
+        <v>2364</v>
       </c>
       <c r="T52" s="244"/>
       <c r="U52" s="244"/>
       <c r="V52" s="244"/>
       <c r="W52" s="244"/>
       <c r="X52" s="244" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="Y52" s="244"/>
       <c r="Z52" s="244" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="AA52" s="252"/>
     </row>
     <row r="53" spans="1:27" s="3" customFormat="1" ht="54.95" customHeight="1">
       <c r="A53" s="277" t="s">
-        <v>2365</v>
+        <v>2364</v>
       </c>
       <c r="B53" s="244"/>
       <c r="C53" s="244" t="s">
-        <v>2375</v>
+        <v>2374</v>
       </c>
       <c r="D53" s="244">
         <v>1</v>
       </c>
       <c r="E53" s="244" t="s">
-        <v>2366</v>
+        <v>2365</v>
       </c>
       <c r="F53" s="244" t="s">
-        <v>2369</v>
+        <v>2368</v>
       </c>
       <c r="G53" s="244"/>
       <c r="H53" s="244" t="s">
@@ -44878,7 +44878,7 @@
         <v>2228</v>
       </c>
       <c r="O53" s="244" t="s">
-        <v>2381</v>
+        <v>2380</v>
       </c>
       <c r="P53" s="244"/>
       <c r="Q53" s="244">
@@ -44886,20 +44886,20 @@
       </c>
       <c r="R53" s="244"/>
       <c r="S53" s="244" t="s">
-        <v>2373</v>
+        <v>2372</v>
       </c>
       <c r="T53" s="244"/>
       <c r="U53" s="244"/>
       <c r="V53" s="244"/>
       <c r="W53" s="244"/>
       <c r="X53" s="244" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="Y53" s="244" t="s">
         <v>2247</v>
       </c>
       <c r="Z53" s="244" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="AA53" s="252" t="s">
         <v>2336</v>
@@ -44907,7 +44907,7 @@
     </row>
     <row r="54" spans="1:27" s="3" customFormat="1" ht="54.95" customHeight="1">
       <c r="A54" s="277" t="s">
-        <v>2365</v>
+        <v>2364</v>
       </c>
       <c r="B54" s="244"/>
       <c r="C54" s="244"/>
@@ -44915,10 +44915,10 @@
         <v>2</v>
       </c>
       <c r="E54" s="244" t="s">
-        <v>2367</v>
+        <v>2366</v>
       </c>
       <c r="F54" s="273" t="s">
-        <v>2469</v>
+        <v>2467</v>
       </c>
       <c r="G54" s="244" t="s">
         <v>2286</v>
@@ -44927,7 +44927,7 @@
         <v>2285</v>
       </c>
       <c r="I54" s="244" t="s">
-        <v>2426</v>
+        <v>2425</v>
       </c>
       <c r="J54" s="244" t="s">
         <v>2288</v>
@@ -44943,7 +44943,7 @@
         <v>2238</v>
       </c>
       <c r="O54" s="244" t="s">
-        <v>2382</v>
+        <v>2381</v>
       </c>
       <c r="P54" s="244" t="s">
         <v>2313</v>
@@ -44955,28 +44955,28 @@
         <v>3</v>
       </c>
       <c r="S54" s="244" t="s">
-        <v>2373</v>
+        <v>2372</v>
       </c>
       <c r="T54" s="244"/>
       <c r="U54" s="244"/>
       <c r="V54" s="244"/>
       <c r="W54" s="244"/>
       <c r="X54" s="244" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="Y54" s="161" t="s">
-        <v>2383</v>
+        <v>2382</v>
       </c>
       <c r="Z54" s="244" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="AA54" s="252" t="s">
-        <v>2372</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="55" spans="1:27" ht="54.95" customHeight="1">
       <c r="A55" s="277" t="s">
-        <v>2365</v>
+        <v>2364</v>
       </c>
       <c r="B55" s="244"/>
       <c r="C55" s="244"/>
@@ -44984,10 +44984,10 @@
         <v>3</v>
       </c>
       <c r="E55" s="244" t="s">
-        <v>2368</v>
+        <v>2367</v>
       </c>
       <c r="F55" s="273" t="s">
-        <v>2470</v>
+        <v>2468</v>
       </c>
       <c r="G55" s="244" t="s">
         <v>2286</v>
@@ -44996,7 +44996,7 @@
         <v>2285</v>
       </c>
       <c r="I55" s="244" t="s">
-        <v>2427</v>
+        <v>2426</v>
       </c>
       <c r="J55" s="244" t="s">
         <v>2288</v>
@@ -45012,7 +45012,7 @@
         <v>2238</v>
       </c>
       <c r="O55" s="244" t="s">
-        <v>2382</v>
+        <v>2381</v>
       </c>
       <c r="P55" s="244" t="s">
         <v>2314</v>
@@ -45024,32 +45024,32 @@
         <v>3</v>
       </c>
       <c r="S55" s="244" t="s">
-        <v>2373</v>
+        <v>2372</v>
       </c>
       <c r="T55" s="244"/>
       <c r="U55" s="244"/>
       <c r="V55" s="244"/>
       <c r="W55" s="244"/>
       <c r="X55" s="244" t="s">
-        <v>2371</v>
+        <v>2370</v>
       </c>
       <c r="Y55" s="161" t="s">
         <v>1415</v>
       </c>
       <c r="Z55" s="244" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="AA55" s="252" t="s">
-        <v>2404</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="56" spans="1:27" ht="54.95" customHeight="1" thickBot="1">
       <c r="A56" s="278" t="s">
-        <v>2373</v>
+        <v>2372</v>
       </c>
       <c r="B56" s="245"/>
       <c r="C56" s="245" t="s">
-        <v>2376</v>
+        <v>2375</v>
       </c>
       <c r="D56" s="245"/>
       <c r="E56" s="245"/>
@@ -45072,32 +45072,32 @@
       <c r="V56" s="245"/>
       <c r="W56" s="245"/>
       <c r="X56" s="245" t="s">
-        <v>2371</v>
+        <v>2370</v>
       </c>
       <c r="Y56" s="245"/>
       <c r="Z56" s="245" t="s">
-        <v>2371</v>
+        <v>2370</v>
       </c>
       <c r="AA56" s="255"/>
     </row>
     <row r="57" spans="1:27" ht="54.95" customHeight="1">
       <c r="A57" s="279" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="B57" s="253" t="s">
+        <v>2390</v>
+      </c>
+      <c r="C57" s="253" t="s">
         <v>2391</v>
       </c>
-      <c r="C57" s="253" t="s">
-        <v>2392</v>
-      </c>
       <c r="D57" s="253">
         <v>1</v>
       </c>
       <c r="E57" s="253" t="s">
-        <v>2396</v>
+        <v>2395</v>
       </c>
       <c r="F57" s="253" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
       <c r="G57" s="253"/>
       <c r="H57" s="253" t="s">
@@ -45109,7 +45109,7 @@
       <c r="L57" s="253"/>
       <c r="M57" s="253"/>
       <c r="N57" s="253" t="s">
-        <v>2401</v>
+        <v>2400</v>
       </c>
       <c r="O57" s="253" t="s">
         <v>2229</v>
@@ -45120,14 +45120,14 @@
       </c>
       <c r="R57" s="253"/>
       <c r="S57" s="253" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="T57" s="253"/>
       <c r="U57" s="253"/>
       <c r="V57" s="253"/>
       <c r="W57" s="253"/>
       <c r="X57" s="253" t="s">
-        <v>2403</v>
+        <v>2402</v>
       </c>
       <c r="Y57" s="253" t="s">
         <v>2247</v>
@@ -45149,10 +45149,10 @@
         <v>2</v>
       </c>
       <c r="E58" s="244" t="s">
-        <v>2397</v>
+        <v>2396</v>
       </c>
       <c r="F58" s="244" t="s">
-        <v>2399</v>
+        <v>2398</v>
       </c>
       <c r="G58" s="244"/>
       <c r="H58" s="244" t="s">
@@ -45164,7 +45164,7 @@
       <c r="L58" s="244"/>
       <c r="M58" s="244"/>
       <c r="N58" s="244" t="s">
-        <v>2402</v>
+        <v>2401</v>
       </c>
       <c r="O58" s="244" t="s">
         <v>2229</v>
@@ -45175,7 +45175,7 @@
       </c>
       <c r="R58" s="244"/>
       <c r="S58" s="244" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="T58" s="244"/>
       <c r="U58" s="244"/>
@@ -45185,13 +45185,13 @@
         <v>1424</v>
       </c>
       <c r="Y58" s="161" t="s">
-        <v>2383</v>
+        <v>2382</v>
       </c>
       <c r="Z58" s="244" t="s">
         <v>1424</v>
       </c>
       <c r="AA58" s="252" t="s">
-        <v>2372</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="59" spans="1:27" ht="54.95" customHeight="1">
@@ -45204,10 +45204,10 @@
         <v>3</v>
       </c>
       <c r="E59" s="244" t="s">
-        <v>2398</v>
+        <v>2397</v>
       </c>
       <c r="F59" s="244" t="s">
-        <v>2400</v>
+        <v>2399</v>
       </c>
       <c r="G59" s="244"/>
       <c r="H59" s="244" t="s">
@@ -45230,7 +45230,7 @@
       </c>
       <c r="R59" s="244"/>
       <c r="S59" s="244" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="T59" s="244"/>
       <c r="U59" s="244"/>
@@ -45246,16 +45246,16 @@
         <v>1424</v>
       </c>
       <c r="AA59" s="252" t="s">
-        <v>2404</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="60" spans="1:27" ht="54.95" customHeight="1">
       <c r="A60" s="280" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="B60" s="244"/>
       <c r="C60" s="244" t="s">
-        <v>2393</v>
+        <v>2392</v>
       </c>
       <c r="D60" s="244"/>
       <c r="E60" s="244"/>
@@ -45288,11 +45288,11 @@
     </row>
     <row r="61" spans="1:27" ht="54.95" customHeight="1">
       <c r="A61" s="280" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="B61" s="244"/>
       <c r="C61" s="244" t="s">
-        <v>2394</v>
+        <v>2393</v>
       </c>
       <c r="D61" s="244"/>
       <c r="E61" s="244"/>
@@ -45315,7 +45315,7 @@
       <c r="V61" s="244"/>
       <c r="W61" s="244"/>
       <c r="X61" s="244" t="s">
-        <v>2403</v>
+        <v>2402</v>
       </c>
       <c r="Y61" s="244"/>
       <c r="Z61" s="244" t="s">
@@ -45325,11 +45325,11 @@
     </row>
     <row r="62" spans="1:27" ht="54.95" customHeight="1" thickBot="1">
       <c r="A62" s="281" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="B62" s="245"/>
       <c r="C62" s="245" t="s">
-        <v>2395</v>
+        <v>2394</v>
       </c>
       <c r="D62" s="245"/>
       <c r="E62" s="245"/>
@@ -45362,34 +45362,34 @@
     </row>
     <row r="63" spans="1:27" ht="54.95" customHeight="1">
       <c r="A63" s="276" t="s">
+        <v>2405</v>
+      </c>
+      <c r="B63" s="253" t="s">
         <v>2406</v>
       </c>
-      <c r="B63" s="253" t="s">
-        <v>2407</v>
-      </c>
       <c r="C63" s="253" t="s">
-        <v>2429</v>
+        <v>2428</v>
       </c>
       <c r="D63" s="253">
         <v>1</v>
       </c>
       <c r="E63" s="253" t="s">
-        <v>2412</v>
+        <v>2411</v>
       </c>
       <c r="F63" s="282" t="s">
-        <v>2471</v>
+        <v>2469</v>
       </c>
       <c r="G63" s="253" t="s">
-        <v>2422</v>
+        <v>2421</v>
       </c>
       <c r="H63" s="253" t="s">
         <v>2285</v>
       </c>
       <c r="I63" s="253" t="s">
-        <v>2423</v>
+        <v>2422</v>
       </c>
       <c r="J63" s="253" t="s">
-        <v>2421</v>
+        <v>2420</v>
       </c>
       <c r="K63" s="253" t="s">
         <v>2229</v>
@@ -45412,20 +45412,20 @@
       </c>
       <c r="R63" s="253"/>
       <c r="S63" s="253" t="s">
-        <v>2408</v>
+        <v>2407</v>
       </c>
       <c r="T63" s="253"/>
       <c r="U63" s="253"/>
       <c r="V63" s="253"/>
       <c r="W63" s="253"/>
       <c r="X63" s="253" t="s">
-        <v>2420</v>
+        <v>2419</v>
       </c>
       <c r="Y63" s="253" t="s">
         <v>2247</v>
       </c>
       <c r="Z63" s="253" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
       <c r="AA63" s="254" t="s">
         <v>2336</v>
@@ -45433,7 +45433,7 @@
     </row>
     <row r="64" spans="1:27" ht="54.95" customHeight="1">
       <c r="A64" s="280" t="s">
-        <v>2406</v>
+        <v>2405</v>
       </c>
       <c r="B64" s="244"/>
       <c r="C64" s="244"/>
@@ -45441,21 +45441,21 @@
         <v>2</v>
       </c>
       <c r="E64" s="244" t="s">
-        <v>2413</v>
+        <v>2412</v>
       </c>
       <c r="F64" s="273" t="s">
-        <v>2472</v>
+        <v>2470</v>
       </c>
       <c r="G64" s="244"/>
       <c r="H64" s="244" t="s">
-        <v>2357</v>
+        <v>2356</v>
       </c>
       <c r="I64" s="244"/>
       <c r="J64" s="244"/>
       <c r="K64" s="244"/>
       <c r="L64" s="244"/>
       <c r="M64" s="244" t="s">
-        <v>2450</v>
+        <v>2449</v>
       </c>
       <c r="N64" s="244" t="s">
         <v>2224</v>
@@ -45471,30 +45471,30 @@
       </c>
       <c r="R64" s="244"/>
       <c r="S64" s="244" t="s">
+        <v>2408</v>
+      </c>
+      <c r="T64" s="244" t="s">
         <v>2409</v>
-      </c>
-      <c r="T64" s="244" t="s">
-        <v>2410</v>
       </c>
       <c r="U64" s="244"/>
       <c r="V64" s="244"/>
       <c r="W64" s="244"/>
       <c r="X64" s="244" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
       <c r="Y64" s="161" t="s">
-        <v>2383</v>
+        <v>2382</v>
       </c>
       <c r="Z64" s="244" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
       <c r="AA64" s="252" t="s">
-        <v>2372</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="65" spans="1:27" ht="54.95" customHeight="1">
       <c r="A65" s="280" t="s">
-        <v>2406</v>
+        <v>2405</v>
       </c>
       <c r="B65" s="244"/>
       <c r="C65" s="244"/>
@@ -45502,10 +45502,10 @@
         <v>3</v>
       </c>
       <c r="E65" s="244" t="s">
-        <v>2414</v>
+        <v>2413</v>
       </c>
       <c r="F65" s="273" t="s">
-        <v>2473</v>
+        <v>2471</v>
       </c>
       <c r="G65" s="244"/>
       <c r="H65" s="244" t="s">
@@ -45513,7 +45513,7 @@
       </c>
       <c r="I65" s="244"/>
       <c r="J65" s="244" t="s">
-        <v>2428</v>
+        <v>2427</v>
       </c>
       <c r="K65" s="244" t="s">
         <v>2227</v>
@@ -45536,32 +45536,32 @@
       </c>
       <c r="R65" s="244"/>
       <c r="S65" s="244" t="s">
-        <v>2411</v>
+        <v>2410</v>
       </c>
       <c r="T65" s="244"/>
       <c r="U65" s="244"/>
       <c r="V65" s="244"/>
       <c r="W65" s="244"/>
       <c r="X65" s="244" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
       <c r="Y65" s="161" t="s">
         <v>1415</v>
       </c>
       <c r="Z65" s="244" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
       <c r="AA65" s="252" t="s">
-        <v>2404</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="66" spans="1:27" ht="54.95" customHeight="1">
       <c r="A66" s="280" t="s">
-        <v>2408</v>
+        <v>2407</v>
       </c>
       <c r="B66" s="244"/>
       <c r="C66" s="244" t="s">
-        <v>2415</v>
+        <v>2414</v>
       </c>
       <c r="D66" s="244"/>
       <c r="E66" s="244"/>
@@ -45584,21 +45584,21 @@
       <c r="V66" s="244"/>
       <c r="W66" s="244"/>
       <c r="X66" s="244" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
       <c r="Y66" s="244"/>
       <c r="Z66" s="244" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
       <c r="AA66" s="252"/>
     </row>
     <row r="67" spans="1:27" ht="54.95" customHeight="1">
       <c r="A67" s="280" t="s">
-        <v>2409</v>
+        <v>2408</v>
       </c>
       <c r="B67" s="244"/>
       <c r="C67" s="244" t="s">
-        <v>2417</v>
+        <v>2416</v>
       </c>
       <c r="D67" s="244"/>
       <c r="E67" s="244"/>
@@ -45621,21 +45621,21 @@
       <c r="V67" s="244"/>
       <c r="W67" s="244"/>
       <c r="X67" s="244" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
       <c r="Y67" s="244"/>
       <c r="Z67" s="244" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
       <c r="AA67" s="252"/>
     </row>
     <row r="68" spans="1:27" ht="54.95" customHeight="1">
       <c r="A68" s="280" t="s">
-        <v>2410</v>
+        <v>2409</v>
       </c>
       <c r="B68" s="244"/>
       <c r="C68" s="244" t="s">
-        <v>2418</v>
+        <v>2417</v>
       </c>
       <c r="D68" s="244"/>
       <c r="E68" s="244"/>
@@ -45658,21 +45658,21 @@
       <c r="V68" s="244"/>
       <c r="W68" s="244"/>
       <c r="X68" s="244" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
       <c r="Y68" s="244"/>
       <c r="Z68" s="244" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
       <c r="AA68" s="252"/>
     </row>
     <row r="69" spans="1:27" ht="54.95" customHeight="1" thickBot="1">
       <c r="A69" s="281" t="s">
-        <v>2411</v>
+        <v>2410</v>
       </c>
       <c r="B69" s="245"/>
       <c r="C69" s="245" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="D69" s="245"/>
       <c r="E69" s="245"/>
@@ -45695,32 +45695,32 @@
       <c r="V69" s="245"/>
       <c r="W69" s="245"/>
       <c r="X69" s="245" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
       <c r="Y69" s="245"/>
       <c r="Z69" s="245" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
       <c r="AA69" s="255"/>
     </row>
     <row r="70" spans="1:27" ht="54.95" customHeight="1">
       <c r="A70" s="256" t="s">
-        <v>2441</v>
+        <v>2440</v>
       </c>
       <c r="B70" s="256" t="s">
+        <v>2536</v>
+      </c>
+      <c r="C70" s="256" t="s">
+        <v>2550</v>
+      </c>
+      <c r="D70" s="256">
+        <v>1</v>
+      </c>
+      <c r="E70" s="256" t="s">
+        <v>2537</v>
+      </c>
+      <c r="F70" s="283" t="s">
         <v>2538</v>
-      </c>
-      <c r="C70" s="256" t="s">
-        <v>2552</v>
-      </c>
-      <c r="D70" s="256">
-        <v>1</v>
-      </c>
-      <c r="E70" s="256" t="s">
-        <v>2539</v>
-      </c>
-      <c r="F70" s="283" t="s">
-        <v>2540</v>
       </c>
       <c r="G70" s="256"/>
       <c r="H70" s="256" t="s">
@@ -45743,20 +45743,20 @@
       </c>
       <c r="R70" s="256"/>
       <c r="S70" s="256" t="s">
-        <v>2541</v>
+        <v>2539</v>
       </c>
       <c r="T70" s="256"/>
       <c r="U70" s="256"/>
       <c r="V70" s="256"/>
       <c r="W70" s="256"/>
       <c r="X70" s="256" t="s">
-        <v>2551</v>
+        <v>2549</v>
       </c>
       <c r="Y70" s="256" t="s">
         <v>2247</v>
       </c>
       <c r="Z70" s="256" t="s">
-        <v>2551</v>
+        <v>2549</v>
       </c>
       <c r="AA70" s="256" t="s">
         <v>2336</v>
@@ -45764,11 +45764,11 @@
     </row>
     <row r="71" spans="1:27" ht="54.95" customHeight="1">
       <c r="A71" s="256" t="s">
-        <v>2541</v>
+        <v>2539</v>
       </c>
       <c r="B71" s="244"/>
       <c r="C71" s="244" t="s">
-        <v>2550</v>
+        <v>2548</v>
       </c>
       <c r="D71" s="244"/>
       <c r="E71" s="244"/>
@@ -45791,11 +45791,11 @@
       <c r="V71" s="244"/>
       <c r="W71" s="244"/>
       <c r="X71" s="244" t="s">
-        <v>2551</v>
+        <v>2549</v>
       </c>
       <c r="Y71" s="244"/>
       <c r="Z71" s="244" t="s">
-        <v>2551</v>
+        <v>2549</v>
       </c>
       <c r="AA71" s="244"/>
     </row>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erang\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{126D2177-7889-4AE9-83B3-929CF329F742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B59056A-4CBF-4036-BF9E-8B3D94F7C228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -32,6 +32,17 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -40,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5196" uniqueCount="2558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5196" uniqueCount="2555">
   <si>
     <t>캐릭터ID</t>
   </si>
@@ -12994,13 +13005,6 @@
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
   <si>
-    <t>Coin</t>
-  </si>
-  <si>
-    <t>Coin</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
     <t>“광맥 곳곳에 균열이 생겼다."</t>
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
@@ -13345,18 +13349,11 @@
     <t>EndEvent</t>
   </si>
   <si>
-    <t>PlayerChoice</t>
-  </si>
-  <si>
     <t>Event_07_E</t>
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
   <si>
     <t>“광맥을 건드리지 않고 자리를 떠났다.”</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>PlayerChoice</t>
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
   <si>
@@ -13398,48 +13395,6 @@
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
   <si>
-    <t>주사위 6 이상
-무작위 일반~레어 유물 획득</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>주사위 8 이상
-무작위 레어~에픽 유물 획득</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>주사위 10 이상
-무작위 에픽~유니크 유물 획득</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>주사위 6 이상
-레드 더스티움 30 획득
-실패 : 생명력 5 감소</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>주사위 10 이상
-레드 더스티움 50 획득
-실패 : 생명력 5 감소</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>예측 : 앞면 or 뒷면
-레드 더스티움 25 획득</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>예측 : 앞면 or 뒷면
-레드 더스티움 30 획득</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>예측 : 앞면 or 뒷면
-레드 더스티움 35 획득</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
     <t>레드 더스티움 20 소모
 레어~에픽 기억 발현</t>
     <phoneticPr fontId="40" type="noConversion"/>
@@ -13455,11 +13410,6 @@
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
   <si>
-    <t>예측 : 앞면 or 뒷면
-무작위 유물 획득</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
     <t>침식도 20 증가
 무작위 일반~유니크 유물 획득</t>
     <phoneticPr fontId="40" type="noConversion"/>
@@ -13690,11 +13640,6 @@
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
   <si>
-    <t>새로운 방에 진입하면 3, 피해를 받으면 1,
-전투불능이 되면 10의 침식도가 증가합니다.</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
     <t>침식도가 최대치인 100에 도달하면
 매 턴 생명력이 10씩 감소합니다.</t>
     <phoneticPr fontId="40" type="noConversion"/>
@@ -13755,13 +13700,73 @@
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
   <si>
-    <t>주사위 12 이상
-무작위 에픽 유물 획득
+    <t>12~18</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>주사위 6 이상
+레드 더스티움 25 획득</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>주사위 8 이상
+레드 더스티움 30 획득</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>주사위 10 이상
+레드 더스티움 35 획득</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>주사위 6 이상
+성공 : 무작위 일반~레어 유물 획득
+실패 : 이벤트 종료</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>주사위 8 이상
+성공 : 무작위 레어~에픽 유물 획득
+실패 : 이벤트 종료</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>주사위 10 이상
+성공 : 무작위 에픽~유니크 유물 획득
+실패 : 이벤트 종료</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>주사위 6 이상
+성공 : 레드 더스티움 30 획득
 실패 : 생명력 5 감소</t>
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
   <si>
-    <t>12~18</t>
+    <t>주사위 10 이상
+성공 : 레드 더스티움 50 획득
+실패 : 생명력 5 감소</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>주사위 12 이상
+성공 : 무작위 에픽 유물 획득
+실패 : 생명력 5 감소</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>주사위 9 이상
+성공 : 무작위 유물 획득
+실패 : 이벤트 종료</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>9~18</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>침식도는 새로운 방에 진입하면 3, 턴이 진행되거나
+피해를 받을 때마다 1, 전투불능이 되면 10 증가합니다.</t>
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
 </sst>
@@ -14626,7 +14631,7 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="284">
+  <cellXfs count="290">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -15435,16 +15440,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -15465,11 +15461,38 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
@@ -16148,7 +16171,7 @@
         <v>64</v>
       </c>
       <c r="C4" s="12">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D4" s="11">
         <v>12</v>
@@ -16219,7 +16242,7 @@
         <v>80</v>
       </c>
       <c r="C5" s="12">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D5" s="11">
         <v>14</v>
@@ -26742,487 +26765,487 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="263" t="s">
-        <v>2483</v>
+        <v>2470</v>
       </c>
       <c r="B1" s="263" t="s">
-        <v>2484</v>
+        <v>2471</v>
       </c>
       <c r="C1" s="263" t="s">
         <v>1299</v>
       </c>
       <c r="D1" s="263" t="s">
-        <v>2485</v>
+        <v>2472</v>
       </c>
       <c r="E1" s="263" t="s">
-        <v>2486</v>
+        <v>2473</v>
       </c>
       <c r="F1" s="263" t="s">
-        <v>2487</v>
+        <v>2474</v>
       </c>
       <c r="G1" s="263" t="s">
-        <v>2488</v>
+        <v>2475</v>
       </c>
       <c r="H1" s="263" t="s">
         <v>1955</v>
       </c>
       <c r="I1" s="263" t="s">
-        <v>2489</v>
+        <v>2476</v>
       </c>
       <c r="J1" s="263" t="s">
-        <v>2525</v>
+        <v>2512</v>
       </c>
       <c r="K1" s="263" t="s">
-        <v>2490</v>
+        <v>2477</v>
       </c>
       <c r="L1" s="264" t="s">
-        <v>2491</v>
+        <v>2478</v>
       </c>
       <c r="M1" s="263" t="s">
-        <v>2492</v>
+        <v>2479</v>
       </c>
       <c r="N1" s="263" t="s">
-        <v>2493</v>
+        <v>2480</v>
       </c>
       <c r="O1" s="263" t="s">
-        <v>2543</v>
+        <v>2529</v>
       </c>
       <c r="P1" s="263" t="s">
-        <v>2545</v>
+        <v>2531</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="263" t="s">
-        <v>2494</v>
+        <v>2481</v>
       </c>
       <c r="B2" s="263" t="s">
-        <v>2495</v>
+        <v>2482</v>
       </c>
       <c r="C2" s="263" t="s">
         <v>1305</v>
       </c>
       <c r="D2" s="263" t="s">
-        <v>2496</v>
+        <v>2483</v>
       </c>
       <c r="E2" s="263" t="s">
-        <v>2497</v>
+        <v>2484</v>
       </c>
       <c r="F2" s="263" t="s">
-        <v>2498</v>
+        <v>2485</v>
       </c>
       <c r="G2" s="263" t="s">
-        <v>2499</v>
+        <v>2486</v>
       </c>
       <c r="H2" s="263" t="s">
         <v>147</v>
       </c>
       <c r="I2" s="263" t="s">
-        <v>2500</v>
+        <v>2487</v>
       </c>
       <c r="J2" s="263" t="s">
-        <v>2526</v>
+        <v>2513</v>
       </c>
       <c r="K2" s="263" t="s">
-        <v>2501</v>
+        <v>2488</v>
       </c>
       <c r="L2" s="264" t="s">
-        <v>2502</v>
+        <v>2489</v>
       </c>
       <c r="M2" s="263" t="s">
-        <v>2503</v>
+        <v>2490</v>
       </c>
       <c r="N2" s="263" t="s">
-        <v>2504</v>
+        <v>2491</v>
       </c>
       <c r="O2" s="263" t="s">
-        <v>2544</v>
+        <v>2530</v>
       </c>
       <c r="P2" s="263" t="s">
-        <v>2546</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="140" t="s">
-        <v>2505</v>
+        <v>2492</v>
       </c>
       <c r="B3" s="140">
         <v>1</v>
       </c>
       <c r="C3" s="140" t="s">
-        <v>2474</v>
+        <v>2461</v>
       </c>
       <c r="D3" s="140" t="s">
-        <v>2506</v>
+        <v>2493</v>
       </c>
       <c r="E3" s="140">
         <v>42</v>
       </c>
       <c r="F3" s="140" t="s">
-        <v>2524</v>
+        <v>2511</v>
       </c>
       <c r="G3" s="140">
         <v>1</v>
       </c>
       <c r="H3" s="140" t="s">
-        <v>2507</v>
+        <v>2494</v>
       </c>
       <c r="I3" s="140"/>
       <c r="J3" s="140" t="s">
-        <v>2529</v>
+        <v>2516</v>
       </c>
       <c r="K3" s="140" t="s">
-        <v>2508</v>
+        <v>2495</v>
       </c>
       <c r="L3" s="141" t="s">
-        <v>2509</v>
+        <v>2496</v>
       </c>
       <c r="M3" s="140" t="s">
-        <v>2510</v>
+        <v>2497</v>
       </c>
       <c r="N3" s="140"/>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="140" t="s">
-        <v>2505</v>
+        <v>2492</v>
       </c>
       <c r="B4" s="140">
         <v>2</v>
       </c>
       <c r="C4" s="140" t="s">
-        <v>2474</v>
+        <v>2461</v>
       </c>
       <c r="D4" s="140"/>
       <c r="E4" s="140"/>
       <c r="F4" s="140"/>
       <c r="G4" s="140"/>
       <c r="H4" s="140" t="s">
-        <v>2511</v>
+        <v>2498</v>
       </c>
       <c r="I4" s="140" t="s">
         <v>46</v>
       </c>
       <c r="J4" s="140" t="s">
-        <v>2527</v>
+        <v>2514</v>
       </c>
       <c r="K4" s="140" t="s">
-        <v>2512</v>
+        <v>2499</v>
       </c>
       <c r="L4" s="141" t="s">
-        <v>2533</v>
+        <v>2520</v>
       </c>
       <c r="M4" s="140" t="s">
-        <v>2513</v>
+        <v>2500</v>
       </c>
       <c r="N4" s="140"/>
       <c r="O4" t="s">
-        <v>2542</v>
+        <v>2528</v>
       </c>
       <c r="P4" t="s">
-        <v>2547</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="140" t="s">
-        <v>2505</v>
+        <v>2492</v>
       </c>
       <c r="B5" s="140">
         <v>3</v>
       </c>
       <c r="C5" s="140" t="s">
-        <v>2474</v>
+        <v>2461</v>
       </c>
       <c r="D5" s="140"/>
       <c r="E5" s="140"/>
       <c r="F5" s="140"/>
       <c r="G5" s="140"/>
       <c r="H5" s="140" t="s">
-        <v>2511</v>
+        <v>2498</v>
       </c>
       <c r="I5" s="140" t="s">
         <v>46</v>
       </c>
       <c r="J5" s="140" t="s">
-        <v>2527</v>
+        <v>2514</v>
       </c>
       <c r="K5" s="140" t="s">
-        <v>2514</v>
+        <v>2501</v>
       </c>
       <c r="L5" s="141" t="s">
-        <v>2531</v>
+        <v>2518</v>
       </c>
       <c r="M5" s="140" t="s">
-        <v>2513</v>
+        <v>2500</v>
       </c>
       <c r="N5" s="140"/>
       <c r="O5" t="s">
-        <v>2542</v>
+        <v>2528</v>
       </c>
       <c r="P5" t="s">
-        <v>2547</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="140" t="s">
-        <v>2505</v>
+        <v>2492</v>
       </c>
       <c r="B6" s="140">
         <v>4</v>
       </c>
       <c r="C6" s="140" t="s">
-        <v>2474</v>
+        <v>2461</v>
       </c>
       <c r="D6" s="140"/>
       <c r="E6" s="140"/>
       <c r="F6" s="140"/>
       <c r="G6" s="140"/>
       <c r="H6" s="140" t="s">
-        <v>2511</v>
+        <v>2498</v>
       </c>
       <c r="I6" s="140" t="s">
         <v>63</v>
       </c>
       <c r="J6" s="140" t="s">
-        <v>2527</v>
+        <v>2514</v>
       </c>
       <c r="K6" s="140" t="s">
-        <v>2515</v>
+        <v>2502</v>
       </c>
       <c r="L6" s="141" t="s">
-        <v>2532</v>
+        <v>2519</v>
       </c>
       <c r="M6" s="140" t="s">
-        <v>2513</v>
+        <v>2500</v>
       </c>
       <c r="N6" s="140"/>
       <c r="O6" t="s">
-        <v>2542</v>
+        <v>2528</v>
       </c>
       <c r="P6" t="s">
-        <v>2547</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="140" t="s">
-        <v>2505</v>
+        <v>2492</v>
       </c>
       <c r="B7" s="140">
         <v>5</v>
       </c>
       <c r="C7" s="140" t="s">
-        <v>2474</v>
+        <v>2461</v>
       </c>
       <c r="D7" s="140"/>
       <c r="E7" s="140"/>
       <c r="F7" s="140"/>
       <c r="G7" s="140"/>
       <c r="H7" s="140" t="s">
-        <v>2516</v>
+        <v>2503</v>
       </c>
       <c r="I7" s="140"/>
       <c r="J7" s="140" t="s">
+        <v>2515</v>
+      </c>
+      <c r="K7" s="140" t="s">
+        <v>2504</v>
+      </c>
+      <c r="L7" s="141" t="s">
+        <v>2517</v>
+      </c>
+      <c r="M7" s="140" t="s">
+        <v>2500</v>
+      </c>
+      <c r="N7" s="140" t="s">
+        <v>2505</v>
+      </c>
+      <c r="O7" t="s">
         <v>2528</v>
       </c>
-      <c r="K7" s="140" t="s">
-        <v>2517</v>
-      </c>
-      <c r="L7" s="141" t="s">
-        <v>2530</v>
-      </c>
-      <c r="M7" s="140" t="s">
-        <v>2513</v>
-      </c>
-      <c r="N7" s="140" t="s">
-        <v>2518</v>
-      </c>
-      <c r="O7" t="s">
-        <v>2542</v>
-      </c>
       <c r="P7" t="s">
-        <v>2547</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="33">
       <c r="A8" s="140" t="s">
-        <v>2505</v>
+        <v>2492</v>
       </c>
       <c r="B8" s="140">
         <v>6</v>
       </c>
       <c r="C8" s="140" t="s">
-        <v>2474</v>
+        <v>2461</v>
       </c>
       <c r="D8" s="140"/>
       <c r="E8" s="140"/>
       <c r="F8" s="140"/>
       <c r="G8" s="140"/>
       <c r="H8" s="140" t="s">
-        <v>2516</v>
+        <v>2503</v>
       </c>
       <c r="I8" s="140"/>
       <c r="J8" s="140" t="s">
+        <v>2515</v>
+      </c>
+      <c r="K8" s="140" t="s">
+        <v>2506</v>
+      </c>
+      <c r="L8" s="265" t="s">
+        <v>2554</v>
+      </c>
+      <c r="M8" s="140" t="s">
+        <v>2500</v>
+      </c>
+      <c r="N8" s="140" t="s">
+        <v>2505</v>
+      </c>
+      <c r="O8" t="s">
         <v>2528</v>
       </c>
-      <c r="K8" s="140" t="s">
-        <v>2519</v>
-      </c>
-      <c r="L8" s="265" t="s">
-        <v>2540</v>
-      </c>
-      <c r="M8" s="140" t="s">
-        <v>2513</v>
-      </c>
-      <c r="N8" s="140" t="s">
-        <v>2518</v>
-      </c>
-      <c r="O8" t="s">
-        <v>2542</v>
-      </c>
       <c r="P8" t="s">
-        <v>2547</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="33">
       <c r="A9" s="140" t="s">
-        <v>2505</v>
+        <v>2492</v>
       </c>
       <c r="B9" s="140">
         <v>7</v>
       </c>
       <c r="C9" s="140" t="s">
-        <v>2474</v>
+        <v>2461</v>
       </c>
       <c r="D9" s="140"/>
       <c r="E9" s="140"/>
       <c r="F9" s="140"/>
       <c r="G9" s="140"/>
       <c r="H9" s="140" t="s">
-        <v>2516</v>
+        <v>2503</v>
       </c>
       <c r="I9" s="140"/>
       <c r="J9" s="140" t="s">
+        <v>2515</v>
+      </c>
+      <c r="K9" s="140" t="s">
+        <v>2507</v>
+      </c>
+      <c r="L9" s="265" t="s">
+        <v>2527</v>
+      </c>
+      <c r="M9" s="140" t="s">
+        <v>2500</v>
+      </c>
+      <c r="N9" s="140" t="s">
+        <v>2505</v>
+      </c>
+      <c r="O9" t="s">
         <v>2528</v>
       </c>
-      <c r="K9" s="140" t="s">
-        <v>2520</v>
-      </c>
-      <c r="L9" s="265" t="s">
-        <v>2541</v>
-      </c>
-      <c r="M9" s="140" t="s">
-        <v>2513</v>
-      </c>
-      <c r="N9" s="140" t="s">
-        <v>2518</v>
-      </c>
-      <c r="O9" t="s">
-        <v>2542</v>
-      </c>
       <c r="P9" t="s">
-        <v>2547</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="140" t="s">
-        <v>2505</v>
+        <v>2492</v>
       </c>
       <c r="B10" s="140">
         <v>8</v>
       </c>
       <c r="C10" s="140" t="s">
-        <v>2474</v>
+        <v>2461</v>
       </c>
       <c r="D10" s="140"/>
       <c r="E10" s="140"/>
       <c r="F10" s="140"/>
       <c r="G10" s="140"/>
       <c r="H10" s="140" t="s">
-        <v>2521</v>
+        <v>2508</v>
       </c>
       <c r="I10" s="140"/>
       <c r="J10" s="140"/>
       <c r="K10" s="140"/>
       <c r="M10" s="140" t="s">
-        <v>2510</v>
+        <v>2497</v>
       </c>
       <c r="N10" s="140"/>
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="140" t="s">
-        <v>2505</v>
+        <v>2492</v>
       </c>
       <c r="B11" s="140">
         <v>9</v>
       </c>
       <c r="C11" s="140" t="s">
-        <v>2474</v>
+        <v>2461</v>
       </c>
       <c r="D11" s="140"/>
       <c r="E11" s="140"/>
       <c r="F11" s="140"/>
       <c r="G11" s="140"/>
       <c r="H11" s="140" t="s">
-        <v>2511</v>
+        <v>2498</v>
       </c>
       <c r="I11" s="140" t="s">
         <v>63</v>
       </c>
       <c r="J11" s="140" t="s">
-        <v>2527</v>
+        <v>2514</v>
       </c>
       <c r="K11" s="140" t="s">
-        <v>2522</v>
+        <v>2509</v>
       </c>
       <c r="L11" s="141" t="s">
-        <v>2534</v>
+        <v>2521</v>
       </c>
       <c r="M11" s="140" t="s">
-        <v>2513</v>
+        <v>2500</v>
       </c>
       <c r="N11" s="140"/>
       <c r="O11" t="s">
-        <v>2542</v>
+        <v>2528</v>
       </c>
       <c r="P11" t="s">
-        <v>2547</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="140" t="s">
-        <v>2505</v>
+        <v>2492</v>
       </c>
       <c r="B12" s="140">
         <v>10</v>
       </c>
       <c r="C12" s="140" t="s">
-        <v>2474</v>
+        <v>2461</v>
       </c>
       <c r="D12" s="140"/>
       <c r="E12" s="140"/>
       <c r="F12" s="140"/>
       <c r="G12" s="140"/>
       <c r="H12" s="140" t="s">
-        <v>2511</v>
+        <v>2498</v>
       </c>
       <c r="I12" s="140" t="s">
         <v>46</v>
       </c>
       <c r="J12" s="140" t="s">
-        <v>2527</v>
+        <v>2514</v>
       </c>
       <c r="K12" s="140" t="s">
-        <v>2523</v>
+        <v>2510</v>
       </c>
       <c r="L12" s="141" t="s">
-        <v>2535</v>
+        <v>2522</v>
       </c>
       <c r="M12" s="140" t="s">
-        <v>2513</v>
+        <v>2500</v>
       </c>
       <c r="N12" s="140"/>
       <c r="O12" t="s">
-        <v>2542</v>
+        <v>2528</v>
       </c>
       <c r="P12" t="s">
-        <v>2547</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -39948,7 +39971,7 @@
         <v>216</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>2432</v>
+        <v>2430</v>
       </c>
       <c r="E11" s="16">
         <v>0</v>
@@ -39974,7 +39997,7 @@
         <v>216</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>2434</v>
+        <v>2432</v>
       </c>
       <c r="E12" s="16">
         <v>0</v>
@@ -40306,7 +40329,7 @@
         <v>1371</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>2429</v>
+        <v>2427</v>
       </c>
       <c r="C25" s="16" t="s">
         <v>1356</v>
@@ -40315,7 +40338,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>2361</v>
+        <v>2359</v>
       </c>
       <c r="F25" s="16" t="s">
         <v>1314</v>
@@ -40329,7 +40352,7 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="16" t="s">
-        <v>2431</v>
+        <v>2429</v>
       </c>
       <c r="B26" s="16" t="s">
         <v>1372</v>
@@ -40355,10 +40378,10 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="16" t="s">
-        <v>2473</v>
+        <v>2460</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>2430</v>
+        <v>2428</v>
       </c>
       <c r="C27" s="16" t="s">
         <v>1356</v>
@@ -40367,7 +40390,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>2404</v>
+        <v>2402</v>
       </c>
       <c r="F27" s="16" t="s">
         <v>1314</v>
@@ -40381,16 +40404,16 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="16" t="s">
-        <v>2475</v>
+        <v>2462</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>2476</v>
+        <v>2463</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>2477</v>
+        <v>2464</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>2472</v>
+        <v>2459</v>
       </c>
       <c r="E28" s="16">
         <v>0</v>
@@ -40407,16 +40430,16 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="16" t="s">
-        <v>2478</v>
+        <v>2465</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>2479</v>
+        <v>2466</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>2477</v>
+        <v>2464</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>2481</v>
+        <v>2468</v>
       </c>
       <c r="E29" s="16">
         <v>0</v>
@@ -40436,16 +40459,16 @@
         <v>1377</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>2480</v>
+        <v>2467</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>2477</v>
+        <v>2464</v>
       </c>
       <c r="D30" s="16">
         <v>0</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>2440</v>
+        <v>2438</v>
       </c>
       <c r="F30" s="16" t="s">
         <v>1314</v>
@@ -40556,7 +40579,7 @@
         <v>1396</v>
       </c>
       <c r="H2" s="143" t="s">
-        <v>2555</v>
+        <v>2541</v>
       </c>
       <c r="I2" s="143" t="s">
         <v>1397</v>
@@ -41439,7 +41462,7 @@
     </row>
     <row r="24" spans="1:26" ht="17.25" customHeight="1">
       <c r="A24" s="233" t="s">
-        <v>2433</v>
+        <v>2431</v>
       </c>
       <c r="B24" s="187" t="s">
         <v>214</v>
@@ -41498,7 +41521,7 @@
     </row>
     <row r="25" spans="1:26" ht="17.25" thickBot="1">
       <c r="A25" s="151" t="s">
-        <v>2433</v>
+        <v>2431</v>
       </c>
       <c r="B25" s="152" t="s">
         <v>178</v>
@@ -41537,7 +41560,7 @@
     </row>
     <row r="26" spans="1:26">
       <c r="A26" s="144" t="s">
-        <v>2435</v>
+        <v>2433</v>
       </c>
       <c r="B26" s="145" t="s">
         <v>214</v>
@@ -41596,7 +41619,7 @@
     </row>
     <row r="27" spans="1:26" ht="17.25" customHeight="1" thickBot="1">
       <c r="A27" s="151" t="s">
-        <v>2435</v>
+        <v>2433</v>
       </c>
       <c r="B27" s="152" t="s">
         <v>185</v>
@@ -41635,7 +41658,7 @@
     </row>
     <row r="28" spans="1:26" ht="17.25" thickBot="1">
       <c r="A28" s="156" t="s">
-        <v>2436</v>
+        <v>2434</v>
       </c>
       <c r="B28" s="157" t="s">
         <v>222</v>
@@ -41689,7 +41712,7 @@
     </row>
     <row r="29" spans="1:26">
       <c r="A29" s="144" t="s">
-        <v>2437</v>
+        <v>2435</v>
       </c>
       <c r="B29" s="145" t="s">
         <v>202</v>
@@ -41743,7 +41766,7 @@
     </row>
     <row r="30" spans="1:26" ht="17.25" customHeight="1" thickBot="1">
       <c r="A30" s="151" t="s">
-        <v>2437</v>
+        <v>2435</v>
       </c>
       <c r="B30" s="152" t="s">
         <v>229</v>
@@ -41778,7 +41801,7 @@
     </row>
     <row r="31" spans="1:26">
       <c r="A31" s="144" t="s">
-        <v>2438</v>
+        <v>2436</v>
       </c>
       <c r="B31" s="145" t="s">
         <v>208</v>
@@ -41837,7 +41860,7 @@
     </row>
     <row r="32" spans="1:26" ht="17.25" customHeight="1" thickBot="1">
       <c r="A32" s="151" t="s">
-        <v>2438</v>
+        <v>2436</v>
       </c>
       <c r="B32" s="152" t="s">
         <v>229</v>
@@ -41876,7 +41899,7 @@
     </row>
     <row r="33" spans="1:26" ht="17.25" thickBot="1">
       <c r="A33" s="156" t="s">
-        <v>2439</v>
+        <v>2437</v>
       </c>
       <c r="B33" s="157" t="s">
         <v>2107</v>
@@ -41935,7 +41958,7 @@
     </row>
     <row r="34" spans="1:26" ht="17.25" customHeight="1">
       <c r="A34" s="187" t="s">
-        <v>2472</v>
+        <v>2459</v>
       </c>
       <c r="B34" s="187" t="s">
         <v>2110</v>
@@ -41994,7 +42017,7 @@
     </row>
     <row r="35" spans="1:26" ht="17.25" customHeight="1">
       <c r="A35" s="16" t="s">
-        <v>2481</v>
+        <v>2468</v>
       </c>
       <c r="B35" s="16" t="s">
         <v>2116</v>
@@ -42012,7 +42035,7 @@
         <v>-1</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>2482</v>
+        <v>2469</v>
       </c>
       <c r="H35" s="17">
         <v>0</v>
@@ -42053,7 +42076,7 @@
     </row>
     <row r="36" spans="1:26">
       <c r="A36" s="16" t="s">
-        <v>2481</v>
+        <v>2468</v>
       </c>
       <c r="B36" s="16" t="s">
         <v>2113</v>
@@ -42410,7 +42433,7 @@
       <c r="E3" s="241" t="s">
         <v>2235</v>
       </c>
-      <c r="F3" s="241" t="s">
+      <c r="F3" s="279" t="s">
         <v>2276</v>
       </c>
       <c r="G3" s="241"/>
@@ -42429,7 +42452,7 @@
         <v>2239</v>
       </c>
       <c r="P3" s="241" t="s">
-        <v>2551</v>
+        <v>2537</v>
       </c>
       <c r="Q3" s="241">
         <v>1</v>
@@ -42469,7 +42492,7 @@
       <c r="E4" s="161" t="s">
         <v>2236</v>
       </c>
-      <c r="F4" s="161" t="s">
+      <c r="F4" s="280" t="s">
         <v>2277</v>
       </c>
       <c r="G4" s="161"/>
@@ -42488,7 +42511,7 @@
         <v>2240</v>
       </c>
       <c r="P4" s="161" t="s">
-        <v>2551</v>
+        <v>2537</v>
       </c>
       <c r="Q4" s="161">
         <v>1</v>
@@ -42528,7 +42551,7 @@
       <c r="E5" s="161" t="s">
         <v>2237</v>
       </c>
-      <c r="F5" s="161" t="s">
+      <c r="F5" s="280" t="s">
         <v>2278</v>
       </c>
       <c r="G5" s="161"/>
@@ -42547,7 +42570,7 @@
         <v>2241</v>
       </c>
       <c r="P5" s="161" t="s">
-        <v>2551</v>
+        <v>2537</v>
       </c>
       <c r="Q5" s="161">
         <v>1</v>
@@ -42585,7 +42608,7 @@
       </c>
       <c r="D6" s="240"/>
       <c r="E6" s="240"/>
-      <c r="F6" s="240"/>
+      <c r="F6" s="281"/>
       <c r="G6" s="240"/>
       <c r="H6" s="240"/>
       <c r="I6" s="240"/>
@@ -42628,7 +42651,7 @@
       <c r="E7" s="241" t="s">
         <v>2255</v>
       </c>
-      <c r="F7" s="241" t="s">
+      <c r="F7" s="279" t="s">
         <v>2280</v>
       </c>
       <c r="G7" s="241"/>
@@ -42683,7 +42706,7 @@
       <c r="E8" s="161" t="s">
         <v>2256</v>
       </c>
-      <c r="F8" s="161" t="s">
+      <c r="F8" s="280" t="s">
         <v>2279</v>
       </c>
       <c r="G8" s="161"/>
@@ -42728,11 +42751,11 @@
       </c>
       <c r="B9" s="161"/>
       <c r="C9" s="161" t="s">
-        <v>2383</v>
+        <v>2381</v>
       </c>
       <c r="D9" s="161"/>
       <c r="E9" s="161"/>
-      <c r="F9" s="161"/>
+      <c r="F9" s="280"/>
       <c r="G9" s="161"/>
       <c r="H9" s="161"/>
       <c r="I9" s="161"/>
@@ -42769,7 +42792,7 @@
       </c>
       <c r="D10" s="161"/>
       <c r="E10" s="161"/>
-      <c r="F10" s="161"/>
+      <c r="F10" s="280"/>
       <c r="G10" s="161"/>
       <c r="H10" s="161"/>
       <c r="I10" s="161"/>
@@ -42806,7 +42829,7 @@
       </c>
       <c r="D11" s="161"/>
       <c r="E11" s="161"/>
-      <c r="F11" s="161"/>
+      <c r="F11" s="280"/>
       <c r="G11" s="161"/>
       <c r="H11" s="161"/>
       <c r="I11" s="161"/>
@@ -42849,7 +42872,7 @@
       <c r="E12" s="241" t="s">
         <v>2212</v>
       </c>
-      <c r="F12" s="241" t="s">
+      <c r="F12" s="279" t="s">
         <v>2215</v>
       </c>
       <c r="G12" s="241"/>
@@ -42906,7 +42929,7 @@
       <c r="E13" s="161" t="s">
         <v>2213</v>
       </c>
-      <c r="F13" s="161" t="s">
+      <c r="F13" s="280" t="s">
         <v>2216</v>
       </c>
       <c r="G13" s="161"/>
@@ -42961,7 +42984,7 @@
       <c r="E14" s="161" t="s">
         <v>2214</v>
       </c>
-      <c r="F14" s="161" t="s">
+      <c r="F14" s="280" t="s">
         <v>2217</v>
       </c>
       <c r="G14" s="161"/>
@@ -43014,7 +43037,7 @@
       </c>
       <c r="D15" s="161"/>
       <c r="E15" s="161"/>
-      <c r="F15" s="161"/>
+      <c r="F15" s="280"/>
       <c r="G15" s="161"/>
       <c r="H15" s="161"/>
       <c r="I15" s="161"/>
@@ -43051,7 +43074,7 @@
       </c>
       <c r="D16" s="161"/>
       <c r="E16" s="161"/>
-      <c r="F16" s="161"/>
+      <c r="F16" s="280"/>
       <c r="G16" s="161"/>
       <c r="H16" s="161"/>
       <c r="I16" s="161"/>
@@ -43088,7 +43111,7 @@
       </c>
       <c r="D17" s="240"/>
       <c r="E17" s="240"/>
-      <c r="F17" s="240"/>
+      <c r="F17" s="281"/>
       <c r="G17" s="240"/>
       <c r="H17" s="240"/>
       <c r="I17" s="240"/>
@@ -43131,8 +43154,8 @@
       <c r="E18" s="161" t="s">
         <v>2289</v>
       </c>
-      <c r="F18" s="161" t="s">
-        <v>2457</v>
+      <c r="F18" s="280" t="s">
+        <v>2453</v>
       </c>
       <c r="G18" s="241" t="s">
         <v>2286</v>
@@ -43141,7 +43164,7 @@
         <v>2285</v>
       </c>
       <c r="I18" s="241" t="s">
-        <v>2423</v>
+        <v>2421</v>
       </c>
       <c r="J18" s="241" t="s">
         <v>2288</v>
@@ -43200,8 +43223,8 @@
       <c r="E19" s="161" t="s">
         <v>2290</v>
       </c>
-      <c r="F19" s="161" t="s">
-        <v>2458</v>
+      <c r="F19" s="280" t="s">
+        <v>2454</v>
       </c>
       <c r="G19" s="161" t="s">
         <v>2286</v>
@@ -43210,7 +43233,7 @@
         <v>2285</v>
       </c>
       <c r="I19" s="161" t="s">
-        <v>2424</v>
+        <v>2422</v>
       </c>
       <c r="J19" s="161" t="s">
         <v>2288</v>
@@ -43269,7 +43292,7 @@
       <c r="E20" s="161" t="s">
         <v>2275</v>
       </c>
-      <c r="F20" s="161" t="s">
+      <c r="F20" s="280" t="s">
         <v>2279</v>
       </c>
       <c r="G20" s="161"/>
@@ -43318,7 +43341,7 @@
       </c>
       <c r="D21" s="161"/>
       <c r="E21" s="161"/>
-      <c r="F21" s="161"/>
+      <c r="F21" s="280"/>
       <c r="G21" s="161"/>
       <c r="H21" s="161"/>
       <c r="I21" s="161"/>
@@ -43355,7 +43378,7 @@
       </c>
       <c r="D22" s="161"/>
       <c r="E22" s="161"/>
-      <c r="F22" s="161"/>
+      <c r="F22" s="280"/>
       <c r="G22" s="161"/>
       <c r="H22" s="161"/>
       <c r="I22" s="161"/>
@@ -43388,11 +43411,11 @@
       </c>
       <c r="B23" s="245"/>
       <c r="C23" s="240" t="s">
-        <v>2384</v>
+        <v>2382</v>
       </c>
       <c r="D23" s="240"/>
       <c r="E23" s="240"/>
-      <c r="F23" s="240"/>
+      <c r="F23" s="281"/>
       <c r="G23" s="240"/>
       <c r="H23" s="240"/>
       <c r="I23" s="240"/>
@@ -43435,8 +43458,8 @@
       <c r="E24" s="241" t="s">
         <v>2296</v>
       </c>
-      <c r="F24" s="241" t="s">
-        <v>2459</v>
+      <c r="F24" s="279" t="s">
+        <v>2546</v>
       </c>
       <c r="G24" s="241"/>
       <c r="H24" s="241" t="s">
@@ -43496,8 +43519,8 @@
       <c r="E25" s="161" t="s">
         <v>2297</v>
       </c>
-      <c r="F25" s="161" t="s">
-        <v>2460</v>
+      <c r="F25" s="280" t="s">
+        <v>2547</v>
       </c>
       <c r="G25" s="161"/>
       <c r="H25" s="161" t="s">
@@ -43557,8 +43580,8 @@
       <c r="E26" s="161" t="s">
         <v>2298</v>
       </c>
-      <c r="F26" s="161" t="s">
-        <v>2461</v>
+      <c r="F26" s="280" t="s">
+        <v>2548</v>
       </c>
       <c r="G26" s="161"/>
       <c r="H26" s="161" t="s">
@@ -43616,7 +43639,7 @@
       </c>
       <c r="D27" s="161"/>
       <c r="E27" s="161"/>
-      <c r="F27" s="161"/>
+      <c r="F27" s="280"/>
       <c r="G27" s="161"/>
       <c r="H27" s="161"/>
       <c r="I27" s="161"/>
@@ -43653,7 +43676,7 @@
       </c>
       <c r="D28" s="161"/>
       <c r="E28" s="161"/>
-      <c r="F28" s="161"/>
+      <c r="F28" s="280"/>
       <c r="G28" s="161"/>
       <c r="H28" s="161"/>
       <c r="I28" s="161"/>
@@ -43690,7 +43713,7 @@
       </c>
       <c r="D29" s="161"/>
       <c r="E29" s="161"/>
-      <c r="F29" s="161"/>
+      <c r="F29" s="280"/>
       <c r="G29" s="161"/>
       <c r="H29" s="161"/>
       <c r="I29" s="161"/>
@@ -43727,7 +43750,7 @@
       </c>
       <c r="D30" s="240"/>
       <c r="E30" s="240"/>
-      <c r="F30" s="240"/>
+      <c r="F30" s="281"/>
       <c r="G30" s="240"/>
       <c r="H30" s="240"/>
       <c r="I30" s="240"/>
@@ -43770,8 +43793,8 @@
       <c r="E31" s="241" t="s">
         <v>2317</v>
       </c>
-      <c r="F31" s="241" t="s">
-        <v>2462</v>
+      <c r="F31" s="279" t="s">
+        <v>2549</v>
       </c>
       <c r="G31" s="241"/>
       <c r="H31" s="241" t="s">
@@ -43835,7 +43858,7 @@
       <c r="E32" s="161" t="s">
         <v>2318</v>
       </c>
-      <c r="F32" s="161" t="s">
+      <c r="F32" s="280" t="s">
         <v>2279</v>
       </c>
       <c r="G32" s="161"/>
@@ -43865,13 +43888,13 @@
         <v>1422</v>
       </c>
       <c r="Y32" s="161" t="s">
-        <v>2552</v>
+        <v>2538</v>
       </c>
       <c r="Z32" s="161" t="s">
         <v>1422</v>
       </c>
       <c r="AA32" s="249" t="s">
-        <v>2554</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="33" spans="1:27" ht="54.95" customHeight="1">
@@ -43888,8 +43911,8 @@
       <c r="E33" s="161" t="s">
         <v>2321</v>
       </c>
-      <c r="F33" s="161" t="s">
-        <v>2463</v>
+      <c r="F33" s="280" t="s">
+        <v>2550</v>
       </c>
       <c r="G33" s="161"/>
       <c r="H33" s="161" t="s">
@@ -43932,7 +43955,7 @@
         <v>1422</v>
       </c>
       <c r="Y33" s="161" t="s">
-        <v>2382</v>
+        <v>2380</v>
       </c>
       <c r="Z33" s="161" t="s">
         <v>1422</v>
@@ -43953,7 +43976,7 @@
       <c r="E34" s="161" t="s">
         <v>2322</v>
       </c>
-      <c r="F34" s="161" t="s">
+      <c r="F34" s="280" t="s">
         <v>2279</v>
       </c>
       <c r="G34" s="161"/>
@@ -43983,13 +44006,13 @@
         <v>1422</v>
       </c>
       <c r="Y34" s="161" t="s">
-        <v>2552</v>
+        <v>2538</v>
       </c>
       <c r="Z34" s="161" t="s">
         <v>1422</v>
       </c>
       <c r="AA34" s="249" t="s">
-        <v>2554</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="35" spans="1:27" ht="54.95" customHeight="1">
@@ -44006,8 +44029,8 @@
       <c r="E35" s="161" t="s">
         <v>2324</v>
       </c>
-      <c r="F35" s="161" t="s">
-        <v>2556</v>
+      <c r="F35" s="280" t="s">
+        <v>2551</v>
       </c>
       <c r="G35" s="161"/>
       <c r="H35" s="161" t="s">
@@ -44018,7 +44041,7 @@
       <c r="K35" s="161"/>
       <c r="L35" s="161"/>
       <c r="M35" s="161" t="s">
-        <v>2557</v>
+        <v>2542</v>
       </c>
       <c r="N35" s="161" t="s">
         <v>2224</v>
@@ -44052,7 +44075,7 @@
         <v>1422</v>
       </c>
       <c r="Y35" s="161" t="s">
-        <v>2553</v>
+        <v>2539</v>
       </c>
       <c r="Z35" s="161" t="s">
         <v>1422</v>
@@ -44073,7 +44096,7 @@
       <c r="E36" s="161" t="s">
         <v>2322</v>
       </c>
-      <c r="F36" s="161" t="s">
+      <c r="F36" s="280" t="s">
         <v>2279</v>
       </c>
       <c r="G36" s="161"/>
@@ -44103,13 +44126,13 @@
         <v>2335</v>
       </c>
       <c r="Y36" s="161" t="s">
-        <v>2552</v>
+        <v>2538</v>
       </c>
       <c r="Z36" s="161" t="s">
         <v>1422</v>
       </c>
       <c r="AA36" s="249" t="s">
-        <v>2554</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="37" spans="1:27" ht="54.95" customHeight="1">
@@ -44122,7 +44145,7 @@
       </c>
       <c r="D37" s="161"/>
       <c r="E37" s="161"/>
-      <c r="F37" s="161"/>
+      <c r="F37" s="280"/>
       <c r="G37" s="161"/>
       <c r="H37" s="161"/>
       <c r="I37" s="161"/>
@@ -44159,7 +44182,7 @@
       </c>
       <c r="D38" s="161"/>
       <c r="E38" s="161"/>
-      <c r="F38" s="161"/>
+      <c r="F38" s="280"/>
       <c r="G38" s="161"/>
       <c r="H38" s="161"/>
       <c r="I38" s="161"/>
@@ -44196,7 +44219,7 @@
       </c>
       <c r="D39" s="161"/>
       <c r="E39" s="161"/>
-      <c r="F39" s="161"/>
+      <c r="F39" s="280"/>
       <c r="G39" s="161"/>
       <c r="H39" s="161"/>
       <c r="I39" s="161"/>
@@ -44233,7 +44256,7 @@
       </c>
       <c r="D40" s="242"/>
       <c r="E40" s="242"/>
-      <c r="F40" s="242"/>
+      <c r="F40" s="282"/>
       <c r="G40" s="242"/>
       <c r="H40" s="242"/>
       <c r="I40" s="242"/>
@@ -44268,27 +44291,27 @@
         <v>2346</v>
       </c>
       <c r="C41" s="241" t="s">
-        <v>2385</v>
+        <v>2383</v>
       </c>
       <c r="D41" s="241">
         <v>1</v>
       </c>
       <c r="E41" s="241" t="s">
-        <v>2358</v>
-      </c>
-      <c r="F41" s="241" t="s">
-        <v>2464</v>
+        <v>2356</v>
+      </c>
+      <c r="F41" s="279" t="s">
+        <v>2543</v>
       </c>
       <c r="G41" s="241"/>
       <c r="H41" s="241" t="s">
-        <v>2356</v>
+        <v>2308</v>
       </c>
       <c r="I41" s="241"/>
       <c r="J41" s="241"/>
       <c r="K41" s="241"/>
       <c r="L41" s="241"/>
       <c r="M41" s="241" t="s">
-        <v>2446</v>
+        <v>2309</v>
       </c>
       <c r="N41" s="241" t="s">
         <v>2337</v>
@@ -44333,10 +44356,10 @@
         <v>2</v>
       </c>
       <c r="E42" s="161" t="s">
-        <v>2442</v>
-      </c>
-      <c r="F42" s="161" t="s">
-        <v>2441</v>
+        <v>2440</v>
+      </c>
+      <c r="F42" s="280" t="s">
+        <v>2439</v>
       </c>
       <c r="G42" s="161"/>
       <c r="H42" s="161" t="s">
@@ -44355,7 +44378,7 @@
       <c r="Q42" s="161"/>
       <c r="R42" s="161"/>
       <c r="S42" s="161" t="s">
-        <v>2447</v>
+        <v>2444</v>
       </c>
       <c r="T42" s="161"/>
       <c r="U42" s="161"/>
@@ -44382,21 +44405,21 @@
         <v>1</v>
       </c>
       <c r="E43" s="161" t="s">
-        <v>2359</v>
-      </c>
-      <c r="F43" s="161" t="s">
-        <v>2465</v>
+        <v>2357</v>
+      </c>
+      <c r="F43" s="280" t="s">
+        <v>2544</v>
       </c>
       <c r="G43" s="161"/>
       <c r="H43" s="161" t="s">
-        <v>2355</v>
+        <v>2308</v>
       </c>
       <c r="I43" s="161"/>
       <c r="J43" s="161"/>
       <c r="K43" s="161"/>
       <c r="L43" s="161"/>
       <c r="M43" s="161" t="s">
-        <v>2446</v>
+        <v>2310</v>
       </c>
       <c r="N43" s="161" t="s">
         <v>1417</v>
@@ -44441,14 +44464,14 @@
         <v>2</v>
       </c>
       <c r="E44" s="161" t="s">
-        <v>2443</v>
-      </c>
-      <c r="F44" s="161" t="s">
         <v>2441</v>
+      </c>
+      <c r="F44" s="280" t="s">
+        <v>2439</v>
       </c>
       <c r="G44" s="161"/>
       <c r="H44" s="161" t="s">
-        <v>2444</v>
+        <v>2442</v>
       </c>
       <c r="I44" s="161"/>
       <c r="J44" s="161"/>
@@ -44456,14 +44479,14 @@
       <c r="L44" s="161"/>
       <c r="M44" s="161"/>
       <c r="N44" s="161" t="s">
-        <v>2445</v>
+        <v>2443</v>
       </c>
       <c r="O44" s="161"/>
       <c r="P44" s="161"/>
       <c r="Q44" s="161"/>
       <c r="R44" s="161"/>
       <c r="S44" s="161" t="s">
-        <v>2447</v>
+        <v>2444</v>
       </c>
       <c r="T44" s="161"/>
       <c r="U44" s="161"/>
@@ -44484,27 +44507,27 @@
       </c>
       <c r="B45" s="244"/>
       <c r="C45" s="161" t="s">
-        <v>2357</v>
+        <v>2355</v>
       </c>
       <c r="D45" s="161">
         <v>1</v>
       </c>
       <c r="E45" s="161" t="s">
-        <v>2360</v>
-      </c>
-      <c r="F45" s="161" t="s">
-        <v>2466</v>
+        <v>2358</v>
+      </c>
+      <c r="F45" s="280" t="s">
+        <v>2545</v>
       </c>
       <c r="G45" s="161"/>
       <c r="H45" s="161" t="s">
-        <v>2356</v>
+        <v>2308</v>
       </c>
       <c r="I45" s="161"/>
       <c r="J45" s="161"/>
       <c r="K45" s="161"/>
       <c r="L45" s="161"/>
       <c r="M45" s="161" t="s">
-        <v>2446</v>
+        <v>2311</v>
       </c>
       <c r="N45" s="161" t="s">
         <v>1417</v>
@@ -44549,14 +44572,14 @@
         <v>2</v>
       </c>
       <c r="E46" s="161" t="s">
-        <v>2443</v>
-      </c>
-      <c r="F46" s="161" t="s">
         <v>2441</v>
+      </c>
+      <c r="F46" s="280" t="s">
+        <v>2439</v>
       </c>
       <c r="G46" s="161"/>
       <c r="H46" s="161" t="s">
-        <v>2444</v>
+        <v>2442</v>
       </c>
       <c r="I46" s="161"/>
       <c r="J46" s="161"/>
@@ -44564,14 +44587,14 @@
       <c r="L46" s="161"/>
       <c r="M46" s="161"/>
       <c r="N46" s="161" t="s">
-        <v>2445</v>
+        <v>2443</v>
       </c>
       <c r="O46" s="161"/>
       <c r="P46" s="161"/>
       <c r="Q46" s="161"/>
       <c r="R46" s="161"/>
       <c r="S46" s="161" t="s">
-        <v>2447</v>
+        <v>2444</v>
       </c>
       <c r="T46" s="161"/>
       <c r="U46" s="161"/>
@@ -44596,7 +44619,7 @@
       </c>
       <c r="D47" s="244"/>
       <c r="E47" s="244"/>
-      <c r="F47" s="272"/>
+      <c r="F47" s="283"/>
       <c r="G47" s="244"/>
       <c r="H47" s="244"/>
       <c r="I47" s="244"/>
@@ -44633,7 +44656,7 @@
       </c>
       <c r="D48" s="244"/>
       <c r="E48" s="244"/>
-      <c r="F48" s="273"/>
+      <c r="F48" s="124"/>
       <c r="G48" s="244"/>
       <c r="H48" s="161"/>
       <c r="I48" s="244"/>
@@ -44661,16 +44684,16 @@
       <c r="AA48" s="249"/>
     </row>
     <row r="49" spans="1:27" ht="54.95" customHeight="1" thickBot="1">
-      <c r="A49" s="274" t="s">
-        <v>2447</v>
+      <c r="A49" s="272" t="s">
+        <v>2444</v>
       </c>
       <c r="B49" s="260"/>
       <c r="C49" s="260" t="s">
-        <v>2448</v>
+        <v>2445</v>
       </c>
       <c r="D49" s="260"/>
       <c r="E49" s="260"/>
-      <c r="F49" s="275"/>
+      <c r="F49" s="284"/>
       <c r="G49" s="260"/>
       <c r="H49" s="261"/>
       <c r="I49" s="260"/>
@@ -44698,23 +44721,23 @@
       <c r="AA49" s="262"/>
     </row>
     <row r="50" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A50" s="276" t="s">
-        <v>2362</v>
+      <c r="A50" s="273" t="s">
+        <v>2360</v>
       </c>
       <c r="B50" s="253" t="s">
-        <v>2363</v>
+        <v>2361</v>
       </c>
       <c r="C50" s="253" t="s">
-        <v>2373</v>
+        <v>2371</v>
       </c>
       <c r="D50" s="253">
         <v>1</v>
       </c>
       <c r="E50" s="253" t="s">
-        <v>2454</v>
-      </c>
-      <c r="F50" s="253" t="s">
         <v>2450</v>
+      </c>
+      <c r="F50" s="285" t="s">
+        <v>2446</v>
       </c>
       <c r="G50" s="253"/>
       <c r="H50" s="253" t="s">
@@ -44726,33 +44749,33 @@
       <c r="L50" s="253"/>
       <c r="M50" s="253"/>
       <c r="N50" s="253" t="s">
-        <v>2376</v>
+        <v>2374</v>
       </c>
       <c r="O50" s="253" t="s">
-        <v>2377</v>
+        <v>2375</v>
       </c>
       <c r="P50" s="253"/>
       <c r="Q50" s="253"/>
       <c r="R50" s="253"/>
       <c r="S50" s="253" t="s">
-        <v>2364</v>
+        <v>2362</v>
       </c>
       <c r="T50" s="253"/>
       <c r="U50" s="253"/>
       <c r="V50" s="253"/>
       <c r="W50" s="253"/>
       <c r="X50" s="253" t="s">
-        <v>2370</v>
+        <v>2368</v>
       </c>
       <c r="Y50" s="253"/>
       <c r="Z50" s="253" t="s">
-        <v>2369</v>
+        <v>2367</v>
       </c>
       <c r="AA50" s="254"/>
     </row>
     <row r="51" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A51" s="277" t="s">
-        <v>2361</v>
+      <c r="A51" s="274" t="s">
+        <v>2359</v>
       </c>
       <c r="B51" s="244"/>
       <c r="C51" s="244"/>
@@ -44760,10 +44783,10 @@
         <v>2</v>
       </c>
       <c r="E51" s="244" t="s">
-        <v>2455</v>
-      </c>
-      <c r="F51" s="244" t="s">
         <v>2451</v>
+      </c>
+      <c r="F51" s="286" t="s">
+        <v>2447</v>
       </c>
       <c r="G51" s="244"/>
       <c r="H51" s="244" t="s">
@@ -44775,33 +44798,33 @@
       <c r="L51" s="244"/>
       <c r="M51" s="244"/>
       <c r="N51" s="244" t="s">
+        <v>2374</v>
+      </c>
+      <c r="O51" s="244" t="s">
         <v>2376</v>
-      </c>
-      <c r="O51" s="244" t="s">
-        <v>2378</v>
       </c>
       <c r="P51" s="244"/>
       <c r="Q51" s="244"/>
       <c r="R51" s="244"/>
       <c r="S51" s="244" t="s">
-        <v>2364</v>
+        <v>2362</v>
       </c>
       <c r="T51" s="244"/>
       <c r="U51" s="244"/>
       <c r="V51" s="244"/>
       <c r="W51" s="244"/>
       <c r="X51" s="244" t="s">
-        <v>2369</v>
+        <v>2367</v>
       </c>
       <c r="Y51" s="244"/>
       <c r="Z51" s="244" t="s">
-        <v>2369</v>
+        <v>2367</v>
       </c>
       <c r="AA51" s="252"/>
     </row>
     <row r="52" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A52" s="277" t="s">
-        <v>2362</v>
+      <c r="A52" s="274" t="s">
+        <v>2360</v>
       </c>
       <c r="B52" s="244"/>
       <c r="C52" s="244"/>
@@ -44809,10 +44832,10 @@
         <v>3</v>
       </c>
       <c r="E52" s="244" t="s">
-        <v>2456</v>
-      </c>
-      <c r="F52" s="244" t="s">
         <v>2452</v>
+      </c>
+      <c r="F52" s="286" t="s">
+        <v>2448</v>
       </c>
       <c r="G52" s="244"/>
       <c r="H52" s="244" t="s">
@@ -44824,46 +44847,46 @@
       <c r="L52" s="244"/>
       <c r="M52" s="244"/>
       <c r="N52" s="244" t="s">
-        <v>2376</v>
+        <v>2374</v>
       </c>
       <c r="O52" s="244" t="s">
-        <v>2379</v>
+        <v>2377</v>
       </c>
       <c r="P52" s="244"/>
       <c r="Q52" s="244"/>
       <c r="R52" s="244"/>
       <c r="S52" s="244" t="s">
-        <v>2364</v>
+        <v>2362</v>
       </c>
       <c r="T52" s="244"/>
       <c r="U52" s="244"/>
       <c r="V52" s="244"/>
       <c r="W52" s="244"/>
       <c r="X52" s="244" t="s">
-        <v>2369</v>
+        <v>2367</v>
       </c>
       <c r="Y52" s="244"/>
       <c r="Z52" s="244" t="s">
-        <v>2369</v>
+        <v>2367</v>
       </c>
       <c r="AA52" s="252"/>
     </row>
     <row r="53" spans="1:27" s="3" customFormat="1" ht="54.95" customHeight="1">
-      <c r="A53" s="277" t="s">
-        <v>2364</v>
+      <c r="A53" s="274" t="s">
+        <v>2362</v>
       </c>
       <c r="B53" s="244"/>
       <c r="C53" s="244" t="s">
-        <v>2374</v>
+        <v>2372</v>
       </c>
       <c r="D53" s="244">
         <v>1</v>
       </c>
       <c r="E53" s="244" t="s">
-        <v>2365</v>
-      </c>
-      <c r="F53" s="244" t="s">
-        <v>2368</v>
+        <v>2363</v>
+      </c>
+      <c r="F53" s="286" t="s">
+        <v>2366</v>
       </c>
       <c r="G53" s="244"/>
       <c r="H53" s="244" t="s">
@@ -44878,7 +44901,7 @@
         <v>2228</v>
       </c>
       <c r="O53" s="244" t="s">
-        <v>2380</v>
+        <v>2378</v>
       </c>
       <c r="P53" s="244"/>
       <c r="Q53" s="244">
@@ -44886,28 +44909,28 @@
       </c>
       <c r="R53" s="244"/>
       <c r="S53" s="244" t="s">
-        <v>2372</v>
+        <v>2370</v>
       </c>
       <c r="T53" s="244"/>
       <c r="U53" s="244"/>
       <c r="V53" s="244"/>
       <c r="W53" s="244"/>
       <c r="X53" s="244" t="s">
-        <v>2369</v>
+        <v>2367</v>
       </c>
       <c r="Y53" s="244" t="s">
         <v>2247</v>
       </c>
       <c r="Z53" s="244" t="s">
-        <v>2369</v>
+        <v>2367</v>
       </c>
       <c r="AA53" s="252" t="s">
         <v>2336</v>
       </c>
     </row>
     <row r="54" spans="1:27" s="3" customFormat="1" ht="54.95" customHeight="1">
-      <c r="A54" s="277" t="s">
-        <v>2364</v>
+      <c r="A54" s="274" t="s">
+        <v>2362</v>
       </c>
       <c r="B54" s="244"/>
       <c r="C54" s="244"/>
@@ -44915,10 +44938,10 @@
         <v>2</v>
       </c>
       <c r="E54" s="244" t="s">
-        <v>2366</v>
-      </c>
-      <c r="F54" s="273" t="s">
-        <v>2467</v>
+        <v>2364</v>
+      </c>
+      <c r="F54" s="124" t="s">
+        <v>2455</v>
       </c>
       <c r="G54" s="244" t="s">
         <v>2286</v>
@@ -44927,7 +44950,7 @@
         <v>2285</v>
       </c>
       <c r="I54" s="244" t="s">
-        <v>2425</v>
+        <v>2423</v>
       </c>
       <c r="J54" s="244" t="s">
         <v>2288</v>
@@ -44943,7 +44966,7 @@
         <v>2238</v>
       </c>
       <c r="O54" s="244" t="s">
-        <v>2381</v>
+        <v>2379</v>
       </c>
       <c r="P54" s="244" t="s">
         <v>2313</v>
@@ -44955,28 +44978,28 @@
         <v>3</v>
       </c>
       <c r="S54" s="244" t="s">
-        <v>2372</v>
+        <v>2370</v>
       </c>
       <c r="T54" s="244"/>
       <c r="U54" s="244"/>
       <c r="V54" s="244"/>
       <c r="W54" s="244"/>
       <c r="X54" s="244" t="s">
+        <v>2367</v>
+      </c>
+      <c r="Y54" s="161" t="s">
+        <v>2380</v>
+      </c>
+      <c r="Z54" s="244" t="s">
+        <v>2367</v>
+      </c>
+      <c r="AA54" s="252" t="s">
         <v>2369</v>
       </c>
-      <c r="Y54" s="161" t="s">
-        <v>2382</v>
-      </c>
-      <c r="Z54" s="244" t="s">
-        <v>2369</v>
-      </c>
-      <c r="AA54" s="252" t="s">
-        <v>2371</v>
-      </c>
     </row>
     <row r="55" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A55" s="277" t="s">
-        <v>2364</v>
+      <c r="A55" s="274" t="s">
+        <v>2362</v>
       </c>
       <c r="B55" s="244"/>
       <c r="C55" s="244"/>
@@ -44984,10 +45007,10 @@
         <v>3</v>
       </c>
       <c r="E55" s="244" t="s">
-        <v>2367</v>
-      </c>
-      <c r="F55" s="273" t="s">
-        <v>2468</v>
+        <v>2365</v>
+      </c>
+      <c r="F55" s="124" t="s">
+        <v>2456</v>
       </c>
       <c r="G55" s="244" t="s">
         <v>2286</v>
@@ -44996,7 +45019,7 @@
         <v>2285</v>
       </c>
       <c r="I55" s="244" t="s">
-        <v>2426</v>
+        <v>2424</v>
       </c>
       <c r="J55" s="244" t="s">
         <v>2288</v>
@@ -45012,7 +45035,7 @@
         <v>2238</v>
       </c>
       <c r="O55" s="244" t="s">
-        <v>2381</v>
+        <v>2379</v>
       </c>
       <c r="P55" s="244" t="s">
         <v>2314</v>
@@ -45024,36 +45047,36 @@
         <v>3</v>
       </c>
       <c r="S55" s="244" t="s">
-        <v>2372</v>
+        <v>2370</v>
       </c>
       <c r="T55" s="244"/>
       <c r="U55" s="244"/>
       <c r="V55" s="244"/>
       <c r="W55" s="244"/>
       <c r="X55" s="244" t="s">
-        <v>2370</v>
+        <v>2368</v>
       </c>
       <c r="Y55" s="161" t="s">
         <v>1415</v>
       </c>
       <c r="Z55" s="244" t="s">
-        <v>2369</v>
+        <v>2367</v>
       </c>
       <c r="AA55" s="252" t="s">
-        <v>2403</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="56" spans="1:27" ht="54.95" customHeight="1" thickBot="1">
-      <c r="A56" s="278" t="s">
-        <v>2372</v>
+      <c r="A56" s="275" t="s">
+        <v>2370</v>
       </c>
       <c r="B56" s="245"/>
       <c r="C56" s="245" t="s">
-        <v>2375</v>
+        <v>2373</v>
       </c>
       <c r="D56" s="245"/>
       <c r="E56" s="245"/>
-      <c r="F56" s="245"/>
+      <c r="F56" s="287"/>
       <c r="G56" s="245"/>
       <c r="H56" s="245"/>
       <c r="I56" s="245"/>
@@ -45072,32 +45095,32 @@
       <c r="V56" s="245"/>
       <c r="W56" s="245"/>
       <c r="X56" s="245" t="s">
-        <v>2370</v>
+        <v>2368</v>
       </c>
       <c r="Y56" s="245"/>
       <c r="Z56" s="245" t="s">
-        <v>2370</v>
+        <v>2368</v>
       </c>
       <c r="AA56" s="255"/>
     </row>
     <row r="57" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A57" s="279" t="s">
-        <v>2386</v>
+      <c r="A57" s="276" t="s">
+        <v>2384</v>
       </c>
       <c r="B57" s="253" t="s">
-        <v>2390</v>
+        <v>2388</v>
       </c>
       <c r="C57" s="253" t="s">
-        <v>2391</v>
+        <v>2389</v>
       </c>
       <c r="D57" s="253">
         <v>1</v>
       </c>
       <c r="E57" s="253" t="s">
-        <v>2395</v>
-      </c>
-      <c r="F57" s="253" t="s">
-        <v>2453</v>
+        <v>2393</v>
+      </c>
+      <c r="F57" s="285" t="s">
+        <v>2449</v>
       </c>
       <c r="G57" s="253"/>
       <c r="H57" s="253" t="s">
@@ -45109,7 +45132,7 @@
       <c r="L57" s="253"/>
       <c r="M57" s="253"/>
       <c r="N57" s="253" t="s">
-        <v>2400</v>
+        <v>2398</v>
       </c>
       <c r="O57" s="253" t="s">
         <v>2229</v>
@@ -45120,14 +45143,14 @@
       </c>
       <c r="R57" s="253"/>
       <c r="S57" s="253" t="s">
-        <v>2387</v>
+        <v>2385</v>
       </c>
       <c r="T57" s="253"/>
       <c r="U57" s="253"/>
       <c r="V57" s="253"/>
       <c r="W57" s="253"/>
       <c r="X57" s="253" t="s">
-        <v>2402</v>
+        <v>2400</v>
       </c>
       <c r="Y57" s="253" t="s">
         <v>2247</v>
@@ -45140,7 +45163,7 @@
       </c>
     </row>
     <row r="58" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A58" s="280" t="s">
+      <c r="A58" s="277" t="s">
         <v>1375</v>
       </c>
       <c r="B58" s="244"/>
@@ -45149,10 +45172,10 @@
         <v>2</v>
       </c>
       <c r="E58" s="244" t="s">
+        <v>2394</v>
+      </c>
+      <c r="F58" s="286" t="s">
         <v>2396</v>
-      </c>
-      <c r="F58" s="244" t="s">
-        <v>2398</v>
       </c>
       <c r="G58" s="244"/>
       <c r="H58" s="244" t="s">
@@ -45164,7 +45187,7 @@
       <c r="L58" s="244"/>
       <c r="M58" s="244"/>
       <c r="N58" s="244" t="s">
-        <v>2401</v>
+        <v>2399</v>
       </c>
       <c r="O58" s="244" t="s">
         <v>2229</v>
@@ -45175,7 +45198,7 @@
       </c>
       <c r="R58" s="244"/>
       <c r="S58" s="244" t="s">
-        <v>2388</v>
+        <v>2386</v>
       </c>
       <c r="T58" s="244"/>
       <c r="U58" s="244"/>
@@ -45185,17 +45208,17 @@
         <v>1424</v>
       </c>
       <c r="Y58" s="161" t="s">
-        <v>2382</v>
+        <v>2380</v>
       </c>
       <c r="Z58" s="244" t="s">
         <v>1424</v>
       </c>
       <c r="AA58" s="252" t="s">
-        <v>2371</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="59" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A59" s="280" t="s">
+      <c r="A59" s="277" t="s">
         <v>1375</v>
       </c>
       <c r="B59" s="244"/>
@@ -45204,10 +45227,10 @@
         <v>3</v>
       </c>
       <c r="E59" s="244" t="s">
+        <v>2395</v>
+      </c>
+      <c r="F59" s="286" t="s">
         <v>2397</v>
-      </c>
-      <c r="F59" s="244" t="s">
-        <v>2399</v>
       </c>
       <c r="G59" s="244"/>
       <c r="H59" s="244" t="s">
@@ -45230,7 +45253,7 @@
       </c>
       <c r="R59" s="244"/>
       <c r="S59" s="244" t="s">
-        <v>2389</v>
+        <v>2387</v>
       </c>
       <c r="T59" s="244"/>
       <c r="U59" s="244"/>
@@ -45246,20 +45269,20 @@
         <v>1424</v>
       </c>
       <c r="AA59" s="252" t="s">
-        <v>2403</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="60" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A60" s="280" t="s">
-        <v>2387</v>
+      <c r="A60" s="277" t="s">
+        <v>2385</v>
       </c>
       <c r="B60" s="244"/>
       <c r="C60" s="244" t="s">
-        <v>2392</v>
+        <v>2390</v>
       </c>
       <c r="D60" s="244"/>
       <c r="E60" s="244"/>
-      <c r="F60" s="244"/>
+      <c r="F60" s="286"/>
       <c r="G60" s="244"/>
       <c r="H60" s="244"/>
       <c r="I60" s="244"/>
@@ -45287,16 +45310,16 @@
       <c r="AA60" s="252"/>
     </row>
     <row r="61" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A61" s="280" t="s">
-        <v>2388</v>
+      <c r="A61" s="277" t="s">
+        <v>2386</v>
       </c>
       <c r="B61" s="244"/>
       <c r="C61" s="244" t="s">
-        <v>2393</v>
+        <v>2391</v>
       </c>
       <c r="D61" s="244"/>
       <c r="E61" s="244"/>
-      <c r="F61" s="244"/>
+      <c r="F61" s="286"/>
       <c r="G61" s="244"/>
       <c r="H61" s="244"/>
       <c r="I61" s="244"/>
@@ -45315,7 +45338,7 @@
       <c r="V61" s="244"/>
       <c r="W61" s="244"/>
       <c r="X61" s="244" t="s">
-        <v>2402</v>
+        <v>2400</v>
       </c>
       <c r="Y61" s="244"/>
       <c r="Z61" s="244" t="s">
@@ -45324,16 +45347,16 @@
       <c r="AA61" s="252"/>
     </row>
     <row r="62" spans="1:27" ht="54.95" customHeight="1" thickBot="1">
-      <c r="A62" s="281" t="s">
-        <v>2389</v>
+      <c r="A62" s="278" t="s">
+        <v>2387</v>
       </c>
       <c r="B62" s="245"/>
       <c r="C62" s="245" t="s">
-        <v>2394</v>
+        <v>2392</v>
       </c>
       <c r="D62" s="245"/>
       <c r="E62" s="245"/>
-      <c r="F62" s="245"/>
+      <c r="F62" s="287"/>
       <c r="G62" s="245"/>
       <c r="H62" s="245"/>
       <c r="I62" s="245"/>
@@ -45361,35 +45384,35 @@
       <c r="AA62" s="255"/>
     </row>
     <row r="63" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A63" s="276" t="s">
-        <v>2405</v>
+      <c r="A63" s="273" t="s">
+        <v>2403</v>
       </c>
       <c r="B63" s="253" t="s">
-        <v>2406</v>
+        <v>2404</v>
       </c>
       <c r="C63" s="253" t="s">
-        <v>2428</v>
+        <v>2426</v>
       </c>
       <c r="D63" s="253">
         <v>1</v>
       </c>
       <c r="E63" s="253" t="s">
-        <v>2411</v>
-      </c>
-      <c r="F63" s="282" t="s">
-        <v>2469</v>
+        <v>2409</v>
+      </c>
+      <c r="F63" s="288" t="s">
+        <v>2457</v>
       </c>
       <c r="G63" s="253" t="s">
-        <v>2421</v>
+        <v>2419</v>
       </c>
       <c r="H63" s="253" t="s">
         <v>2285</v>
       </c>
       <c r="I63" s="253" t="s">
-        <v>2422</v>
+        <v>2420</v>
       </c>
       <c r="J63" s="253" t="s">
-        <v>2420</v>
+        <v>2418</v>
       </c>
       <c r="K63" s="253" t="s">
         <v>2229</v>
@@ -45412,28 +45435,28 @@
       </c>
       <c r="R63" s="253"/>
       <c r="S63" s="253" t="s">
-        <v>2407</v>
+        <v>2405</v>
       </c>
       <c r="T63" s="253"/>
       <c r="U63" s="253"/>
       <c r="V63" s="253"/>
       <c r="W63" s="253"/>
       <c r="X63" s="253" t="s">
-        <v>2419</v>
+        <v>2417</v>
       </c>
       <c r="Y63" s="253" t="s">
         <v>2247</v>
       </c>
       <c r="Z63" s="253" t="s">
-        <v>2418</v>
+        <v>2416</v>
       </c>
       <c r="AA63" s="254" t="s">
         <v>2336</v>
       </c>
     </row>
     <row r="64" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A64" s="280" t="s">
-        <v>2405</v>
+      <c r="A64" s="277" t="s">
+        <v>2403</v>
       </c>
       <c r="B64" s="244"/>
       <c r="C64" s="244"/>
@@ -45441,21 +45464,21 @@
         <v>2</v>
       </c>
       <c r="E64" s="244" t="s">
-        <v>2412</v>
-      </c>
-      <c r="F64" s="273" t="s">
-        <v>2470</v>
+        <v>2410</v>
+      </c>
+      <c r="F64" s="124" t="s">
+        <v>2552</v>
       </c>
       <c r="G64" s="244"/>
       <c r="H64" s="244" t="s">
-        <v>2356</v>
+        <v>2308</v>
       </c>
       <c r="I64" s="244"/>
       <c r="J64" s="244"/>
       <c r="K64" s="244"/>
       <c r="L64" s="244"/>
       <c r="M64" s="244" t="s">
-        <v>2449</v>
+        <v>2553</v>
       </c>
       <c r="N64" s="244" t="s">
         <v>2224</v>
@@ -45471,30 +45494,30 @@
       </c>
       <c r="R64" s="244"/>
       <c r="S64" s="244" t="s">
-        <v>2408</v>
+        <v>2406</v>
       </c>
       <c r="T64" s="244" t="s">
-        <v>2409</v>
+        <v>2407</v>
       </c>
       <c r="U64" s="244"/>
       <c r="V64" s="244"/>
       <c r="W64" s="244"/>
       <c r="X64" s="244" t="s">
-        <v>2418</v>
+        <v>2416</v>
       </c>
       <c r="Y64" s="161" t="s">
-        <v>2382</v>
+        <v>2380</v>
       </c>
       <c r="Z64" s="244" t="s">
-        <v>2418</v>
+        <v>2416</v>
       </c>
       <c r="AA64" s="252" t="s">
-        <v>2371</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="65" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A65" s="280" t="s">
-        <v>2405</v>
+      <c r="A65" s="277" t="s">
+        <v>2403</v>
       </c>
       <c r="B65" s="244"/>
       <c r="C65" s="244"/>
@@ -45502,10 +45525,10 @@
         <v>3</v>
       </c>
       <c r="E65" s="244" t="s">
-        <v>2413</v>
-      </c>
-      <c r="F65" s="273" t="s">
-        <v>2471</v>
+        <v>2411</v>
+      </c>
+      <c r="F65" s="124" t="s">
+        <v>2458</v>
       </c>
       <c r="G65" s="244"/>
       <c r="H65" s="244" t="s">
@@ -45513,7 +45536,7 @@
       </c>
       <c r="I65" s="244"/>
       <c r="J65" s="244" t="s">
-        <v>2427</v>
+        <v>2425</v>
       </c>
       <c r="K65" s="244" t="s">
         <v>2227</v>
@@ -45536,36 +45559,36 @@
       </c>
       <c r="R65" s="244"/>
       <c r="S65" s="244" t="s">
-        <v>2410</v>
+        <v>2408</v>
       </c>
       <c r="T65" s="244"/>
       <c r="U65" s="244"/>
       <c r="V65" s="244"/>
       <c r="W65" s="244"/>
       <c r="X65" s="244" t="s">
-        <v>2418</v>
+        <v>2416</v>
       </c>
       <c r="Y65" s="161" t="s">
         <v>1415</v>
       </c>
       <c r="Z65" s="244" t="s">
-        <v>2418</v>
+        <v>2416</v>
       </c>
       <c r="AA65" s="252" t="s">
-        <v>2403</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="66" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A66" s="280" t="s">
-        <v>2407</v>
+      <c r="A66" s="277" t="s">
+        <v>2405</v>
       </c>
       <c r="B66" s="244"/>
       <c r="C66" s="244" t="s">
-        <v>2414</v>
+        <v>2412</v>
       </c>
       <c r="D66" s="244"/>
       <c r="E66" s="244"/>
-      <c r="F66" s="244"/>
+      <c r="F66" s="286"/>
       <c r="G66" s="244"/>
       <c r="H66" s="244"/>
       <c r="I66" s="244"/>
@@ -45584,25 +45607,25 @@
       <c r="V66" s="244"/>
       <c r="W66" s="244"/>
       <c r="X66" s="244" t="s">
-        <v>2418</v>
+        <v>2416</v>
       </c>
       <c r="Y66" s="244"/>
       <c r="Z66" s="244" t="s">
-        <v>2418</v>
+        <v>2416</v>
       </c>
       <c r="AA66" s="252"/>
     </row>
     <row r="67" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A67" s="280" t="s">
-        <v>2408</v>
+      <c r="A67" s="277" t="s">
+        <v>2406</v>
       </c>
       <c r="B67" s="244"/>
       <c r="C67" s="244" t="s">
-        <v>2416</v>
+        <v>2414</v>
       </c>
       <c r="D67" s="244"/>
       <c r="E67" s="244"/>
-      <c r="F67" s="244"/>
+      <c r="F67" s="286"/>
       <c r="G67" s="244"/>
       <c r="H67" s="244"/>
       <c r="I67" s="244"/>
@@ -45621,25 +45644,25 @@
       <c r="V67" s="244"/>
       <c r="W67" s="244"/>
       <c r="X67" s="244" t="s">
-        <v>2418</v>
+        <v>2416</v>
       </c>
       <c r="Y67" s="244"/>
       <c r="Z67" s="244" t="s">
-        <v>2418</v>
+        <v>2416</v>
       </c>
       <c r="AA67" s="252"/>
     </row>
     <row r="68" spans="1:27" ht="54.95" customHeight="1">
-      <c r="A68" s="280" t="s">
-        <v>2409</v>
+      <c r="A68" s="277" t="s">
+        <v>2407</v>
       </c>
       <c r="B68" s="244"/>
       <c r="C68" s="244" t="s">
-        <v>2417</v>
+        <v>2415</v>
       </c>
       <c r="D68" s="244"/>
       <c r="E68" s="244"/>
-      <c r="F68" s="244"/>
+      <c r="F68" s="286"/>
       <c r="G68" s="244"/>
       <c r="H68" s="244"/>
       <c r="I68" s="244"/>
@@ -45658,25 +45681,25 @@
       <c r="V68" s="244"/>
       <c r="W68" s="244"/>
       <c r="X68" s="244" t="s">
-        <v>2418</v>
+        <v>2416</v>
       </c>
       <c r="Y68" s="244"/>
       <c r="Z68" s="244" t="s">
-        <v>2418</v>
+        <v>2416</v>
       </c>
       <c r="AA68" s="252"/>
     </row>
     <row r="69" spans="1:27" ht="54.95" customHeight="1" thickBot="1">
-      <c r="A69" s="281" t="s">
-        <v>2410</v>
+      <c r="A69" s="278" t="s">
+        <v>2408</v>
       </c>
       <c r="B69" s="245"/>
       <c r="C69" s="245" t="s">
-        <v>2415</v>
+        <v>2413</v>
       </c>
       <c r="D69" s="245"/>
       <c r="E69" s="245"/>
-      <c r="F69" s="245"/>
+      <c r="F69" s="287"/>
       <c r="G69" s="245"/>
       <c r="H69" s="245"/>
       <c r="I69" s="245"/>
@@ -45695,32 +45718,32 @@
       <c r="V69" s="245"/>
       <c r="W69" s="245"/>
       <c r="X69" s="245" t="s">
-        <v>2418</v>
+        <v>2416</v>
       </c>
       <c r="Y69" s="245"/>
       <c r="Z69" s="245" t="s">
-        <v>2418</v>
+        <v>2416</v>
       </c>
       <c r="AA69" s="255"/>
     </row>
     <row r="70" spans="1:27" ht="54.95" customHeight="1">
       <c r="A70" s="256" t="s">
-        <v>2440</v>
+        <v>2438</v>
       </c>
       <c r="B70" s="256" t="s">
+        <v>2523</v>
+      </c>
+      <c r="C70" s="256" t="s">
         <v>2536</v>
       </c>
-      <c r="C70" s="256" t="s">
-        <v>2550</v>
-      </c>
       <c r="D70" s="256">
         <v>1</v>
       </c>
       <c r="E70" s="256" t="s">
-        <v>2537</v>
-      </c>
-      <c r="F70" s="283" t="s">
-        <v>2538</v>
+        <v>2524</v>
+      </c>
+      <c r="F70" s="289" t="s">
+        <v>2525</v>
       </c>
       <c r="G70" s="256"/>
       <c r="H70" s="256" t="s">
@@ -45743,20 +45766,20 @@
       </c>
       <c r="R70" s="256"/>
       <c r="S70" s="256" t="s">
-        <v>2539</v>
+        <v>2526</v>
       </c>
       <c r="T70" s="256"/>
       <c r="U70" s="256"/>
       <c r="V70" s="256"/>
       <c r="W70" s="256"/>
       <c r="X70" s="256" t="s">
-        <v>2549</v>
+        <v>2535</v>
       </c>
       <c r="Y70" s="256" t="s">
         <v>2247</v>
       </c>
       <c r="Z70" s="256" t="s">
-        <v>2549</v>
+        <v>2535</v>
       </c>
       <c r="AA70" s="256" t="s">
         <v>2336</v>
@@ -45764,15 +45787,15 @@
     </row>
     <row r="71" spans="1:27" ht="54.95" customHeight="1">
       <c r="A71" s="256" t="s">
-        <v>2539</v>
+        <v>2526</v>
       </c>
       <c r="B71" s="244"/>
       <c r="C71" s="244" t="s">
-        <v>2548</v>
+        <v>2534</v>
       </c>
       <c r="D71" s="244"/>
       <c r="E71" s="244"/>
-      <c r="F71" s="244"/>
+      <c r="F71" s="286"/>
       <c r="G71" s="244"/>
       <c r="H71" s="244"/>
       <c r="I71" s="244"/>
@@ -45791,11 +45814,11 @@
       <c r="V71" s="244"/>
       <c r="W71" s="244"/>
       <c r="X71" s="244" t="s">
-        <v>2549</v>
+        <v>2535</v>
       </c>
       <c r="Y71" s="244"/>
       <c r="Z71" s="244" t="s">
-        <v>2549</v>
+        <v>2535</v>
       </c>
       <c r="AA71" s="244"/>
     </row>
@@ -45805,7 +45828,7 @@
       <c r="C72" s="244"/>
       <c r="D72" s="244"/>
       <c r="E72" s="244"/>
-      <c r="F72" s="244"/>
+      <c r="F72" s="286"/>
       <c r="G72" s="244"/>
       <c r="H72" s="244"/>
       <c r="I72" s="244"/>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erang\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B59056A-4CBF-4036-BF9E-8B3D94F7C228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C5D811-D3C6-4B38-BE6B-782E60E51F5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -13765,8 +13765,9 @@
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
   <si>
-    <t>침식도는 새로운 방에 진입하면 3, 턴이 진행되거나
-피해를 받을 때마다 1, 전투불능이 되면 10 증가합니다.</t>
+    <t>침식도는 새로운 방에 진입하면 3,
+턴이 진행되거나 피해를 받을 때마다 1,
+전투불능이 되면 10 증가합니다.</t>
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
 </sst>
@@ -16100,7 +16101,7 @@
         <v>47</v>
       </c>
       <c r="C3" s="8">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D3" s="7">
         <v>10</v>
@@ -16171,7 +16172,7 @@
         <v>64</v>
       </c>
       <c r="C4" s="12">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D4" s="11">
         <v>12</v>
@@ -16242,7 +16243,7 @@
         <v>80</v>
       </c>
       <c r="C5" s="12">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D5" s="11">
         <v>14</v>
@@ -16313,7 +16314,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="12">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D6" s="11">
         <v>11</v>
@@ -16384,7 +16385,7 @@
         <v>111</v>
       </c>
       <c r="C7" s="12">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D7" s="11">
         <v>12</v>
@@ -27063,7 +27064,7 @@
         <v>2533</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="33">
+    <row r="8" spans="1:16" ht="49.5">
       <c r="A8" s="140" t="s">
         <v>2492</v>
       </c>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erang\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C5D811-D3C6-4B38-BE6B-782E60E51F5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C03783DB-18C9-4438-900D-75428B325520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -34746,7 +34746,7 @@
         <v>737</v>
       </c>
       <c r="J6" s="16">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K6" s="16" t="s">
         <v>738</v>
@@ -34822,7 +34822,7 @@
         <v>737</v>
       </c>
       <c r="J8" s="16">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="K8" s="16" t="s">
         <v>727</v>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erang\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C03783DB-18C9-4438-900D-75428B325520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{185F4270-2D1B-4A28-93E0-C06E2BE5254A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5196" uniqueCount="2555">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5406" uniqueCount="2628">
   <si>
     <t>캐릭터ID</t>
   </si>
@@ -13533,9 +13533,6 @@
     <t>tutorial.t01.arrival</t>
   </si>
   <si>
-    <t>거점으로 향하는 길</t>
-  </si>
-  <si>
     <t>Auto</t>
   </si>
   <si>
@@ -13603,10 +13600,6 @@
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
   <si>
-    <t>하하, 이러다 거점에 도착하기도 전에 지치겠어!</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
     <t>불필요한 체력 소모는 피하시죠. 거점까지 얼마 남지 않았습니다.</t>
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
@@ -13616,10 +13609,6 @@
   </si>
   <si>
     <t>변이체군요. 아무래도 그냥 지나가긴 어렵겠습니다.</t>
-    <phoneticPr fontId="40" type="noConversion"/>
-  </si>
-  <si>
-    <t>좋아! 그럼 녀석부터 처리하고 가자!</t>
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
   <si>
@@ -13768,6 +13757,274 @@
     <t>침식도는 새로운 방에 진입하면 3,
 턴이 진행되거나 피해를 받을 때마다 1,
 전투불능이 되면 10 증가합니다.</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>tutorial.t01.hud.01</t>
+  </si>
+  <si>
+    <t>Char01/Back</t>
+  </si>
+  <si>
+    <t>아무 곳이나 클릭하여 계속</t>
+  </si>
+  <si>
+    <t>tutorial.t01.hud.02</t>
+  </si>
+  <si>
+    <t>tutorial.t01.hud.03</t>
+  </si>
+  <si>
+    <t>Dialogbox</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>tutorial.t01.dialogue.06</t>
+  </si>
+  <si>
+    <t>tutorial.t01.dialogue.07</t>
+  </si>
+  <si>
+    <t>tutorial.t01.dialogue.08</t>
+  </si>
+  <si>
+    <t>tutorial.t01.dialogue.09</t>
+  </si>
+  <si>
+    <t>그럼 녀석부터 처리하고 가자!</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>좋아! 녀석이 움직이기 전에 먼저 처리해 버릴까?</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>Guide</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>TutorialTooltip</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>tutorial.t01.hud.04</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>tutorial.t01.battleslot.01</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>tutorial.t01.battleslot.02</t>
+  </si>
+  <si>
+    <t>타임라인은 총 5개의 슬롯으로 구성되며, 각 슬롯은 5칸으로 이루어져 있습니다.</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClickAny</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>tutorial.prompt.click_any</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClickTarget</t>
+  </si>
+  <si>
+    <t>BattleCharacterPanel/Active/Move</t>
+  </si>
+  <si>
+    <t>ReserveMove</t>
+  </si>
+  <si>
+    <t>BattleCharacterPanel/Active/Skill01</t>
+  </si>
+  <si>
+    <t>ReserveAction</t>
+  </si>
+  <si>
+    <t>tutorial.t01.action.01</t>
+  </si>
+  <si>
+    <t>BattleCharacterPanel/Active</t>
+  </si>
+  <si>
+    <t>tutorial.t01.action.02</t>
+  </si>
+  <si>
+    <t>tutorial.t01.action.03</t>
+  </si>
+  <si>
+    <t>tutorial.prompt.click_move</t>
+  </si>
+  <si>
+    <t>tutorial.t01.action.04</t>
+  </si>
+  <si>
+    <t>Grid_16</t>
+  </si>
+  <si>
+    <t>tutorial.prompt.click_grid</t>
+  </si>
+  <si>
+    <t>tutorial.t01.action.05</t>
+  </si>
+  <si>
+    <t>tutorial.prompt.click_memory</t>
+  </si>
+  <si>
+    <t>A 또는 버튼을 클릭하여 계속</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동할 위치를 클릭하여 계속</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>Q 또는 버튼을 클릭하여 게속</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>BattleSlot/Back</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>tutorial.t01.action.06</t>
+  </si>
+  <si>
+    <t>BattleCharacterPanel/Char_Select/Char02</t>
+  </si>
+  <si>
+    <t>tutorial.prompt.select_char02</t>
+  </si>
+  <si>
+    <t>tutorial.t01.action.07</t>
+  </si>
+  <si>
+    <t>ReserveActionTwice</t>
+  </si>
+  <si>
+    <t>tutorial.prompt.click_memory_twice</t>
+  </si>
+  <si>
+    <t>Q 또는 버튼을 두 번 클릭하여 계속</t>
+  </si>
+  <si>
+    <t>tutorial.t01.action.08</t>
+  </si>
+  <si>
+    <t>BattleCharacterPanel/EndButton</t>
+  </si>
+  <si>
+    <t>tutorial.prompt.end_turn</t>
+  </si>
+  <si>
+    <t>Tab 또는 버튼을 클릭하여 게속</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>Space 또는 버튼을 클릭하여 계속</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>행동에 따라 1칸에서 3칸을 사용하며, 턴을 종료하면 첫 번째 슬롯부터 순서대로 실행됩니다.</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>캐릭터는 이동과 방향 전환 등의 기본 행동을 사용할 수 있습니다.</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>이외에도 피해를 주거나 버프, 디버프 등의 효과를 가진 행동인 '기억'을 사용할 수 있습니다.</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>캐릭터를 변경하면 예약할 슬롯도 자동으로 변경됩니다.</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>거점 인근</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>이러다 거점에 도착하기도 전에 지치겠어!</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>마나와 카르마는 행동에 필요한 자원입니다.
+마나는 재생량에 따라, 카르마는 매 턴 1씩 회복됩니다.</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>캐릭터가 장착한 유물과 룬의 정보도 각 슬롯에서 살펴볼 수 있습니다.</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>변이체가 먼저 행동을 예약하며, 하나의 슬롯에는 서로 다른 캐릭터의 행동을 등록할 수 없습니다.</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동은 1칸을 사용하는 행동으로, 예약한 거리에 따라 마나를 소모합니다.</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동할 위치를 선택하면 해당 행동이 타임라인에 예약됩니다.</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>기억의 범위는 캐릭터가 바라보는 방향을 기준으로 자동 설정됩니다.</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>같은 기억을 여러 번 등록할 수도 있으며, 각각의 행동이 타임라인에 예약됩니다.</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>행동 예약을 마쳤다면 턴을 종료합니다. 그러면 등록한 행동이 순서대로 실행되며 전투가 진행됩니다.</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>캐릭터 상태창에서는 생명력과 마나, 카르마를 비롯한 다양한 전투 정보를 확인할 수 있습니다.</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>현재 캐릭터에게 적용된 버프와 디버프도 상태창에 표시됩니다.</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>무작정 달려들기보다는 신중하게 움직이는 편이 좋겠습니다.</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>일단 녀석에게 접근해서 제대로 한 방 먹여주겠어!</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>하아… 어쩔 수 없군요. 뒤는 제가 마무리하겠습니다.</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>툴팁 위치</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>TooltipPosition</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>Below</t>
+  </si>
+  <si>
+    <t>Below</t>
+    <phoneticPr fontId="40" type="noConversion"/>
+  </si>
+  <si>
+    <t>Above</t>
+  </si>
+  <si>
+    <t>Above</t>
     <phoneticPr fontId="40" type="noConversion"/>
   </si>
 </sst>
@@ -26744,7 +27001,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BEBF3C2-6F22-465F-9281-A2A155740600}">
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:Q31"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="16.625" customWidth="1"/>
@@ -26756,15 +27013,16 @@
     <col min="8" max="8" width="21" customWidth="1"/>
     <col min="9" max="9" width="16.875" customWidth="1"/>
     <col min="10" max="10" width="19.875" customWidth="1"/>
-    <col min="11" max="11" width="25.125" customWidth="1"/>
-    <col min="12" max="12" width="78.375" style="141" customWidth="1"/>
+    <col min="11" max="11" width="33.875" customWidth="1"/>
+    <col min="12" max="12" width="85" style="141" customWidth="1"/>
     <col min="13" max="13" width="18.25" customWidth="1"/>
-    <col min="14" max="14" width="19.5" customWidth="1"/>
-    <col min="15" max="15" width="27.5" customWidth="1"/>
-    <col min="16" max="16" width="40.625" customWidth="1"/>
+    <col min="14" max="14" width="39.125" customWidth="1"/>
+    <col min="15" max="15" width="31.875" style="140" customWidth="1"/>
+    <col min="16" max="16" width="31.375" customWidth="1"/>
+    <col min="17" max="17" width="16.75" style="140" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17">
       <c r="A1" s="263" t="s">
         <v>2470</v>
       </c>
@@ -26793,7 +27051,7 @@
         <v>2476</v>
       </c>
       <c r="J1" s="263" t="s">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="K1" s="263" t="s">
         <v>2477</v>
@@ -26808,13 +27066,16 @@
         <v>2480</v>
       </c>
       <c r="O1" s="263" t="s">
-        <v>2529</v>
+        <v>2526</v>
       </c>
       <c r="P1" s="263" t="s">
-        <v>2531</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16">
+        <v>2528</v>
+      </c>
+      <c r="Q1" s="263" t="s">
+        <v>2622</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" s="263" t="s">
         <v>2481</v>
       </c>
@@ -26843,7 +27104,7 @@
         <v>2487</v>
       </c>
       <c r="J2" s="263" t="s">
-        <v>2513</v>
+        <v>2512</v>
       </c>
       <c r="K2" s="263" t="s">
         <v>2488</v>
@@ -26858,13 +27119,16 @@
         <v>2491</v>
       </c>
       <c r="O2" s="263" t="s">
-        <v>2530</v>
+        <v>2527</v>
       </c>
       <c r="P2" s="263" t="s">
-        <v>2532</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
+        <v>2529</v>
+      </c>
+      <c r="Q2" s="263" t="s">
+        <v>2623</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" s="140" t="s">
         <v>2492</v>
       </c>
@@ -26881,7 +27145,7 @@
         <v>42</v>
       </c>
       <c r="F3" s="140" t="s">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="G3" s="140">
         <v>1</v>
@@ -26891,20 +27155,20 @@
       </c>
       <c r="I3" s="140"/>
       <c r="J3" s="140" t="s">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="K3" s="140" t="s">
         <v>2495</v>
       </c>
       <c r="L3" s="141" t="s">
+        <v>2607</v>
+      </c>
+      <c r="M3" s="140" t="s">
         <v>2496</v>
       </c>
-      <c r="M3" s="140" t="s">
-        <v>2497</v>
-      </c>
       <c r="N3" s="140"/>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:17">
       <c r="A4" s="140" t="s">
         <v>2492</v>
       </c>
@@ -26919,32 +27183,32 @@
       <c r="F4" s="140"/>
       <c r="G4" s="140"/>
       <c r="H4" s="140" t="s">
-        <v>2498</v>
+        <v>2497</v>
       </c>
       <c r="I4" s="140" t="s">
         <v>46</v>
       </c>
       <c r="J4" s="140" t="s">
-        <v>2514</v>
+        <v>2513</v>
       </c>
       <c r="K4" s="140" t="s">
+        <v>2498</v>
+      </c>
+      <c r="L4" s="141" t="s">
+        <v>2518</v>
+      </c>
+      <c r="M4" s="140" t="s">
         <v>2499</v>
       </c>
-      <c r="L4" s="141" t="s">
-        <v>2520</v>
-      </c>
-      <c r="M4" s="140" t="s">
-        <v>2500</v>
-      </c>
       <c r="N4" s="140"/>
-      <c r="O4" t="s">
-        <v>2528</v>
+      <c r="O4" s="140" t="s">
+        <v>2525</v>
       </c>
       <c r="P4" t="s">
-        <v>2533</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" s="140" t="s">
         <v>2492</v>
       </c>
@@ -26959,32 +27223,32 @@
       <c r="F5" s="140"/>
       <c r="G5" s="140"/>
       <c r="H5" s="140" t="s">
-        <v>2498</v>
+        <v>2497</v>
       </c>
       <c r="I5" s="140" t="s">
         <v>46</v>
       </c>
       <c r="J5" s="140" t="s">
-        <v>2514</v>
+        <v>2513</v>
       </c>
       <c r="K5" s="140" t="s">
-        <v>2501</v>
+        <v>2500</v>
       </c>
       <c r="L5" s="141" t="s">
-        <v>2518</v>
+        <v>2608</v>
       </c>
       <c r="M5" s="140" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="N5" s="140"/>
-      <c r="O5" t="s">
-        <v>2528</v>
+      <c r="O5" s="140" t="s">
+        <v>2525</v>
       </c>
       <c r="P5" t="s">
-        <v>2533</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" s="140" t="s">
         <v>2492</v>
       </c>
@@ -26999,32 +27263,32 @@
       <c r="F6" s="140"/>
       <c r="G6" s="140"/>
       <c r="H6" s="140" t="s">
-        <v>2498</v>
+        <v>2497</v>
       </c>
       <c r="I6" s="140" t="s">
         <v>63</v>
       </c>
       <c r="J6" s="140" t="s">
-        <v>2514</v>
+        <v>2557</v>
       </c>
       <c r="K6" s="140" t="s">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="L6" s="141" t="s">
-        <v>2519</v>
+        <v>2517</v>
       </c>
       <c r="M6" s="140" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="N6" s="140"/>
-      <c r="O6" t="s">
-        <v>2528</v>
+      <c r="O6" s="140" t="s">
+        <v>2525</v>
       </c>
       <c r="P6" t="s">
-        <v>2533</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7" s="140" t="s">
         <v>2492</v>
       </c>
@@ -27039,32 +27303,35 @@
       <c r="F7" s="140"/>
       <c r="G7" s="140"/>
       <c r="H7" s="140" t="s">
-        <v>2503</v>
+        <v>2502</v>
       </c>
       <c r="I7" s="140"/>
       <c r="J7" s="140" t="s">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="K7" s="140" t="s">
+        <v>2503</v>
+      </c>
+      <c r="L7" s="141" t="s">
+        <v>2516</v>
+      </c>
+      <c r="M7" s="140" t="s">
+        <v>2499</v>
+      </c>
+      <c r="N7" s="140" t="s">
         <v>2504</v>
       </c>
-      <c r="L7" s="141" t="s">
-        <v>2517</v>
-      </c>
-      <c r="M7" s="140" t="s">
-        <v>2500</v>
-      </c>
-      <c r="N7" s="140" t="s">
-        <v>2505</v>
-      </c>
-      <c r="O7" t="s">
-        <v>2528</v>
+      <c r="O7" s="140" t="s">
+        <v>2525</v>
       </c>
       <c r="P7" t="s">
-        <v>2533</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" ht="49.5">
+        <v>2530</v>
+      </c>
+      <c r="Q7" s="140" t="s">
+        <v>2624</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="49.5">
       <c r="A8" s="140" t="s">
         <v>2492</v>
       </c>
@@ -27079,32 +27346,35 @@
       <c r="F8" s="140"/>
       <c r="G8" s="140"/>
       <c r="H8" s="140" t="s">
-        <v>2503</v>
+        <v>2502</v>
       </c>
       <c r="I8" s="140"/>
       <c r="J8" s="140" t="s">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="K8" s="140" t="s">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="L8" s="265" t="s">
-        <v>2554</v>
+        <v>2551</v>
       </c>
       <c r="M8" s="140" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="N8" s="140" t="s">
-        <v>2505</v>
-      </c>
-      <c r="O8" t="s">
-        <v>2528</v>
+        <v>2504</v>
+      </c>
+      <c r="O8" s="140" t="s">
+        <v>2525</v>
       </c>
       <c r="P8" t="s">
-        <v>2533</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="33">
+        <v>2530</v>
+      </c>
+      <c r="Q8" s="140" t="s">
+        <v>2624</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="33">
       <c r="A9" s="140" t="s">
         <v>2492</v>
       </c>
@@ -27119,32 +27389,35 @@
       <c r="F9" s="140"/>
       <c r="G9" s="140"/>
       <c r="H9" s="140" t="s">
-        <v>2503</v>
+        <v>2502</v>
       </c>
       <c r="I9" s="140"/>
       <c r="J9" s="140" t="s">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="K9" s="140" t="s">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="L9" s="265" t="s">
-        <v>2527</v>
+        <v>2524</v>
       </c>
       <c r="M9" s="140" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="N9" s="140" t="s">
-        <v>2505</v>
-      </c>
-      <c r="O9" t="s">
-        <v>2528</v>
+        <v>2504</v>
+      </c>
+      <c r="O9" s="140" t="s">
+        <v>2525</v>
       </c>
       <c r="P9" t="s">
-        <v>2533</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
+        <v>2530</v>
+      </c>
+      <c r="Q9" s="140" t="s">
+        <v>2625</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10" s="140" t="s">
         <v>2492</v>
       </c>
@@ -27159,17 +27432,17 @@
       <c r="F10" s="140"/>
       <c r="G10" s="140"/>
       <c r="H10" s="140" t="s">
-        <v>2508</v>
+        <v>2507</v>
       </c>
       <c r="I10" s="140"/>
       <c r="J10" s="140"/>
       <c r="K10" s="140"/>
       <c r="M10" s="140" t="s">
-        <v>2497</v>
+        <v>2496</v>
       </c>
       <c r="N10" s="140"/>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:17">
       <c r="A11" s="140" t="s">
         <v>2492</v>
       </c>
@@ -27184,32 +27457,32 @@
       <c r="F11" s="140"/>
       <c r="G11" s="140"/>
       <c r="H11" s="140" t="s">
-        <v>2498</v>
+        <v>2497</v>
       </c>
       <c r="I11" s="140" t="s">
         <v>63</v>
       </c>
       <c r="J11" s="140" t="s">
-        <v>2514</v>
+        <v>2513</v>
       </c>
       <c r="K11" s="140" t="s">
-        <v>2509</v>
+        <v>2508</v>
       </c>
       <c r="L11" s="141" t="s">
-        <v>2521</v>
+        <v>2519</v>
       </c>
       <c r="M11" s="140" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="N11" s="140"/>
-      <c r="O11" t="s">
-        <v>2528</v>
+      <c r="O11" s="140" t="s">
+        <v>2525</v>
       </c>
       <c r="P11" t="s">
-        <v>2533</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
       <c r="A12" s="140" t="s">
         <v>2492</v>
       </c>
@@ -27217,52 +27490,816 @@
         <v>10</v>
       </c>
       <c r="C12" s="140" t="s">
-        <v>2461</v>
+        <v>2462</v>
       </c>
       <c r="D12" s="140"/>
       <c r="E12" s="140"/>
       <c r="F12" s="140"/>
       <c r="G12" s="140"/>
       <c r="H12" s="140" t="s">
-        <v>2498</v>
+        <v>2497</v>
       </c>
       <c r="I12" s="140" t="s">
         <v>46</v>
       </c>
       <c r="J12" s="140" t="s">
-        <v>2514</v>
+        <v>2513</v>
       </c>
       <c r="K12" s="140" t="s">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="L12" s="141" t="s">
-        <v>2522</v>
+        <v>2562</v>
       </c>
       <c r="M12" s="140" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="N12" s="140"/>
-      <c r="O12" t="s">
-        <v>2528</v>
+      <c r="O12" s="140" t="s">
+        <v>2525</v>
       </c>
       <c r="P12" t="s">
-        <v>2533</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16">
-      <c r="A13" s="140"/>
-      <c r="B13" s="140"/>
-      <c r="C13" s="140"/>
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="33" customHeight="1">
+      <c r="A13" s="140" t="s">
+        <v>2492</v>
+      </c>
+      <c r="B13" s="140">
+        <v>11</v>
+      </c>
+      <c r="C13" s="140" t="s">
+        <v>2462</v>
+      </c>
       <c r="D13" s="140"/>
       <c r="E13" s="140"/>
       <c r="F13" s="140"/>
       <c r="G13" s="140"/>
-      <c r="H13" s="140"/>
+      <c r="H13" s="140" t="s">
+        <v>2502</v>
+      </c>
       <c r="I13" s="140"/>
-      <c r="J13" s="140"/>
-      <c r="K13" s="140"/>
-      <c r="M13" s="140"/>
-      <c r="N13" s="140"/>
+      <c r="J13" s="140" t="s">
+        <v>2514</v>
+      </c>
+      <c r="K13" s="140" t="s">
+        <v>2552</v>
+      </c>
+      <c r="L13" s="141" t="s">
+        <v>2617</v>
+      </c>
+      <c r="M13" s="140" t="s">
+        <v>2499</v>
+      </c>
+      <c r="N13" s="140" t="s">
+        <v>2553</v>
+      </c>
+      <c r="O13" s="140" t="s">
+        <v>2525</v>
+      </c>
+      <c r="P13" s="141" t="s">
+        <v>2554</v>
+      </c>
+      <c r="Q13" s="140" t="s">
+        <v>2627</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="33" customHeight="1">
+      <c r="A14" s="140" t="s">
+        <v>2492</v>
+      </c>
+      <c r="B14" s="140">
+        <v>12</v>
+      </c>
+      <c r="C14" s="140" t="s">
+        <v>2461</v>
+      </c>
+      <c r="D14" s="140"/>
+      <c r="E14" s="140"/>
+      <c r="F14" s="140"/>
+      <c r="G14" s="140"/>
+      <c r="H14" s="140" t="s">
+        <v>2502</v>
+      </c>
+      <c r="I14" s="140"/>
+      <c r="J14" s="140" t="s">
+        <v>2514</v>
+      </c>
+      <c r="K14" s="140" t="s">
+        <v>2555</v>
+      </c>
+      <c r="L14" s="265" t="s">
+        <v>2609</v>
+      </c>
+      <c r="M14" s="140" t="s">
+        <v>2499</v>
+      </c>
+      <c r="N14" s="140" t="s">
+        <v>2553</v>
+      </c>
+      <c r="O14" s="140" t="s">
+        <v>2525</v>
+      </c>
+      <c r="P14" s="141" t="s">
+        <v>2554</v>
+      </c>
+      <c r="Q14" s="140" t="s">
+        <v>2626</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="33" customHeight="1">
+      <c r="A15" s="140" t="s">
+        <v>2492</v>
+      </c>
+      <c r="B15" s="140">
+        <v>13</v>
+      </c>
+      <c r="C15" s="140" t="s">
+        <v>2461</v>
+      </c>
+      <c r="D15" s="140"/>
+      <c r="E15" s="140"/>
+      <c r="F15" s="140"/>
+      <c r="G15" s="140"/>
+      <c r="H15" s="140" t="s">
+        <v>2502</v>
+      </c>
+      <c r="I15" s="140"/>
+      <c r="J15" s="140" t="s">
+        <v>2565</v>
+      </c>
+      <c r="K15" s="140" t="s">
+        <v>2556</v>
+      </c>
+      <c r="L15" s="141" t="s">
+        <v>2610</v>
+      </c>
+      <c r="M15" s="140" t="s">
+        <v>2499</v>
+      </c>
+      <c r="N15" s="140" t="s">
+        <v>2553</v>
+      </c>
+      <c r="O15" s="140" t="s">
+        <v>2525</v>
+      </c>
+      <c r="P15" s="141" t="s">
+        <v>2554</v>
+      </c>
+      <c r="Q15" s="140" t="s">
+        <v>2627</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="33" customHeight="1">
+      <c r="A16" s="140" t="s">
+        <v>2492</v>
+      </c>
+      <c r="B16" s="140">
+        <v>14</v>
+      </c>
+      <c r="C16" s="140" t="s">
+        <v>2461</v>
+      </c>
+      <c r="D16" s="140"/>
+      <c r="E16" s="140"/>
+      <c r="F16" s="140"/>
+      <c r="G16" s="140"/>
+      <c r="H16" s="140" t="s">
+        <v>2564</v>
+      </c>
+      <c r="I16" s="140"/>
+      <c r="J16" s="140" t="s">
+        <v>2514</v>
+      </c>
+      <c r="K16" s="140" t="s">
+        <v>2566</v>
+      </c>
+      <c r="L16" s="141" t="s">
+        <v>2618</v>
+      </c>
+      <c r="M16" s="140" t="s">
+        <v>2499</v>
+      </c>
+      <c r="N16" s="140" t="s">
+        <v>2553</v>
+      </c>
+      <c r="O16" s="140" t="s">
+        <v>2525</v>
+      </c>
+      <c r="P16" s="141" t="s">
+        <v>2554</v>
+      </c>
+      <c r="Q16" s="140" t="s">
+        <v>2627</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17">
+      <c r="A17" s="140" t="s">
+        <v>2492</v>
+      </c>
+      <c r="B17" s="140">
+        <v>15</v>
+      </c>
+      <c r="C17" s="140" t="s">
+        <v>2462</v>
+      </c>
+      <c r="H17" s="140" t="s">
+        <v>2497</v>
+      </c>
+      <c r="I17" s="140" t="s">
+        <v>46</v>
+      </c>
+      <c r="J17" s="140" t="s">
+        <v>2513</v>
+      </c>
+      <c r="K17" s="140" t="s">
+        <v>2558</v>
+      </c>
+      <c r="L17" s="141" t="s">
+        <v>2563</v>
+      </c>
+      <c r="M17" s="140" t="s">
+        <v>2499</v>
+      </c>
+      <c r="N17" s="140"/>
+      <c r="O17" s="140" t="s">
+        <v>2525</v>
+      </c>
+      <c r="P17" s="141" t="s">
+        <v>2554</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17">
+      <c r="A18" s="140" t="s">
+        <v>2492</v>
+      </c>
+      <c r="B18" s="140">
+        <v>16</v>
+      </c>
+      <c r="C18" s="140" t="s">
+        <v>2461</v>
+      </c>
+      <c r="H18" s="140" t="s">
+        <v>2497</v>
+      </c>
+      <c r="I18" s="140" t="s">
+        <v>63</v>
+      </c>
+      <c r="J18" s="140" t="s">
+        <v>2513</v>
+      </c>
+      <c r="K18" s="140" t="s">
+        <v>2559</v>
+      </c>
+      <c r="L18" s="141" t="s">
+        <v>2619</v>
+      </c>
+      <c r="M18" s="140" t="s">
+        <v>2499</v>
+      </c>
+      <c r="N18" s="140"/>
+      <c r="O18" s="140" t="s">
+        <v>2525</v>
+      </c>
+      <c r="P18" s="141" t="s">
+        <v>2554</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17">
+      <c r="A19" s="140" t="s">
+        <v>2492</v>
+      </c>
+      <c r="B19" s="140">
+        <v>17</v>
+      </c>
+      <c r="C19" s="140" t="s">
+        <v>2461</v>
+      </c>
+      <c r="H19" s="140" t="s">
+        <v>2497</v>
+      </c>
+      <c r="I19" s="140" t="s">
+        <v>46</v>
+      </c>
+      <c r="J19" s="140" t="s">
+        <v>2513</v>
+      </c>
+      <c r="K19" s="140" t="s">
+        <v>2560</v>
+      </c>
+      <c r="L19" s="141" t="s">
+        <v>2620</v>
+      </c>
+      <c r="M19" s="140" t="s">
+        <v>2499</v>
+      </c>
+      <c r="N19" s="140"/>
+      <c r="O19" s="140" t="s">
+        <v>2525</v>
+      </c>
+      <c r="P19" s="141" t="s">
+        <v>2554</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17">
+      <c r="A20" s="140" t="s">
+        <v>2492</v>
+      </c>
+      <c r="B20" s="140">
+        <v>18</v>
+      </c>
+      <c r="C20" s="140" t="s">
+        <v>2461</v>
+      </c>
+      <c r="H20" s="140" t="s">
+        <v>2497</v>
+      </c>
+      <c r="I20" s="140" t="s">
+        <v>63</v>
+      </c>
+      <c r="J20" s="140" t="s">
+        <v>2513</v>
+      </c>
+      <c r="K20" s="140" t="s">
+        <v>2561</v>
+      </c>
+      <c r="L20" s="141" t="s">
+        <v>2621</v>
+      </c>
+      <c r="M20" s="140" t="s">
+        <v>2570</v>
+      </c>
+      <c r="N20" s="140"/>
+      <c r="O20" s="140" t="s">
+        <v>2571</v>
+      </c>
+      <c r="P20" s="141" t="s">
+        <v>2554</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" ht="33" customHeight="1">
+      <c r="A21" s="140" t="s">
+        <v>2492</v>
+      </c>
+      <c r="B21" s="140">
+        <v>19</v>
+      </c>
+      <c r="C21" s="140" t="s">
+        <v>2461</v>
+      </c>
+      <c r="H21" s="140" t="s">
+        <v>2564</v>
+      </c>
+      <c r="J21" s="140" t="s">
+        <v>2565</v>
+      </c>
+      <c r="K21" s="140" t="s">
+        <v>2567</v>
+      </c>
+      <c r="L21" s="141" t="s">
+        <v>2569</v>
+      </c>
+      <c r="M21" s="140" t="s">
+        <v>2570</v>
+      </c>
+      <c r="N21" s="140" t="s">
+        <v>2590</v>
+      </c>
+      <c r="O21" s="140" t="s">
+        <v>2571</v>
+      </c>
+      <c r="P21" s="141" t="s">
+        <v>2554</v>
+      </c>
+      <c r="Q21" s="140" t="s">
+        <v>2625</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="33" customHeight="1">
+      <c r="A22" s="140" t="s">
+        <v>2492</v>
+      </c>
+      <c r="B22" s="140">
+        <v>20</v>
+      </c>
+      <c r="C22" s="140" t="s">
+        <v>2461</v>
+      </c>
+      <c r="H22" s="140" t="s">
+        <v>2564</v>
+      </c>
+      <c r="J22" s="140" t="s">
+        <v>2565</v>
+      </c>
+      <c r="K22" s="140" t="s">
+        <v>2568</v>
+      </c>
+      <c r="L22" s="265" t="s">
+        <v>2611</v>
+      </c>
+      <c r="M22" s="140" t="s">
+        <v>2570</v>
+      </c>
+      <c r="N22" s="140" t="s">
+        <v>2590</v>
+      </c>
+      <c r="O22" s="140" t="s">
+        <v>2571</v>
+      </c>
+      <c r="P22" s="141" t="s">
+        <v>2554</v>
+      </c>
+      <c r="Q22" s="140" t="s">
+        <v>2625</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17">
+      <c r="A23" s="140" t="s">
+        <v>2492</v>
+      </c>
+      <c r="B23" s="140">
+        <v>21</v>
+      </c>
+      <c r="C23" s="140" t="s">
+        <v>2461</v>
+      </c>
+      <c r="D23" s="140"/>
+      <c r="E23" s="140"/>
+      <c r="F23" s="140"/>
+      <c r="G23" s="140"/>
+      <c r="H23" s="140" t="s">
+        <v>2502</v>
+      </c>
+      <c r="I23" s="140"/>
+      <c r="J23" s="140" t="s">
+        <v>2514</v>
+      </c>
+      <c r="K23" s="140" t="s">
+        <v>2577</v>
+      </c>
+      <c r="L23" s="265" t="s">
+        <v>2603</v>
+      </c>
+      <c r="M23" s="140" t="s">
+        <v>2499</v>
+      </c>
+      <c r="N23" s="140" t="s">
+        <v>2590</v>
+      </c>
+      <c r="O23" s="140" t="s">
+        <v>2525</v>
+      </c>
+      <c r="P23" s="141" t="s">
+        <v>2554</v>
+      </c>
+      <c r="Q23" s="140" t="s">
+        <v>2625</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17">
+      <c r="A24" s="140" t="s">
+        <v>2492</v>
+      </c>
+      <c r="B24" s="140">
+        <v>22</v>
+      </c>
+      <c r="C24" s="140" t="s">
+        <v>2461</v>
+      </c>
+      <c r="D24" s="140"/>
+      <c r="E24" s="140"/>
+      <c r="F24" s="140"/>
+      <c r="G24" s="140"/>
+      <c r="H24" s="140" t="s">
+        <v>2502</v>
+      </c>
+      <c r="I24" s="140"/>
+      <c r="J24" s="140" t="s">
+        <v>2514</v>
+      </c>
+      <c r="K24" s="140" t="s">
+        <v>2577</v>
+      </c>
+      <c r="L24" s="141" t="s">
+        <v>2604</v>
+      </c>
+      <c r="M24" s="140" t="s">
+        <v>2499</v>
+      </c>
+      <c r="N24" s="140" t="s">
+        <v>2578</v>
+      </c>
+      <c r="O24" s="140" t="s">
+        <v>2525</v>
+      </c>
+      <c r="P24" s="141" t="s">
+        <v>2554</v>
+      </c>
+      <c r="Q24" s="140" t="s">
+        <v>2626</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17">
+      <c r="A25" s="140" t="s">
+        <v>2492</v>
+      </c>
+      <c r="B25" s="140">
+        <v>23</v>
+      </c>
+      <c r="C25" s="140" t="s">
+        <v>2461</v>
+      </c>
+      <c r="D25" s="140"/>
+      <c r="E25" s="140"/>
+      <c r="F25" s="140"/>
+      <c r="G25" s="140"/>
+      <c r="H25" s="140" t="s">
+        <v>2502</v>
+      </c>
+      <c r="I25" s="140"/>
+      <c r="J25" s="140" t="s">
+        <v>2514</v>
+      </c>
+      <c r="K25" s="140" t="s">
+        <v>2579</v>
+      </c>
+      <c r="L25" s="141" t="s">
+        <v>2605</v>
+      </c>
+      <c r="M25" s="140" t="s">
+        <v>2499</v>
+      </c>
+      <c r="N25" s="140" t="s">
+        <v>2578</v>
+      </c>
+      <c r="O25" s="140" t="s">
+        <v>2525</v>
+      </c>
+      <c r="P25" s="141" t="s">
+        <v>2554</v>
+      </c>
+      <c r="Q25" s="140" t="s">
+        <v>2626</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17">
+      <c r="A26" s="140" t="s">
+        <v>2492</v>
+      </c>
+      <c r="B26" s="140">
+        <v>24</v>
+      </c>
+      <c r="C26" s="140" t="s">
+        <v>2461</v>
+      </c>
+      <c r="D26" s="140"/>
+      <c r="E26" s="140"/>
+      <c r="F26" s="140"/>
+      <c r="G26" s="140"/>
+      <c r="H26" s="140" t="s">
+        <v>2502</v>
+      </c>
+      <c r="I26" s="140"/>
+      <c r="J26" s="140" t="s">
+        <v>2514</v>
+      </c>
+      <c r="K26" s="140" t="s">
+        <v>2580</v>
+      </c>
+      <c r="L26" s="141" t="s">
+        <v>2612</v>
+      </c>
+      <c r="M26" s="140" t="s">
+        <v>2572</v>
+      </c>
+      <c r="N26" s="140" t="s">
+        <v>2573</v>
+      </c>
+      <c r="O26" s="140" t="s">
+        <v>2581</v>
+      </c>
+      <c r="P26" s="141" t="s">
+        <v>2587</v>
+      </c>
+      <c r="Q26" s="140" t="s">
+        <v>2626</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17">
+      <c r="A27" s="140" t="s">
+        <v>2492</v>
+      </c>
+      <c r="B27" s="140">
+        <v>25</v>
+      </c>
+      <c r="C27" s="140" t="s">
+        <v>2461</v>
+      </c>
+      <c r="D27" s="140"/>
+      <c r="E27" s="140"/>
+      <c r="F27" s="140"/>
+      <c r="G27" s="140"/>
+      <c r="H27" s="140" t="s">
+        <v>2502</v>
+      </c>
+      <c r="I27" s="140"/>
+      <c r="J27" s="140" t="s">
+        <v>2514</v>
+      </c>
+      <c r="K27" s="140" t="s">
+        <v>2582</v>
+      </c>
+      <c r="L27" s="141" t="s">
+        <v>2613</v>
+      </c>
+      <c r="M27" s="140" t="s">
+        <v>2574</v>
+      </c>
+      <c r="N27" s="140" t="s">
+        <v>2583</v>
+      </c>
+      <c r="O27" s="140" t="s">
+        <v>2584</v>
+      </c>
+      <c r="P27" s="141" t="s">
+        <v>2588</v>
+      </c>
+      <c r="Q27" s="140" t="s">
+        <v>2626</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17">
+      <c r="A28" s="140" t="s">
+        <v>2492</v>
+      </c>
+      <c r="B28" s="140">
+        <v>26</v>
+      </c>
+      <c r="C28" s="140" t="s">
+        <v>2461</v>
+      </c>
+      <c r="D28" s="140"/>
+      <c r="E28" s="140"/>
+      <c r="F28" s="140"/>
+      <c r="G28" s="140"/>
+      <c r="H28" s="140" t="s">
+        <v>2502</v>
+      </c>
+      <c r="I28" s="140"/>
+      <c r="J28" s="140" t="s">
+        <v>2514</v>
+      </c>
+      <c r="K28" s="140" t="s">
+        <v>2585</v>
+      </c>
+      <c r="L28" s="141" t="s">
+        <v>2614</v>
+      </c>
+      <c r="M28" s="140" t="s">
+        <v>2576</v>
+      </c>
+      <c r="N28" s="140" t="s">
+        <v>2575</v>
+      </c>
+      <c r="O28" s="140" t="s">
+        <v>2586</v>
+      </c>
+      <c r="P28" s="141" t="s">
+        <v>2589</v>
+      </c>
+      <c r="Q28" s="140" t="s">
+        <v>2626</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17">
+      <c r="A29" s="140" t="s">
+        <v>2492</v>
+      </c>
+      <c r="B29" s="140">
+        <v>27</v>
+      </c>
+      <c r="C29" s="140" t="s">
+        <v>2461</v>
+      </c>
+      <c r="D29" s="140"/>
+      <c r="E29" s="140"/>
+      <c r="F29" s="140"/>
+      <c r="G29" s="140"/>
+      <c r="H29" s="140" t="s">
+        <v>2502</v>
+      </c>
+      <c r="I29" s="140"/>
+      <c r="J29" s="140" t="s">
+        <v>2514</v>
+      </c>
+      <c r="K29" s="140" t="s">
+        <v>2591</v>
+      </c>
+      <c r="L29" s="141" t="s">
+        <v>2606</v>
+      </c>
+      <c r="M29" s="140" t="s">
+        <v>2572</v>
+      </c>
+      <c r="N29" s="140" t="s">
+        <v>2592</v>
+      </c>
+      <c r="O29" s="140" t="s">
+        <v>2593</v>
+      </c>
+      <c r="P29" s="141" t="s">
+        <v>2601</v>
+      </c>
+      <c r="Q29" s="140" t="s">
+        <v>2626</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17">
+      <c r="A30" s="140" t="s">
+        <v>2492</v>
+      </c>
+      <c r="B30" s="140">
+        <v>28</v>
+      </c>
+      <c r="C30" s="140" t="s">
+        <v>2461</v>
+      </c>
+      <c r="D30" s="140"/>
+      <c r="E30" s="140"/>
+      <c r="F30" s="140"/>
+      <c r="G30" s="140"/>
+      <c r="H30" s="140" t="s">
+        <v>2502</v>
+      </c>
+      <c r="I30" s="140"/>
+      <c r="J30" s="140" t="s">
+        <v>2514</v>
+      </c>
+      <c r="K30" s="140" t="s">
+        <v>2594</v>
+      </c>
+      <c r="L30" s="141" t="s">
+        <v>2615</v>
+      </c>
+      <c r="M30" s="140" t="s">
+        <v>2595</v>
+      </c>
+      <c r="N30" s="140" t="s">
+        <v>2575</v>
+      </c>
+      <c r="O30" s="140" t="s">
+        <v>2596</v>
+      </c>
+      <c r="P30" s="141" t="s">
+        <v>2597</v>
+      </c>
+      <c r="Q30" s="140" t="s">
+        <v>2626</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17">
+      <c r="A31" s="140" t="s">
+        <v>2492</v>
+      </c>
+      <c r="B31" s="140">
+        <v>29</v>
+      </c>
+      <c r="C31" s="140" t="s">
+        <v>2461</v>
+      </c>
+      <c r="D31" s="140"/>
+      <c r="E31" s="140"/>
+      <c r="F31" s="140"/>
+      <c r="G31" s="140"/>
+      <c r="H31" s="140" t="s">
+        <v>2502</v>
+      </c>
+      <c r="I31" s="140"/>
+      <c r="J31" s="140" t="s">
+        <v>2514</v>
+      </c>
+      <c r="K31" s="140" t="s">
+        <v>2598</v>
+      </c>
+      <c r="L31" s="141" t="s">
+        <v>2616</v>
+      </c>
+      <c r="M31" s="140" t="s">
+        <v>2572</v>
+      </c>
+      <c r="N31" s="140" t="s">
+        <v>2599</v>
+      </c>
+      <c r="O31" s="140" t="s">
+        <v>2600</v>
+      </c>
+      <c r="P31" s="141" t="s">
+        <v>2602</v>
+      </c>
+      <c r="Q31" s="140" t="s">
+        <v>2626</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="40" type="noConversion"/>
@@ -40580,7 +41617,7 @@
         <v>1396</v>
       </c>
       <c r="H2" s="143" t="s">
-        <v>2541</v>
+        <v>2538</v>
       </c>
       <c r="I2" s="143" t="s">
         <v>1397</v>
@@ -42453,7 +43490,7 @@
         <v>2239</v>
       </c>
       <c r="P3" s="241" t="s">
-        <v>2537</v>
+        <v>2534</v>
       </c>
       <c r="Q3" s="241">
         <v>1</v>
@@ -42512,7 +43549,7 @@
         <v>2240</v>
       </c>
       <c r="P4" s="161" t="s">
-        <v>2537</v>
+        <v>2534</v>
       </c>
       <c r="Q4" s="161">
         <v>1</v>
@@ -42571,7 +43608,7 @@
         <v>2241</v>
       </c>
       <c r="P5" s="161" t="s">
-        <v>2537</v>
+        <v>2534</v>
       </c>
       <c r="Q5" s="161">
         <v>1</v>
@@ -43460,7 +44497,7 @@
         <v>2296</v>
       </c>
       <c r="F24" s="279" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="G24" s="241"/>
       <c r="H24" s="241" t="s">
@@ -43521,7 +44558,7 @@
         <v>2297</v>
       </c>
       <c r="F25" s="280" t="s">
-        <v>2547</v>
+        <v>2544</v>
       </c>
       <c r="G25" s="161"/>
       <c r="H25" s="161" t="s">
@@ -43582,7 +44619,7 @@
         <v>2298</v>
       </c>
       <c r="F26" s="280" t="s">
-        <v>2548</v>
+        <v>2545</v>
       </c>
       <c r="G26" s="161"/>
       <c r="H26" s="161" t="s">
@@ -43795,7 +44832,7 @@
         <v>2317</v>
       </c>
       <c r="F31" s="279" t="s">
-        <v>2549</v>
+        <v>2546</v>
       </c>
       <c r="G31" s="241"/>
       <c r="H31" s="241" t="s">
@@ -43889,13 +44926,13 @@
         <v>1422</v>
       </c>
       <c r="Y32" s="161" t="s">
-        <v>2538</v>
+        <v>2535</v>
       </c>
       <c r="Z32" s="161" t="s">
         <v>1422</v>
       </c>
       <c r="AA32" s="249" t="s">
-        <v>2540</v>
+        <v>2537</v>
       </c>
     </row>
     <row r="33" spans="1:27" ht="54.95" customHeight="1">
@@ -43913,7 +44950,7 @@
         <v>2321</v>
       </c>
       <c r="F33" s="280" t="s">
-        <v>2550</v>
+        <v>2547</v>
       </c>
       <c r="G33" s="161"/>
       <c r="H33" s="161" t="s">
@@ -44007,13 +45044,13 @@
         <v>1422</v>
       </c>
       <c r="Y34" s="161" t="s">
-        <v>2538</v>
+        <v>2535</v>
       </c>
       <c r="Z34" s="161" t="s">
         <v>1422</v>
       </c>
       <c r="AA34" s="249" t="s">
-        <v>2540</v>
+        <v>2537</v>
       </c>
     </row>
     <row r="35" spans="1:27" ht="54.95" customHeight="1">
@@ -44031,7 +45068,7 @@
         <v>2324</v>
       </c>
       <c r="F35" s="280" t="s">
-        <v>2551</v>
+        <v>2548</v>
       </c>
       <c r="G35" s="161"/>
       <c r="H35" s="161" t="s">
@@ -44042,7 +45079,7 @@
       <c r="K35" s="161"/>
       <c r="L35" s="161"/>
       <c r="M35" s="161" t="s">
-        <v>2542</v>
+        <v>2539</v>
       </c>
       <c r="N35" s="161" t="s">
         <v>2224</v>
@@ -44076,7 +45113,7 @@
         <v>1422</v>
       </c>
       <c r="Y35" s="161" t="s">
-        <v>2539</v>
+        <v>2536</v>
       </c>
       <c r="Z35" s="161" t="s">
         <v>1422</v>
@@ -44127,13 +45164,13 @@
         <v>2335</v>
       </c>
       <c r="Y36" s="161" t="s">
-        <v>2538</v>
+        <v>2535</v>
       </c>
       <c r="Z36" s="161" t="s">
         <v>1422</v>
       </c>
       <c r="AA36" s="249" t="s">
-        <v>2540</v>
+        <v>2537</v>
       </c>
     </row>
     <row r="37" spans="1:27" ht="54.95" customHeight="1">
@@ -44301,7 +45338,7 @@
         <v>2356</v>
       </c>
       <c r="F41" s="279" t="s">
-        <v>2543</v>
+        <v>2540</v>
       </c>
       <c r="G41" s="241"/>
       <c r="H41" s="241" t="s">
@@ -44409,7 +45446,7 @@
         <v>2357</v>
       </c>
       <c r="F43" s="280" t="s">
-        <v>2544</v>
+        <v>2541</v>
       </c>
       <c r="G43" s="161"/>
       <c r="H43" s="161" t="s">
@@ -44517,7 +45554,7 @@
         <v>2358</v>
       </c>
       <c r="F45" s="280" t="s">
-        <v>2545</v>
+        <v>2542</v>
       </c>
       <c r="G45" s="161"/>
       <c r="H45" s="161" t="s">
@@ -45468,7 +46505,7 @@
         <v>2410</v>
       </c>
       <c r="F64" s="124" t="s">
-        <v>2552</v>
+        <v>2549</v>
       </c>
       <c r="G64" s="244"/>
       <c r="H64" s="244" t="s">
@@ -45479,7 +46516,7 @@
       <c r="K64" s="244"/>
       <c r="L64" s="244"/>
       <c r="M64" s="244" t="s">
-        <v>2553</v>
+        <v>2550</v>
       </c>
       <c r="N64" s="244" t="s">
         <v>2224</v>
@@ -45732,19 +46769,19 @@
         <v>2438</v>
       </c>
       <c r="B70" s="256" t="s">
-        <v>2523</v>
+        <v>2520</v>
       </c>
       <c r="C70" s="256" t="s">
-        <v>2536</v>
+        <v>2533</v>
       </c>
       <c r="D70" s="256">
         <v>1</v>
       </c>
       <c r="E70" s="256" t="s">
-        <v>2524</v>
+        <v>2521</v>
       </c>
       <c r="F70" s="289" t="s">
-        <v>2525</v>
+        <v>2522</v>
       </c>
       <c r="G70" s="256"/>
       <c r="H70" s="256" t="s">
@@ -45767,20 +46804,20 @@
       </c>
       <c r="R70" s="256"/>
       <c r="S70" s="256" t="s">
-        <v>2526</v>
+        <v>2523</v>
       </c>
       <c r="T70" s="256"/>
       <c r="U70" s="256"/>
       <c r="V70" s="256"/>
       <c r="W70" s="256"/>
       <c r="X70" s="256" t="s">
-        <v>2535</v>
+        <v>2532</v>
       </c>
       <c r="Y70" s="256" t="s">
         <v>2247</v>
       </c>
       <c r="Z70" s="256" t="s">
-        <v>2535</v>
+        <v>2532</v>
       </c>
       <c r="AA70" s="256" t="s">
         <v>2336</v>
@@ -45788,11 +46825,11 @@
     </row>
     <row r="71" spans="1:27" ht="54.95" customHeight="1">
       <c r="A71" s="256" t="s">
-        <v>2526</v>
+        <v>2523</v>
       </c>
       <c r="B71" s="244"/>
       <c r="C71" s="244" t="s">
-        <v>2534</v>
+        <v>2531</v>
       </c>
       <c r="D71" s="244"/>
       <c r="E71" s="244"/>
@@ -45815,11 +46852,11 @@
       <c r="V71" s="244"/>
       <c r="W71" s="244"/>
       <c r="X71" s="244" t="s">
-        <v>2535</v>
+        <v>2532</v>
       </c>
       <c r="Y71" s="244"/>
       <c r="Z71" s="244" t="s">
-        <v>2535</v>
+        <v>2532</v>
       </c>
       <c r="AA71" s="244"/>
     </row>

--- a/Assets/ExcelSource/GameData.xlsx
+++ b/Assets/ExcelSource/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erang\Desktop\RELIC\Assets\ExcelSource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{185F4270-2D1B-4A28-93E0-C06E2BE5254A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB1CA53A-9619-4E2F-AA6D-172AB96ADE14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="1" r:id="rId1"/>
@@ -16358,7 +16358,7 @@
         <v>47</v>
       </c>
       <c r="C3" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D3" s="7">
         <v>10</v>
@@ -16429,7 +16429,7 @@
         <v>64</v>
       </c>
       <c r="C4" s="12">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D4" s="11">
         <v>12</v>
@@ -16500,7 +16500,7 @@
         <v>80</v>
       </c>
       <c r="C5" s="12">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D5" s="11">
         <v>14</v>
@@ -16571,7 +16571,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="12">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D6" s="11">
         <v>11</v>
@@ -16642,7 +16642,7 @@
         <v>111</v>
       </c>
       <c r="C7" s="12">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D7" s="11">
         <v>12</v>
